--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England EFL League One_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England EFL League One_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2030" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2102" uniqueCount="441">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -910,6 +910,30 @@
     <t>['10', '29', '90+2']</t>
   </si>
   <si>
+    <t>['11', '17', '76', '80']</t>
+  </si>
+  <si>
+    <t>['36']</t>
+  </si>
+  <si>
+    <t>['54', '63']</t>
+  </si>
+  <si>
+    <t>['32', '40', '51']</t>
+  </si>
+  <si>
+    <t>['90']</t>
+  </si>
+  <si>
+    <t>['74', '87']</t>
+  </si>
+  <si>
+    <t>['54', '81']</t>
+  </si>
+  <si>
+    <t>['16', '62', '83']</t>
+  </si>
+  <si>
     <t>['13', '18']</t>
   </si>
   <si>
@@ -1302,6 +1326,18 @@
   <si>
     <t>['32', '57']</t>
   </si>
+  <si>
+    <t>['70', '82']</t>
+  </si>
+  <si>
+    <t>['2', '90+5']</t>
+  </si>
+  <si>
+    <t>['52', '54']</t>
+  </si>
+  <si>
+    <t>['44']</t>
+  </si>
 </sst>
 </file>
 
@@ -1662,7 +1698,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP328"/>
+  <dimension ref="A1:BP340"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1918,7 +1954,7 @@
         <v>94</v>
       </c>
       <c r="P2" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -1996,10 +2032,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ2">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2205,7 +2241,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ3">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2330,7 +2366,7 @@
         <v>96</v>
       </c>
       <c r="P4" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -2408,10 +2444,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ4">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2742,7 +2778,7 @@
         <v>96</v>
       </c>
       <c r="P6" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="Q6">
         <v>2.75</v>
@@ -2823,7 +2859,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ6">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2948,7 +2984,7 @@
         <v>98</v>
       </c>
       <c r="P7" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="Q7">
         <v>4</v>
@@ -3026,10 +3062,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ7">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -3232,7 +3268,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ8">
         <v>0.43</v>
@@ -3438,7 +3474,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ9">
         <v>1.5</v>
@@ -3566,7 +3602,7 @@
         <v>101</v>
       </c>
       <c r="P10" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="Q10">
         <v>3.75</v>
@@ -3647,7 +3683,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ10">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3850,7 +3886,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ11">
         <v>0.75</v>
@@ -3978,7 +4014,7 @@
         <v>103</v>
       </c>
       <c r="P12" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="Q12">
         <v>2.1</v>
@@ -4056,7 +4092,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ12">
         <v>0.93</v>
@@ -4265,7 +4301,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ13">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4390,7 +4426,7 @@
         <v>105</v>
       </c>
       <c r="P14" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="Q14">
         <v>4</v>
@@ -4468,10 +4504,10 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ14">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4880,7 +4916,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ16">
         <v>1.29</v>
@@ -5214,7 +5250,7 @@
         <v>107</v>
       </c>
       <c r="P18" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="Q18">
         <v>4.33</v>
@@ -5498,10 +5534,10 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ19">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5704,7 +5740,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ20">
         <v>0.8</v>
@@ -5832,7 +5868,7 @@
         <v>109</v>
       </c>
       <c r="P21" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="Q21">
         <v>2.75</v>
@@ -6038,7 +6074,7 @@
         <v>110</v>
       </c>
       <c r="P22" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="Q22">
         <v>2.3</v>
@@ -6244,7 +6280,7 @@
         <v>96</v>
       </c>
       <c r="P23" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="Q23">
         <v>2.75</v>
@@ -6322,10 +6358,10 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ23">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR23">
         <v>0</v>
@@ -6450,7 +6486,7 @@
         <v>111</v>
       </c>
       <c r="P24" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="Q24">
         <v>2.5</v>
@@ -6531,7 +6567,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ24">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR24">
         <v>0</v>
@@ -6737,7 +6773,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ25">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR25">
         <v>0</v>
@@ -7355,7 +7391,7 @@
         <v>2</v>
       </c>
       <c r="AQ28">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR28">
         <v>0.87</v>
@@ -7764,7 +7800,7 @@
         <v>3</v>
       </c>
       <c r="AP30">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ30">
         <v>0.8</v>
@@ -7892,7 +7928,7 @@
         <v>116</v>
       </c>
       <c r="P31" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -7973,7 +8009,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ31">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR31">
         <v>1.84</v>
@@ -8098,7 +8134,7 @@
         <v>117</v>
       </c>
       <c r="P32" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="Q32">
         <v>4.5</v>
@@ -8176,7 +8212,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ32">
         <v>1.5</v>
@@ -8510,7 +8546,7 @@
         <v>119</v>
       </c>
       <c r="P34" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="Q34">
         <v>3.75</v>
@@ -8591,7 +8627,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ34">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR34">
         <v>1.76</v>
@@ -8797,7 +8833,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ35">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR35">
         <v>1.31</v>
@@ -8922,7 +8958,7 @@
         <v>121</v>
       </c>
       <c r="P36" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="Q36">
         <v>2.2</v>
@@ -9000,7 +9036,7 @@
         <v>0</v>
       </c>
       <c r="AP36">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ36">
         <v>0.75</v>
@@ -9128,7 +9164,7 @@
         <v>122</v>
       </c>
       <c r="P37" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="Q37">
         <v>4.33</v>
@@ -9206,7 +9242,7 @@
         <v>3</v>
       </c>
       <c r="AP37">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ37">
         <v>2.14</v>
@@ -9334,7 +9370,7 @@
         <v>123</v>
       </c>
       <c r="P38" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="Q38">
         <v>2.63</v>
@@ -9412,10 +9448,10 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ38">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AR38">
         <v>0.68</v>
@@ -9621,7 +9657,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ39">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR39">
         <v>2.14</v>
@@ -9824,10 +9860,10 @@
         <v>3</v>
       </c>
       <c r="AP40">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ40">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR40">
         <v>1.58</v>
@@ -10030,7 +10066,7 @@
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ41">
         <v>1.54</v>
@@ -10236,10 +10272,10 @@
         <v>3</v>
       </c>
       <c r="AP42">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ42">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR42">
         <v>1.98</v>
@@ -10364,7 +10400,7 @@
         <v>96</v>
       </c>
       <c r="P43" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="Q43">
         <v>2.63</v>
@@ -10445,7 +10481,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ43">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR43">
         <v>0.79</v>
@@ -10648,10 +10684,10 @@
         <v>1</v>
       </c>
       <c r="AP44">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ44">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR44">
         <v>1.4</v>
@@ -10776,7 +10812,7 @@
         <v>96</v>
       </c>
       <c r="P45" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="Q45">
         <v>3.6</v>
@@ -10854,7 +10890,7 @@
         <v>3</v>
       </c>
       <c r="AP45">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ45">
         <v>1.79</v>
@@ -11060,7 +11096,7 @@
         <v>0</v>
       </c>
       <c r="AP46">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ46">
         <v>0.43</v>
@@ -11188,7 +11224,7 @@
         <v>96</v>
       </c>
       <c r="P47" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="Q47">
         <v>2.05</v>
@@ -11269,7 +11305,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ47">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR47">
         <v>1.76</v>
@@ -11472,7 +11508,7 @@
         <v>0</v>
       </c>
       <c r="AP48">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ48">
         <v>1.29</v>
@@ -11681,7 +11717,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ49">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR49">
         <v>1.81</v>
@@ -11884,7 +11920,7 @@
         <v>0.5</v>
       </c>
       <c r="AP50">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ50">
         <v>0.67</v>
@@ -12299,7 +12335,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ52">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR52">
         <v>1.21</v>
@@ -12630,7 +12666,7 @@
         <v>119</v>
       </c>
       <c r="P54" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="Q54">
         <v>3.5</v>
@@ -12708,10 +12744,10 @@
         <v>0.5</v>
       </c>
       <c r="AP54">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ54">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AR54">
         <v>1.36</v>
@@ -12914,7 +12950,7 @@
         <v>3</v>
       </c>
       <c r="AP55">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ55">
         <v>1.79</v>
@@ -13120,10 +13156,10 @@
         <v>1.5</v>
       </c>
       <c r="AP56">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ56">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR56">
         <v>1.21</v>
@@ -13248,7 +13284,7 @@
         <v>135</v>
       </c>
       <c r="P57" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="Q57">
         <v>2.2</v>
@@ -13329,7 +13365,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ57">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR57">
         <v>1.85</v>
@@ -13454,7 +13490,7 @@
         <v>136</v>
       </c>
       <c r="P58" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="Q58">
         <v>2.75</v>
@@ -13535,7 +13571,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ58">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR58">
         <v>0.83</v>
@@ -13738,10 +13774,10 @@
         <v>2</v>
       </c>
       <c r="AP59">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ59">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR59">
         <v>0.65</v>
@@ -13866,7 +13902,7 @@
         <v>96</v>
       </c>
       <c r="P60" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="Q60">
         <v>2.75</v>
@@ -13944,7 +13980,7 @@
         <v>0</v>
       </c>
       <c r="AP60">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ60">
         <v>1.29</v>
@@ -14150,7 +14186,7 @@
         <v>0</v>
       </c>
       <c r="AP61">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ61">
         <v>1.54</v>
@@ -14356,10 +14392,10 @@
         <v>1.5</v>
       </c>
       <c r="AP62">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ62">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR62">
         <v>1.44</v>
@@ -14484,7 +14520,7 @@
         <v>96</v>
       </c>
       <c r="P63" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="Q63">
         <v>2.88</v>
@@ -14565,7 +14601,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ63">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR63">
         <v>1.7</v>
@@ -14690,7 +14726,7 @@
         <v>139</v>
       </c>
       <c r="P64" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="Q64">
         <v>2.5</v>
@@ -14768,10 +14804,10 @@
         <v>2</v>
       </c>
       <c r="AP64">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ64">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR64">
         <v>1.77</v>
@@ -15308,7 +15344,7 @@
         <v>141</v>
       </c>
       <c r="P67" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -15514,7 +15550,7 @@
         <v>142</v>
       </c>
       <c r="P68" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="Q68">
         <v>1.83</v>
@@ -15720,7 +15756,7 @@
         <v>143</v>
       </c>
       <c r="P69" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="Q69">
         <v>3.1</v>
@@ -15926,7 +15962,7 @@
         <v>144</v>
       </c>
       <c r="P70" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="Q70">
         <v>4.33</v>
@@ -16132,7 +16168,7 @@
         <v>145</v>
       </c>
       <c r="P71" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="Q71">
         <v>2.4</v>
@@ -16338,7 +16374,7 @@
         <v>146</v>
       </c>
       <c r="P72" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="Q72">
         <v>2.05</v>
@@ -16956,7 +16992,7 @@
         <v>149</v>
       </c>
       <c r="P75" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="Q75">
         <v>2.3</v>
@@ -17162,7 +17198,7 @@
         <v>96</v>
       </c>
       <c r="P76" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="Q76">
         <v>3.75</v>
@@ -17446,7 +17482,7 @@
         <v>0.33</v>
       </c>
       <c r="AP77">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ77">
         <v>1.17</v>
@@ -17574,7 +17610,7 @@
         <v>96</v>
       </c>
       <c r="P78" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="Q78">
         <v>2.4</v>
@@ -17780,7 +17816,7 @@
         <v>150</v>
       </c>
       <c r="P79" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="Q79">
         <v>3.15</v>
@@ -17858,10 +17894,10 @@
         <v>3</v>
       </c>
       <c r="AP79">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ79">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR79">
         <v>1.23</v>
@@ -18064,10 +18100,10 @@
         <v>2</v>
       </c>
       <c r="AP80">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ80">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR80">
         <v>1.41</v>
@@ -18192,7 +18228,7 @@
         <v>96</v>
       </c>
       <c r="P81" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="Q81">
         <v>4.33</v>
@@ -18270,10 +18306,10 @@
         <v>1.5</v>
       </c>
       <c r="AP81">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ81">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR81">
         <v>0.8100000000000001</v>
@@ -18476,10 +18512,10 @@
         <v>0.33</v>
       </c>
       <c r="AP82">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ82">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR82">
         <v>1.22</v>
@@ -18682,10 +18718,10 @@
         <v>2</v>
       </c>
       <c r="AP83">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ83">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR83">
         <v>1.2</v>
@@ -18888,10 +18924,10 @@
         <v>1</v>
       </c>
       <c r="AP84">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ84">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR84">
         <v>0.73</v>
@@ -19016,7 +19052,7 @@
         <v>96</v>
       </c>
       <c r="P85" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="Q85">
         <v>3.4</v>
@@ -19094,10 +19130,10 @@
         <v>1.5</v>
       </c>
       <c r="AP85">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ85">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR85">
         <v>1.19</v>
@@ -19300,10 +19336,10 @@
         <v>1.33</v>
       </c>
       <c r="AP86">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ86">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR86">
         <v>1.36</v>
@@ -19428,7 +19464,7 @@
         <v>153</v>
       </c>
       <c r="P87" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="Q87">
         <v>3.4</v>
@@ -19506,10 +19542,10 @@
         <v>1.33</v>
       </c>
       <c r="AP87">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ87">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AR87">
         <v>1.24</v>
@@ -19712,10 +19748,10 @@
         <v>1</v>
       </c>
       <c r="AP88">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ88">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR88">
         <v>1.55</v>
@@ -19840,7 +19876,7 @@
         <v>155</v>
       </c>
       <c r="P89" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="Q89">
         <v>2.05</v>
@@ -19918,10 +19954,10 @@
         <v>2.33</v>
       </c>
       <c r="AP89">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ89">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR89">
         <v>1.7</v>
@@ -20046,7 +20082,7 @@
         <v>96</v>
       </c>
       <c r="P90" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="Q90">
         <v>4</v>
@@ -20124,10 +20160,10 @@
         <v>2.33</v>
       </c>
       <c r="AP90">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ90">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR90">
         <v>1.42</v>
@@ -20252,7 +20288,7 @@
         <v>119</v>
       </c>
       <c r="P91" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="Q91">
         <v>2.88</v>
@@ -20330,10 +20366,10 @@
         <v>1.67</v>
       </c>
       <c r="AP91">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ91">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR91">
         <v>1.71</v>
@@ -20458,7 +20494,7 @@
         <v>156</v>
       </c>
       <c r="P92" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="Q92">
         <v>4.75</v>
@@ -20536,10 +20572,10 @@
         <v>2</v>
       </c>
       <c r="AP92">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ92">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR92">
         <v>1.4</v>
@@ -20742,10 +20778,10 @@
         <v>1.75</v>
       </c>
       <c r="AP93">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ93">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR93">
         <v>0.93</v>
@@ -20948,10 +20984,10 @@
         <v>1.25</v>
       </c>
       <c r="AP94">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ94">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR94">
         <v>1.15</v>
@@ -21076,7 +21112,7 @@
         <v>96</v>
       </c>
       <c r="P95" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="Q95">
         <v>4.5</v>
@@ -21154,10 +21190,10 @@
         <v>1.5</v>
       </c>
       <c r="AP95">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ95">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR95">
         <v>1.05</v>
@@ -21360,10 +21396,10 @@
         <v>1</v>
       </c>
       <c r="AP96">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ96">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR96">
         <v>1.27</v>
@@ -21488,7 +21524,7 @@
         <v>96</v>
       </c>
       <c r="P97" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="Q97">
         <v>3.2</v>
@@ -21566,10 +21602,10 @@
         <v>2</v>
       </c>
       <c r="AP97">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ97">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR97">
         <v>0.86</v>
@@ -21772,10 +21808,10 @@
         <v>0.5</v>
       </c>
       <c r="AP98">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ98">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR98">
         <v>1.36</v>
@@ -21900,7 +21936,7 @@
         <v>159</v>
       </c>
       <c r="P99" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="Q99">
         <v>3.6</v>
@@ -21978,10 +22014,10 @@
         <v>1.5</v>
       </c>
       <c r="AP99">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ99">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR99">
         <v>1.12</v>
@@ -22106,7 +22142,7 @@
         <v>160</v>
       </c>
       <c r="P100" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="Q100">
         <v>2.5</v>
@@ -22184,10 +22220,10 @@
         <v>2.5</v>
       </c>
       <c r="AP100">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ100">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR100">
         <v>1.61</v>
@@ -22390,10 +22426,10 @@
         <v>1.5</v>
       </c>
       <c r="AP101">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ101">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR101">
         <v>1.61</v>
@@ -22518,7 +22554,7 @@
         <v>162</v>
       </c>
       <c r="P102" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="Q102">
         <v>2.75</v>
@@ -22596,10 +22632,10 @@
         <v>1.75</v>
       </c>
       <c r="AP102">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ102">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AR102">
         <v>1.6</v>
@@ -22802,10 +22838,10 @@
         <v>0.75</v>
       </c>
       <c r="AP103">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ103">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR103">
         <v>1.21</v>
@@ -22930,7 +22966,7 @@
         <v>164</v>
       </c>
       <c r="P104" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="Q104">
         <v>2.63</v>
@@ -24372,7 +24408,7 @@
         <v>170</v>
       </c>
       <c r="P111" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="Q111">
         <v>3</v>
@@ -24578,7 +24614,7 @@
         <v>171</v>
       </c>
       <c r="P112" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="Q112">
         <v>1.91</v>
@@ -25402,7 +25438,7 @@
         <v>174</v>
       </c>
       <c r="P116" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="Q116">
         <v>3</v>
@@ -25483,7 +25519,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ116">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR116">
         <v>1.13</v>
@@ -25608,7 +25644,7 @@
         <v>175</v>
       </c>
       <c r="P117" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25686,7 +25722,7 @@
         <v>0.2</v>
       </c>
       <c r="AP117">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ117">
         <v>0.43</v>
@@ -25814,7 +25850,7 @@
         <v>96</v>
       </c>
       <c r="P118" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="Q118">
         <v>3.4</v>
@@ -25892,10 +25928,10 @@
         <v>1.4</v>
       </c>
       <c r="AP118">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ118">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR118">
         <v>0.98</v>
@@ -26098,7 +26134,7 @@
         <v>0.75</v>
       </c>
       <c r="AP119">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ119">
         <v>0.8</v>
@@ -26307,7 +26343,7 @@
         <v>2</v>
       </c>
       <c r="AQ120">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR120">
         <v>1.35</v>
@@ -26638,7 +26674,7 @@
         <v>178</v>
       </c>
       <c r="P122" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="Q122">
         <v>4.5</v>
@@ -26844,7 +26880,7 @@
         <v>179</v>
       </c>
       <c r="P123" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="Q123">
         <v>2</v>
@@ -27050,7 +27086,7 @@
         <v>180</v>
       </c>
       <c r="P124" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="Q124">
         <v>3.2</v>
@@ -27131,7 +27167,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ124">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR124">
         <v>1.2</v>
@@ -27334,7 +27370,7 @@
         <v>1</v>
       </c>
       <c r="AP125">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ125">
         <v>1.29</v>
@@ -27543,7 +27579,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ126">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR126">
         <v>1.58</v>
@@ -27749,7 +27785,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ127">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR127">
         <v>1.5</v>
@@ -27874,7 +27910,7 @@
         <v>137</v>
       </c>
       <c r="P128" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="Q128">
         <v>2.6</v>
@@ -27952,7 +27988,7 @@
         <v>1.8</v>
       </c>
       <c r="AP128">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ128">
         <v>1.79</v>
@@ -28158,7 +28194,7 @@
         <v>1.2</v>
       </c>
       <c r="AP129">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ129">
         <v>1.54</v>
@@ -28364,10 +28400,10 @@
         <v>1</v>
       </c>
       <c r="AP130">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ130">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR130">
         <v>1.33</v>
@@ -28492,7 +28528,7 @@
         <v>184</v>
       </c>
       <c r="P131" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="Q131">
         <v>4.5</v>
@@ -28573,7 +28609,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ131">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AR131">
         <v>1.07</v>
@@ -28776,7 +28812,7 @@
         <v>0.67</v>
       </c>
       <c r="AP132">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ132">
         <v>0.43</v>
@@ -28982,10 +29018,10 @@
         <v>2.25</v>
       </c>
       <c r="AP133">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ133">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR133">
         <v>1.64</v>
@@ -29316,7 +29352,7 @@
         <v>96</v>
       </c>
       <c r="P135" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="Q135">
         <v>2.3</v>
@@ -29394,7 +29430,7 @@
         <v>0</v>
       </c>
       <c r="AP135">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ135">
         <v>0.43</v>
@@ -29522,7 +29558,7 @@
         <v>188</v>
       </c>
       <c r="P136" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="Q136">
         <v>2.88</v>
@@ -29600,10 +29636,10 @@
         <v>1.2</v>
       </c>
       <c r="AP136">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ136">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR136">
         <v>1.54</v>
@@ -29934,7 +29970,7 @@
         <v>189</v>
       </c>
       <c r="P138" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="Q138">
         <v>3</v>
@@ -30012,10 +30048,10 @@
         <v>2.25</v>
       </c>
       <c r="AP138">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ138">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR138">
         <v>0.95</v>
@@ -30221,7 +30257,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ139">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR139">
         <v>1.61</v>
@@ -30346,7 +30382,7 @@
         <v>99</v>
       </c>
       <c r="P140" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="Q140">
         <v>3.1</v>
@@ -30630,10 +30666,10 @@
         <v>2.2</v>
       </c>
       <c r="AP141">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ141">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR141">
         <v>1.01</v>
@@ -31042,7 +31078,7 @@
         <v>0.67</v>
       </c>
       <c r="AP143">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ143">
         <v>0.67</v>
@@ -31170,7 +31206,7 @@
         <v>191</v>
       </c>
       <c r="P144" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="Q144">
         <v>3.25</v>
@@ -31251,7 +31287,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ144">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR144">
         <v>1.28</v>
@@ -31457,7 +31493,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ145">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR145">
         <v>1.46</v>
@@ -31663,7 +31699,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ146">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR146">
         <v>1.33</v>
@@ -31866,7 +31902,7 @@
         <v>0.6</v>
       </c>
       <c r="AP147">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ147">
         <v>0.8</v>
@@ -32200,7 +32236,7 @@
         <v>96</v>
       </c>
       <c r="P149" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="Q149">
         <v>4</v>
@@ -32278,7 +32314,7 @@
         <v>2</v>
       </c>
       <c r="AP149">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ149">
         <v>1.79</v>
@@ -32690,10 +32726,10 @@
         <v>0.5</v>
       </c>
       <c r="AP151">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ151">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR151">
         <v>1.31</v>
@@ -32899,7 +32935,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ152">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR152">
         <v>1.5</v>
@@ -33024,7 +33060,7 @@
         <v>199</v>
       </c>
       <c r="P153" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="Q153">
         <v>2.38</v>
@@ -33102,7 +33138,7 @@
         <v>0.83</v>
       </c>
       <c r="AP153">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ153">
         <v>1.29</v>
@@ -33436,7 +33472,7 @@
         <v>201</v>
       </c>
       <c r="P155" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="Q155">
         <v>2.5</v>
@@ -33642,7 +33678,7 @@
         <v>109</v>
       </c>
       <c r="P156" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="Q156">
         <v>3.5</v>
@@ -33720,10 +33756,10 @@
         <v>1.8</v>
       </c>
       <c r="AP156">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ156">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR156">
         <v>1.12</v>
@@ -34054,7 +34090,7 @@
         <v>96</v>
       </c>
       <c r="P158" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="Q158">
         <v>2.75</v>
@@ -34135,7 +34171,7 @@
         <v>2</v>
       </c>
       <c r="AQ158">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AR158">
         <v>1.7</v>
@@ -34338,10 +34374,10 @@
         <v>0.86</v>
       </c>
       <c r="AP159">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ159">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR159">
         <v>1.65</v>
@@ -34547,7 +34583,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ160">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR160">
         <v>1.49</v>
@@ -34878,7 +34914,7 @@
         <v>205</v>
       </c>
       <c r="P162" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="Q162">
         <v>3.6</v>
@@ -34956,10 +34992,10 @@
         <v>1.83</v>
       </c>
       <c r="AP162">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ162">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR162">
         <v>1.2</v>
@@ -35162,7 +35198,7 @@
         <v>0.83</v>
       </c>
       <c r="AP163">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ163">
         <v>0.75</v>
@@ -35290,7 +35326,7 @@
         <v>96</v>
       </c>
       <c r="P164" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="Q164">
         <v>3.25</v>
@@ -35368,10 +35404,10 @@
         <v>2</v>
       </c>
       <c r="AP164">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ164">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AR164">
         <v>1.09</v>
@@ -35574,7 +35610,7 @@
         <v>0.67</v>
       </c>
       <c r="AP165">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ165">
         <v>0.93</v>
@@ -35986,7 +36022,7 @@
         <v>1.17</v>
       </c>
       <c r="AP167">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ167">
         <v>1.5</v>
@@ -36195,7 +36231,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ168">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR168">
         <v>1.49</v>
@@ -36401,7 +36437,7 @@
         <v>2</v>
       </c>
       <c r="AQ169">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR169">
         <v>1.5</v>
@@ -36526,7 +36562,7 @@
         <v>211</v>
       </c>
       <c r="P170" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="Q170">
         <v>4.33</v>
@@ -36604,10 +36640,10 @@
         <v>1.17</v>
       </c>
       <c r="AP170">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ170">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR170">
         <v>1.01</v>
@@ -36813,7 +36849,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ171">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR171">
         <v>1.45</v>
@@ -37016,7 +37052,7 @@
         <v>0.86</v>
       </c>
       <c r="AP172">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ172">
         <v>0.75</v>
@@ -37222,7 +37258,7 @@
         <v>0.57</v>
       </c>
       <c r="AP173">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ173">
         <v>0.8</v>
@@ -37428,7 +37464,7 @@
         <v>2.14</v>
       </c>
       <c r="AP174">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ174">
         <v>1.79</v>
@@ -37637,7 +37673,7 @@
         <v>2</v>
       </c>
       <c r="AQ175">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR175">
         <v>1.58</v>
@@ -37968,7 +38004,7 @@
         <v>214</v>
       </c>
       <c r="P177" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="Q177">
         <v>7.5</v>
@@ -38046,7 +38082,7 @@
         <v>2.17</v>
       </c>
       <c r="AP177">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ177">
         <v>2.14</v>
@@ -38252,7 +38288,7 @@
         <v>0.86</v>
       </c>
       <c r="AP178">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ178">
         <v>1.54</v>
@@ -38458,10 +38494,10 @@
         <v>0.75</v>
       </c>
       <c r="AP179">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ179">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR179">
         <v>0.97</v>
@@ -38667,7 +38703,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ180">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR180">
         <v>1.41</v>
@@ -38792,7 +38828,7 @@
         <v>216</v>
       </c>
       <c r="P181" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="Q181">
         <v>3.4</v>
@@ -38873,7 +38909,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ181">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AR181">
         <v>1.35</v>
@@ -38998,7 +39034,7 @@
         <v>96</v>
       </c>
       <c r="P182" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="Q182">
         <v>2.3</v>
@@ -39282,7 +39318,7 @@
         <v>0.43</v>
       </c>
       <c r="AP183">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ183">
         <v>0.43</v>
@@ -39491,7 +39527,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ184">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR184">
         <v>1.44</v>
@@ -39616,7 +39652,7 @@
         <v>96</v>
       </c>
       <c r="P185" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="Q185">
         <v>2.6</v>
@@ -39694,7 +39730,7 @@
         <v>0.86</v>
       </c>
       <c r="AP185">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ185">
         <v>1.29</v>
@@ -39822,7 +39858,7 @@
         <v>96</v>
       </c>
       <c r="P186" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="Q186">
         <v>4.33</v>
@@ -39903,7 +39939,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ186">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR186">
         <v>1.08</v>
@@ -40028,7 +40064,7 @@
         <v>143</v>
       </c>
       <c r="P187" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="Q187">
         <v>2.4</v>
@@ -40234,7 +40270,7 @@
         <v>218</v>
       </c>
       <c r="P188" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="Q188">
         <v>2.4</v>
@@ -40312,7 +40348,7 @@
         <v>0.88</v>
       </c>
       <c r="AP188">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ188">
         <v>0.75</v>
@@ -40521,7 +40557,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ189">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR189">
         <v>1.4</v>
@@ -40646,7 +40682,7 @@
         <v>96</v>
       </c>
       <c r="P190" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="Q190">
         <v>3.75</v>
@@ -40724,7 +40760,7 @@
         <v>0.88</v>
       </c>
       <c r="AP190">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ190">
         <v>1.5</v>
@@ -40852,7 +40888,7 @@
         <v>96</v>
       </c>
       <c r="P191" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="Q191">
         <v>3.5</v>
@@ -40930,10 +40966,10 @@
         <v>1.14</v>
       </c>
       <c r="AP191">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ191">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR191">
         <v>1.43</v>
@@ -41136,10 +41172,10 @@
         <v>1.71</v>
       </c>
       <c r="AP192">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ192">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR192">
         <v>1.31</v>
@@ -41264,7 +41300,7 @@
         <v>96</v>
       </c>
       <c r="P193" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="Q193">
         <v>5.5</v>
@@ -41551,7 +41587,7 @@
         <v>2</v>
       </c>
       <c r="AQ194">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR194">
         <v>1.45</v>
@@ -41676,7 +41712,7 @@
         <v>221</v>
       </c>
       <c r="P195" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="Q195">
         <v>2.4</v>
@@ -41754,7 +41790,7 @@
         <v>1</v>
       </c>
       <c r="AP195">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ195">
         <v>0.93</v>
@@ -41963,7 +41999,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ196">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR196">
         <v>1.04</v>
@@ -42166,7 +42202,7 @@
         <v>0.88</v>
       </c>
       <c r="AP197">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ197">
         <v>0.67</v>
@@ -42294,7 +42330,7 @@
         <v>137</v>
       </c>
       <c r="P198" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="Q198">
         <v>2.25</v>
@@ -42581,7 +42617,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ199">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR199">
         <v>1.67</v>
@@ -42912,7 +42948,7 @@
         <v>224</v>
       </c>
       <c r="P201" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="Q201">
         <v>4</v>
@@ -42993,7 +43029,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ201">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AR201">
         <v>1.26</v>
@@ -43196,7 +43232,7 @@
         <v>0.78</v>
       </c>
       <c r="AP202">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ202">
         <v>0.75</v>
@@ -43608,7 +43644,7 @@
         <v>0.5</v>
       </c>
       <c r="AP204">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ204">
         <v>0.43</v>
@@ -43817,7 +43853,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ205">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR205">
         <v>1.59</v>
@@ -43942,7 +43978,7 @@
         <v>119</v>
       </c>
       <c r="P206" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="Q206">
         <v>4</v>
@@ -44020,7 +44056,7 @@
         <v>1.11</v>
       </c>
       <c r="AP206">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ206">
         <v>1.5</v>
@@ -44226,10 +44262,10 @@
         <v>1.63</v>
       </c>
       <c r="AP207">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ207">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR207">
         <v>1.67</v>
@@ -44354,7 +44390,7 @@
         <v>96</v>
       </c>
       <c r="P208" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="Q208">
         <v>2.05</v>
@@ -44435,7 +44471,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ208">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR208">
         <v>1.3</v>
@@ -44641,7 +44677,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ209">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR209">
         <v>1.37</v>
@@ -44766,7 +44802,7 @@
         <v>96</v>
       </c>
       <c r="P210" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="Q210">
         <v>3.1</v>
@@ -44844,7 +44880,7 @@
         <v>0.88</v>
       </c>
       <c r="AP210">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ210">
         <v>1.54</v>
@@ -44972,7 +45008,7 @@
         <v>99</v>
       </c>
       <c r="P211" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="Q211">
         <v>4.33</v>
@@ -45050,7 +45086,7 @@
         <v>2</v>
       </c>
       <c r="AP211">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ211">
         <v>2.14</v>
@@ -45259,7 +45295,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ212">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR212">
         <v>1.02</v>
@@ -45462,7 +45498,7 @@
         <v>0.5</v>
       </c>
       <c r="AP213">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ213">
         <v>0.43</v>
@@ -45590,7 +45626,7 @@
         <v>230</v>
       </c>
       <c r="P214" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="Q214">
         <v>3.75</v>
@@ -45671,7 +45707,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ214">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR214">
         <v>1.37</v>
@@ -45877,7 +45913,7 @@
         <v>2</v>
       </c>
       <c r="AQ215">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR215">
         <v>1.61</v>
@@ -46208,7 +46244,7 @@
         <v>233</v>
       </c>
       <c r="P217" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="Q217">
         <v>3.75</v>
@@ -46286,10 +46322,10 @@
         <v>1</v>
       </c>
       <c r="AP217">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ217">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR217">
         <v>1.24</v>
@@ -46492,10 +46528,10 @@
         <v>0.75</v>
       </c>
       <c r="AP218">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ218">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR218">
         <v>1.48</v>
@@ -46620,7 +46656,7 @@
         <v>96</v>
       </c>
       <c r="P219" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="Q219">
         <v>2.3</v>
@@ -46826,7 +46862,7 @@
         <v>234</v>
       </c>
       <c r="P220" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="Q220">
         <v>2.1</v>
@@ -47032,7 +47068,7 @@
         <v>96</v>
       </c>
       <c r="P221" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="Q221">
         <v>2.88</v>
@@ -47110,7 +47146,7 @@
         <v>1.3</v>
       </c>
       <c r="AP221">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ221">
         <v>1.5</v>
@@ -47319,7 +47355,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ222">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR222">
         <v>1.36</v>
@@ -47650,7 +47686,7 @@
         <v>132</v>
       </c>
       <c r="P224" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="Q224">
         <v>5</v>
@@ -47728,10 +47764,10 @@
         <v>2.1</v>
       </c>
       <c r="AP224">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ224">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AR224">
         <v>1</v>
@@ -47934,10 +47970,10 @@
         <v>1.44</v>
       </c>
       <c r="AP225">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ225">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR225">
         <v>1.15</v>
@@ -48062,7 +48098,7 @@
         <v>237</v>
       </c>
       <c r="P226" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="Q226">
         <v>2.2</v>
@@ -48346,7 +48382,7 @@
         <v>0.78</v>
       </c>
       <c r="AP227">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ227">
         <v>0.67</v>
@@ -48474,7 +48510,7 @@
         <v>239</v>
       </c>
       <c r="P228" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="Q228">
         <v>2.5</v>
@@ -48555,7 +48591,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ228">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR228">
         <v>1.43</v>
@@ -48680,7 +48716,7 @@
         <v>240</v>
       </c>
       <c r="P229" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="Q229">
         <v>3.75</v>
@@ -48967,7 +49003,7 @@
         <v>2</v>
       </c>
       <c r="AQ230">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR230">
         <v>1.34</v>
@@ -49173,7 +49209,7 @@
         <v>2</v>
       </c>
       <c r="AQ231">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR231">
         <v>1.64</v>
@@ -49298,7 +49334,7 @@
         <v>96</v>
       </c>
       <c r="P232" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="Q232">
         <v>4.5</v>
@@ -49376,10 +49412,10 @@
         <v>1.56</v>
       </c>
       <c r="AP232">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ232">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR232">
         <v>1.32</v>
@@ -49788,10 +49824,10 @@
         <v>1.33</v>
       </c>
       <c r="AP234">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ234">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR234">
         <v>1.1</v>
@@ -49916,7 +49952,7 @@
         <v>244</v>
       </c>
       <c r="P235" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="Q235">
         <v>3.5</v>
@@ -49997,7 +50033,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ235">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR235">
         <v>0.97</v>
@@ -50200,7 +50236,7 @@
         <v>0.71</v>
       </c>
       <c r="AP236">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ236">
         <v>1.17</v>
@@ -50328,7 +50364,7 @@
         <v>96</v>
       </c>
       <c r="P237" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="Q237">
         <v>2.6</v>
@@ -50406,7 +50442,7 @@
         <v>1.11</v>
       </c>
       <c r="AP237">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ237">
         <v>1.54</v>
@@ -50534,7 +50570,7 @@
         <v>245</v>
       </c>
       <c r="P238" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="Q238">
         <v>2.38</v>
@@ -50612,7 +50648,7 @@
         <v>0.44</v>
       </c>
       <c r="AP238">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ238">
         <v>0.43</v>
@@ -50740,7 +50776,7 @@
         <v>96</v>
       </c>
       <c r="P239" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="Q239">
         <v>4</v>
@@ -50818,10 +50854,10 @@
         <v>1.1</v>
       </c>
       <c r="AP239">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ239">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR239">
         <v>1.24</v>
@@ -51027,7 +51063,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ240">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR240">
         <v>1.39</v>
@@ -51152,7 +51188,7 @@
         <v>96</v>
       </c>
       <c r="P241" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="Q241">
         <v>6.5</v>
@@ -51230,7 +51266,7 @@
         <v>2.11</v>
       </c>
       <c r="AP241">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ241">
         <v>2.14</v>
@@ -51436,7 +51472,7 @@
         <v>0.8</v>
       </c>
       <c r="AP242">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ242">
         <v>0.8</v>
@@ -51642,10 +51678,10 @@
         <v>0.78</v>
       </c>
       <c r="AP243">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ243">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR243">
         <v>1.71</v>
@@ -51770,7 +51806,7 @@
         <v>249</v>
       </c>
       <c r="P244" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="Q244">
         <v>2.6</v>
@@ -51976,7 +52012,7 @@
         <v>250</v>
       </c>
       <c r="P245" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="Q245">
         <v>2.4</v>
@@ -52469,7 +52505,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ247">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR247">
         <v>1.39</v>
@@ -52594,7 +52630,7 @@
         <v>96</v>
       </c>
       <c r="P248" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="Q248">
         <v>2.75</v>
@@ -52675,7 +52711,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ248">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR248">
         <v>1.32</v>
@@ -52800,7 +52836,7 @@
         <v>252</v>
       </c>
       <c r="P249" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="Q249">
         <v>2.2</v>
@@ -52878,7 +52914,7 @@
         <v>0.64</v>
       </c>
       <c r="AP249">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ249">
         <v>0.75</v>
@@ -53006,7 +53042,7 @@
         <v>253</v>
       </c>
       <c r="P250" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="Q250">
         <v>2.5</v>
@@ -53212,7 +53248,7 @@
         <v>96</v>
       </c>
       <c r="P251" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="Q251">
         <v>3.75</v>
@@ -53290,10 +53326,10 @@
         <v>2.18</v>
       </c>
       <c r="AP251">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ251">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AR251">
         <v>1.13</v>
@@ -53418,7 +53454,7 @@
         <v>96</v>
       </c>
       <c r="P252" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="Q252">
         <v>2.75</v>
@@ -53702,10 +53738,10 @@
         <v>1.27</v>
       </c>
       <c r="AP253">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ253">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR253">
         <v>0.99</v>
@@ -53911,7 +53947,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ254">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR254">
         <v>1.52</v>
@@ -54117,7 +54153,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ255">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AR255">
         <v>1.31</v>
@@ -54242,7 +54278,7 @@
         <v>257</v>
       </c>
       <c r="P256" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="Q256">
         <v>2.75</v>
@@ -54320,10 +54356,10 @@
         <v>1.6</v>
       </c>
       <c r="AP256">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ256">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR256">
         <v>1.34</v>
@@ -54448,7 +54484,7 @@
         <v>160</v>
       </c>
       <c r="P257" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="Q257">
         <v>3.1</v>
@@ -54732,7 +54768,7 @@
         <v>0.45</v>
       </c>
       <c r="AP258">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ258">
         <v>0.43</v>
@@ -54941,7 +54977,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ259">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR259">
         <v>1.32</v>
@@ -55066,7 +55102,7 @@
         <v>259</v>
       </c>
       <c r="P260" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="Q260">
         <v>2.5</v>
@@ -55353,7 +55389,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ261">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR261">
         <v>1.61</v>
@@ -55556,7 +55592,7 @@
         <v>1.33</v>
       </c>
       <c r="AP262">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ262">
         <v>1.5</v>
@@ -55762,7 +55798,7 @@
         <v>0.58</v>
       </c>
       <c r="AP263">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ263">
         <v>0.75</v>
@@ -55968,7 +56004,7 @@
         <v>0.64</v>
       </c>
       <c r="AP264">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ264">
         <v>0.67</v>
@@ -56096,7 +56132,7 @@
         <v>263</v>
       </c>
       <c r="P265" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="Q265">
         <v>2.38</v>
@@ -56302,7 +56338,7 @@
         <v>264</v>
       </c>
       <c r="P266" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="Q266">
         <v>3.75</v>
@@ -56589,7 +56625,7 @@
         <v>2</v>
       </c>
       <c r="AQ267">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR267">
         <v>1.34</v>
@@ -56792,7 +56828,7 @@
         <v>0.75</v>
       </c>
       <c r="AP268">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ268">
         <v>1.17</v>
@@ -57001,7 +57037,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ269">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR269">
         <v>1.35</v>
@@ -57204,7 +57240,7 @@
         <v>0.5</v>
       </c>
       <c r="AP270">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ270">
         <v>0.43</v>
@@ -57332,7 +57368,7 @@
         <v>268</v>
       </c>
       <c r="P271" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="Q271">
         <v>3.75</v>
@@ -57410,7 +57446,7 @@
         <v>1.3</v>
       </c>
       <c r="AP271">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ271">
         <v>1.54</v>
@@ -57538,7 +57574,7 @@
         <v>96</v>
       </c>
       <c r="P272" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="Q272">
         <v>2.63</v>
@@ -57619,7 +57655,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ272">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR272">
         <v>1.38</v>
@@ -57744,7 +57780,7 @@
         <v>183</v>
       </c>
       <c r="P273" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="Q273">
         <v>3.25</v>
@@ -57822,7 +57858,7 @@
         <v>0.91</v>
       </c>
       <c r="AP273">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ273">
         <v>0.93</v>
@@ -57950,7 +57986,7 @@
         <v>269</v>
       </c>
       <c r="P274" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="Q274">
         <v>3.2</v>
@@ -58031,7 +58067,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ274">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR274">
         <v>1</v>
@@ -58234,10 +58270,10 @@
         <v>1.3</v>
       </c>
       <c r="AP275">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ275">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR275">
         <v>1.64</v>
@@ -58646,7 +58682,7 @@
         <v>0.58</v>
       </c>
       <c r="AP277">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ277">
         <v>0.67</v>
@@ -58855,7 +58891,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ278">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR278">
         <v>1.38</v>
@@ -58980,7 +59016,7 @@
         <v>96</v>
       </c>
       <c r="P279" t="s">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="Q279">
         <v>5.5</v>
@@ -59058,7 +59094,7 @@
         <v>2.09</v>
       </c>
       <c r="AP279">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ279">
         <v>2.14</v>
@@ -59186,7 +59222,7 @@
         <v>118</v>
       </c>
       <c r="P280" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="Q280">
         <v>2.6</v>
@@ -59267,7 +59303,7 @@
         <v>2</v>
       </c>
       <c r="AQ280">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR280">
         <v>1.62</v>
@@ -59676,7 +59712,7 @@
         <v>0.55</v>
       </c>
       <c r="AP282">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ282">
         <v>0.43</v>
@@ -59885,7 +59921,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ283">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR283">
         <v>1.41</v>
@@ -60010,7 +60046,7 @@
         <v>172</v>
       </c>
       <c r="P284" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="Q284">
         <v>3.6</v>
@@ -60091,7 +60127,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ284">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR284">
         <v>1.31</v>
@@ -60500,7 +60536,7 @@
         <v>0.75</v>
       </c>
       <c r="AP286">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ286">
         <v>0.8</v>
@@ -60915,7 +60951,7 @@
         <v>2</v>
       </c>
       <c r="AQ288">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR288">
         <v>1.29</v>
@@ -61121,7 +61157,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ289">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR289">
         <v>1.47</v>
@@ -61324,10 +61360,10 @@
         <v>1.18</v>
       </c>
       <c r="AP290">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ290">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AR290">
         <v>1.02</v>
@@ -61658,7 +61694,7 @@
         <v>275</v>
       </c>
       <c r="P292" t="s">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="Q292">
         <v>3.4</v>
@@ -61736,10 +61772,10 @@
         <v>1.82</v>
       </c>
       <c r="AP292">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ292">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AR292">
         <v>1.55</v>
@@ -61942,10 +61978,10 @@
         <v>1.08</v>
       </c>
       <c r="AP293">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ293">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR293">
         <v>1.2</v>
@@ -62148,10 +62184,10 @@
         <v>1.18</v>
       </c>
       <c r="AP294">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ294">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR294">
         <v>1.64</v>
@@ -62276,7 +62312,7 @@
         <v>277</v>
       </c>
       <c r="P295" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="Q295">
         <v>3.2</v>
@@ -62354,7 +62390,7 @@
         <v>1.25</v>
       </c>
       <c r="AP295">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AQ295">
         <v>1.29</v>
@@ -62482,7 +62518,7 @@
         <v>278</v>
       </c>
       <c r="P296" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="Q296">
         <v>2</v>
@@ -62688,7 +62724,7 @@
         <v>279</v>
       </c>
       <c r="P297" t="s">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="Q297">
         <v>3.25</v>
@@ -62769,7 +62805,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ297">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR297">
         <v>1.53</v>
@@ -62894,7 +62930,7 @@
         <v>267</v>
       </c>
       <c r="P298" t="s">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="Q298">
         <v>3.6</v>
@@ -62972,10 +63008,10 @@
         <v>1.17</v>
       </c>
       <c r="AP298">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ298">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR298">
         <v>1.33</v>
@@ -63100,7 +63136,7 @@
         <v>137</v>
       </c>
       <c r="P299" t="s">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="Q299">
         <v>3.25</v>
@@ -63181,7 +63217,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ299">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AR299">
         <v>1.37</v>
@@ -63306,7 +63342,7 @@
         <v>132</v>
       </c>
       <c r="P300" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="Q300">
         <v>2.75</v>
@@ -63384,10 +63420,10 @@
         <v>0.73</v>
       </c>
       <c r="AP300">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ300">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR300">
         <v>0.91</v>
@@ -63590,7 +63626,7 @@
         <v>2.08</v>
       </c>
       <c r="AP301">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ301">
         <v>1.79</v>
@@ -63718,7 +63754,7 @@
         <v>281</v>
       </c>
       <c r="P302" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="Q302">
         <v>2.63</v>
@@ -63799,7 +63835,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ302">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR302">
         <v>1.22</v>
@@ -63924,7 +63960,7 @@
         <v>282</v>
       </c>
       <c r="P303" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="Q303">
         <v>2.88</v>
@@ -64005,7 +64041,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ303">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AR303">
         <v>1.68</v>
@@ -64130,7 +64166,7 @@
         <v>94</v>
       </c>
       <c r="P304" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="Q304">
         <v>2.25</v>
@@ -64208,10 +64244,10 @@
         <v>0.75</v>
       </c>
       <c r="AP304">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ304">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR304">
         <v>1.18</v>
@@ -64542,7 +64578,7 @@
         <v>283</v>
       </c>
       <c r="P306" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="Q306">
         <v>4</v>
@@ -64620,10 +64656,10 @@
         <v>1.58</v>
       </c>
       <c r="AP306">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ306">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR306">
         <v>1.4</v>
@@ -64829,7 +64865,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ307">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AR307">
         <v>1.46</v>
@@ -65035,7 +65071,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ308">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR308">
         <v>1.29</v>
@@ -65160,7 +65196,7 @@
         <v>285</v>
       </c>
       <c r="P309" t="s">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="Q309">
         <v>4.33</v>
@@ -65241,7 +65277,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ309">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR309">
         <v>1</v>
@@ -65444,7 +65480,7 @@
         <v>0.8</v>
       </c>
       <c r="AP310">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AQ310">
         <v>1.17</v>
@@ -65778,7 +65814,7 @@
         <v>287</v>
       </c>
       <c r="P312" t="s">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="Q312">
         <v>3.25</v>
@@ -66474,7 +66510,7 @@
         <v>1.08</v>
       </c>
       <c r="AP315">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ315">
         <v>0.93</v>
@@ -66680,7 +66716,7 @@
         <v>0.77</v>
       </c>
       <c r="AP316">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ316">
         <v>0.67</v>
@@ -67014,7 +67050,7 @@
         <v>291</v>
       </c>
       <c r="P318" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="Q318">
         <v>3.75</v>
@@ -67632,7 +67668,7 @@
         <v>293</v>
       </c>
       <c r="P321" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="Q321">
         <v>2.38</v>
@@ -68044,7 +68080,7 @@
         <v>295</v>
       </c>
       <c r="P323" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="Q323">
         <v>2.88</v>
@@ -68456,7 +68492,7 @@
         <v>297</v>
       </c>
       <c r="P325" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="Q325">
         <v>3.25</v>
@@ -68662,7 +68698,7 @@
         <v>96</v>
       </c>
       <c r="P326" t="s">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="Q326">
         <v>3</v>
@@ -68868,7 +68904,7 @@
         <v>96</v>
       </c>
       <c r="P327" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="Q327">
         <v>2.1</v>
@@ -69074,7 +69110,7 @@
         <v>96</v>
       </c>
       <c r="P328" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="Q328">
         <v>3.5</v>
@@ -69231,6 +69267,2478 @@
       </c>
       <c r="BP328">
         <v>1.4</v>
+      </c>
+    </row>
+    <row r="329" spans="1:68">
+      <c r="A329" s="1">
+        <v>328</v>
+      </c>
+      <c r="B329">
+        <v>7727226</v>
+      </c>
+      <c r="C329" t="s">
+        <v>68</v>
+      </c>
+      <c r="D329" t="s">
+        <v>69</v>
+      </c>
+      <c r="E329" s="2">
+        <v>45689.39583333334</v>
+      </c>
+      <c r="F329">
+        <v>30</v>
+      </c>
+      <c r="G329" t="s">
+        <v>76</v>
+      </c>
+      <c r="H329" t="s">
+        <v>81</v>
+      </c>
+      <c r="I329">
+        <v>2</v>
+      </c>
+      <c r="J329">
+        <v>1</v>
+      </c>
+      <c r="K329">
+        <v>3</v>
+      </c>
+      <c r="L329">
+        <v>4</v>
+      </c>
+      <c r="M329">
+        <v>1</v>
+      </c>
+      <c r="N329">
+        <v>5</v>
+      </c>
+      <c r="O329" t="s">
+        <v>298</v>
+      </c>
+      <c r="P329" t="s">
+        <v>333</v>
+      </c>
+      <c r="Q329">
+        <v>2.6</v>
+      </c>
+      <c r="R329">
+        <v>1.95</v>
+      </c>
+      <c r="S329">
+        <v>5.5</v>
+      </c>
+      <c r="T329">
+        <v>1.53</v>
+      </c>
+      <c r="U329">
+        <v>2.38</v>
+      </c>
+      <c r="V329">
+        <v>3.75</v>
+      </c>
+      <c r="W329">
+        <v>1.25</v>
+      </c>
+      <c r="X329">
+        <v>11</v>
+      </c>
+      <c r="Y329">
+        <v>1.05</v>
+      </c>
+      <c r="Z329">
+        <v>1.82</v>
+      </c>
+      <c r="AA329">
+        <v>3.23</v>
+      </c>
+      <c r="AB329">
+        <v>4.7</v>
+      </c>
+      <c r="AC329">
+        <v>1.1</v>
+      </c>
+      <c r="AD329">
+        <v>6.5</v>
+      </c>
+      <c r="AE329">
+        <v>1.48</v>
+      </c>
+      <c r="AF329">
+        <v>2.6</v>
+      </c>
+      <c r="AG329">
+        <v>2.15</v>
+      </c>
+      <c r="AH329">
+        <v>1.61</v>
+      </c>
+      <c r="AI329">
+        <v>2.2</v>
+      </c>
+      <c r="AJ329">
+        <v>1.62</v>
+      </c>
+      <c r="AK329">
+        <v>1.18</v>
+      </c>
+      <c r="AL329">
+        <v>1.28</v>
+      </c>
+      <c r="AM329">
+        <v>1.93</v>
+      </c>
+      <c r="AN329">
+        <v>1.64</v>
+      </c>
+      <c r="AO329">
+        <v>1.08</v>
+      </c>
+      <c r="AP329">
+        <v>1.73</v>
+      </c>
+      <c r="AQ329">
+        <v>1</v>
+      </c>
+      <c r="AR329">
+        <v>1.18</v>
+      </c>
+      <c r="AS329">
+        <v>0.91</v>
+      </c>
+      <c r="AT329">
+        <v>2.09</v>
+      </c>
+      <c r="AU329">
+        <v>7</v>
+      </c>
+      <c r="AV329">
+        <v>2</v>
+      </c>
+      <c r="AW329">
+        <v>8</v>
+      </c>
+      <c r="AX329">
+        <v>4</v>
+      </c>
+      <c r="AY329">
+        <v>16</v>
+      </c>
+      <c r="AZ329">
+        <v>9</v>
+      </c>
+      <c r="BA329">
+        <v>4</v>
+      </c>
+      <c r="BB329">
+        <v>4</v>
+      </c>
+      <c r="BC329">
+        <v>8</v>
+      </c>
+      <c r="BD329">
+        <v>1.49</v>
+      </c>
+      <c r="BE329">
+        <v>7</v>
+      </c>
+      <c r="BF329">
+        <v>2.9</v>
+      </c>
+      <c r="BG329">
+        <v>1.3</v>
+      </c>
+      <c r="BH329">
+        <v>3.15</v>
+      </c>
+      <c r="BI329">
+        <v>1.5</v>
+      </c>
+      <c r="BJ329">
+        <v>2.35</v>
+      </c>
+      <c r="BK329">
+        <v>1.83</v>
+      </c>
+      <c r="BL329">
+        <v>1.85</v>
+      </c>
+      <c r="BM329">
+        <v>2.3</v>
+      </c>
+      <c r="BN329">
+        <v>1.54</v>
+      </c>
+      <c r="BO329">
+        <v>2.9</v>
+      </c>
+      <c r="BP329">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="330" spans="1:68">
+      <c r="A330" s="1">
+        <v>329</v>
+      </c>
+      <c r="B330">
+        <v>7727216</v>
+      </c>
+      <c r="C330" t="s">
+        <v>68</v>
+      </c>
+      <c r="D330" t="s">
+        <v>69</v>
+      </c>
+      <c r="E330" s="2">
+        <v>45689.39583333334</v>
+      </c>
+      <c r="F330">
+        <v>30</v>
+      </c>
+      <c r="G330" t="s">
+        <v>70</v>
+      </c>
+      <c r="H330" t="s">
+        <v>78</v>
+      </c>
+      <c r="I330">
+        <v>0</v>
+      </c>
+      <c r="J330">
+        <v>0</v>
+      </c>
+      <c r="K330">
+        <v>0</v>
+      </c>
+      <c r="L330">
+        <v>0</v>
+      </c>
+      <c r="M330">
+        <v>0</v>
+      </c>
+      <c r="N330">
+        <v>0</v>
+      </c>
+      <c r="O330" t="s">
+        <v>96</v>
+      </c>
+      <c r="P330" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q330">
+        <v>2</v>
+      </c>
+      <c r="R330">
+        <v>2.38</v>
+      </c>
+      <c r="S330">
+        <v>6</v>
+      </c>
+      <c r="T330">
+        <v>1.33</v>
+      </c>
+      <c r="U330">
+        <v>3.25</v>
+      </c>
+      <c r="V330">
+        <v>2.63</v>
+      </c>
+      <c r="W330">
+        <v>1.44</v>
+      </c>
+      <c r="X330">
+        <v>6.5</v>
+      </c>
+      <c r="Y330">
+        <v>1.11</v>
+      </c>
+      <c r="Z330">
+        <v>1.44</v>
+      </c>
+      <c r="AA330">
+        <v>4.6</v>
+      </c>
+      <c r="AB330">
+        <v>6.4</v>
+      </c>
+      <c r="AC330">
+        <v>1.04</v>
+      </c>
+      <c r="AD330">
+        <v>10</v>
+      </c>
+      <c r="AE330">
+        <v>1.22</v>
+      </c>
+      <c r="AF330">
+        <v>4.2</v>
+      </c>
+      <c r="AG330">
+        <v>1.75</v>
+      </c>
+      <c r="AH330">
+        <v>2</v>
+      </c>
+      <c r="AI330">
+        <v>1.91</v>
+      </c>
+      <c r="AJ330">
+        <v>1.91</v>
+      </c>
+      <c r="AK330">
+        <v>1.11</v>
+      </c>
+      <c r="AL330">
+        <v>1.15</v>
+      </c>
+      <c r="AM330">
+        <v>2.6</v>
+      </c>
+      <c r="AN330">
+        <v>1.21</v>
+      </c>
+      <c r="AO330">
+        <v>0.92</v>
+      </c>
+      <c r="AP330">
+        <v>1.2</v>
+      </c>
+      <c r="AQ330">
+        <v>0.93</v>
+      </c>
+      <c r="AR330">
+        <v>1.56</v>
+      </c>
+      <c r="AS330">
+        <v>1.07</v>
+      </c>
+      <c r="AT330">
+        <v>2.63</v>
+      </c>
+      <c r="AU330">
+        <v>10</v>
+      </c>
+      <c r="AV330">
+        <v>3</v>
+      </c>
+      <c r="AW330">
+        <v>9</v>
+      </c>
+      <c r="AX330">
+        <v>2</v>
+      </c>
+      <c r="AY330">
+        <v>22</v>
+      </c>
+      <c r="AZ330">
+        <v>6</v>
+      </c>
+      <c r="BA330">
+        <v>6</v>
+      </c>
+      <c r="BB330">
+        <v>4</v>
+      </c>
+      <c r="BC330">
+        <v>10</v>
+      </c>
+      <c r="BD330">
+        <v>1.34</v>
+      </c>
+      <c r="BE330">
+        <v>7</v>
+      </c>
+      <c r="BF330">
+        <v>3.55</v>
+      </c>
+      <c r="BG330">
+        <v>1.24</v>
+      </c>
+      <c r="BH330">
+        <v>3.55</v>
+      </c>
+      <c r="BI330">
+        <v>1.41</v>
+      </c>
+      <c r="BJ330">
+        <v>2.65</v>
+      </c>
+      <c r="BK330">
+        <v>1.67</v>
+      </c>
+      <c r="BL330">
+        <v>2.05</v>
+      </c>
+      <c r="BM330">
+        <v>2.06</v>
+      </c>
+      <c r="BN330">
+        <v>1.66</v>
+      </c>
+      <c r="BO330">
+        <v>2.55</v>
+      </c>
+      <c r="BP330">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="331" spans="1:68">
+      <c r="A331" s="1">
+        <v>330</v>
+      </c>
+      <c r="B331">
+        <v>7727227</v>
+      </c>
+      <c r="C331" t="s">
+        <v>68</v>
+      </c>
+      <c r="D331" t="s">
+        <v>69</v>
+      </c>
+      <c r="E331" s="2">
+        <v>45689.5</v>
+      </c>
+      <c r="F331">
+        <v>30</v>
+      </c>
+      <c r="G331" t="s">
+        <v>72</v>
+      </c>
+      <c r="H331" t="s">
+        <v>89</v>
+      </c>
+      <c r="I331">
+        <v>1</v>
+      </c>
+      <c r="J331">
+        <v>0</v>
+      </c>
+      <c r="K331">
+        <v>1</v>
+      </c>
+      <c r="L331">
+        <v>1</v>
+      </c>
+      <c r="M331">
+        <v>1</v>
+      </c>
+      <c r="N331">
+        <v>2</v>
+      </c>
+      <c r="O331" t="s">
+        <v>299</v>
+      </c>
+      <c r="P331" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q331">
+        <v>3.4</v>
+      </c>
+      <c r="R331">
+        <v>2</v>
+      </c>
+      <c r="S331">
+        <v>3.6</v>
+      </c>
+      <c r="T331">
+        <v>1.5</v>
+      </c>
+      <c r="U331">
+        <v>2.5</v>
+      </c>
+      <c r="V331">
+        <v>3.5</v>
+      </c>
+      <c r="W331">
+        <v>1.29</v>
+      </c>
+      <c r="X331">
+        <v>11</v>
+      </c>
+      <c r="Y331">
+        <v>1.05</v>
+      </c>
+      <c r="Z331">
+        <v>2.58</v>
+      </c>
+      <c r="AA331">
+        <v>3.17</v>
+      </c>
+      <c r="AB331">
+        <v>2.73</v>
+      </c>
+      <c r="AC331">
+        <v>1.1</v>
+      </c>
+      <c r="AD331">
+        <v>6.5</v>
+      </c>
+      <c r="AE331">
+        <v>1.5</v>
+      </c>
+      <c r="AF331">
+        <v>2.45</v>
+      </c>
+      <c r="AG331">
+        <v>2.31</v>
+      </c>
+      <c r="AH331">
+        <v>1.61</v>
+      </c>
+      <c r="AI331">
+        <v>1.95</v>
+      </c>
+      <c r="AJ331">
+        <v>1.8</v>
+      </c>
+      <c r="AK331">
+        <v>1.42</v>
+      </c>
+      <c r="AL331">
+        <v>1.3</v>
+      </c>
+      <c r="AM331">
+        <v>1.44</v>
+      </c>
+      <c r="AN331">
+        <v>1.15</v>
+      </c>
+      <c r="AO331">
+        <v>1.21</v>
+      </c>
+      <c r="AP331">
+        <v>1.14</v>
+      </c>
+      <c r="AQ331">
+        <v>1.2</v>
+      </c>
+      <c r="AR331">
+        <v>1.19</v>
+      </c>
+      <c r="AS331">
+        <v>1.1</v>
+      </c>
+      <c r="AT331">
+        <v>2.29</v>
+      </c>
+      <c r="AU331">
+        <v>4</v>
+      </c>
+      <c r="AV331">
+        <v>4</v>
+      </c>
+      <c r="AW331">
+        <v>7</v>
+      </c>
+      <c r="AX331">
+        <v>5</v>
+      </c>
+      <c r="AY331">
+        <v>13</v>
+      </c>
+      <c r="AZ331">
+        <v>12</v>
+      </c>
+      <c r="BA331">
+        <v>4</v>
+      </c>
+      <c r="BB331">
+        <v>6</v>
+      </c>
+      <c r="BC331">
+        <v>10</v>
+      </c>
+      <c r="BD331">
+        <v>1.81</v>
+      </c>
+      <c r="BE331">
+        <v>6.4</v>
+      </c>
+      <c r="BF331">
+        <v>2.2</v>
+      </c>
+      <c r="BG331">
+        <v>1.35</v>
+      </c>
+      <c r="BH331">
+        <v>2.9</v>
+      </c>
+      <c r="BI331">
+        <v>1.61</v>
+      </c>
+      <c r="BJ331">
+        <v>2.15</v>
+      </c>
+      <c r="BK331">
+        <v>1.97</v>
+      </c>
+      <c r="BL331">
+        <v>1.73</v>
+      </c>
+      <c r="BM331">
+        <v>2.5</v>
+      </c>
+      <c r="BN331">
+        <v>1.46</v>
+      </c>
+      <c r="BO331">
+        <v>3.3</v>
+      </c>
+      <c r="BP331">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="332" spans="1:68">
+      <c r="A332" s="1">
+        <v>331</v>
+      </c>
+      <c r="B332">
+        <v>7727225</v>
+      </c>
+      <c r="C332" t="s">
+        <v>68</v>
+      </c>
+      <c r="D332" t="s">
+        <v>69</v>
+      </c>
+      <c r="E332" s="2">
+        <v>45689.5</v>
+      </c>
+      <c r="F332">
+        <v>30</v>
+      </c>
+      <c r="G332" t="s">
+        <v>82</v>
+      </c>
+      <c r="H332" t="s">
+        <v>92</v>
+      </c>
+      <c r="I332">
+        <v>0</v>
+      </c>
+      <c r="J332">
+        <v>1</v>
+      </c>
+      <c r="K332">
+        <v>1</v>
+      </c>
+      <c r="L332">
+        <v>2</v>
+      </c>
+      <c r="M332">
+        <v>1</v>
+      </c>
+      <c r="N332">
+        <v>3</v>
+      </c>
+      <c r="O332" t="s">
+        <v>300</v>
+      </c>
+      <c r="P332" t="s">
+        <v>413</v>
+      </c>
+      <c r="Q332">
+        <v>3.75</v>
+      </c>
+      <c r="R332">
+        <v>2.2</v>
+      </c>
+      <c r="S332">
+        <v>2.75</v>
+      </c>
+      <c r="T332">
+        <v>1.4</v>
+      </c>
+      <c r="U332">
+        <v>2.75</v>
+      </c>
+      <c r="V332">
+        <v>2.75</v>
+      </c>
+      <c r="W332">
+        <v>1.4</v>
+      </c>
+      <c r="X332">
+        <v>8</v>
+      </c>
+      <c r="Y332">
+        <v>1.08</v>
+      </c>
+      <c r="Z332">
+        <v>3.38</v>
+      </c>
+      <c r="AA332">
+        <v>3.38</v>
+      </c>
+      <c r="AB332">
+        <v>2.09</v>
+      </c>
+      <c r="AC332">
+        <v>1.06</v>
+      </c>
+      <c r="AD332">
+        <v>9.5</v>
+      </c>
+      <c r="AE332">
+        <v>1.36</v>
+      </c>
+      <c r="AF332">
+        <v>3.2</v>
+      </c>
+      <c r="AG332">
+        <v>1.87</v>
+      </c>
+      <c r="AH332">
+        <v>1.87</v>
+      </c>
+      <c r="AI332">
+        <v>1.7</v>
+      </c>
+      <c r="AJ332">
+        <v>2.05</v>
+      </c>
+      <c r="AK332">
+        <v>1.7</v>
+      </c>
+      <c r="AL332">
+        <v>1.3</v>
+      </c>
+      <c r="AM332">
+        <v>1.3</v>
+      </c>
+      <c r="AN332">
+        <v>1.08</v>
+      </c>
+      <c r="AO332">
+        <v>1.46</v>
+      </c>
+      <c r="AP332">
+        <v>1.21</v>
+      </c>
+      <c r="AQ332">
+        <v>1.36</v>
+      </c>
+      <c r="AR332">
+        <v>1.04</v>
+      </c>
+      <c r="AS332">
+        <v>1.25</v>
+      </c>
+      <c r="AT332">
+        <v>2.29</v>
+      </c>
+      <c r="AU332">
+        <v>6</v>
+      </c>
+      <c r="AV332">
+        <v>4</v>
+      </c>
+      <c r="AW332">
+        <v>3</v>
+      </c>
+      <c r="AX332">
+        <v>17</v>
+      </c>
+      <c r="AY332">
+        <v>17</v>
+      </c>
+      <c r="AZ332">
+        <v>26</v>
+      </c>
+      <c r="BA332">
+        <v>7</v>
+      </c>
+      <c r="BB332">
+        <v>7</v>
+      </c>
+      <c r="BC332">
+        <v>14</v>
+      </c>
+      <c r="BD332">
+        <v>2.35</v>
+      </c>
+      <c r="BE332">
+        <v>6.4</v>
+      </c>
+      <c r="BF332">
+        <v>1.73</v>
+      </c>
+      <c r="BG332">
+        <v>1.33</v>
+      </c>
+      <c r="BH332">
+        <v>2.95</v>
+      </c>
+      <c r="BI332">
+        <v>1.56</v>
+      </c>
+      <c r="BJ332">
+        <v>2.23</v>
+      </c>
+      <c r="BK332">
+        <v>1.91</v>
+      </c>
+      <c r="BL332">
+        <v>1.78</v>
+      </c>
+      <c r="BM332">
+        <v>2.4</v>
+      </c>
+      <c r="BN332">
+        <v>1.49</v>
+      </c>
+      <c r="BO332">
+        <v>3.05</v>
+      </c>
+      <c r="BP332">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="333" spans="1:68">
+      <c r="A333" s="1">
+        <v>332</v>
+      </c>
+      <c r="B333">
+        <v>7727224</v>
+      </c>
+      <c r="C333" t="s">
+        <v>68</v>
+      </c>
+      <c r="D333" t="s">
+        <v>69</v>
+      </c>
+      <c r="E333" s="2">
+        <v>45689.5</v>
+      </c>
+      <c r="F333">
+        <v>30</v>
+      </c>
+      <c r="G333" t="s">
+        <v>84</v>
+      </c>
+      <c r="H333" t="s">
+        <v>93</v>
+      </c>
+      <c r="I333">
+        <v>0</v>
+      </c>
+      <c r="J333">
+        <v>0</v>
+      </c>
+      <c r="K333">
+        <v>0</v>
+      </c>
+      <c r="L333">
+        <v>1</v>
+      </c>
+      <c r="M333">
+        <v>0</v>
+      </c>
+      <c r="N333">
+        <v>1</v>
+      </c>
+      <c r="O333" t="s">
+        <v>219</v>
+      </c>
+      <c r="P333" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q333">
+        <v>3.5</v>
+      </c>
+      <c r="R333">
+        <v>2.25</v>
+      </c>
+      <c r="S333">
+        <v>2.88</v>
+      </c>
+      <c r="T333">
+        <v>1.33</v>
+      </c>
+      <c r="U333">
+        <v>3.25</v>
+      </c>
+      <c r="V333">
+        <v>2.63</v>
+      </c>
+      <c r="W333">
+        <v>1.44</v>
+      </c>
+      <c r="X333">
+        <v>6.5</v>
+      </c>
+      <c r="Y333">
+        <v>1.11</v>
+      </c>
+      <c r="Z333">
+        <v>2.98</v>
+      </c>
+      <c r="AA333">
+        <v>3.47</v>
+      </c>
+      <c r="AB333">
+        <v>2.24</v>
+      </c>
+      <c r="AC333">
+        <v>1.05</v>
+      </c>
+      <c r="AD333">
+        <v>9.5</v>
+      </c>
+      <c r="AE333">
+        <v>1.22</v>
+      </c>
+      <c r="AF333">
+        <v>4</v>
+      </c>
+      <c r="AG333">
+        <v>1.7</v>
+      </c>
+      <c r="AH333">
+        <v>2.05</v>
+      </c>
+      <c r="AI333">
+        <v>1.57</v>
+      </c>
+      <c r="AJ333">
+        <v>2.25</v>
+      </c>
+      <c r="AK333">
+        <v>1.62</v>
+      </c>
+      <c r="AL333">
+        <v>1.25</v>
+      </c>
+      <c r="AM333">
+        <v>1.38</v>
+      </c>
+      <c r="AN333">
+        <v>2.25</v>
+      </c>
+      <c r="AO333">
+        <v>1.54</v>
+      </c>
+      <c r="AP333">
+        <v>2.31</v>
+      </c>
+      <c r="AQ333">
+        <v>1.43</v>
+      </c>
+      <c r="AR333">
+        <v>1.3</v>
+      </c>
+      <c r="AS333">
+        <v>1.12</v>
+      </c>
+      <c r="AT333">
+        <v>2.42</v>
+      </c>
+      <c r="AU333">
+        <v>3</v>
+      </c>
+      <c r="AV333">
+        <v>5</v>
+      </c>
+      <c r="AW333">
+        <v>9</v>
+      </c>
+      <c r="AX333">
+        <v>8</v>
+      </c>
+      <c r="AY333">
+        <v>16</v>
+      </c>
+      <c r="AZ333">
+        <v>13</v>
+      </c>
+      <c r="BA333">
+        <v>2</v>
+      </c>
+      <c r="BB333">
+        <v>4</v>
+      </c>
+      <c r="BC333">
+        <v>6</v>
+      </c>
+      <c r="BD333">
+        <v>2.3</v>
+      </c>
+      <c r="BE333">
+        <v>6.75</v>
+      </c>
+      <c r="BF333">
+        <v>1.74</v>
+      </c>
+      <c r="BG333">
+        <v>1.21</v>
+      </c>
+      <c r="BH333">
+        <v>3.8</v>
+      </c>
+      <c r="BI333">
+        <v>1.37</v>
+      </c>
+      <c r="BJ333">
+        <v>2.8</v>
+      </c>
+      <c r="BK333">
+        <v>1.61</v>
+      </c>
+      <c r="BL333">
+        <v>2.15</v>
+      </c>
+      <c r="BM333">
+        <v>1.97</v>
+      </c>
+      <c r="BN333">
+        <v>1.72</v>
+      </c>
+      <c r="BO333">
+        <v>2.45</v>
+      </c>
+      <c r="BP333">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="334" spans="1:68">
+      <c r="A334" s="1">
+        <v>333</v>
+      </c>
+      <c r="B334">
+        <v>7727223</v>
+      </c>
+      <c r="C334" t="s">
+        <v>68</v>
+      </c>
+      <c r="D334" t="s">
+        <v>69</v>
+      </c>
+      <c r="E334" s="2">
+        <v>45689.5</v>
+      </c>
+      <c r="F334">
+        <v>30</v>
+      </c>
+      <c r="G334" t="s">
+        <v>87</v>
+      </c>
+      <c r="H334" t="s">
+        <v>90</v>
+      </c>
+      <c r="I334">
+        <v>2</v>
+      </c>
+      <c r="J334">
+        <v>0</v>
+      </c>
+      <c r="K334">
+        <v>2</v>
+      </c>
+      <c r="L334">
+        <v>3</v>
+      </c>
+      <c r="M334">
+        <v>2</v>
+      </c>
+      <c r="N334">
+        <v>5</v>
+      </c>
+      <c r="O334" t="s">
+        <v>301</v>
+      </c>
+      <c r="P334" t="s">
+        <v>437</v>
+      </c>
+      <c r="Q334">
+        <v>4.75</v>
+      </c>
+      <c r="R334">
+        <v>2.1</v>
+      </c>
+      <c r="S334">
+        <v>2.5</v>
+      </c>
+      <c r="T334">
+        <v>1.4</v>
+      </c>
+      <c r="U334">
+        <v>2.75</v>
+      </c>
+      <c r="V334">
+        <v>3</v>
+      </c>
+      <c r="W334">
+        <v>1.36</v>
+      </c>
+      <c r="X334">
+        <v>8</v>
+      </c>
+      <c r="Y334">
+        <v>1.08</v>
+      </c>
+      <c r="Z334">
+        <v>4.5</v>
+      </c>
+      <c r="AA334">
+        <v>3.47</v>
+      </c>
+      <c r="AB334">
+        <v>1.79</v>
+      </c>
+      <c r="AC334">
+        <v>1.06</v>
+      </c>
+      <c r="AD334">
+        <v>8.5</v>
+      </c>
+      <c r="AE334">
+        <v>1.33</v>
+      </c>
+      <c r="AF334">
+        <v>3.25</v>
+      </c>
+      <c r="AG334">
+        <v>1.98</v>
+      </c>
+      <c r="AH334">
+        <v>1.77</v>
+      </c>
+      <c r="AI334">
+        <v>1.91</v>
+      </c>
+      <c r="AJ334">
+        <v>1.91</v>
+      </c>
+      <c r="AK334">
+        <v>1.95</v>
+      </c>
+      <c r="AL334">
+        <v>1.25</v>
+      </c>
+      <c r="AM334">
+        <v>1.2</v>
+      </c>
+      <c r="AN334">
+        <v>1.25</v>
+      </c>
+      <c r="AO334">
+        <v>1.75</v>
+      </c>
+      <c r="AP334">
+        <v>1.38</v>
+      </c>
+      <c r="AQ334">
+        <v>1.62</v>
+      </c>
+      <c r="AR334">
+        <v>1.22</v>
+      </c>
+      <c r="AS334">
+        <v>1.37</v>
+      </c>
+      <c r="AT334">
+        <v>2.59</v>
+      </c>
+      <c r="AU334">
+        <v>6</v>
+      </c>
+      <c r="AV334">
+        <v>6</v>
+      </c>
+      <c r="AW334">
+        <v>7</v>
+      </c>
+      <c r="AX334">
+        <v>9</v>
+      </c>
+      <c r="AY334">
+        <v>15</v>
+      </c>
+      <c r="AZ334">
+        <v>19</v>
+      </c>
+      <c r="BA334">
+        <v>4</v>
+      </c>
+      <c r="BB334">
+        <v>6</v>
+      </c>
+      <c r="BC334">
+        <v>10</v>
+      </c>
+      <c r="BD334">
+        <v>2.7</v>
+      </c>
+      <c r="BE334">
+        <v>7.5</v>
+      </c>
+      <c r="BF334">
+        <v>1.53</v>
+      </c>
+      <c r="BG334">
+        <v>1.25</v>
+      </c>
+      <c r="BH334">
+        <v>3.45</v>
+      </c>
+      <c r="BI334">
+        <v>1.41</v>
+      </c>
+      <c r="BJ334">
+        <v>2.63</v>
+      </c>
+      <c r="BK334">
+        <v>1.68</v>
+      </c>
+      <c r="BL334">
+        <v>2.04</v>
+      </c>
+      <c r="BM334">
+        <v>2.05</v>
+      </c>
+      <c r="BN334">
+        <v>1.67</v>
+      </c>
+      <c r="BO334">
+        <v>2.55</v>
+      </c>
+      <c r="BP334">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="335" spans="1:68">
+      <c r="A335" s="1">
+        <v>334</v>
+      </c>
+      <c r="B335">
+        <v>7727222</v>
+      </c>
+      <c r="C335" t="s">
+        <v>68</v>
+      </c>
+      <c r="D335" t="s">
+        <v>69</v>
+      </c>
+      <c r="E335" s="2">
+        <v>45689.5</v>
+      </c>
+      <c r="F335">
+        <v>30</v>
+      </c>
+      <c r="G335" t="s">
+        <v>75</v>
+      </c>
+      <c r="H335" t="s">
+        <v>73</v>
+      </c>
+      <c r="I335">
+        <v>0</v>
+      </c>
+      <c r="J335">
+        <v>1</v>
+      </c>
+      <c r="K335">
+        <v>1</v>
+      </c>
+      <c r="L335">
+        <v>0</v>
+      </c>
+      <c r="M335">
+        <v>1</v>
+      </c>
+      <c r="N335">
+        <v>1</v>
+      </c>
+      <c r="O335" t="s">
+        <v>96</v>
+      </c>
+      <c r="P335" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q335">
+        <v>3.1</v>
+      </c>
+      <c r="R335">
+        <v>2.05</v>
+      </c>
+      <c r="S335">
+        <v>3.75</v>
+      </c>
+      <c r="T335">
+        <v>1.5</v>
+      </c>
+      <c r="U335">
+        <v>2.5</v>
+      </c>
+      <c r="V335">
+        <v>3.4</v>
+      </c>
+      <c r="W335">
+        <v>1.3</v>
+      </c>
+      <c r="X335">
+        <v>10</v>
+      </c>
+      <c r="Y335">
+        <v>1.06</v>
+      </c>
+      <c r="Z335">
+        <v>2.29</v>
+      </c>
+      <c r="AA335">
+        <v>3.37</v>
+      </c>
+      <c r="AB335">
+        <v>2.98</v>
+      </c>
+      <c r="AC335">
+        <v>1.06</v>
+      </c>
+      <c r="AD335">
+        <v>8.5</v>
+      </c>
+      <c r="AE335">
+        <v>1.38</v>
+      </c>
+      <c r="AF335">
+        <v>2.95</v>
+      </c>
+      <c r="AG335">
+        <v>2.2</v>
+      </c>
+      <c r="AH335">
+        <v>1.61</v>
+      </c>
+      <c r="AI335">
+        <v>1.95</v>
+      </c>
+      <c r="AJ335">
+        <v>1.8</v>
+      </c>
+      <c r="AK335">
+        <v>1.36</v>
+      </c>
+      <c r="AL335">
+        <v>1.25</v>
+      </c>
+      <c r="AM335">
+        <v>1.57</v>
+      </c>
+      <c r="AN335">
+        <v>1.71</v>
+      </c>
+      <c r="AO335">
+        <v>1.31</v>
+      </c>
+      <c r="AP335">
+        <v>1.6</v>
+      </c>
+      <c r="AQ335">
+        <v>1.43</v>
+      </c>
+      <c r="AR335">
+        <v>1.52</v>
+      </c>
+      <c r="AS335">
+        <v>1.34</v>
+      </c>
+      <c r="AT335">
+        <v>2.86</v>
+      </c>
+      <c r="AU335">
+        <v>2</v>
+      </c>
+      <c r="AV335">
+        <v>5</v>
+      </c>
+      <c r="AW335">
+        <v>8</v>
+      </c>
+      <c r="AX335">
+        <v>5</v>
+      </c>
+      <c r="AY335">
+        <v>14</v>
+      </c>
+      <c r="AZ335">
+        <v>12</v>
+      </c>
+      <c r="BA335">
+        <v>4</v>
+      </c>
+      <c r="BB335">
+        <v>6</v>
+      </c>
+      <c r="BC335">
+        <v>10</v>
+      </c>
+      <c r="BD335">
+        <v>1.66</v>
+      </c>
+      <c r="BE335">
+        <v>6.4</v>
+      </c>
+      <c r="BF335">
+        <v>2.48</v>
+      </c>
+      <c r="BG335">
+        <v>1.38</v>
+      </c>
+      <c r="BH335">
+        <v>2.7</v>
+      </c>
+      <c r="BI335">
+        <v>1.65</v>
+      </c>
+      <c r="BJ335">
+        <v>2.08</v>
+      </c>
+      <c r="BK335">
+        <v>2.04</v>
+      </c>
+      <c r="BL335">
+        <v>1.68</v>
+      </c>
+      <c r="BM335">
+        <v>2.55</v>
+      </c>
+      <c r="BN335">
+        <v>1.44</v>
+      </c>
+      <c r="BO335">
+        <v>3.4</v>
+      </c>
+      <c r="BP335">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="336" spans="1:68">
+      <c r="A336" s="1">
+        <v>335</v>
+      </c>
+      <c r="B336">
+        <v>7727221</v>
+      </c>
+      <c r="C336" t="s">
+        <v>68</v>
+      </c>
+      <c r="D336" t="s">
+        <v>69</v>
+      </c>
+      <c r="E336" s="2">
+        <v>45689.5</v>
+      </c>
+      <c r="F336">
+        <v>30</v>
+      </c>
+      <c r="G336" t="s">
+        <v>77</v>
+      </c>
+      <c r="H336" t="s">
+        <v>71</v>
+      </c>
+      <c r="I336">
+        <v>0</v>
+      </c>
+      <c r="J336">
+        <v>1</v>
+      </c>
+      <c r="K336">
+        <v>1</v>
+      </c>
+      <c r="L336">
+        <v>1</v>
+      </c>
+      <c r="M336">
+        <v>2</v>
+      </c>
+      <c r="N336">
+        <v>3</v>
+      </c>
+      <c r="O336" t="s">
+        <v>302</v>
+      </c>
+      <c r="P336" t="s">
+        <v>438</v>
+      </c>
+      <c r="Q336">
+        <v>4.33</v>
+      </c>
+      <c r="R336">
+        <v>2.2</v>
+      </c>
+      <c r="S336">
+        <v>2.6</v>
+      </c>
+      <c r="T336">
+        <v>1.4</v>
+      </c>
+      <c r="U336">
+        <v>2.75</v>
+      </c>
+      <c r="V336">
+        <v>3</v>
+      </c>
+      <c r="W336">
+        <v>1.36</v>
+      </c>
+      <c r="X336">
+        <v>8</v>
+      </c>
+      <c r="Y336">
+        <v>1.08</v>
+      </c>
+      <c r="Z336">
+        <v>3.78</v>
+      </c>
+      <c r="AA336">
+        <v>3.58</v>
+      </c>
+      <c r="AB336">
+        <v>1.9</v>
+      </c>
+      <c r="AC336">
+        <v>1.05</v>
+      </c>
+      <c r="AD336">
+        <v>11</v>
+      </c>
+      <c r="AE336">
+        <v>1.3</v>
+      </c>
+      <c r="AF336">
+        <v>3.4</v>
+      </c>
+      <c r="AG336">
+        <v>1.91</v>
+      </c>
+      <c r="AH336">
+        <v>1.83</v>
+      </c>
+      <c r="AI336">
+        <v>1.8</v>
+      </c>
+      <c r="AJ336">
+        <v>1.95</v>
+      </c>
+      <c r="AK336">
+        <v>1.85</v>
+      </c>
+      <c r="AL336">
+        <v>1.28</v>
+      </c>
+      <c r="AM336">
+        <v>1.24</v>
+      </c>
+      <c r="AN336">
+        <v>1.09</v>
+      </c>
+      <c r="AO336">
+        <v>1.08</v>
+      </c>
+      <c r="AP336">
+        <v>1</v>
+      </c>
+      <c r="AQ336">
+        <v>1.23</v>
+      </c>
+      <c r="AR336">
+        <v>1</v>
+      </c>
+      <c r="AS336">
+        <v>1.21</v>
+      </c>
+      <c r="AT336">
+        <v>2.21</v>
+      </c>
+      <c r="AU336">
+        <v>3</v>
+      </c>
+      <c r="AV336">
+        <v>6</v>
+      </c>
+      <c r="AW336">
+        <v>15</v>
+      </c>
+      <c r="AX336">
+        <v>4</v>
+      </c>
+      <c r="AY336">
+        <v>25</v>
+      </c>
+      <c r="AZ336">
+        <v>11</v>
+      </c>
+      <c r="BA336">
+        <v>7</v>
+      </c>
+      <c r="BB336">
+        <v>6</v>
+      </c>
+      <c r="BC336">
+        <v>13</v>
+      </c>
+      <c r="BD336">
+        <v>2.35</v>
+      </c>
+      <c r="BE336">
+        <v>6.75</v>
+      </c>
+      <c r="BF336">
+        <v>1.71</v>
+      </c>
+      <c r="BG336">
+        <v>1.28</v>
+      </c>
+      <c r="BH336">
+        <v>3.3</v>
+      </c>
+      <c r="BI336">
+        <v>1.48</v>
+      </c>
+      <c r="BJ336">
+        <v>2.43</v>
+      </c>
+      <c r="BK336">
+        <v>1.77</v>
+      </c>
+      <c r="BL336">
+        <v>1.92</v>
+      </c>
+      <c r="BM336">
+        <v>2.2</v>
+      </c>
+      <c r="BN336">
+        <v>1.58</v>
+      </c>
+      <c r="BO336">
+        <v>2.8</v>
+      </c>
+      <c r="BP336">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="337" spans="1:68">
+      <c r="A337" s="1">
+        <v>336</v>
+      </c>
+      <c r="B337">
+        <v>7727220</v>
+      </c>
+      <c r="C337" t="s">
+        <v>68</v>
+      </c>
+      <c r="D337" t="s">
+        <v>69</v>
+      </c>
+      <c r="E337" s="2">
+        <v>45689.5</v>
+      </c>
+      <c r="F337">
+        <v>30</v>
+      </c>
+      <c r="G337" t="s">
+        <v>88</v>
+      </c>
+      <c r="H337" t="s">
+        <v>86</v>
+      </c>
+      <c r="I337">
+        <v>0</v>
+      </c>
+      <c r="J337">
+        <v>1</v>
+      </c>
+      <c r="K337">
+        <v>1</v>
+      </c>
+      <c r="L337">
+        <v>1</v>
+      </c>
+      <c r="M337">
+        <v>1</v>
+      </c>
+      <c r="N337">
+        <v>2</v>
+      </c>
+      <c r="O337" t="s">
+        <v>277</v>
+      </c>
+      <c r="P337" t="s">
+        <v>205</v>
+      </c>
+      <c r="Q337">
+        <v>4</v>
+      </c>
+      <c r="R337">
+        <v>2.25</v>
+      </c>
+      <c r="S337">
+        <v>2.63</v>
+      </c>
+      <c r="T337">
+        <v>1.36</v>
+      </c>
+      <c r="U337">
+        <v>3</v>
+      </c>
+      <c r="V337">
+        <v>2.63</v>
+      </c>
+      <c r="W337">
+        <v>1.44</v>
+      </c>
+      <c r="X337">
+        <v>7</v>
+      </c>
+      <c r="Y337">
+        <v>1.1</v>
+      </c>
+      <c r="Z337">
+        <v>3.57</v>
+      </c>
+      <c r="AA337">
+        <v>3.47</v>
+      </c>
+      <c r="AB337">
+        <v>1.99</v>
+      </c>
+      <c r="AC337">
+        <v>1.05</v>
+      </c>
+      <c r="AD337">
+        <v>9.5</v>
+      </c>
+      <c r="AE337">
+        <v>1.25</v>
+      </c>
+      <c r="AF337">
+        <v>3.8</v>
+      </c>
+      <c r="AG337">
+        <v>1.83</v>
+      </c>
+      <c r="AH337">
+        <v>1.91</v>
+      </c>
+      <c r="AI337">
+        <v>1.67</v>
+      </c>
+      <c r="AJ337">
+        <v>2.1</v>
+      </c>
+      <c r="AK337">
+        <v>1.77</v>
+      </c>
+      <c r="AL337">
+        <v>1.25</v>
+      </c>
+      <c r="AM337">
+        <v>1.28</v>
+      </c>
+      <c r="AN337">
+        <v>1.15</v>
+      </c>
+      <c r="AO337">
+        <v>2.14</v>
+      </c>
+      <c r="AP337">
+        <v>1.14</v>
+      </c>
+      <c r="AQ337">
+        <v>2.07</v>
+      </c>
+      <c r="AR337">
+        <v>1.43</v>
+      </c>
+      <c r="AS337">
+        <v>1.44</v>
+      </c>
+      <c r="AT337">
+        <v>2.87</v>
+      </c>
+      <c r="AU337">
+        <v>6</v>
+      </c>
+      <c r="AV337">
+        <v>3</v>
+      </c>
+      <c r="AW337">
+        <v>10</v>
+      </c>
+      <c r="AX337">
+        <v>7</v>
+      </c>
+      <c r="AY337">
+        <v>20</v>
+      </c>
+      <c r="AZ337">
+        <v>10</v>
+      </c>
+      <c r="BA337">
+        <v>5</v>
+      </c>
+      <c r="BB337">
+        <v>2</v>
+      </c>
+      <c r="BC337">
+        <v>7</v>
+      </c>
+      <c r="BD337">
+        <v>2.18</v>
+      </c>
+      <c r="BE337">
+        <v>6.5</v>
+      </c>
+      <c r="BF337">
+        <v>1.81</v>
+      </c>
+      <c r="BG337">
+        <v>1.3</v>
+      </c>
+      <c r="BH337">
+        <v>3.15</v>
+      </c>
+      <c r="BI337">
+        <v>1.52</v>
+      </c>
+      <c r="BJ337">
+        <v>2.33</v>
+      </c>
+      <c r="BK337">
+        <v>1.85</v>
+      </c>
+      <c r="BL337">
+        <v>1.83</v>
+      </c>
+      <c r="BM337">
+        <v>2.32</v>
+      </c>
+      <c r="BN337">
+        <v>1.53</v>
+      </c>
+      <c r="BO337">
+        <v>2.95</v>
+      </c>
+      <c r="BP337">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="338" spans="1:68">
+      <c r="A338" s="1">
+        <v>337</v>
+      </c>
+      <c r="B338">
+        <v>7727218</v>
+      </c>
+      <c r="C338" t="s">
+        <v>68</v>
+      </c>
+      <c r="D338" t="s">
+        <v>69</v>
+      </c>
+      <c r="E338" s="2">
+        <v>45689.5</v>
+      </c>
+      <c r="F338">
+        <v>30</v>
+      </c>
+      <c r="G338" t="s">
+        <v>91</v>
+      </c>
+      <c r="H338" t="s">
+        <v>83</v>
+      </c>
+      <c r="I338">
+        <v>0</v>
+      </c>
+      <c r="J338">
+        <v>0</v>
+      </c>
+      <c r="K338">
+        <v>0</v>
+      </c>
+      <c r="L338">
+        <v>2</v>
+      </c>
+      <c r="M338">
+        <v>2</v>
+      </c>
+      <c r="N338">
+        <v>4</v>
+      </c>
+      <c r="O338" t="s">
+        <v>303</v>
+      </c>
+      <c r="P338" t="s">
+        <v>439</v>
+      </c>
+      <c r="Q338">
+        <v>2.88</v>
+      </c>
+      <c r="R338">
+        <v>2.05</v>
+      </c>
+      <c r="S338">
+        <v>4</v>
+      </c>
+      <c r="T338">
+        <v>1.44</v>
+      </c>
+      <c r="U338">
+        <v>2.63</v>
+      </c>
+      <c r="V338">
+        <v>3.4</v>
+      </c>
+      <c r="W338">
+        <v>1.3</v>
+      </c>
+      <c r="X338">
+        <v>10</v>
+      </c>
+      <c r="Y338">
+        <v>1.06</v>
+      </c>
+      <c r="Z338">
+        <v>2.14</v>
+      </c>
+      <c r="AA338">
+        <v>3.37</v>
+      </c>
+      <c r="AB338">
+        <v>3.27</v>
+      </c>
+      <c r="AC338">
+        <v>1.06</v>
+      </c>
+      <c r="AD338">
+        <v>8.5</v>
+      </c>
+      <c r="AE338">
+        <v>1.38</v>
+      </c>
+      <c r="AF338">
+        <v>3</v>
+      </c>
+      <c r="AG338">
+        <v>1.94</v>
+      </c>
+      <c r="AH338">
+        <v>1.8</v>
+      </c>
+      <c r="AI338">
+        <v>1.95</v>
+      </c>
+      <c r="AJ338">
+        <v>1.8</v>
+      </c>
+      <c r="AK338">
+        <v>1.33</v>
+      </c>
+      <c r="AL338">
+        <v>1.25</v>
+      </c>
+      <c r="AM338">
+        <v>1.67</v>
+      </c>
+      <c r="AN338">
+        <v>1.18</v>
+      </c>
+      <c r="AO338">
+        <v>1.31</v>
+      </c>
+      <c r="AP338">
+        <v>1.17</v>
+      </c>
+      <c r="AQ338">
+        <v>1.29</v>
+      </c>
+      <c r="AR338">
+        <v>1.55</v>
+      </c>
+      <c r="AS338">
+        <v>1.29</v>
+      </c>
+      <c r="AT338">
+        <v>2.84</v>
+      </c>
+      <c r="AU338">
+        <v>6</v>
+      </c>
+      <c r="AV338">
+        <v>3</v>
+      </c>
+      <c r="AW338">
+        <v>9</v>
+      </c>
+      <c r="AX338">
+        <v>11</v>
+      </c>
+      <c r="AY338">
+        <v>17</v>
+      </c>
+      <c r="AZ338">
+        <v>18</v>
+      </c>
+      <c r="BA338">
+        <v>6</v>
+      </c>
+      <c r="BB338">
+        <v>3</v>
+      </c>
+      <c r="BC338">
+        <v>9</v>
+      </c>
+      <c r="BD338">
+        <v>1.61</v>
+      </c>
+      <c r="BE338">
+        <v>6.75</v>
+      </c>
+      <c r="BF338">
+        <v>2.55</v>
+      </c>
+      <c r="BG338">
+        <v>1.3</v>
+      </c>
+      <c r="BH338">
+        <v>3.05</v>
+      </c>
+      <c r="BI338">
+        <v>1.53</v>
+      </c>
+      <c r="BJ338">
+        <v>2.32</v>
+      </c>
+      <c r="BK338">
+        <v>1.86</v>
+      </c>
+      <c r="BL338">
+        <v>1.82</v>
+      </c>
+      <c r="BM338">
+        <v>2.33</v>
+      </c>
+      <c r="BN338">
+        <v>1.5</v>
+      </c>
+      <c r="BO338">
+        <v>3</v>
+      </c>
+      <c r="BP338">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="339" spans="1:68">
+      <c r="A339" s="1">
+        <v>338</v>
+      </c>
+      <c r="B339">
+        <v>7727217</v>
+      </c>
+      <c r="C339" t="s">
+        <v>68</v>
+      </c>
+      <c r="D339" t="s">
+        <v>69</v>
+      </c>
+      <c r="E339" s="2">
+        <v>45689.5</v>
+      </c>
+      <c r="F339">
+        <v>30</v>
+      </c>
+      <c r="G339" t="s">
+        <v>80</v>
+      </c>
+      <c r="H339" t="s">
+        <v>85</v>
+      </c>
+      <c r="I339">
+        <v>0</v>
+      </c>
+      <c r="J339">
+        <v>1</v>
+      </c>
+      <c r="K339">
+        <v>1</v>
+      </c>
+      <c r="L339">
+        <v>2</v>
+      </c>
+      <c r="M339">
+        <v>1</v>
+      </c>
+      <c r="N339">
+        <v>3</v>
+      </c>
+      <c r="O339" t="s">
+        <v>304</v>
+      </c>
+      <c r="P339" t="s">
+        <v>440</v>
+      </c>
+      <c r="Q339">
+        <v>2.1</v>
+      </c>
+      <c r="R339">
+        <v>2.2</v>
+      </c>
+      <c r="S339">
+        <v>7</v>
+      </c>
+      <c r="T339">
+        <v>1.44</v>
+      </c>
+      <c r="U339">
+        <v>2.63</v>
+      </c>
+      <c r="V339">
+        <v>3.25</v>
+      </c>
+      <c r="W339">
+        <v>1.33</v>
+      </c>
+      <c r="X339">
+        <v>9</v>
+      </c>
+      <c r="Y339">
+        <v>1.07</v>
+      </c>
+      <c r="Z339">
+        <v>1.5</v>
+      </c>
+      <c r="AA339">
+        <v>4.1</v>
+      </c>
+      <c r="AB339">
+        <v>6.4</v>
+      </c>
+      <c r="AC339">
+        <v>1.05</v>
+      </c>
+      <c r="AD339">
+        <v>9</v>
+      </c>
+      <c r="AE339">
+        <v>1.33</v>
+      </c>
+      <c r="AF339">
+        <v>3.2</v>
+      </c>
+      <c r="AG339">
+        <v>1.94</v>
+      </c>
+      <c r="AH339">
+        <v>1.8</v>
+      </c>
+      <c r="AI339">
+        <v>2.2</v>
+      </c>
+      <c r="AJ339">
+        <v>1.62</v>
+      </c>
+      <c r="AK339">
+        <v>1.11</v>
+      </c>
+      <c r="AL339">
+        <v>1.18</v>
+      </c>
+      <c r="AM339">
+        <v>2.5</v>
+      </c>
+      <c r="AN339">
+        <v>2.5</v>
+      </c>
+      <c r="AO339">
+        <v>0.77</v>
+      </c>
+      <c r="AP339">
+        <v>2.54</v>
+      </c>
+      <c r="AQ339">
+        <v>0.71</v>
+      </c>
+      <c r="AR339">
+        <v>1.62</v>
+      </c>
+      <c r="AS339">
+        <v>1.32</v>
+      </c>
+      <c r="AT339">
+        <v>2.94</v>
+      </c>
+      <c r="AU339">
+        <v>9</v>
+      </c>
+      <c r="AV339">
+        <v>2</v>
+      </c>
+      <c r="AW339">
+        <v>16</v>
+      </c>
+      <c r="AX339">
+        <v>6</v>
+      </c>
+      <c r="AY339">
+        <v>25</v>
+      </c>
+      <c r="AZ339">
+        <v>8</v>
+      </c>
+      <c r="BA339">
+        <v>8</v>
+      </c>
+      <c r="BB339">
+        <v>3</v>
+      </c>
+      <c r="BC339">
+        <v>11</v>
+      </c>
+      <c r="BD339">
+        <v>1.38</v>
+      </c>
+      <c r="BE339">
+        <v>7</v>
+      </c>
+      <c r="BF339">
+        <v>3.4</v>
+      </c>
+      <c r="BG339">
+        <v>1.35</v>
+      </c>
+      <c r="BH339">
+        <v>2.9</v>
+      </c>
+      <c r="BI339">
+        <v>1.58</v>
+      </c>
+      <c r="BJ339">
+        <v>2.18</v>
+      </c>
+      <c r="BK339">
+        <v>1.96</v>
+      </c>
+      <c r="BL339">
+        <v>1.73</v>
+      </c>
+      <c r="BM339">
+        <v>2.48</v>
+      </c>
+      <c r="BN339">
+        <v>1.47</v>
+      </c>
+      <c r="BO339">
+        <v>3.15</v>
+      </c>
+      <c r="BP339">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="340" spans="1:68">
+      <c r="A340" s="1">
+        <v>339</v>
+      </c>
+      <c r="B340">
+        <v>7727219</v>
+      </c>
+      <c r="C340" t="s">
+        <v>68</v>
+      </c>
+      <c r="D340" t="s">
+        <v>69</v>
+      </c>
+      <c r="E340" s="2">
+        <v>45690.5</v>
+      </c>
+      <c r="F340">
+        <v>30</v>
+      </c>
+      <c r="G340" t="s">
+        <v>79</v>
+      </c>
+      <c r="H340" t="s">
+        <v>74</v>
+      </c>
+      <c r="I340">
+        <v>1</v>
+      </c>
+      <c r="J340">
+        <v>0</v>
+      </c>
+      <c r="K340">
+        <v>1</v>
+      </c>
+      <c r="L340">
+        <v>3</v>
+      </c>
+      <c r="M340">
+        <v>1</v>
+      </c>
+      <c r="N340">
+        <v>4</v>
+      </c>
+      <c r="O340" t="s">
+        <v>305</v>
+      </c>
+      <c r="P340" t="s">
+        <v>348</v>
+      </c>
+      <c r="Q340">
+        <v>3.4</v>
+      </c>
+      <c r="R340">
+        <v>2.25</v>
+      </c>
+      <c r="S340">
+        <v>2.88</v>
+      </c>
+      <c r="T340">
+        <v>1.33</v>
+      </c>
+      <c r="U340">
+        <v>3.25</v>
+      </c>
+      <c r="V340">
+        <v>2.63</v>
+      </c>
+      <c r="W340">
+        <v>1.44</v>
+      </c>
+      <c r="X340">
+        <v>6.5</v>
+      </c>
+      <c r="Y340">
+        <v>1.11</v>
+      </c>
+      <c r="Z340">
+        <v>2.58</v>
+      </c>
+      <c r="AA340">
+        <v>3.57</v>
+      </c>
+      <c r="AB340">
+        <v>2.48</v>
+      </c>
+      <c r="AC340">
+        <v>1.03</v>
+      </c>
+      <c r="AD340">
+        <v>13</v>
+      </c>
+      <c r="AE340">
+        <v>1.22</v>
+      </c>
+      <c r="AF340">
+        <v>4</v>
+      </c>
+      <c r="AG340">
+        <v>1.67</v>
+      </c>
+      <c r="AH340">
+        <v>2.1</v>
+      </c>
+      <c r="AI340">
+        <v>1.62</v>
+      </c>
+      <c r="AJ340">
+        <v>2.2</v>
+      </c>
+      <c r="AK340">
+        <v>1.55</v>
+      </c>
+      <c r="AL340">
+        <v>1.28</v>
+      </c>
+      <c r="AM340">
+        <v>1.43</v>
+      </c>
+      <c r="AN340">
+        <v>1.5</v>
+      </c>
+      <c r="AO340">
+        <v>0.67</v>
+      </c>
+      <c r="AP340">
+        <v>1.62</v>
+      </c>
+      <c r="AQ340">
+        <v>0.62</v>
+      </c>
+      <c r="AR340">
+        <v>1.1</v>
+      </c>
+      <c r="AS340">
+        <v>1.18</v>
+      </c>
+      <c r="AT340">
+        <v>2.28</v>
+      </c>
+      <c r="AU340">
+        <v>7</v>
+      </c>
+      <c r="AV340">
+        <v>7</v>
+      </c>
+      <c r="AW340">
+        <v>6</v>
+      </c>
+      <c r="AX340">
+        <v>11</v>
+      </c>
+      <c r="AY340">
+        <v>14</v>
+      </c>
+      <c r="AZ340">
+        <v>23</v>
+      </c>
+      <c r="BA340">
+        <v>7</v>
+      </c>
+      <c r="BB340">
+        <v>6</v>
+      </c>
+      <c r="BC340">
+        <v>13</v>
+      </c>
+      <c r="BD340">
+        <v>2</v>
+      </c>
+      <c r="BE340">
+        <v>6.75</v>
+      </c>
+      <c r="BF340">
+        <v>1.95</v>
+      </c>
+      <c r="BG340">
+        <v>1.2</v>
+      </c>
+      <c r="BH340">
+        <v>3.9</v>
+      </c>
+      <c r="BI340">
+        <v>1.36</v>
+      </c>
+      <c r="BJ340">
+        <v>2.8</v>
+      </c>
+      <c r="BK340">
+        <v>1.6</v>
+      </c>
+      <c r="BL340">
+        <v>2.17</v>
+      </c>
+      <c r="BM340">
+        <v>1.96</v>
+      </c>
+      <c r="BN340">
+        <v>1.73</v>
+      </c>
+      <c r="BO340">
+        <v>2.45</v>
+      </c>
+      <c r="BP340">
+        <v>1.48</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England EFL League One_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England EFL League One_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2102" uniqueCount="441">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2108" uniqueCount="441">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1698,7 +1698,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP340"/>
+  <dimension ref="A1:BP341"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -3889,7 +3889,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ11">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -6564,7 +6564,7 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ24">
         <v>0.93</v>
@@ -9039,7 +9039,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ36">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="AR36">
         <v>1.62</v>
@@ -11714,7 +11714,7 @@
         <v>3</v>
       </c>
       <c r="AP49">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ49">
         <v>1.43</v>
@@ -12538,7 +12538,7 @@
         <v>0</v>
       </c>
       <c r="AP53">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ53">
         <v>0.43</v>
@@ -15422,7 +15422,7 @@
         <v>0</v>
       </c>
       <c r="AP67">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ67">
         <v>0.43</v>
@@ -15631,7 +15631,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ68">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="AR68">
         <v>1.27</v>
@@ -23456,7 +23456,7 @@
         <v>1.75</v>
       </c>
       <c r="AP106">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ106">
         <v>1.5</v>
@@ -25313,7 +25313,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ115">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="AR115">
         <v>1.52</v>
@@ -26546,7 +26546,7 @@
         <v>0.4</v>
       </c>
       <c r="AP121">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ121">
         <v>1.17</v>
@@ -29845,7 +29845,7 @@
         <v>2</v>
       </c>
       <c r="AQ137">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="AR137">
         <v>1.63</v>
@@ -30872,7 +30872,7 @@
         <v>2.4</v>
       </c>
       <c r="AP142">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ142">
         <v>2.14</v>
@@ -33553,7 +33553,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ155">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="AR155">
         <v>1.34</v>
@@ -35201,7 +35201,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ163">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="AR163">
         <v>1.64</v>
@@ -37055,7 +37055,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ172">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="AR172">
         <v>1.6</v>
@@ -39112,7 +39112,7 @@
         <v>0.57</v>
       </c>
       <c r="AP182">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ182">
         <v>0.67</v>
@@ -40351,7 +40351,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ188">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="AR188">
         <v>1.1</v>
@@ -43235,7 +43235,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ202">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="AR202">
         <v>1.07</v>
@@ -45704,7 +45704,7 @@
         <v>1.38</v>
       </c>
       <c r="AP214">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ214">
         <v>1.62</v>
@@ -47561,7 +47561,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ223">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="AR223">
         <v>1.55</v>
@@ -51060,7 +51060,7 @@
         <v>0.67</v>
       </c>
       <c r="AP240">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ240">
         <v>0.71</v>
@@ -52917,7 +52917,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ249">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="AR249">
         <v>1.35</v>
@@ -55801,7 +55801,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ263">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="AR263">
         <v>1</v>
@@ -57034,7 +57034,7 @@
         <v>1.56</v>
       </c>
       <c r="AP269">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ269">
         <v>1.43</v>
@@ -58685,7 +58685,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ277">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="AR277">
         <v>0.99</v>
@@ -62596,7 +62596,7 @@
         <v>2.08</v>
       </c>
       <c r="AP296">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ296">
         <v>2.07</v>
@@ -65483,7 +65483,7 @@
         <v>2</v>
       </c>
       <c r="AQ310">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="AR310">
         <v>1.3</v>
@@ -66925,7 +66925,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ317">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="AR317">
         <v>1.71</v>
@@ -68982,7 +68982,7 @@
         <v>0.64</v>
       </c>
       <c r="AP327">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ327">
         <v>0.8</v>
@@ -71739,6 +71739,212 @@
       </c>
       <c r="BP340">
         <v>1.48</v>
+      </c>
+    </row>
+    <row r="341" spans="1:68">
+      <c r="A341" s="1">
+        <v>340</v>
+      </c>
+      <c r="B341">
+        <v>7727234</v>
+      </c>
+      <c r="C341" t="s">
+        <v>68</v>
+      </c>
+      <c r="D341" t="s">
+        <v>69</v>
+      </c>
+      <c r="E341" s="2">
+        <v>45695.69791666666</v>
+      </c>
+      <c r="F341">
+        <v>31</v>
+      </c>
+      <c r="G341" t="s">
+        <v>92</v>
+      </c>
+      <c r="H341" t="s">
+        <v>87</v>
+      </c>
+      <c r="I341">
+        <v>0</v>
+      </c>
+      <c r="J341">
+        <v>0</v>
+      </c>
+      <c r="K341">
+        <v>0</v>
+      </c>
+      <c r="L341">
+        <v>0</v>
+      </c>
+      <c r="M341">
+        <v>1</v>
+      </c>
+      <c r="N341">
+        <v>1</v>
+      </c>
+      <c r="O341" t="s">
+        <v>96</v>
+      </c>
+      <c r="P341" t="s">
+        <v>282</v>
+      </c>
+      <c r="Q341">
+        <v>2.3</v>
+      </c>
+      <c r="R341">
+        <v>2.2</v>
+      </c>
+      <c r="S341">
+        <v>5.5</v>
+      </c>
+      <c r="T341">
+        <v>1.4</v>
+      </c>
+      <c r="U341">
+        <v>2.75</v>
+      </c>
+      <c r="V341">
+        <v>3</v>
+      </c>
+      <c r="W341">
+        <v>1.36</v>
+      </c>
+      <c r="X341">
+        <v>8</v>
+      </c>
+      <c r="Y341">
+        <v>1.08</v>
+      </c>
+      <c r="Z341">
+        <v>1.6</v>
+      </c>
+      <c r="AA341">
+        <v>3.8</v>
+      </c>
+      <c r="AB341">
+        <v>5.25</v>
+      </c>
+      <c r="AC341">
+        <v>1.05</v>
+      </c>
+      <c r="AD341">
+        <v>9</v>
+      </c>
+      <c r="AE341">
+        <v>1.3</v>
+      </c>
+      <c r="AF341">
+        <v>3.45</v>
+      </c>
+      <c r="AG341">
+        <v>1.91</v>
+      </c>
+      <c r="AH341">
+        <v>1.83</v>
+      </c>
+      <c r="AI341">
+        <v>1.95</v>
+      </c>
+      <c r="AJ341">
+        <v>1.8</v>
+      </c>
+      <c r="AK341">
+        <v>1.13</v>
+      </c>
+      <c r="AL341">
+        <v>1.2</v>
+      </c>
+      <c r="AM341">
+        <v>2.3</v>
+      </c>
+      <c r="AN341">
+        <v>1.38</v>
+      </c>
+      <c r="AO341">
+        <v>0.75</v>
+      </c>
+      <c r="AP341">
+        <v>1.29</v>
+      </c>
+      <c r="AQ341">
+        <v>0.88</v>
+      </c>
+      <c r="AR341">
+        <v>1.39</v>
+      </c>
+      <c r="AS341">
+        <v>1.01</v>
+      </c>
+      <c r="AT341">
+        <v>2.4</v>
+      </c>
+      <c r="AU341">
+        <v>5</v>
+      </c>
+      <c r="AV341">
+        <v>6</v>
+      </c>
+      <c r="AW341">
+        <v>16</v>
+      </c>
+      <c r="AX341">
+        <v>5</v>
+      </c>
+      <c r="AY341">
+        <v>28</v>
+      </c>
+      <c r="AZ341">
+        <v>14</v>
+      </c>
+      <c r="BA341">
+        <v>4</v>
+      </c>
+      <c r="BB341">
+        <v>3</v>
+      </c>
+      <c r="BC341">
+        <v>7</v>
+      </c>
+      <c r="BD341">
+        <v>1.38</v>
+      </c>
+      <c r="BE341">
+        <v>7</v>
+      </c>
+      <c r="BF341">
+        <v>3.4</v>
+      </c>
+      <c r="BG341">
+        <v>1.27</v>
+      </c>
+      <c r="BH341">
+        <v>3.3</v>
+      </c>
+      <c r="BI341">
+        <v>1.48</v>
+      </c>
+      <c r="BJ341">
+        <v>2.45</v>
+      </c>
+      <c r="BK341">
+        <v>1.77</v>
+      </c>
+      <c r="BL341">
+        <v>1.92</v>
+      </c>
+      <c r="BM341">
+        <v>2.2</v>
+      </c>
+      <c r="BN341">
+        <v>1.58</v>
+      </c>
+      <c r="BO341">
+        <v>2.8</v>
+      </c>
+      <c r="BP341">
+        <v>1.37</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England EFL League One_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England EFL League One_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2108" uniqueCount="441">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2120" uniqueCount="443">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -934,6 +934,12 @@
     <t>['16', '62', '83']</t>
   </si>
   <si>
+    <t>['44', '48']</t>
+  </si>
+  <si>
+    <t>['31', '35']</t>
+  </si>
+  <si>
     <t>['13', '18']</t>
   </si>
   <si>
@@ -1698,7 +1704,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP341"/>
+  <dimension ref="A1:BP343"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1954,7 +1960,7 @@
         <v>94</v>
       </c>
       <c r="P2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -2366,7 +2372,7 @@
         <v>96</v>
       </c>
       <c r="P4" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -2650,7 +2656,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ5">
         <v>0.43</v>
@@ -2778,7 +2784,7 @@
         <v>96</v>
       </c>
       <c r="P6" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q6">
         <v>2.75</v>
@@ -2984,7 +2990,7 @@
         <v>98</v>
       </c>
       <c r="P7" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q7">
         <v>4</v>
@@ -3602,7 +3608,7 @@
         <v>101</v>
       </c>
       <c r="P10" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q10">
         <v>3.75</v>
@@ -4014,7 +4020,7 @@
         <v>103</v>
       </c>
       <c r="P12" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q12">
         <v>2.1</v>
@@ -4426,7 +4432,7 @@
         <v>105</v>
       </c>
       <c r="P14" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q14">
         <v>4</v>
@@ -4710,7 +4716,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ15">
         <v>1.54</v>
@@ -5250,7 +5256,7 @@
         <v>107</v>
       </c>
       <c r="P18" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q18">
         <v>4.33</v>
@@ -5868,7 +5874,7 @@
         <v>109</v>
       </c>
       <c r="P21" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q21">
         <v>2.75</v>
@@ -5949,7 +5955,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ21">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AR21">
         <v>0</v>
@@ -6074,7 +6080,7 @@
         <v>110</v>
       </c>
       <c r="P22" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q22">
         <v>2.3</v>
@@ -6155,7 +6161,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ22">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -6280,7 +6286,7 @@
         <v>96</v>
       </c>
       <c r="P23" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q23">
         <v>2.75</v>
@@ -6486,7 +6492,7 @@
         <v>111</v>
       </c>
       <c r="P24" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q24">
         <v>2.5</v>
@@ -6976,7 +6982,7 @@
         <v>1</v>
       </c>
       <c r="AP26">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ26">
         <v>0.67</v>
@@ -7185,7 +7191,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ27">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR27">
         <v>1.26</v>
@@ -7928,7 +7934,7 @@
         <v>116</v>
       </c>
       <c r="P31" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -8134,7 +8140,7 @@
         <v>117</v>
       </c>
       <c r="P32" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q32">
         <v>4.5</v>
@@ -8546,7 +8552,7 @@
         <v>119</v>
       </c>
       <c r="P34" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q34">
         <v>3.75</v>
@@ -8830,7 +8836,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ35">
         <v>1.43</v>
@@ -8958,7 +8964,7 @@
         <v>121</v>
       </c>
       <c r="P36" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q36">
         <v>2.2</v>
@@ -9164,7 +9170,7 @@
         <v>122</v>
       </c>
       <c r="P37" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q37">
         <v>4.33</v>
@@ -9370,7 +9376,7 @@
         <v>123</v>
       </c>
       <c r="P38" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q38">
         <v>2.63</v>
@@ -10400,7 +10406,7 @@
         <v>96</v>
       </c>
       <c r="P43" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q43">
         <v>2.63</v>
@@ -10812,7 +10818,7 @@
         <v>96</v>
       </c>
       <c r="P45" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q45">
         <v>3.6</v>
@@ -10893,7 +10899,7 @@
         <v>1</v>
       </c>
       <c r="AQ45">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AR45">
         <v>1.22</v>
@@ -11224,7 +11230,7 @@
         <v>96</v>
       </c>
       <c r="P47" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q47">
         <v>2.05</v>
@@ -12332,7 +12338,7 @@
         <v>0</v>
       </c>
       <c r="AP52">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ52">
         <v>0.71</v>
@@ -12666,7 +12672,7 @@
         <v>119</v>
       </c>
       <c r="P54" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q54">
         <v>3.5</v>
@@ -12953,7 +12959,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ55">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AR55">
         <v>1.23</v>
@@ -13284,7 +13290,7 @@
         <v>135</v>
       </c>
       <c r="P57" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q57">
         <v>2.2</v>
@@ -13490,7 +13496,7 @@
         <v>136</v>
       </c>
       <c r="P58" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q58">
         <v>2.75</v>
@@ -13902,7 +13908,7 @@
         <v>96</v>
       </c>
       <c r="P60" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q60">
         <v>2.75</v>
@@ -14520,7 +14526,7 @@
         <v>96</v>
       </c>
       <c r="P63" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q63">
         <v>2.88</v>
@@ -14726,7 +14732,7 @@
         <v>139</v>
       </c>
       <c r="P64" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q64">
         <v>2.5</v>
@@ -15219,7 +15225,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ66">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR66">
         <v>1.55</v>
@@ -15344,7 +15350,7 @@
         <v>141</v>
       </c>
       <c r="P67" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -15550,7 +15556,7 @@
         <v>142</v>
       </c>
       <c r="P68" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q68">
         <v>1.83</v>
@@ -15756,7 +15762,7 @@
         <v>143</v>
       </c>
       <c r="P69" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q69">
         <v>3.1</v>
@@ -15834,7 +15840,7 @@
         <v>0.5</v>
       </c>
       <c r="AP69">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ69">
         <v>1.5</v>
@@ -15962,7 +15968,7 @@
         <v>144</v>
       </c>
       <c r="P70" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q70">
         <v>4.33</v>
@@ -16043,7 +16049,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ70">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AR70">
         <v>0.86</v>
@@ -16168,7 +16174,7 @@
         <v>145</v>
       </c>
       <c r="P71" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q71">
         <v>2.4</v>
@@ -16246,7 +16252,7 @@
         <v>1</v>
       </c>
       <c r="AP71">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ71">
         <v>1.54</v>
@@ -16374,7 +16380,7 @@
         <v>146</v>
       </c>
       <c r="P72" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q72">
         <v>2.05</v>
@@ -16992,7 +16998,7 @@
         <v>149</v>
       </c>
       <c r="P75" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q75">
         <v>2.3</v>
@@ -17198,7 +17204,7 @@
         <v>96</v>
       </c>
       <c r="P76" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q76">
         <v>3.75</v>
@@ -17485,7 +17491,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ77">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR77">
         <v>0.73</v>
@@ -17610,7 +17616,7 @@
         <v>96</v>
       </c>
       <c r="P78" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q78">
         <v>2.4</v>
@@ -17816,7 +17822,7 @@
         <v>150</v>
       </c>
       <c r="P79" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q79">
         <v>3.15</v>
@@ -18228,7 +18234,7 @@
         <v>96</v>
       </c>
       <c r="P81" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q81">
         <v>4.33</v>
@@ -19052,7 +19058,7 @@
         <v>96</v>
       </c>
       <c r="P85" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q85">
         <v>3.4</v>
@@ -19464,7 +19470,7 @@
         <v>153</v>
       </c>
       <c r="P87" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q87">
         <v>3.4</v>
@@ -19876,7 +19882,7 @@
         <v>155</v>
       </c>
       <c r="P89" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q89">
         <v>2.05</v>
@@ -20082,7 +20088,7 @@
         <v>96</v>
       </c>
       <c r="P90" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q90">
         <v>4</v>
@@ -20288,7 +20294,7 @@
         <v>119</v>
       </c>
       <c r="P91" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q91">
         <v>2.88</v>
@@ -20494,7 +20500,7 @@
         <v>156</v>
       </c>
       <c r="P92" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q92">
         <v>4.75</v>
@@ -21112,7 +21118,7 @@
         <v>96</v>
       </c>
       <c r="P95" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q95">
         <v>4.5</v>
@@ -21524,7 +21530,7 @@
         <v>96</v>
       </c>
       <c r="P97" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="Q97">
         <v>3.2</v>
@@ -21936,7 +21942,7 @@
         <v>159</v>
       </c>
       <c r="P99" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Q99">
         <v>3.6</v>
@@ -22142,7 +22148,7 @@
         <v>160</v>
       </c>
       <c r="P100" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q100">
         <v>2.5</v>
@@ -22554,7 +22560,7 @@
         <v>162</v>
       </c>
       <c r="P102" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q102">
         <v>2.75</v>
@@ -22966,7 +22972,7 @@
         <v>164</v>
       </c>
       <c r="P104" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Q104">
         <v>2.63</v>
@@ -23047,7 +23053,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ104">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR104">
         <v>1.16</v>
@@ -23253,7 +23259,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ105">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AR105">
         <v>1.27</v>
@@ -24280,7 +24286,7 @@
         <v>1</v>
       </c>
       <c r="AP110">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ110">
         <v>1.29</v>
@@ -24408,7 +24414,7 @@
         <v>170</v>
       </c>
       <c r="P111" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Q111">
         <v>3</v>
@@ -24614,7 +24620,7 @@
         <v>171</v>
       </c>
       <c r="P112" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q112">
         <v>1.91</v>
@@ -25104,7 +25110,7 @@
         <v>3</v>
       </c>
       <c r="AP114">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ114">
         <v>2.14</v>
@@ -25438,7 +25444,7 @@
         <v>174</v>
       </c>
       <c r="P116" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="Q116">
         <v>3</v>
@@ -25644,7 +25650,7 @@
         <v>175</v>
       </c>
       <c r="P117" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25850,7 +25856,7 @@
         <v>96</v>
       </c>
       <c r="P118" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="Q118">
         <v>3.4</v>
@@ -26549,7 +26555,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ121">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR121">
         <v>1.32</v>
@@ -26674,7 +26680,7 @@
         <v>178</v>
       </c>
       <c r="P122" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="Q122">
         <v>4.5</v>
@@ -26880,7 +26886,7 @@
         <v>179</v>
       </c>
       <c r="P123" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q123">
         <v>2</v>
@@ -27086,7 +27092,7 @@
         <v>180</v>
       </c>
       <c r="P124" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="Q124">
         <v>3.2</v>
@@ -27164,7 +27170,7 @@
         <v>1.8</v>
       </c>
       <c r="AP124">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ124">
         <v>1.43</v>
@@ -27910,7 +27916,7 @@
         <v>137</v>
       </c>
       <c r="P128" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="Q128">
         <v>2.6</v>
@@ -27991,7 +27997,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ128">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AR128">
         <v>1.56</v>
@@ -28528,7 +28534,7 @@
         <v>184</v>
       </c>
       <c r="P131" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="Q131">
         <v>4.5</v>
@@ -29352,7 +29358,7 @@
         <v>96</v>
       </c>
       <c r="P135" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="Q135">
         <v>2.3</v>
@@ -29558,7 +29564,7 @@
         <v>188</v>
       </c>
       <c r="P136" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="Q136">
         <v>2.88</v>
@@ -29842,7 +29848,7 @@
         <v>1</v>
       </c>
       <c r="AP137">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ137">
         <v>0.88</v>
@@ -29970,7 +29976,7 @@
         <v>189</v>
       </c>
       <c r="P138" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="Q138">
         <v>3</v>
@@ -30382,7 +30388,7 @@
         <v>99</v>
       </c>
       <c r="P140" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="Q140">
         <v>3.1</v>
@@ -31206,7 +31212,7 @@
         <v>191</v>
       </c>
       <c r="P144" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="Q144">
         <v>3.25</v>
@@ -31284,7 +31290,7 @@
         <v>1.33</v>
       </c>
       <c r="AP144">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ144">
         <v>1.23</v>
@@ -32111,7 +32117,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ148">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR148">
         <v>1.62</v>
@@ -32236,7 +32242,7 @@
         <v>96</v>
       </c>
       <c r="P149" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="Q149">
         <v>4</v>
@@ -32317,7 +32323,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ149">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AR149">
         <v>1.04</v>
@@ -33060,7 +33066,7 @@
         <v>199</v>
       </c>
       <c r="P153" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="Q153">
         <v>2.38</v>
@@ -33344,7 +33350,7 @@
         <v>0.8</v>
       </c>
       <c r="AP154">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ154">
         <v>0.93</v>
@@ -33472,7 +33478,7 @@
         <v>201</v>
       </c>
       <c r="P155" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q155">
         <v>2.5</v>
@@ -33678,7 +33684,7 @@
         <v>109</v>
       </c>
       <c r="P156" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="Q156">
         <v>3.5</v>
@@ -34090,7 +34096,7 @@
         <v>96</v>
       </c>
       <c r="P158" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="Q158">
         <v>2.75</v>
@@ -34168,7 +34174,7 @@
         <v>1.83</v>
       </c>
       <c r="AP158">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ158">
         <v>2.07</v>
@@ -34914,7 +34920,7 @@
         <v>205</v>
       </c>
       <c r="P162" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Q162">
         <v>3.6</v>
@@ -35326,7 +35332,7 @@
         <v>96</v>
       </c>
       <c r="P164" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="Q164">
         <v>3.25</v>
@@ -36434,7 +36440,7 @@
         <v>2</v>
       </c>
       <c r="AP169">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ169">
         <v>1.43</v>
@@ -36562,7 +36568,7 @@
         <v>211</v>
       </c>
       <c r="P170" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="Q170">
         <v>4.33</v>
@@ -37467,7 +37473,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ174">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AR174">
         <v>1.32</v>
@@ -37670,7 +37676,7 @@
         <v>1.29</v>
       </c>
       <c r="AP175">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ175">
         <v>1.23</v>
@@ -38004,7 +38010,7 @@
         <v>214</v>
       </c>
       <c r="P177" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="Q177">
         <v>7.5</v>
@@ -38828,7 +38834,7 @@
         <v>216</v>
       </c>
       <c r="P181" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="Q181">
         <v>3.4</v>
@@ -39034,7 +39040,7 @@
         <v>96</v>
       </c>
       <c r="P182" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="Q182">
         <v>2.3</v>
@@ -39652,7 +39658,7 @@
         <v>96</v>
       </c>
       <c r="P185" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q185">
         <v>2.6</v>
@@ -39858,7 +39864,7 @@
         <v>96</v>
       </c>
       <c r="P186" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="Q186">
         <v>4.33</v>
@@ -40064,7 +40070,7 @@
         <v>143</v>
       </c>
       <c r="P187" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="Q187">
         <v>2.4</v>
@@ -40270,7 +40276,7 @@
         <v>218</v>
       </c>
       <c r="P188" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="Q188">
         <v>2.4</v>
@@ -40682,7 +40688,7 @@
         <v>96</v>
       </c>
       <c r="P190" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="Q190">
         <v>3.75</v>
@@ -40888,7 +40894,7 @@
         <v>96</v>
       </c>
       <c r="P191" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="Q191">
         <v>3.5</v>
@@ -41300,7 +41306,7 @@
         <v>96</v>
       </c>
       <c r="P193" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="Q193">
         <v>5.5</v>
@@ -41712,7 +41718,7 @@
         <v>221</v>
       </c>
       <c r="P195" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="Q195">
         <v>2.4</v>
@@ -42330,7 +42336,7 @@
         <v>137</v>
       </c>
       <c r="P198" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="Q198">
         <v>2.25</v>
@@ -42408,7 +42414,7 @@
         <v>0.63</v>
       </c>
       <c r="AP198">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ198">
         <v>0.8</v>
@@ -42823,7 +42829,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ200">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AR200">
         <v>1.39</v>
@@ -42948,7 +42954,7 @@
         <v>224</v>
       </c>
       <c r="P201" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="Q201">
         <v>4</v>
@@ -43978,7 +43984,7 @@
         <v>119</v>
       </c>
       <c r="P206" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="Q206">
         <v>4</v>
@@ -44390,7 +44396,7 @@
         <v>96</v>
       </c>
       <c r="P208" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Q208">
         <v>2.05</v>
@@ -44802,7 +44808,7 @@
         <v>96</v>
       </c>
       <c r="P210" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="Q210">
         <v>3.1</v>
@@ -45008,7 +45014,7 @@
         <v>99</v>
       </c>
       <c r="P211" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="Q211">
         <v>4.33</v>
@@ -45626,7 +45632,7 @@
         <v>230</v>
       </c>
       <c r="P214" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="Q214">
         <v>3.75</v>
@@ -45910,7 +45916,7 @@
         <v>1.25</v>
       </c>
       <c r="AP215">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ215">
         <v>1</v>
@@ -46244,7 +46250,7 @@
         <v>233</v>
       </c>
       <c r="P217" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="Q217">
         <v>3.75</v>
@@ -46656,7 +46662,7 @@
         <v>96</v>
       </c>
       <c r="P219" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="Q219">
         <v>2.3</v>
@@ -46862,7 +46868,7 @@
         <v>234</v>
       </c>
       <c r="P220" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="Q220">
         <v>2.1</v>
@@ -47068,7 +47074,7 @@
         <v>96</v>
       </c>
       <c r="P221" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="Q221">
         <v>2.88</v>
@@ -47352,7 +47358,7 @@
         <v>1.5</v>
       </c>
       <c r="AP222">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ222">
         <v>1.36</v>
@@ -47686,7 +47692,7 @@
         <v>132</v>
       </c>
       <c r="P224" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="Q224">
         <v>5</v>
@@ -48098,7 +48104,7 @@
         <v>237</v>
       </c>
       <c r="P226" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="Q226">
         <v>2.2</v>
@@ -48510,7 +48516,7 @@
         <v>239</v>
       </c>
       <c r="P228" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="Q228">
         <v>2.5</v>
@@ -48716,7 +48722,7 @@
         <v>240</v>
       </c>
       <c r="P229" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="Q229">
         <v>3.75</v>
@@ -48797,7 +48803,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ229">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AR229">
         <v>1.22</v>
@@ -49206,7 +49212,7 @@
         <v>0.88</v>
       </c>
       <c r="AP231">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ231">
         <v>0.62</v>
@@ -49334,7 +49340,7 @@
         <v>96</v>
       </c>
       <c r="P232" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="Q232">
         <v>4.5</v>
@@ -49952,7 +49958,7 @@
         <v>244</v>
       </c>
       <c r="P235" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="Q235">
         <v>3.5</v>
@@ -50239,7 +50245,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ236">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR236">
         <v>1.6</v>
@@ -50364,7 +50370,7 @@
         <v>96</v>
       </c>
       <c r="P237" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="Q237">
         <v>2.6</v>
@@ -50570,7 +50576,7 @@
         <v>245</v>
       </c>
       <c r="P238" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="Q238">
         <v>2.38</v>
@@ -50776,7 +50782,7 @@
         <v>96</v>
       </c>
       <c r="P239" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="Q239">
         <v>4</v>
@@ -51188,7 +51194,7 @@
         <v>96</v>
       </c>
       <c r="P241" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="Q241">
         <v>6.5</v>
@@ -51806,7 +51812,7 @@
         <v>249</v>
       </c>
       <c r="P244" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="Q244">
         <v>2.6</v>
@@ -51887,7 +51893,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ244">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AR244">
         <v>1.65</v>
@@ -52012,7 +52018,7 @@
         <v>250</v>
       </c>
       <c r="P245" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="Q245">
         <v>2.4</v>
@@ -52090,7 +52096,7 @@
         <v>0.5</v>
       </c>
       <c r="AP245">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ245">
         <v>0.43</v>
@@ -52630,7 +52636,7 @@
         <v>96</v>
       </c>
       <c r="P248" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="Q248">
         <v>2.75</v>
@@ -52836,7 +52842,7 @@
         <v>252</v>
       </c>
       <c r="P249" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q249">
         <v>2.2</v>
@@ -53042,7 +53048,7 @@
         <v>253</v>
       </c>
       <c r="P250" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q250">
         <v>2.5</v>
@@ -53248,7 +53254,7 @@
         <v>96</v>
       </c>
       <c r="P251" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="Q251">
         <v>3.75</v>
@@ -53454,7 +53460,7 @@
         <v>96</v>
       </c>
       <c r="P252" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="Q252">
         <v>2.75</v>
@@ -54150,7 +54156,7 @@
         <v>2.25</v>
       </c>
       <c r="AP255">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ255">
         <v>2.07</v>
@@ -54278,7 +54284,7 @@
         <v>257</v>
       </c>
       <c r="P256" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="Q256">
         <v>2.75</v>
@@ -54484,7 +54490,7 @@
         <v>160</v>
       </c>
       <c r="P257" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="Q257">
         <v>3.1</v>
@@ -54565,7 +54571,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ257">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AR257">
         <v>1.28</v>
@@ -55102,7 +55108,7 @@
         <v>259</v>
       </c>
       <c r="P260" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="Q260">
         <v>2.5</v>
@@ -56132,7 +56138,7 @@
         <v>263</v>
       </c>
       <c r="P265" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="Q265">
         <v>2.38</v>
@@ -56338,7 +56344,7 @@
         <v>264</v>
       </c>
       <c r="P266" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="Q266">
         <v>3.75</v>
@@ -56416,7 +56422,7 @@
         <v>2.2</v>
       </c>
       <c r="AP266">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ266">
         <v>2.14</v>
@@ -56831,7 +56837,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ268">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR268">
         <v>1.19</v>
@@ -57368,7 +57374,7 @@
         <v>268</v>
       </c>
       <c r="P271" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="Q271">
         <v>3.75</v>
@@ -57574,7 +57580,7 @@
         <v>96</v>
       </c>
       <c r="P272" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="Q272">
         <v>2.63</v>
@@ -57780,7 +57786,7 @@
         <v>183</v>
       </c>
       <c r="P273" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="Q273">
         <v>3.25</v>
@@ -57986,7 +57992,7 @@
         <v>269</v>
       </c>
       <c r="P274" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="Q274">
         <v>3.2</v>
@@ -59222,7 +59228,7 @@
         <v>96</v>
       </c>
       <c r="P280" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="Q280">
         <v>5.5</v>
@@ -59428,7 +59434,7 @@
         <v>118</v>
       </c>
       <c r="P281" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="Q281">
         <v>2.6</v>
@@ -59506,7 +59512,7 @@
         <v>1.45</v>
       </c>
       <c r="AP281">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ281">
         <v>1.36</v>
@@ -59715,7 +59721,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ282">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR282">
         <v>1.32</v>
@@ -60330,7 +60336,7 @@
         <v>1.08</v>
       </c>
       <c r="AP285">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ285">
         <v>0.93</v>
@@ -60664,7 +60670,7 @@
         <v>172</v>
       </c>
       <c r="P287" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="Q287">
         <v>3.6</v>
@@ -61488,7 +61494,7 @@
         <v>275</v>
       </c>
       <c r="P291" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="Q291">
         <v>3.4</v>
@@ -62187,7 +62193,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ294">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AR294">
         <v>1.08</v>
@@ -62312,7 +62318,7 @@
         <v>132</v>
       </c>
       <c r="P295" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="Q295">
         <v>2.75</v>
@@ -62518,7 +62524,7 @@
         <v>137</v>
       </c>
       <c r="P296" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="Q296">
         <v>3.25</v>
@@ -62930,7 +62936,7 @@
         <v>278</v>
       </c>
       <c r="P298" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="Q298">
         <v>3.2</v>
@@ -63136,7 +63142,7 @@
         <v>279</v>
       </c>
       <c r="P299" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="Q299">
         <v>3.25</v>
@@ -63342,7 +63348,7 @@
         <v>267</v>
       </c>
       <c r="P300" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="Q300">
         <v>3.6</v>
@@ -63548,7 +63554,7 @@
         <v>280</v>
       </c>
       <c r="P301" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="Q301">
         <v>2</v>
@@ -63754,7 +63760,7 @@
         <v>281</v>
       </c>
       <c r="P302" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q302">
         <v>2.63</v>
@@ -63960,7 +63966,7 @@
         <v>282</v>
       </c>
       <c r="P303" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="Q303">
         <v>2.88</v>
@@ -64166,7 +64172,7 @@
         <v>94</v>
       </c>
       <c r="P304" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="Q304">
         <v>2.25</v>
@@ -64784,7 +64790,7 @@
         <v>283</v>
       </c>
       <c r="P307" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="Q307">
         <v>4</v>
@@ -65071,7 +65077,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ308">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR308">
         <v>1.62</v>
@@ -65196,7 +65202,7 @@
         <v>284</v>
       </c>
       <c r="P309" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="Q309">
         <v>4.33</v>
@@ -66098,7 +66104,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AP313">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ313">
         <v>0.8</v>
@@ -66432,7 +66438,7 @@
         <v>289</v>
       </c>
       <c r="P315" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="Q315">
         <v>3.25</v>
@@ -66716,7 +66722,7 @@
         <v>0.5</v>
       </c>
       <c r="AP316">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ316">
         <v>0.43</v>
@@ -67050,7 +67056,7 @@
         <v>291</v>
       </c>
       <c r="P318" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="Q318">
         <v>3.25</v>
@@ -67334,7 +67340,7 @@
         <v>0.71</v>
       </c>
       <c r="AP319">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ319">
         <v>0.67</v>
@@ -67462,7 +67468,7 @@
         <v>293</v>
       </c>
       <c r="P320" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="Q320">
         <v>3.75</v>
@@ -67668,7 +67674,7 @@
         <v>96</v>
       </c>
       <c r="P321" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="Q321">
         <v>3</v>
@@ -68080,7 +68086,7 @@
         <v>294</v>
       </c>
       <c r="P323" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="Q323">
         <v>2.38</v>
@@ -68364,7 +68370,7 @@
         <v>0.46</v>
       </c>
       <c r="AP324">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ324">
         <v>0.43</v>
@@ -68492,7 +68498,7 @@
         <v>296</v>
       </c>
       <c r="P325" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="Q325">
         <v>2.88</v>
@@ -68573,7 +68579,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ325">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AR325">
         <v>1.42</v>
@@ -68779,7 +68785,7 @@
         <v>2</v>
       </c>
       <c r="AQ326">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AR326">
         <v>1.33</v>
@@ -68904,7 +68910,7 @@
         <v>96</v>
       </c>
       <c r="P327" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q327">
         <v>2.1</v>
@@ -69110,7 +69116,7 @@
         <v>96</v>
       </c>
       <c r="P328" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="Q328">
         <v>3.5</v>
@@ -69316,7 +69322,7 @@
         <v>298</v>
       </c>
       <c r="P329" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q329">
         <v>2.6</v>
@@ -69728,7 +69734,7 @@
         <v>299</v>
       </c>
       <c r="P331" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="Q331">
         <v>2.1</v>
@@ -70140,7 +70146,7 @@
         <v>301</v>
       </c>
       <c r="P333" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="Q333">
         <v>3.75</v>
@@ -70552,7 +70558,7 @@
         <v>302</v>
       </c>
       <c r="P335" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="Q335">
         <v>4.75</v>
@@ -70964,7 +70970,7 @@
         <v>303</v>
       </c>
       <c r="P337" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="Q337">
         <v>4.33</v>
@@ -71376,7 +71382,7 @@
         <v>304</v>
       </c>
       <c r="P339" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="Q339">
         <v>2.88</v>
@@ -71582,7 +71588,7 @@
         <v>305</v>
       </c>
       <c r="P340" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q340">
         <v>3.4</v>
@@ -71945,6 +71951,418 @@
       </c>
       <c r="BP341">
         <v>1.37</v>
+      </c>
+    </row>
+    <row r="342" spans="1:68">
+      <c r="A342" s="1">
+        <v>341</v>
+      </c>
+      <c r="B342">
+        <v>7727230</v>
+      </c>
+      <c r="C342" t="s">
+        <v>68</v>
+      </c>
+      <c r="D342" t="s">
+        <v>69</v>
+      </c>
+      <c r="E342" s="2">
+        <v>45696.39583333334</v>
+      </c>
+      <c r="F342">
+        <v>31</v>
+      </c>
+      <c r="G342" t="s">
+        <v>83</v>
+      </c>
+      <c r="H342" t="s">
+        <v>76</v>
+      </c>
+      <c r="I342">
+        <v>1</v>
+      </c>
+      <c r="J342">
+        <v>0</v>
+      </c>
+      <c r="K342">
+        <v>1</v>
+      </c>
+      <c r="L342">
+        <v>2</v>
+      </c>
+      <c r="M342">
+        <v>0</v>
+      </c>
+      <c r="N342">
+        <v>2</v>
+      </c>
+      <c r="O342" t="s">
+        <v>306</v>
+      </c>
+      <c r="P342" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q342">
+        <v>3</v>
+      </c>
+      <c r="R342">
+        <v>1.91</v>
+      </c>
+      <c r="S342">
+        <v>4.5</v>
+      </c>
+      <c r="T342">
+        <v>1.57</v>
+      </c>
+      <c r="U342">
+        <v>2.25</v>
+      </c>
+      <c r="V342">
+        <v>3.75</v>
+      </c>
+      <c r="W342">
+        <v>1.25</v>
+      </c>
+      <c r="X342">
+        <v>13</v>
+      </c>
+      <c r="Y342">
+        <v>1.04</v>
+      </c>
+      <c r="Z342">
+        <v>2.12</v>
+      </c>
+      <c r="AA342">
+        <v>3.06</v>
+      </c>
+      <c r="AB342">
+        <v>3.68</v>
+      </c>
+      <c r="AC342">
+        <v>1.1</v>
+      </c>
+      <c r="AD342">
+        <v>6.5</v>
+      </c>
+      <c r="AE342">
+        <v>1.53</v>
+      </c>
+      <c r="AF342">
+        <v>2.4</v>
+      </c>
+      <c r="AG342">
+        <v>2.47</v>
+      </c>
+      <c r="AH342">
+        <v>1.54</v>
+      </c>
+      <c r="AI342">
+        <v>2.2</v>
+      </c>
+      <c r="AJ342">
+        <v>1.62</v>
+      </c>
+      <c r="AK342">
+        <v>1.25</v>
+      </c>
+      <c r="AL342">
+        <v>1.3</v>
+      </c>
+      <c r="AM342">
+        <v>1.7</v>
+      </c>
+      <c r="AN342">
+        <v>1.86</v>
+      </c>
+      <c r="AO342">
+        <v>1.17</v>
+      </c>
+      <c r="AP342">
+        <v>1.93</v>
+      </c>
+      <c r="AQ342">
+        <v>1.08</v>
+      </c>
+      <c r="AR342">
+        <v>1.41</v>
+      </c>
+      <c r="AS342">
+        <v>1.13</v>
+      </c>
+      <c r="AT342">
+        <v>2.54</v>
+      </c>
+      <c r="AU342">
+        <v>6</v>
+      </c>
+      <c r="AV342">
+        <v>0</v>
+      </c>
+      <c r="AW342">
+        <v>9</v>
+      </c>
+      <c r="AX342">
+        <v>4</v>
+      </c>
+      <c r="AY342">
+        <v>18</v>
+      </c>
+      <c r="AZ342">
+        <v>6</v>
+      </c>
+      <c r="BA342">
+        <v>10</v>
+      </c>
+      <c r="BB342">
+        <v>1</v>
+      </c>
+      <c r="BC342">
+        <v>11</v>
+      </c>
+      <c r="BD342">
+        <v>1.74</v>
+      </c>
+      <c r="BE342">
+        <v>6.5</v>
+      </c>
+      <c r="BF342">
+        <v>2.32</v>
+      </c>
+      <c r="BG342">
+        <v>1.35</v>
+      </c>
+      <c r="BH342">
+        <v>2.9</v>
+      </c>
+      <c r="BI342">
+        <v>1.58</v>
+      </c>
+      <c r="BJ342">
+        <v>2.18</v>
+      </c>
+      <c r="BK342">
+        <v>1.9</v>
+      </c>
+      <c r="BL342">
+        <v>1.9</v>
+      </c>
+      <c r="BM342">
+        <v>2.5</v>
+      </c>
+      <c r="BN342">
+        <v>1.46</v>
+      </c>
+      <c r="BO342">
+        <v>3.3</v>
+      </c>
+      <c r="BP342">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="343" spans="1:68">
+      <c r="A343" s="1">
+        <v>342</v>
+      </c>
+      <c r="B343">
+        <v>7727237</v>
+      </c>
+      <c r="C343" t="s">
+        <v>68</v>
+      </c>
+      <c r="D343" t="s">
+        <v>69</v>
+      </c>
+      <c r="E343" s="2">
+        <v>45696.39583333334</v>
+      </c>
+      <c r="F343">
+        <v>31</v>
+      </c>
+      <c r="G343" t="s">
+        <v>73</v>
+      </c>
+      <c r="H343" t="s">
+        <v>70</v>
+      </c>
+      <c r="I343">
+        <v>2</v>
+      </c>
+      <c r="J343">
+        <v>0</v>
+      </c>
+      <c r="K343">
+        <v>2</v>
+      </c>
+      <c r="L343">
+        <v>2</v>
+      </c>
+      <c r="M343">
+        <v>1</v>
+      </c>
+      <c r="N343">
+        <v>3</v>
+      </c>
+      <c r="O343" t="s">
+        <v>307</v>
+      </c>
+      <c r="P343" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q343">
+        <v>2.5</v>
+      </c>
+      <c r="R343">
+        <v>2.2</v>
+      </c>
+      <c r="S343">
+        <v>4.33</v>
+      </c>
+      <c r="T343">
+        <v>1.36</v>
+      </c>
+      <c r="U343">
+        <v>3</v>
+      </c>
+      <c r="V343">
+        <v>2.75</v>
+      </c>
+      <c r="W343">
+        <v>1.4</v>
+      </c>
+      <c r="X343">
+        <v>8</v>
+      </c>
+      <c r="Y343">
+        <v>1.08</v>
+      </c>
+      <c r="Z343">
+        <v>1.91</v>
+      </c>
+      <c r="AA343">
+        <v>3.53</v>
+      </c>
+      <c r="AB343">
+        <v>3.79</v>
+      </c>
+      <c r="AC343">
+        <v>1.05</v>
+      </c>
+      <c r="AD343">
+        <v>9</v>
+      </c>
+      <c r="AE343">
+        <v>1.28</v>
+      </c>
+      <c r="AF343">
+        <v>3.55</v>
+      </c>
+      <c r="AG343">
+        <v>1.83</v>
+      </c>
+      <c r="AH343">
+        <v>1.91</v>
+      </c>
+      <c r="AI343">
+        <v>1.75</v>
+      </c>
+      <c r="AJ343">
+        <v>2</v>
+      </c>
+      <c r="AK343">
+        <v>1.25</v>
+      </c>
+      <c r="AL343">
+        <v>1.25</v>
+      </c>
+      <c r="AM343">
+        <v>1.85</v>
+      </c>
+      <c r="AN343">
+        <v>2</v>
+      </c>
+      <c r="AO343">
+        <v>1.79</v>
+      </c>
+      <c r="AP343">
+        <v>2.06</v>
+      </c>
+      <c r="AQ343">
+        <v>1.67</v>
+      </c>
+      <c r="AR343">
+        <v>1.6</v>
+      </c>
+      <c r="AS343">
+        <v>1.42</v>
+      </c>
+      <c r="AT343">
+        <v>3.02</v>
+      </c>
+      <c r="AU343">
+        <v>5</v>
+      </c>
+      <c r="AV343">
+        <v>6</v>
+      </c>
+      <c r="AW343">
+        <v>7</v>
+      </c>
+      <c r="AX343">
+        <v>7</v>
+      </c>
+      <c r="AY343">
+        <v>12</v>
+      </c>
+      <c r="AZ343">
+        <v>13</v>
+      </c>
+      <c r="BA343">
+        <v>2</v>
+      </c>
+      <c r="BB343">
+        <v>3</v>
+      </c>
+      <c r="BC343">
+        <v>5</v>
+      </c>
+      <c r="BD343">
+        <v>1.65</v>
+      </c>
+      <c r="BE343">
+        <v>6.5</v>
+      </c>
+      <c r="BF343">
+        <v>2.48</v>
+      </c>
+      <c r="BG343">
+        <v>1.3</v>
+      </c>
+      <c r="BH343">
+        <v>3.15</v>
+      </c>
+      <c r="BI343">
+        <v>1.52</v>
+      </c>
+      <c r="BJ343">
+        <v>2.32</v>
+      </c>
+      <c r="BK343">
+        <v>1.8</v>
+      </c>
+      <c r="BL343">
+        <v>2</v>
+      </c>
+      <c r="BM343">
+        <v>2.32</v>
+      </c>
+      <c r="BN343">
+        <v>1.53</v>
+      </c>
+      <c r="BO343">
+        <v>2.95</v>
+      </c>
+      <c r="BP343">
+        <v>1.33</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England EFL League One_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England EFL League One_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2120" uniqueCount="443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2150" uniqueCount="448">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -940,6 +940,12 @@
     <t>['31', '35']</t>
   </si>
   <si>
+    <t>['76']</t>
+  </si>
+  <si>
+    <t>['52', '68', '85', '90+9']</t>
+  </si>
+  <si>
     <t>['13', '18']</t>
   </si>
   <si>
@@ -1344,6 +1350,15 @@
   <si>
     <t>['52', '54']</t>
   </si>
+  <si>
+    <t>['68', '77']</t>
+  </si>
+  <si>
+    <t>['90+4']</t>
+  </si>
+  <si>
+    <t>['50', '54', '62']</t>
+  </si>
 </sst>
 </file>
 
@@ -1704,7 +1719,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP343"/>
+  <dimension ref="A1:BP348"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1960,7 +1975,7 @@
         <v>94</v>
       </c>
       <c r="P2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -2372,7 +2387,7 @@
         <v>96</v>
       </c>
       <c r="P4" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -2659,7 +2674,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ5">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2784,7 +2799,7 @@
         <v>96</v>
       </c>
       <c r="P6" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q6">
         <v>2.75</v>
@@ -2990,7 +3005,7 @@
         <v>98</v>
       </c>
       <c r="P7" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q7">
         <v>4</v>
@@ -3277,7 +3292,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ8">
-        <v>0.43</v>
+        <v>0.6</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3483,7 +3498,7 @@
         <v>1</v>
       </c>
       <c r="AQ9">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3608,7 +3623,7 @@
         <v>101</v>
       </c>
       <c r="P10" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q10">
         <v>3.75</v>
@@ -3686,7 +3701,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AQ10">
         <v>1.2</v>
@@ -4020,7 +4035,7 @@
         <v>103</v>
       </c>
       <c r="P12" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q12">
         <v>2.1</v>
@@ -4101,7 +4116,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ12">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -4432,7 +4447,7 @@
         <v>105</v>
       </c>
       <c r="P14" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q14">
         <v>4</v>
@@ -5128,7 +5143,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AQ17">
         <v>0.67</v>
@@ -5256,7 +5271,7 @@
         <v>107</v>
       </c>
       <c r="P18" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q18">
         <v>4.33</v>
@@ -5749,7 +5764,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ20">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR20">
         <v>0</v>
@@ -5874,7 +5889,7 @@
         <v>109</v>
       </c>
       <c r="P21" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q21">
         <v>2.75</v>
@@ -5952,7 +5967,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ21">
         <v>1.67</v>
@@ -6080,7 +6095,7 @@
         <v>110</v>
       </c>
       <c r="P22" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q22">
         <v>2.3</v>
@@ -6158,7 +6173,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AQ22">
         <v>1.08</v>
@@ -6286,7 +6301,7 @@
         <v>96</v>
       </c>
       <c r="P23" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q23">
         <v>2.75</v>
@@ -6492,7 +6507,7 @@
         <v>111</v>
       </c>
       <c r="P24" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q24">
         <v>2.5</v>
@@ -6776,7 +6791,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ25">
         <v>1.23</v>
@@ -7188,7 +7203,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AQ27">
         <v>1.08</v>
@@ -7603,7 +7618,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ29">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR29">
         <v>1.43</v>
@@ -7809,7 +7824,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ30">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR30">
         <v>0.89</v>
@@ -7934,7 +7949,7 @@
         <v>116</v>
       </c>
       <c r="P31" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -8012,7 +8027,7 @@
         <v>3</v>
       </c>
       <c r="AP31">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ31">
         <v>1.36</v>
@@ -8140,7 +8155,7 @@
         <v>117</v>
       </c>
       <c r="P32" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q32">
         <v>4.5</v>
@@ -8221,7 +8236,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ32">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR32">
         <v>1.53</v>
@@ -8424,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AQ33">
-        <v>0.43</v>
+        <v>0.6</v>
       </c>
       <c r="AR33">
         <v>1.14</v>
@@ -8552,7 +8567,7 @@
         <v>119</v>
       </c>
       <c r="P34" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q34">
         <v>3.75</v>
@@ -8964,7 +8979,7 @@
         <v>121</v>
       </c>
       <c r="P36" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q36">
         <v>2.2</v>
@@ -9170,7 +9185,7 @@
         <v>122</v>
       </c>
       <c r="P37" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q37">
         <v>4.33</v>
@@ -9376,7 +9391,7 @@
         <v>123</v>
       </c>
       <c r="P38" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q38">
         <v>2.63</v>
@@ -9660,7 +9675,7 @@
         <v>3</v>
       </c>
       <c r="AP39">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AQ39">
         <v>1.62</v>
@@ -10406,7 +10421,7 @@
         <v>96</v>
       </c>
       <c r="P43" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q43">
         <v>2.63</v>
@@ -10818,7 +10833,7 @@
         <v>96</v>
       </c>
       <c r="P45" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q45">
         <v>3.6</v>
@@ -11105,7 +11120,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ46">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="AR46">
         <v>1.46</v>
@@ -11230,7 +11245,7 @@
         <v>96</v>
       </c>
       <c r="P47" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q47">
         <v>2.05</v>
@@ -11308,7 +11323,7 @@
         <v>0</v>
       </c>
       <c r="AP47">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ47">
         <v>1</v>
@@ -12135,7 +12150,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ51">
-        <v>0.43</v>
+        <v>0.6</v>
       </c>
       <c r="AR51">
         <v>1.47</v>
@@ -12547,7 +12562,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ53">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="AR53">
         <v>1.26</v>
@@ -12672,7 +12687,7 @@
         <v>119</v>
       </c>
       <c r="P54" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q54">
         <v>3.5</v>
@@ -13290,7 +13305,7 @@
         <v>135</v>
       </c>
       <c r="P57" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q57">
         <v>2.2</v>
@@ -13368,7 +13383,7 @@
         <v>1</v>
       </c>
       <c r="AP57">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AQ57">
         <v>0.93</v>
@@ -13496,7 +13511,7 @@
         <v>136</v>
       </c>
       <c r="P58" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q58">
         <v>2.75</v>
@@ -13908,7 +13923,7 @@
         <v>96</v>
       </c>
       <c r="P60" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q60">
         <v>2.75</v>
@@ -14526,7 +14541,7 @@
         <v>96</v>
       </c>
       <c r="P63" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q63">
         <v>2.88</v>
@@ -14604,7 +14619,7 @@
         <v>1.5</v>
       </c>
       <c r="AP63">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ63">
         <v>1.62</v>
@@ -14732,7 +14747,7 @@
         <v>139</v>
       </c>
       <c r="P64" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q64">
         <v>2.5</v>
@@ -15016,7 +15031,7 @@
         <v>1</v>
       </c>
       <c r="AP65">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ65">
         <v>1.29</v>
@@ -15350,7 +15365,7 @@
         <v>141</v>
       </c>
       <c r="P67" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -15431,7 +15446,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ67">
-        <v>0.43</v>
+        <v>0.6</v>
       </c>
       <c r="AR67">
         <v>1.39</v>
@@ -15556,7 +15571,7 @@
         <v>142</v>
       </c>
       <c r="P68" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q68">
         <v>1.83</v>
@@ -15634,7 +15649,7 @@
         <v>0.5</v>
       </c>
       <c r="AP68">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AQ68">
         <v>0.88</v>
@@ -15762,7 +15777,7 @@
         <v>143</v>
       </c>
       <c r="P69" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q69">
         <v>3.1</v>
@@ -15843,7 +15858,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ69">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR69">
         <v>1.19</v>
@@ -15968,7 +15983,7 @@
         <v>144</v>
       </c>
       <c r="P70" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q70">
         <v>4.33</v>
@@ -16046,7 +16061,7 @@
         <v>2</v>
       </c>
       <c r="AP70">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AQ70">
         <v>1.67</v>
@@ -16174,7 +16189,7 @@
         <v>145</v>
       </c>
       <c r="P71" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q71">
         <v>2.4</v>
@@ -16380,7 +16395,7 @@
         <v>146</v>
       </c>
       <c r="P72" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q72">
         <v>2.05</v>
@@ -16667,7 +16682,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ73">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR73">
         <v>1.51</v>
@@ -16873,7 +16888,7 @@
         <v>2</v>
       </c>
       <c r="AQ74">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="AR74">
         <v>1.14</v>
@@ -16998,7 +17013,7 @@
         <v>149</v>
       </c>
       <c r="P75" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q75">
         <v>2.3</v>
@@ -17076,10 +17091,10 @@
         <v>0.5</v>
       </c>
       <c r="AP75">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ75">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR75">
         <v>1.34</v>
@@ -17204,7 +17219,7 @@
         <v>96</v>
       </c>
       <c r="P76" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q76">
         <v>3.75</v>
@@ -17282,7 +17297,7 @@
         <v>3</v>
       </c>
       <c r="AP76">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AQ76">
         <v>2.14</v>
@@ -17616,7 +17631,7 @@
         <v>96</v>
       </c>
       <c r="P78" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q78">
         <v>2.4</v>
@@ -17694,10 +17709,10 @@
         <v>1.33</v>
       </c>
       <c r="AP78">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AQ78">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR78">
         <v>1.35</v>
@@ -17822,7 +17837,7 @@
         <v>150</v>
       </c>
       <c r="P79" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q79">
         <v>3.15</v>
@@ -18234,7 +18249,7 @@
         <v>96</v>
       </c>
       <c r="P81" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q81">
         <v>4.33</v>
@@ -19058,7 +19073,7 @@
         <v>96</v>
       </c>
       <c r="P85" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q85">
         <v>3.4</v>
@@ -19470,7 +19485,7 @@
         <v>153</v>
       </c>
       <c r="P87" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q87">
         <v>3.4</v>
@@ -19882,7 +19897,7 @@
         <v>155</v>
       </c>
       <c r="P89" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q89">
         <v>2.05</v>
@@ -20088,7 +20103,7 @@
         <v>96</v>
       </c>
       <c r="P90" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q90">
         <v>4</v>
@@ -20294,7 +20309,7 @@
         <v>119</v>
       </c>
       <c r="P91" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q91">
         <v>2.88</v>
@@ -20500,7 +20515,7 @@
         <v>156</v>
       </c>
       <c r="P92" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="Q92">
         <v>4.75</v>
@@ -21118,7 +21133,7 @@
         <v>96</v>
       </c>
       <c r="P95" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Q95">
         <v>4.5</v>
@@ -21530,7 +21545,7 @@
         <v>96</v>
       </c>
       <c r="P97" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q97">
         <v>3.2</v>
@@ -21942,7 +21957,7 @@
         <v>159</v>
       </c>
       <c r="P99" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Q99">
         <v>3.6</v>
@@ -22148,7 +22163,7 @@
         <v>160</v>
       </c>
       <c r="P100" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q100">
         <v>2.5</v>
@@ -22560,7 +22575,7 @@
         <v>162</v>
       </c>
       <c r="P102" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Q102">
         <v>2.75</v>
@@ -22972,7 +22987,7 @@
         <v>164</v>
       </c>
       <c r="P104" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q104">
         <v>2.63</v>
@@ -23256,7 +23271,7 @@
         <v>2.25</v>
       </c>
       <c r="AP105">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AQ105">
         <v>1.67</v>
@@ -23465,7 +23480,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ106">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR106">
         <v>1.42</v>
@@ -23668,10 +23683,10 @@
         <v>0.33</v>
       </c>
       <c r="AP107">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AQ107">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR107">
         <v>1.55</v>
@@ -23874,7 +23889,7 @@
         <v>1.5</v>
       </c>
       <c r="AP108">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ108">
         <v>1.54</v>
@@ -24083,7 +24098,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ109">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="AR109">
         <v>1.44</v>
@@ -24414,7 +24429,7 @@
         <v>170</v>
       </c>
       <c r="P111" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="Q111">
         <v>3</v>
@@ -24492,7 +24507,7 @@
         <v>0.25</v>
       </c>
       <c r="AP111">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AQ111">
         <v>0.67</v>
@@ -24620,7 +24635,7 @@
         <v>171</v>
       </c>
       <c r="P112" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="Q112">
         <v>1.91</v>
@@ -24698,10 +24713,10 @@
         <v>0</v>
       </c>
       <c r="AP112">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ112">
-        <v>0.43</v>
+        <v>0.6</v>
       </c>
       <c r="AR112">
         <v>1.46</v>
@@ -24907,7 +24922,7 @@
         <v>2</v>
       </c>
       <c r="AQ113">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR113">
         <v>1.39</v>
@@ -25444,7 +25459,7 @@
         <v>174</v>
       </c>
       <c r="P116" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="Q116">
         <v>3</v>
@@ -25650,7 +25665,7 @@
         <v>175</v>
       </c>
       <c r="P117" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25731,7 +25746,7 @@
         <v>1</v>
       </c>
       <c r="AQ117">
-        <v>0.43</v>
+        <v>0.6</v>
       </c>
       <c r="AR117">
         <v>0.93</v>
@@ -25856,7 +25871,7 @@
         <v>96</v>
       </c>
       <c r="P118" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="Q118">
         <v>3.4</v>
@@ -26143,7 +26158,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ119">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR119">
         <v>1.25</v>
@@ -26680,7 +26695,7 @@
         <v>178</v>
       </c>
       <c r="P122" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="Q122">
         <v>4.5</v>
@@ -26758,7 +26773,7 @@
         <v>2.25</v>
       </c>
       <c r="AP122">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ122">
         <v>2.14</v>
@@ -26886,7 +26901,7 @@
         <v>179</v>
       </c>
       <c r="P123" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q123">
         <v>2</v>
@@ -26964,7 +26979,7 @@
         <v>0.8</v>
       </c>
       <c r="AP123">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AQ123">
         <v>0.67</v>
@@ -27092,7 +27107,7 @@
         <v>180</v>
       </c>
       <c r="P124" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="Q124">
         <v>3.2</v>
@@ -27582,7 +27597,7 @@
         <v>1</v>
       </c>
       <c r="AP126">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AQ126">
         <v>1.23</v>
@@ -27788,7 +27803,7 @@
         <v>0.6</v>
       </c>
       <c r="AP127">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ127">
         <v>0.93</v>
@@ -27916,7 +27931,7 @@
         <v>137</v>
       </c>
       <c r="P128" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="Q128">
         <v>2.6</v>
@@ -28534,7 +28549,7 @@
         <v>184</v>
       </c>
       <c r="P131" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="Q131">
         <v>4.5</v>
@@ -28612,7 +28627,7 @@
         <v>1.6</v>
       </c>
       <c r="AP131">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AQ131">
         <v>2.07</v>
@@ -28821,7 +28836,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ132">
-        <v>0.43</v>
+        <v>0.6</v>
       </c>
       <c r="AR132">
         <v>1.15</v>
@@ -29233,7 +29248,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ134">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR134">
         <v>1.19</v>
@@ -29358,7 +29373,7 @@
         <v>96</v>
       </c>
       <c r="P135" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="Q135">
         <v>2.3</v>
@@ -29439,7 +29454,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ135">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="AR135">
         <v>1.1</v>
@@ -29564,7 +29579,7 @@
         <v>188</v>
       </c>
       <c r="P136" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="Q136">
         <v>2.88</v>
@@ -29976,7 +29991,7 @@
         <v>189</v>
       </c>
       <c r="P138" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="Q138">
         <v>3</v>
@@ -30388,7 +30403,7 @@
         <v>99</v>
       </c>
       <c r="P140" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="Q140">
         <v>3.1</v>
@@ -30469,7 +30484,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ140">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR140">
         <v>1.36</v>
@@ -31212,7 +31227,7 @@
         <v>191</v>
       </c>
       <c r="P144" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="Q144">
         <v>3.25</v>
@@ -31496,7 +31511,7 @@
         <v>1.67</v>
       </c>
       <c r="AP145">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AQ145">
         <v>1</v>
@@ -31702,7 +31717,7 @@
         <v>1.67</v>
       </c>
       <c r="AP146">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ146">
         <v>1.43</v>
@@ -31911,7 +31926,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ147">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR147">
         <v>1.26</v>
@@ -32114,7 +32129,7 @@
         <v>0.83</v>
       </c>
       <c r="AP148">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AQ148">
         <v>1.08</v>
@@ -32242,7 +32257,7 @@
         <v>96</v>
       </c>
       <c r="P149" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="Q149">
         <v>4</v>
@@ -32938,7 +32953,7 @@
         <v>1.17</v>
       </c>
       <c r="AP152">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ152">
         <v>0.62</v>
@@ -33066,7 +33081,7 @@
         <v>199</v>
       </c>
       <c r="P153" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="Q153">
         <v>2.38</v>
@@ -33353,7 +33368,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ154">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR154">
         <v>1.62</v>
@@ -33478,7 +33493,7 @@
         <v>201</v>
       </c>
       <c r="P155" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q155">
         <v>2.5</v>
@@ -33556,7 +33571,7 @@
         <v>1</v>
       </c>
       <c r="AP155">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ155">
         <v>0.88</v>
@@ -33684,7 +33699,7 @@
         <v>109</v>
       </c>
       <c r="P156" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="Q156">
         <v>3.5</v>
@@ -33968,10 +33983,10 @@
         <v>0.5</v>
       </c>
       <c r="AP157">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AQ157">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR157">
         <v>1.02</v>
@@ -34096,7 +34111,7 @@
         <v>96</v>
       </c>
       <c r="P158" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="Q158">
         <v>2.75</v>
@@ -34792,10 +34807,10 @@
         <v>0.57</v>
       </c>
       <c r="AP161">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AQ161">
-        <v>0.43</v>
+        <v>0.6</v>
       </c>
       <c r="AR161">
         <v>1.04</v>
@@ -34920,7 +34935,7 @@
         <v>205</v>
       </c>
       <c r="P162" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q162">
         <v>3.6</v>
@@ -35332,7 +35347,7 @@
         <v>96</v>
       </c>
       <c r="P164" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="Q164">
         <v>3.25</v>
@@ -35619,7 +35634,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ165">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR165">
         <v>1.16</v>
@@ -35825,7 +35840,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ166">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="AR166">
         <v>1.2</v>
@@ -36031,7 +36046,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ167">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR167">
         <v>1.35</v>
@@ -36568,7 +36583,7 @@
         <v>211</v>
       </c>
       <c r="P170" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="Q170">
         <v>4.33</v>
@@ -37267,7 +37282,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ173">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR173">
         <v>1.16</v>
@@ -37882,10 +37897,10 @@
         <v>1</v>
       </c>
       <c r="AP176">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ176">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR176">
         <v>1.67</v>
@@ -38010,7 +38025,7 @@
         <v>214</v>
       </c>
       <c r="P177" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="Q177">
         <v>7.5</v>
@@ -38706,7 +38721,7 @@
         <v>1</v>
       </c>
       <c r="AP180">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AQ180">
         <v>1.29</v>
@@ -38834,7 +38849,7 @@
         <v>216</v>
       </c>
       <c r="P181" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="Q181">
         <v>3.4</v>
@@ -38912,7 +38927,7 @@
         <v>2.13</v>
       </c>
       <c r="AP181">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ181">
         <v>2.07</v>
@@ -39040,7 +39055,7 @@
         <v>96</v>
       </c>
       <c r="P182" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="Q182">
         <v>2.3</v>
@@ -39327,7 +39342,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ183">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="AR183">
         <v>1.26</v>
@@ -39658,7 +39673,7 @@
         <v>96</v>
       </c>
       <c r="P185" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q185">
         <v>2.6</v>
@@ -39864,7 +39879,7 @@
         <v>96</v>
       </c>
       <c r="P186" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="Q186">
         <v>4.33</v>
@@ -39942,7 +39957,7 @@
         <v>1.43</v>
       </c>
       <c r="AP186">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AQ186">
         <v>1.43</v>
@@ -40070,7 +40085,7 @@
         <v>143</v>
       </c>
       <c r="P187" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="Q187">
         <v>2.4</v>
@@ -40151,7 +40166,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ187">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR187">
         <v>1.26</v>
@@ -40276,7 +40291,7 @@
         <v>218</v>
       </c>
       <c r="P188" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="Q188">
         <v>2.4</v>
@@ -40688,7 +40703,7 @@
         <v>96</v>
       </c>
       <c r="P190" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="Q190">
         <v>3.75</v>
@@ -40769,7 +40784,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ190">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR190">
         <v>1.16</v>
@@ -40894,7 +40909,7 @@
         <v>96</v>
       </c>
       <c r="P191" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="Q191">
         <v>3.5</v>
@@ -41306,7 +41321,7 @@
         <v>96</v>
       </c>
       <c r="P193" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="Q193">
         <v>5.5</v>
@@ -41718,7 +41733,7 @@
         <v>221</v>
       </c>
       <c r="P195" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="Q195">
         <v>2.4</v>
@@ -41799,7 +41814,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ195">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR195">
         <v>1.71</v>
@@ -42002,7 +42017,7 @@
         <v>0.88</v>
       </c>
       <c r="AP196">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AQ196">
         <v>1.29</v>
@@ -42336,7 +42351,7 @@
         <v>137</v>
       </c>
       <c r="P198" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="Q198">
         <v>2.25</v>
@@ -42417,7 +42432,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ198">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR198">
         <v>1.37</v>
@@ -42620,7 +42635,7 @@
         <v>1.71</v>
       </c>
       <c r="AP199">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ199">
         <v>1.36</v>
@@ -42954,7 +42969,7 @@
         <v>224</v>
       </c>
       <c r="P201" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="Q201">
         <v>4</v>
@@ -43444,7 +43459,7 @@
         <v>1.13</v>
       </c>
       <c r="AP203">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AQ203">
         <v>1.29</v>
@@ -43653,7 +43668,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ204">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="AR204">
         <v>1.32</v>
@@ -43856,7 +43871,7 @@
         <v>1.44</v>
       </c>
       <c r="AP205">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AQ205">
         <v>1.2</v>
@@ -43984,7 +43999,7 @@
         <v>119</v>
       </c>
       <c r="P206" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="Q206">
         <v>4</v>
@@ -44065,7 +44080,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ206">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR206">
         <v>0.99</v>
@@ -44396,7 +44411,7 @@
         <v>96</v>
       </c>
       <c r="P208" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q208">
         <v>2.05</v>
@@ -44680,7 +44695,7 @@
         <v>1.11</v>
       </c>
       <c r="AP209">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ209">
         <v>1.29</v>
@@ -44808,7 +44823,7 @@
         <v>96</v>
       </c>
       <c r="P210" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="Q210">
         <v>3.1</v>
@@ -45014,7 +45029,7 @@
         <v>99</v>
       </c>
       <c r="P211" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="Q211">
         <v>4.33</v>
@@ -45298,7 +45313,7 @@
         <v>1.13</v>
       </c>
       <c r="AP212">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AQ212">
         <v>1.23</v>
@@ -45507,7 +45522,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ213">
-        <v>0.43</v>
+        <v>0.6</v>
       </c>
       <c r="AR213">
         <v>1.31</v>
@@ -45632,7 +45647,7 @@
         <v>230</v>
       </c>
       <c r="P214" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="Q214">
         <v>3.75</v>
@@ -46125,7 +46140,7 @@
         <v>2</v>
       </c>
       <c r="AQ216">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR216">
         <v>1.39</v>
@@ -46250,7 +46265,7 @@
         <v>233</v>
       </c>
       <c r="P217" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="Q217">
         <v>3.75</v>
@@ -46662,7 +46677,7 @@
         <v>96</v>
       </c>
       <c r="P219" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="Q219">
         <v>2.3</v>
@@ -46740,7 +46755,7 @@
         <v>1</v>
       </c>
       <c r="AP219">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ219">
         <v>1.29</v>
@@ -46868,7 +46883,7 @@
         <v>234</v>
       </c>
       <c r="P220" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="Q220">
         <v>2.1</v>
@@ -46949,7 +46964,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ220">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR220">
         <v>1.25</v>
@@ -47074,7 +47089,7 @@
         <v>96</v>
       </c>
       <c r="P221" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="Q221">
         <v>2.88</v>
@@ -47155,7 +47170,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ221">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR221">
         <v>1.39</v>
@@ -47564,7 +47579,7 @@
         <v>0.7</v>
       </c>
       <c r="AP223">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AQ223">
         <v>0.88</v>
@@ -47692,7 +47707,7 @@
         <v>132</v>
       </c>
       <c r="P224" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="Q224">
         <v>5</v>
@@ -48104,7 +48119,7 @@
         <v>237</v>
       </c>
       <c r="P226" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="Q226">
         <v>2.2</v>
@@ -48185,7 +48200,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ226">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="AR226">
         <v>1.41</v>
@@ -48516,7 +48531,7 @@
         <v>239</v>
       </c>
       <c r="P228" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="Q228">
         <v>2.5</v>
@@ -48594,7 +48609,7 @@
         <v>1.3</v>
       </c>
       <c r="AP228">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AQ228">
         <v>1.2</v>
@@ -48722,7 +48737,7 @@
         <v>240</v>
       </c>
       <c r="P229" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="Q229">
         <v>3.75</v>
@@ -49340,7 +49355,7 @@
         <v>96</v>
       </c>
       <c r="P232" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="Q232">
         <v>4.5</v>
@@ -49624,10 +49639,10 @@
         <v>1</v>
       </c>
       <c r="AP233">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ233">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR233">
         <v>1.33</v>
@@ -49958,7 +49973,7 @@
         <v>244</v>
       </c>
       <c r="P235" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="Q235">
         <v>3.5</v>
@@ -50036,7 +50051,7 @@
         <v>1.11</v>
       </c>
       <c r="AP235">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AQ235">
         <v>1</v>
@@ -50370,7 +50385,7 @@
         <v>96</v>
       </c>
       <c r="P237" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="Q237">
         <v>2.6</v>
@@ -50576,7 +50591,7 @@
         <v>245</v>
       </c>
       <c r="P238" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="Q238">
         <v>2.38</v>
@@ -50657,7 +50672,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ238">
-        <v>0.43</v>
+        <v>0.6</v>
       </c>
       <c r="AR238">
         <v>1.17</v>
@@ -50782,7 +50797,7 @@
         <v>96</v>
       </c>
       <c r="P239" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="Q239">
         <v>4</v>
@@ -51194,7 +51209,7 @@
         <v>96</v>
       </c>
       <c r="P241" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="Q241">
         <v>6.5</v>
@@ -51481,7 +51496,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ242">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR242">
         <v>1.45</v>
@@ -51812,7 +51827,7 @@
         <v>249</v>
       </c>
       <c r="P244" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="Q244">
         <v>2.6</v>
@@ -51890,7 +51905,7 @@
         <v>1.9</v>
       </c>
       <c r="AP244">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ244">
         <v>1.67</v>
@@ -52018,7 +52033,7 @@
         <v>250</v>
       </c>
       <c r="P245" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="Q245">
         <v>2.4</v>
@@ -52099,7 +52114,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ245">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="AR245">
         <v>1.31</v>
@@ -52508,7 +52523,7 @@
         <v>1.3</v>
       </c>
       <c r="AP247">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AQ247">
         <v>1.43</v>
@@ -52636,7 +52651,7 @@
         <v>96</v>
       </c>
       <c r="P248" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="Q248">
         <v>2.75</v>
@@ -52842,7 +52857,7 @@
         <v>252</v>
       </c>
       <c r="P249" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q249">
         <v>2.2</v>
@@ -53048,7 +53063,7 @@
         <v>253</v>
       </c>
       <c r="P250" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q250">
         <v>2.5</v>
@@ -53129,7 +53144,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ250">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR250">
         <v>1.4</v>
@@ -53254,7 +53269,7 @@
         <v>96</v>
       </c>
       <c r="P251" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="Q251">
         <v>3.75</v>
@@ -53460,7 +53475,7 @@
         <v>96</v>
       </c>
       <c r="P252" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="Q252">
         <v>2.75</v>
@@ -53538,7 +53553,7 @@
         <v>1.2</v>
       </c>
       <c r="AP252">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AQ252">
         <v>1.29</v>
@@ -53950,7 +53965,7 @@
         <v>1.18</v>
       </c>
       <c r="AP254">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AQ254">
         <v>1.43</v>
@@ -54284,7 +54299,7 @@
         <v>257</v>
       </c>
       <c r="P256" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="Q256">
         <v>2.75</v>
@@ -54490,7 +54505,7 @@
         <v>160</v>
       </c>
       <c r="P257" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="Q257">
         <v>3.1</v>
@@ -54777,7 +54792,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ258">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="AR258">
         <v>1.51</v>
@@ -54980,7 +54995,7 @@
         <v>0.7</v>
       </c>
       <c r="AP259">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AQ259">
         <v>0.93</v>
@@ -55108,7 +55123,7 @@
         <v>259</v>
       </c>
       <c r="P260" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="Q260">
         <v>2.5</v>
@@ -55189,7 +55204,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ260">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR260">
         <v>1.25</v>
@@ -55392,7 +55407,7 @@
         <v>1.17</v>
       </c>
       <c r="AP261">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ261">
         <v>1.2</v>
@@ -55601,7 +55616,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ262">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR262">
         <v>1.67</v>
@@ -56138,7 +56153,7 @@
         <v>263</v>
       </c>
       <c r="P265" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="Q265">
         <v>2.38</v>
@@ -56344,7 +56359,7 @@
         <v>264</v>
       </c>
       <c r="P266" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="Q266">
         <v>3.75</v>
@@ -57249,7 +57264,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ270">
-        <v>0.43</v>
+        <v>0.6</v>
       </c>
       <c r="AR270">
         <v>1.54</v>
@@ -57374,7 +57389,7 @@
         <v>268</v>
       </c>
       <c r="P271" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="Q271">
         <v>3.75</v>
@@ -57580,7 +57595,7 @@
         <v>96</v>
       </c>
       <c r="P272" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="Q272">
         <v>2.63</v>
@@ -57658,7 +57673,7 @@
         <v>0.6</v>
       </c>
       <c r="AP272">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ272">
         <v>0.71</v>
@@ -57786,7 +57801,7 @@
         <v>183</v>
       </c>
       <c r="P273" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="Q273">
         <v>3.25</v>
@@ -57867,7 +57882,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ273">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR273">
         <v>1.3</v>
@@ -57992,7 +58007,7 @@
         <v>269</v>
       </c>
       <c r="P274" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="Q274">
         <v>3.2</v>
@@ -58070,7 +58085,7 @@
         <v>0.78</v>
       </c>
       <c r="AP274">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AQ274">
         <v>0.62</v>
@@ -58688,7 +58703,7 @@
         <v>0.62</v>
       </c>
       <c r="AP277">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AQ277">
         <v>0.88</v>
@@ -58897,7 +58912,7 @@
         <v>2</v>
       </c>
       <c r="AQ278">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR278">
         <v>1.35</v>
@@ -59228,7 +59243,7 @@
         <v>96</v>
       </c>
       <c r="P280" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="Q280">
         <v>5.5</v>
@@ -59434,7 +59449,7 @@
         <v>118</v>
       </c>
       <c r="P281" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="Q281">
         <v>2.6</v>
@@ -59718,7 +59733,7 @@
         <v>0.78</v>
       </c>
       <c r="AP282">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ282">
         <v>1.08</v>
@@ -59927,7 +59942,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ283">
-        <v>0.43</v>
+        <v>0.6</v>
       </c>
       <c r="AR283">
         <v>1.5</v>
@@ -60130,7 +60145,7 @@
         <v>0.82</v>
       </c>
       <c r="AP284">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AQ284">
         <v>0.71</v>
@@ -60339,7 +60354,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ285">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR285">
         <v>1.3</v>
@@ -60545,7 +60560,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ286">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR286">
         <v>1.6</v>
@@ -60670,7 +60685,7 @@
         <v>172</v>
       </c>
       <c r="P287" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="Q287">
         <v>3.6</v>
@@ -61160,7 +61175,7 @@
         <v>1.55</v>
       </c>
       <c r="AP289">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AQ289">
         <v>1.43</v>
@@ -61494,7 +61509,7 @@
         <v>275</v>
       </c>
       <c r="P291" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="Q291">
         <v>3.4</v>
@@ -62318,7 +62333,7 @@
         <v>132</v>
       </c>
       <c r="P295" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="Q295">
         <v>2.75</v>
@@ -62524,7 +62539,7 @@
         <v>137</v>
       </c>
       <c r="P296" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="Q296">
         <v>3.25</v>
@@ -62936,7 +62951,7 @@
         <v>278</v>
       </c>
       <c r="P298" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="Q298">
         <v>3.2</v>
@@ -63142,7 +63157,7 @@
         <v>279</v>
       </c>
       <c r="P299" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="Q299">
         <v>3.25</v>
@@ -63220,7 +63235,7 @@
         <v>1.27</v>
       </c>
       <c r="AP299">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AQ299">
         <v>1.29</v>
@@ -63348,7 +63363,7 @@
         <v>267</v>
       </c>
       <c r="P300" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="Q300">
         <v>3.6</v>
@@ -63554,7 +63569,7 @@
         <v>280</v>
       </c>
       <c r="P301" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="Q301">
         <v>2</v>
@@ -63632,10 +63647,10 @@
         <v>0.42</v>
       </c>
       <c r="AP301">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ301">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="AR301">
         <v>1.64</v>
@@ -63760,7 +63775,7 @@
         <v>281</v>
       </c>
       <c r="P302" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q302">
         <v>2.63</v>
@@ -63966,7 +63981,7 @@
         <v>282</v>
       </c>
       <c r="P303" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="Q303">
         <v>2.88</v>
@@ -64044,7 +64059,7 @@
         <v>1.17</v>
       </c>
       <c r="AP303">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ303">
         <v>1.29</v>
@@ -64172,7 +64187,7 @@
         <v>94</v>
       </c>
       <c r="P304" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="Q304">
         <v>2.25</v>
@@ -64662,7 +64677,7 @@
         <v>1.42</v>
       </c>
       <c r="AP306">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AQ306">
         <v>1.43</v>
@@ -64790,7 +64805,7 @@
         <v>283</v>
       </c>
       <c r="P307" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="Q307">
         <v>4</v>
@@ -65202,7 +65217,7 @@
         <v>284</v>
       </c>
       <c r="P309" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="Q309">
         <v>4.33</v>
@@ -65280,7 +65295,7 @@
         <v>0.83</v>
       </c>
       <c r="AP309">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AQ309">
         <v>0.71</v>
@@ -65695,7 +65710,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ311">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR311">
         <v>1.5</v>
@@ -65898,7 +65913,7 @@
         <v>0.73</v>
       </c>
       <c r="AP312">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ312">
         <v>0.62</v>
@@ -66107,7 +66122,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ313">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR313">
         <v>1.6</v>
@@ -66438,7 +66453,7 @@
         <v>289</v>
       </c>
       <c r="P315" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="Q315">
         <v>3.25</v>
@@ -66519,7 +66534,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ315">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR315">
         <v>1.28</v>
@@ -66725,7 +66740,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ316">
-        <v>0.43</v>
+        <v>0.6</v>
       </c>
       <c r="AR316">
         <v>1.34</v>
@@ -66928,7 +66943,7 @@
         <v>0.8</v>
       </c>
       <c r="AP317">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ317">
         <v>0.88</v>
@@ -67056,7 +67071,7 @@
         <v>291</v>
       </c>
       <c r="P318" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="Q318">
         <v>3.25</v>
@@ -67134,10 +67149,10 @@
         <v>1</v>
       </c>
       <c r="AP318">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AQ318">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR318">
         <v>1.05</v>
@@ -67468,7 +67483,7 @@
         <v>293</v>
       </c>
       <c r="P320" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="Q320">
         <v>3.75</v>
@@ -67674,7 +67689,7 @@
         <v>96</v>
       </c>
       <c r="P321" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="Q321">
         <v>3</v>
@@ -67752,10 +67767,10 @@
         <v>1.4</v>
       </c>
       <c r="AP321">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AQ321">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR321">
         <v>1.33</v>
@@ -68086,7 +68101,7 @@
         <v>294</v>
       </c>
       <c r="P323" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="Q323">
         <v>2.38</v>
@@ -68164,10 +68179,10 @@
         <v>0.46</v>
       </c>
       <c r="AP323">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AQ323">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="AR323">
         <v>1.6</v>
@@ -68373,7 +68388,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ324">
-        <v>0.43</v>
+        <v>0.6</v>
       </c>
       <c r="AR324">
         <v>1.62</v>
@@ -68498,7 +68513,7 @@
         <v>296</v>
       </c>
       <c r="P325" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="Q325">
         <v>2.88</v>
@@ -68910,7 +68925,7 @@
         <v>96</v>
       </c>
       <c r="P327" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q327">
         <v>2.1</v>
@@ -68991,7 +69006,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ327">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR327">
         <v>1.4</v>
@@ -69116,7 +69131,7 @@
         <v>96</v>
       </c>
       <c r="P328" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="Q328">
         <v>3.5</v>
@@ -69194,7 +69209,7 @@
         <v>2.08</v>
       </c>
       <c r="AP328">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AQ328">
         <v>2.14</v>
@@ -69322,7 +69337,7 @@
         <v>298</v>
       </c>
       <c r="P329" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q329">
         <v>2.6</v>
@@ -69734,7 +69749,7 @@
         <v>299</v>
       </c>
       <c r="P331" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="Q331">
         <v>2.1</v>
@@ -70146,7 +70161,7 @@
         <v>301</v>
       </c>
       <c r="P333" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="Q333">
         <v>3.75</v>
@@ -70558,7 +70573,7 @@
         <v>302</v>
       </c>
       <c r="P335" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="Q335">
         <v>4.75</v>
@@ -70970,7 +70985,7 @@
         <v>303</v>
       </c>
       <c r="P337" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="Q337">
         <v>4.33</v>
@@ -71382,7 +71397,7 @@
         <v>304</v>
       </c>
       <c r="P339" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="Q339">
         <v>2.88</v>
@@ -71588,7 +71603,7 @@
         <v>305</v>
       </c>
       <c r="P340" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q340">
         <v>3.4</v>
@@ -72363,6 +72378,1036 @@
       </c>
       <c r="BP343">
         <v>1.33</v>
+      </c>
+    </row>
+    <row r="344" spans="1:68">
+      <c r="A344" s="1">
+        <v>343</v>
+      </c>
+      <c r="B344">
+        <v>7727236</v>
+      </c>
+      <c r="C344" t="s">
+        <v>68</v>
+      </c>
+      <c r="D344" t="s">
+        <v>69</v>
+      </c>
+      <c r="E344" s="2">
+        <v>45696.5</v>
+      </c>
+      <c r="F344">
+        <v>31</v>
+      </c>
+      <c r="G344" t="s">
+        <v>85</v>
+      </c>
+      <c r="H344" t="s">
+        <v>82</v>
+      </c>
+      <c r="I344">
+        <v>0</v>
+      </c>
+      <c r="J344">
+        <v>0</v>
+      </c>
+      <c r="K344">
+        <v>0</v>
+      </c>
+      <c r="L344">
+        <v>1</v>
+      </c>
+      <c r="M344">
+        <v>2</v>
+      </c>
+      <c r="N344">
+        <v>3</v>
+      </c>
+      <c r="O344" t="s">
+        <v>308</v>
+      </c>
+      <c r="P344" t="s">
+        <v>445</v>
+      </c>
+      <c r="Q344">
+        <v>2.3</v>
+      </c>
+      <c r="R344">
+        <v>2.1</v>
+      </c>
+      <c r="S344">
+        <v>5.5</v>
+      </c>
+      <c r="T344">
+        <v>1.44</v>
+      </c>
+      <c r="U344">
+        <v>2.63</v>
+      </c>
+      <c r="V344">
+        <v>3.25</v>
+      </c>
+      <c r="W344">
+        <v>1.33</v>
+      </c>
+      <c r="X344">
+        <v>9</v>
+      </c>
+      <c r="Y344">
+        <v>1.07</v>
+      </c>
+      <c r="Z344">
+        <v>1.66</v>
+      </c>
+      <c r="AA344">
+        <v>3.68</v>
+      </c>
+      <c r="AB344">
+        <v>5.1</v>
+      </c>
+      <c r="AC344">
+        <v>1.06</v>
+      </c>
+      <c r="AD344">
+        <v>8.5</v>
+      </c>
+      <c r="AE344">
+        <v>1.35</v>
+      </c>
+      <c r="AF344">
+        <v>3.1</v>
+      </c>
+      <c r="AG344">
+        <v>2</v>
+      </c>
+      <c r="AH344">
+        <v>1.73</v>
+      </c>
+      <c r="AI344">
+        <v>2</v>
+      </c>
+      <c r="AJ344">
+        <v>1.75</v>
+      </c>
+      <c r="AK344">
+        <v>1.15</v>
+      </c>
+      <c r="AL344">
+        <v>1.22</v>
+      </c>
+      <c r="AM344">
+        <v>2.15</v>
+      </c>
+      <c r="AN344">
+        <v>1.93</v>
+      </c>
+      <c r="AO344">
+        <v>0.43</v>
+      </c>
+      <c r="AP344">
+        <v>1.8</v>
+      </c>
+      <c r="AQ344">
+        <v>0.6</v>
+      </c>
+      <c r="AR344">
+        <v>1.63</v>
+      </c>
+      <c r="AS344">
+        <v>1.01</v>
+      </c>
+      <c r="AT344">
+        <v>2.64</v>
+      </c>
+      <c r="AU344">
+        <v>3</v>
+      </c>
+      <c r="AV344">
+        <v>3</v>
+      </c>
+      <c r="AW344">
+        <v>7</v>
+      </c>
+      <c r="AX344">
+        <v>1</v>
+      </c>
+      <c r="AY344">
+        <v>10</v>
+      </c>
+      <c r="AZ344">
+        <v>4</v>
+      </c>
+      <c r="BA344">
+        <v>8</v>
+      </c>
+      <c r="BB344">
+        <v>1</v>
+      </c>
+      <c r="BC344">
+        <v>9</v>
+      </c>
+      <c r="BD344">
+        <v>1.4</v>
+      </c>
+      <c r="BE344">
+        <v>7.5</v>
+      </c>
+      <c r="BF344">
+        <v>3.3</v>
+      </c>
+      <c r="BG344">
+        <v>1.24</v>
+      </c>
+      <c r="BH344">
+        <v>3.55</v>
+      </c>
+      <c r="BI344">
+        <v>1.43</v>
+      </c>
+      <c r="BJ344">
+        <v>2.55</v>
+      </c>
+      <c r="BK344">
+        <v>1.68</v>
+      </c>
+      <c r="BL344">
+        <v>2.02</v>
+      </c>
+      <c r="BM344">
+        <v>2.07</v>
+      </c>
+      <c r="BN344">
+        <v>1.66</v>
+      </c>
+      <c r="BO344">
+        <v>2.63</v>
+      </c>
+      <c r="BP344">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="345" spans="1:68">
+      <c r="A345" s="1">
+        <v>344</v>
+      </c>
+      <c r="B345">
+        <v>7727233</v>
+      </c>
+      <c r="C345" t="s">
+        <v>68</v>
+      </c>
+      <c r="D345" t="s">
+        <v>69</v>
+      </c>
+      <c r="E345" s="2">
+        <v>45696.5</v>
+      </c>
+      <c r="F345">
+        <v>31</v>
+      </c>
+      <c r="G345" t="s">
+        <v>89</v>
+      </c>
+      <c r="H345" t="s">
+        <v>88</v>
+      </c>
+      <c r="I345">
+        <v>1</v>
+      </c>
+      <c r="J345">
+        <v>1</v>
+      </c>
+      <c r="K345">
+        <v>2</v>
+      </c>
+      <c r="L345">
+        <v>1</v>
+      </c>
+      <c r="M345">
+        <v>1</v>
+      </c>
+      <c r="N345">
+        <v>2</v>
+      </c>
+      <c r="O345" t="s">
+        <v>153</v>
+      </c>
+      <c r="P345" t="s">
+        <v>315</v>
+      </c>
+      <c r="Q345">
+        <v>2.38</v>
+      </c>
+      <c r="R345">
+        <v>2.1</v>
+      </c>
+      <c r="S345">
+        <v>5.5</v>
+      </c>
+      <c r="T345">
+        <v>1.44</v>
+      </c>
+      <c r="U345">
+        <v>2.63</v>
+      </c>
+      <c r="V345">
+        <v>3.25</v>
+      </c>
+      <c r="W345">
+        <v>1.33</v>
+      </c>
+      <c r="X345">
+        <v>9</v>
+      </c>
+      <c r="Y345">
+        <v>1.07</v>
+      </c>
+      <c r="Z345">
+        <v>1.64</v>
+      </c>
+      <c r="AA345">
+        <v>3.74</v>
+      </c>
+      <c r="AB345">
+        <v>5.2</v>
+      </c>
+      <c r="AC345">
+        <v>1.07</v>
+      </c>
+      <c r="AD345">
+        <v>8</v>
+      </c>
+      <c r="AE345">
+        <v>1.38</v>
+      </c>
+      <c r="AF345">
+        <v>3</v>
+      </c>
+      <c r="AG345">
+        <v>2</v>
+      </c>
+      <c r="AH345">
+        <v>1.75</v>
+      </c>
+      <c r="AI345">
+        <v>2</v>
+      </c>
+      <c r="AJ345">
+        <v>1.75</v>
+      </c>
+      <c r="AK345">
+        <v>1.17</v>
+      </c>
+      <c r="AL345">
+        <v>1.25</v>
+      </c>
+      <c r="AM345">
+        <v>2.05</v>
+      </c>
+      <c r="AN345">
+        <v>1.5</v>
+      </c>
+      <c r="AO345">
+        <v>0.43</v>
+      </c>
+      <c r="AP345">
+        <v>1.47</v>
+      </c>
+      <c r="AQ345">
+        <v>0.47</v>
+      </c>
+      <c r="AR345">
+        <v>1.38</v>
+      </c>
+      <c r="AS345">
+        <v>1.1</v>
+      </c>
+      <c r="AT345">
+        <v>2.48</v>
+      </c>
+      <c r="AU345">
+        <v>3</v>
+      </c>
+      <c r="AV345">
+        <v>5</v>
+      </c>
+      <c r="AW345">
+        <v>14</v>
+      </c>
+      <c r="AX345">
+        <v>4</v>
+      </c>
+      <c r="AY345">
+        <v>21</v>
+      </c>
+      <c r="AZ345">
+        <v>11</v>
+      </c>
+      <c r="BA345">
+        <v>4</v>
+      </c>
+      <c r="BB345">
+        <v>3</v>
+      </c>
+      <c r="BC345">
+        <v>7</v>
+      </c>
+      <c r="BD345">
+        <v>1.46</v>
+      </c>
+      <c r="BE345">
+        <v>7</v>
+      </c>
+      <c r="BF345">
+        <v>3.05</v>
+      </c>
+      <c r="BG345">
+        <v>1.27</v>
+      </c>
+      <c r="BH345">
+        <v>3.3</v>
+      </c>
+      <c r="BI345">
+        <v>1.48</v>
+      </c>
+      <c r="BJ345">
+        <v>2.45</v>
+      </c>
+      <c r="BK345">
+        <v>1.85</v>
+      </c>
+      <c r="BL345">
+        <v>1.95</v>
+      </c>
+      <c r="BM345">
+        <v>2.18</v>
+      </c>
+      <c r="BN345">
+        <v>1.58</v>
+      </c>
+      <c r="BO345">
+        <v>2.8</v>
+      </c>
+      <c r="BP345">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="346" spans="1:68">
+      <c r="A346" s="1">
+        <v>345</v>
+      </c>
+      <c r="B346">
+        <v>7727232</v>
+      </c>
+      <c r="C346" t="s">
+        <v>68</v>
+      </c>
+      <c r="D346" t="s">
+        <v>69</v>
+      </c>
+      <c r="E346" s="2">
+        <v>45696.5</v>
+      </c>
+      <c r="F346">
+        <v>31</v>
+      </c>
+      <c r="G346" t="s">
+        <v>90</v>
+      </c>
+      <c r="H346" t="s">
+        <v>84</v>
+      </c>
+      <c r="I346">
+        <v>0</v>
+      </c>
+      <c r="J346">
+        <v>0</v>
+      </c>
+      <c r="K346">
+        <v>0</v>
+      </c>
+      <c r="L346">
+        <v>0</v>
+      </c>
+      <c r="M346">
+        <v>0</v>
+      </c>
+      <c r="N346">
+        <v>0</v>
+      </c>
+      <c r="O346" t="s">
+        <v>96</v>
+      </c>
+      <c r="P346" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q346">
+        <v>2</v>
+      </c>
+      <c r="R346">
+        <v>2.38</v>
+      </c>
+      <c r="S346">
+        <v>6</v>
+      </c>
+      <c r="T346">
+        <v>1.33</v>
+      </c>
+      <c r="U346">
+        <v>3.25</v>
+      </c>
+      <c r="V346">
+        <v>2.63</v>
+      </c>
+      <c r="W346">
+        <v>1.44</v>
+      </c>
+      <c r="X346">
+        <v>6.5</v>
+      </c>
+      <c r="Y346">
+        <v>1.11</v>
+      </c>
+      <c r="Z346">
+        <v>1.51</v>
+      </c>
+      <c r="AA346">
+        <v>4.2</v>
+      </c>
+      <c r="AB346">
+        <v>5.8</v>
+      </c>
+      <c r="AC346">
+        <v>1.04</v>
+      </c>
+      <c r="AD346">
+        <v>10</v>
+      </c>
+      <c r="AE346">
+        <v>1.22</v>
+      </c>
+      <c r="AF346">
+        <v>4.2</v>
+      </c>
+      <c r="AG346">
+        <v>1.73</v>
+      </c>
+      <c r="AH346">
+        <v>2</v>
+      </c>
+      <c r="AI346">
+        <v>1.91</v>
+      </c>
+      <c r="AJ346">
+        <v>1.91</v>
+      </c>
+      <c r="AK346">
+        <v>1.12</v>
+      </c>
+      <c r="AL346">
+        <v>1.17</v>
+      </c>
+      <c r="AM346">
+        <v>2.55</v>
+      </c>
+      <c r="AN346">
+        <v>1.8</v>
+      </c>
+      <c r="AO346">
+        <v>0.93</v>
+      </c>
+      <c r="AP346">
+        <v>1.75</v>
+      </c>
+      <c r="AQ346">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AR346">
+        <v>1.43</v>
+      </c>
+      <c r="AS346">
+        <v>1.21</v>
+      </c>
+      <c r="AT346">
+        <v>2.64</v>
+      </c>
+      <c r="AU346">
+        <v>7</v>
+      </c>
+      <c r="AV346">
+        <v>2</v>
+      </c>
+      <c r="AW346">
+        <v>11</v>
+      </c>
+      <c r="AX346">
+        <v>9</v>
+      </c>
+      <c r="AY346">
+        <v>18</v>
+      </c>
+      <c r="AZ346">
+        <v>12</v>
+      </c>
+      <c r="BA346">
+        <v>6</v>
+      </c>
+      <c r="BB346">
+        <v>0</v>
+      </c>
+      <c r="BC346">
+        <v>6</v>
+      </c>
+      <c r="BD346">
+        <v>1.3</v>
+      </c>
+      <c r="BE346">
+        <v>8</v>
+      </c>
+      <c r="BF346">
+        <v>3.8</v>
+      </c>
+      <c r="BG346">
+        <v>1.17</v>
+      </c>
+      <c r="BH346">
+        <v>4.3</v>
+      </c>
+      <c r="BI346">
+        <v>1.3</v>
+      </c>
+      <c r="BJ346">
+        <v>3.05</v>
+      </c>
+      <c r="BK346">
+        <v>1.52</v>
+      </c>
+      <c r="BL346">
+        <v>2.33</v>
+      </c>
+      <c r="BM346">
+        <v>1.85</v>
+      </c>
+      <c r="BN346">
+        <v>1.95</v>
+      </c>
+      <c r="BO346">
+        <v>2.23</v>
+      </c>
+      <c r="BP346">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="347" spans="1:68">
+      <c r="A347" s="1">
+        <v>346</v>
+      </c>
+      <c r="B347">
+        <v>7727229</v>
+      </c>
+      <c r="C347" t="s">
+        <v>68</v>
+      </c>
+      <c r="D347" t="s">
+        <v>69</v>
+      </c>
+      <c r="E347" s="2">
+        <v>45696.5</v>
+      </c>
+      <c r="F347">
+        <v>31</v>
+      </c>
+      <c r="G347" t="s">
+        <v>78</v>
+      </c>
+      <c r="H347" t="s">
+        <v>91</v>
+      </c>
+      <c r="I347">
+        <v>1</v>
+      </c>
+      <c r="J347">
+        <v>0</v>
+      </c>
+      <c r="K347">
+        <v>1</v>
+      </c>
+      <c r="L347">
+        <v>1</v>
+      </c>
+      <c r="M347">
+        <v>1</v>
+      </c>
+      <c r="N347">
+        <v>2</v>
+      </c>
+      <c r="O347" t="s">
+        <v>255</v>
+      </c>
+      <c r="P347" t="s">
+        <v>446</v>
+      </c>
+      <c r="Q347">
+        <v>4</v>
+      </c>
+      <c r="R347">
+        <v>2.2</v>
+      </c>
+      <c r="S347">
+        <v>2.75</v>
+      </c>
+      <c r="T347">
+        <v>1.4</v>
+      </c>
+      <c r="U347">
+        <v>2.75</v>
+      </c>
+      <c r="V347">
+        <v>2.75</v>
+      </c>
+      <c r="W347">
+        <v>1.4</v>
+      </c>
+      <c r="X347">
+        <v>8</v>
+      </c>
+      <c r="Y347">
+        <v>1.08</v>
+      </c>
+      <c r="Z347">
+        <v>3.5</v>
+      </c>
+      <c r="AA347">
+        <v>3.39</v>
+      </c>
+      <c r="AB347">
+        <v>2.04</v>
+      </c>
+      <c r="AC347">
+        <v>1.05</v>
+      </c>
+      <c r="AD347">
+        <v>9</v>
+      </c>
+      <c r="AE347">
+        <v>1.3</v>
+      </c>
+      <c r="AF347">
+        <v>3.4</v>
+      </c>
+      <c r="AG347">
+        <v>1.91</v>
+      </c>
+      <c r="AH347">
+        <v>1.83</v>
+      </c>
+      <c r="AI347">
+        <v>1.75</v>
+      </c>
+      <c r="AJ347">
+        <v>2</v>
+      </c>
+      <c r="AK347">
+        <v>1.73</v>
+      </c>
+      <c r="AL347">
+        <v>1.25</v>
+      </c>
+      <c r="AM347">
+        <v>1.3</v>
+      </c>
+      <c r="AN347">
+        <v>0.8</v>
+      </c>
+      <c r="AO347">
+        <v>1.5</v>
+      </c>
+      <c r="AP347">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AQ347">
+        <v>1.47</v>
+      </c>
+      <c r="AR347">
+        <v>1.09</v>
+      </c>
+      <c r="AS347">
+        <v>1.33</v>
+      </c>
+      <c r="AT347">
+        <v>2.42</v>
+      </c>
+      <c r="AU347">
+        <v>7</v>
+      </c>
+      <c r="AV347">
+        <v>3</v>
+      </c>
+      <c r="AW347">
+        <v>6</v>
+      </c>
+      <c r="AX347">
+        <v>12</v>
+      </c>
+      <c r="AY347">
+        <v>14</v>
+      </c>
+      <c r="AZ347">
+        <v>20</v>
+      </c>
+      <c r="BA347">
+        <v>2</v>
+      </c>
+      <c r="BB347">
+        <v>7</v>
+      </c>
+      <c r="BC347">
+        <v>9</v>
+      </c>
+      <c r="BD347">
+        <v>2.4</v>
+      </c>
+      <c r="BE347">
+        <v>6.4</v>
+      </c>
+      <c r="BF347">
+        <v>1.71</v>
+      </c>
+      <c r="BG347">
+        <v>1.33</v>
+      </c>
+      <c r="BH347">
+        <v>2.95</v>
+      </c>
+      <c r="BI347">
+        <v>1.56</v>
+      </c>
+      <c r="BJ347">
+        <v>2.23</v>
+      </c>
+      <c r="BK347">
+        <v>2</v>
+      </c>
+      <c r="BL347">
+        <v>1.8</v>
+      </c>
+      <c r="BM347">
+        <v>2.4</v>
+      </c>
+      <c r="BN347">
+        <v>1.49</v>
+      </c>
+      <c r="BO347">
+        <v>3.15</v>
+      </c>
+      <c r="BP347">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="348" spans="1:68">
+      <c r="A348" s="1">
+        <v>347</v>
+      </c>
+      <c r="B348">
+        <v>7727228</v>
+      </c>
+      <c r="C348" t="s">
+        <v>68</v>
+      </c>
+      <c r="D348" t="s">
+        <v>69</v>
+      </c>
+      <c r="E348" s="2">
+        <v>45696.5</v>
+      </c>
+      <c r="F348">
+        <v>31</v>
+      </c>
+      <c r="G348" t="s">
+        <v>93</v>
+      </c>
+      <c r="H348" t="s">
+        <v>77</v>
+      </c>
+      <c r="I348">
+        <v>0</v>
+      </c>
+      <c r="J348">
+        <v>0</v>
+      </c>
+      <c r="K348">
+        <v>0</v>
+      </c>
+      <c r="L348">
+        <v>4</v>
+      </c>
+      <c r="M348">
+        <v>3</v>
+      </c>
+      <c r="N348">
+        <v>7</v>
+      </c>
+      <c r="O348" t="s">
+        <v>309</v>
+      </c>
+      <c r="P348" t="s">
+        <v>447</v>
+      </c>
+      <c r="Q348">
+        <v>1.91</v>
+      </c>
+      <c r="R348">
+        <v>2.5</v>
+      </c>
+      <c r="S348">
+        <v>6</v>
+      </c>
+      <c r="T348">
+        <v>1.29</v>
+      </c>
+      <c r="U348">
+        <v>3.5</v>
+      </c>
+      <c r="V348">
+        <v>2.25</v>
+      </c>
+      <c r="W348">
+        <v>1.57</v>
+      </c>
+      <c r="X348">
+        <v>5.5</v>
+      </c>
+      <c r="Y348">
+        <v>1.14</v>
+      </c>
+      <c r="Z348">
+        <v>1.43</v>
+      </c>
+      <c r="AA348">
+        <v>5</v>
+      </c>
+      <c r="AB348">
+        <v>5.9</v>
+      </c>
+      <c r="AC348">
+        <v>1.04</v>
+      </c>
+      <c r="AD348">
+        <v>10</v>
+      </c>
+      <c r="AE348">
+        <v>1.17</v>
+      </c>
+      <c r="AF348">
+        <v>5</v>
+      </c>
+      <c r="AG348">
+        <v>1.55</v>
+      </c>
+      <c r="AH348">
+        <v>2.37</v>
+      </c>
+      <c r="AI348">
+        <v>1.7</v>
+      </c>
+      <c r="AJ348">
+        <v>2.05</v>
+      </c>
+      <c r="AK348">
+        <v>1.1</v>
+      </c>
+      <c r="AL348">
+        <v>1.14</v>
+      </c>
+      <c r="AM348">
+        <v>2.75</v>
+      </c>
+      <c r="AN348">
+        <v>1.6</v>
+      </c>
+      <c r="AO348">
+        <v>0.8</v>
+      </c>
+      <c r="AP348">
+        <v>1.69</v>
+      </c>
+      <c r="AQ348">
+        <v>0.75</v>
+      </c>
+      <c r="AR348">
+        <v>1.73</v>
+      </c>
+      <c r="AS348">
+        <v>1.32</v>
+      </c>
+      <c r="AT348">
+        <v>3.05</v>
+      </c>
+      <c r="AU348">
+        <v>7</v>
+      </c>
+      <c r="AV348">
+        <v>5</v>
+      </c>
+      <c r="AW348">
+        <v>11</v>
+      </c>
+      <c r="AX348">
+        <v>6</v>
+      </c>
+      <c r="AY348">
+        <v>21</v>
+      </c>
+      <c r="AZ348">
+        <v>11</v>
+      </c>
+      <c r="BA348">
+        <v>4</v>
+      </c>
+      <c r="BB348">
+        <v>5</v>
+      </c>
+      <c r="BC348">
+        <v>9</v>
+      </c>
+      <c r="BD348">
+        <v>1.38</v>
+      </c>
+      <c r="BE348">
+        <v>7.5</v>
+      </c>
+      <c r="BF348">
+        <v>3.4</v>
+      </c>
+      <c r="BG348">
+        <v>1.18</v>
+      </c>
+      <c r="BH348">
+        <v>4.1</v>
+      </c>
+      <c r="BI348">
+        <v>1.32</v>
+      </c>
+      <c r="BJ348">
+        <v>3.05</v>
+      </c>
+      <c r="BK348">
+        <v>1.53</v>
+      </c>
+      <c r="BL348">
+        <v>2.32</v>
+      </c>
+      <c r="BM348">
+        <v>1.98</v>
+      </c>
+      <c r="BN348">
+        <v>1.82</v>
+      </c>
+      <c r="BO348">
+        <v>2.25</v>
+      </c>
+      <c r="BP348">
+        <v>1.55</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England EFL League One_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England EFL League One_20242025.xlsx
@@ -940,10 +940,10 @@
     <t>['31', '35']</t>
   </si>
   <si>
-    <t>['76']</t>
+    <t>['52', '68', '85', '90+9']</t>
   </si>
   <si>
-    <t>['52', '68', '85', '90+9']</t>
+    <t>['76']</t>
   </si>
   <si>
     <t>['13', '18']</t>
@@ -1351,13 +1351,13 @@
     <t>['52', '54']</t>
   </si>
   <si>
-    <t>['68', '77']</t>
+    <t>['50', '54', '62']</t>
   </si>
   <si>
     <t>['90+4']</t>
   </si>
   <si>
-    <t>['50', '54', '62']</t>
+    <t>['68', '77']</t>
   </si>
 </sst>
 </file>
@@ -72385,7 +72385,7 @@
         <v>343</v>
       </c>
       <c r="B344">
-        <v>7727236</v>
+        <v>7727233</v>
       </c>
       <c r="C344" t="s">
         <v>68</v>
@@ -72400,37 +72400,37 @@
         <v>31</v>
       </c>
       <c r="G344" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H344" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="I344">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J344">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K344">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L344">
         <v>1</v>
       </c>
       <c r="M344">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N344">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O344" t="s">
-        <v>308</v>
+        <v>153</v>
       </c>
       <c r="P344" t="s">
-        <v>445</v>
+        <v>315</v>
       </c>
       <c r="Q344">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="R344">
         <v>2.1</v>
@@ -72457,31 +72457,31 @@
         <v>1.07</v>
       </c>
       <c r="Z344">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AA344">
-        <v>3.68</v>
+        <v>3.74</v>
       </c>
       <c r="AB344">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AC344">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AD344">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="AE344">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AF344">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AG344">
         <v>2</v>
       </c>
       <c r="AH344">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AI344">
         <v>2</v>
@@ -72490,100 +72490,100 @@
         <v>1.75</v>
       </c>
       <c r="AK344">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AL344">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AM344">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AN344">
-        <v>1.93</v>
+        <v>1.5</v>
       </c>
       <c r="AO344">
         <v>0.43</v>
       </c>
       <c r="AP344">
-        <v>1.8</v>
+        <v>1.47</v>
       </c>
       <c r="AQ344">
-        <v>0.6</v>
+        <v>0.47</v>
       </c>
       <c r="AR344">
-        <v>1.63</v>
+        <v>1.38</v>
       </c>
       <c r="AS344">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AT344">
-        <v>2.64</v>
+        <v>2.48</v>
       </c>
       <c r="AU344">
         <v>3</v>
       </c>
       <c r="AV344">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AW344">
+        <v>14</v>
+      </c>
+      <c r="AX344">
+        <v>4</v>
+      </c>
+      <c r="AY344">
+        <v>21</v>
+      </c>
+      <c r="AZ344">
+        <v>11</v>
+      </c>
+      <c r="BA344">
+        <v>4</v>
+      </c>
+      <c r="BB344">
+        <v>3</v>
+      </c>
+      <c r="BC344">
         <v>7</v>
       </c>
-      <c r="AX344">
-        <v>1</v>
-      </c>
-      <c r="AY344">
-        <v>10</v>
-      </c>
-      <c r="AZ344">
-        <v>4</v>
-      </c>
-      <c r="BA344">
-        <v>8</v>
-      </c>
-      <c r="BB344">
-        <v>1</v>
-      </c>
-      <c r="BC344">
-        <v>9</v>
-      </c>
       <c r="BD344">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="BE344">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="BF344">
+        <v>3.05</v>
+      </c>
+      <c r="BG344">
+        <v>1.27</v>
+      </c>
+      <c r="BH344">
         <v>3.3</v>
       </c>
-      <c r="BG344">
-        <v>1.24</v>
-      </c>
-      <c r="BH344">
-        <v>3.55</v>
-      </c>
       <c r="BI344">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="BJ344">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="BK344">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="BL344">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="BM344">
-        <v>2.07</v>
+        <v>2.18</v>
       </c>
       <c r="BN344">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="BO344">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="BP344">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="345" spans="1:68">
@@ -72591,7 +72591,7 @@
         <v>344</v>
       </c>
       <c r="B345">
-        <v>7727233</v>
+        <v>7727232</v>
       </c>
       <c r="C345" t="s">
         <v>68</v>
@@ -72606,190 +72606,190 @@
         <v>31</v>
       </c>
       <c r="G345" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H345" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="I345">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J345">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K345">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L345">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M345">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N345">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O345" t="s">
-        <v>153</v>
+        <v>96</v>
       </c>
       <c r="P345" t="s">
-        <v>315</v>
+        <v>96</v>
       </c>
       <c r="Q345">
+        <v>2</v>
+      </c>
+      <c r="R345">
         <v>2.38</v>
       </c>
-      <c r="R345">
-        <v>2.1</v>
-      </c>
       <c r="S345">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="T345">
+        <v>1.33</v>
+      </c>
+      <c r="U345">
+        <v>3.25</v>
+      </c>
+      <c r="V345">
+        <v>2.63</v>
+      </c>
+      <c r="W345">
         <v>1.44</v>
       </c>
-      <c r="U345">
-        <v>2.63</v>
-      </c>
-      <c r="V345">
-        <v>3.25</v>
-      </c>
-      <c r="W345">
-        <v>1.33</v>
-      </c>
       <c r="X345">
+        <v>6.5</v>
+      </c>
+      <c r="Y345">
+        <v>1.11</v>
+      </c>
+      <c r="Z345">
+        <v>1.51</v>
+      </c>
+      <c r="AA345">
+        <v>4.2</v>
+      </c>
+      <c r="AB345">
+        <v>5.8</v>
+      </c>
+      <c r="AC345">
+        <v>1.04</v>
+      </c>
+      <c r="AD345">
+        <v>10</v>
+      </c>
+      <c r="AE345">
+        <v>1.22</v>
+      </c>
+      <c r="AF345">
+        <v>4.2</v>
+      </c>
+      <c r="AG345">
+        <v>1.73</v>
+      </c>
+      <c r="AH345">
+        <v>2</v>
+      </c>
+      <c r="AI345">
+        <v>1.91</v>
+      </c>
+      <c r="AJ345">
+        <v>1.91</v>
+      </c>
+      <c r="AK345">
+        <v>1.12</v>
+      </c>
+      <c r="AL345">
+        <v>1.17</v>
+      </c>
+      <c r="AM345">
+        <v>2.55</v>
+      </c>
+      <c r="AN345">
+        <v>1.8</v>
+      </c>
+      <c r="AO345">
+        <v>0.93</v>
+      </c>
+      <c r="AP345">
+        <v>1.75</v>
+      </c>
+      <c r="AQ345">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AR345">
+        <v>1.43</v>
+      </c>
+      <c r="AS345">
+        <v>1.21</v>
+      </c>
+      <c r="AT345">
+        <v>2.64</v>
+      </c>
+      <c r="AU345">
+        <v>7</v>
+      </c>
+      <c r="AV345">
+        <v>2</v>
+      </c>
+      <c r="AW345">
+        <v>11</v>
+      </c>
+      <c r="AX345">
         <v>9</v>
       </c>
-      <c r="Y345">
-        <v>1.07</v>
-      </c>
-      <c r="Z345">
-        <v>1.64</v>
-      </c>
-      <c r="AA345">
-        <v>3.74</v>
-      </c>
-      <c r="AB345">
-        <v>5.2</v>
-      </c>
-      <c r="AC345">
-        <v>1.07</v>
-      </c>
-      <c r="AD345">
+      <c r="AY345">
+        <v>18</v>
+      </c>
+      <c r="AZ345">
+        <v>12</v>
+      </c>
+      <c r="BA345">
+        <v>6</v>
+      </c>
+      <c r="BB345">
+        <v>0</v>
+      </c>
+      <c r="BC345">
+        <v>6</v>
+      </c>
+      <c r="BD345">
+        <v>1.3</v>
+      </c>
+      <c r="BE345">
         <v>8</v>
       </c>
-      <c r="AE345">
-        <v>1.38</v>
-      </c>
-      <c r="AF345">
-        <v>3</v>
-      </c>
-      <c r="AG345">
-        <v>2</v>
-      </c>
-      <c r="AH345">
-        <v>1.75</v>
-      </c>
-      <c r="AI345">
-        <v>2</v>
-      </c>
-      <c r="AJ345">
-        <v>1.75</v>
-      </c>
-      <c r="AK345">
+      <c r="BF345">
+        <v>3.8</v>
+      </c>
+      <c r="BG345">
         <v>1.17</v>
       </c>
-      <c r="AL345">
-        <v>1.25</v>
-      </c>
-      <c r="AM345">
-        <v>2.05</v>
-      </c>
-      <c r="AN345">
-        <v>1.5</v>
-      </c>
-      <c r="AO345">
-        <v>0.43</v>
-      </c>
-      <c r="AP345">
-        <v>1.47</v>
-      </c>
-      <c r="AQ345">
-        <v>0.47</v>
-      </c>
-      <c r="AR345">
-        <v>1.38</v>
-      </c>
-      <c r="AS345">
-        <v>1.1</v>
-      </c>
-      <c r="AT345">
-        <v>2.48</v>
-      </c>
-      <c r="AU345">
-        <v>3</v>
-      </c>
-      <c r="AV345">
-        <v>5</v>
-      </c>
-      <c r="AW345">
-        <v>14</v>
-      </c>
-      <c r="AX345">
-        <v>4</v>
-      </c>
-      <c r="AY345">
-        <v>21</v>
-      </c>
-      <c r="AZ345">
-        <v>11</v>
-      </c>
-      <c r="BA345">
-        <v>4</v>
-      </c>
-      <c r="BB345">
-        <v>3</v>
-      </c>
-      <c r="BC345">
-        <v>7</v>
-      </c>
-      <c r="BD345">
-        <v>1.46</v>
-      </c>
-      <c r="BE345">
-        <v>7</v>
-      </c>
-      <c r="BF345">
+      <c r="BH345">
+        <v>4.3</v>
+      </c>
+      <c r="BI345">
+        <v>1.3</v>
+      </c>
+      <c r="BJ345">
         <v>3.05</v>
       </c>
-      <c r="BG345">
-        <v>1.27</v>
-      </c>
-      <c r="BH345">
-        <v>3.3</v>
-      </c>
-      <c r="BI345">
-        <v>1.48</v>
-      </c>
-      <c r="BJ345">
-        <v>2.45</v>
-      </c>
       <c r="BK345">
+        <v>1.52</v>
+      </c>
+      <c r="BL345">
+        <v>2.33</v>
+      </c>
+      <c r="BM345">
         <v>1.85</v>
       </c>
-      <c r="BL345">
+      <c r="BN345">
         <v>1.95</v>
       </c>
-      <c r="BM345">
-        <v>2.18</v>
-      </c>
-      <c r="BN345">
-        <v>1.58</v>
-      </c>
       <c r="BO345">
-        <v>2.8</v>
+        <v>2.23</v>
       </c>
       <c r="BP345">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="346" spans="1:68">
@@ -72797,7 +72797,7 @@
         <v>345</v>
       </c>
       <c r="B346">
-        <v>7727232</v>
+        <v>7727228</v>
       </c>
       <c r="C346" t="s">
         <v>68</v>
@@ -72812,10 +72812,10 @@
         <v>31</v>
       </c>
       <c r="G346" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="H346" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I346">
         <v>0</v>
@@ -72827,55 +72827,55 @@
         <v>0</v>
       </c>
       <c r="L346">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M346">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N346">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O346" t="s">
-        <v>96</v>
+        <v>308</v>
       </c>
       <c r="P346" t="s">
-        <v>96</v>
+        <v>445</v>
       </c>
       <c r="Q346">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="R346">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="S346">
         <v>6</v>
       </c>
       <c r="T346">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="U346">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="V346">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="W346">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="X346">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="Y346">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z346">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="AA346">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="AB346">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AC346">
         <v>1.04</v>
@@ -72884,118 +72884,118 @@
         <v>10</v>
       </c>
       <c r="AE346">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AF346">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="AG346">
+        <v>1.55</v>
+      </c>
+      <c r="AH346">
+        <v>2.37</v>
+      </c>
+      <c r="AI346">
+        <v>1.7</v>
+      </c>
+      <c r="AJ346">
+        <v>2.05</v>
+      </c>
+      <c r="AK346">
+        <v>1.1</v>
+      </c>
+      <c r="AL346">
+        <v>1.14</v>
+      </c>
+      <c r="AM346">
+        <v>2.75</v>
+      </c>
+      <c r="AN346">
+        <v>1.6</v>
+      </c>
+      <c r="AO346">
+        <v>0.8</v>
+      </c>
+      <c r="AP346">
+        <v>1.69</v>
+      </c>
+      <c r="AQ346">
+        <v>0.75</v>
+      </c>
+      <c r="AR346">
         <v>1.73</v>
       </c>
-      <c r="AH346">
-        <v>2</v>
-      </c>
-      <c r="AI346">
-        <v>1.91</v>
-      </c>
-      <c r="AJ346">
-        <v>1.91</v>
-      </c>
-      <c r="AK346">
-        <v>1.12</v>
-      </c>
-      <c r="AL346">
-        <v>1.17</v>
-      </c>
-      <c r="AM346">
-        <v>2.55</v>
-      </c>
-      <c r="AN346">
-        <v>1.8</v>
-      </c>
-      <c r="AO346">
-        <v>0.93</v>
-      </c>
-      <c r="AP346">
-        <v>1.75</v>
-      </c>
-      <c r="AQ346">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="AR346">
-        <v>1.43</v>
-      </c>
       <c r="AS346">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="AT346">
-        <v>2.64</v>
+        <v>3.05</v>
       </c>
       <c r="AU346">
         <v>7</v>
       </c>
       <c r="AV346">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AW346">
         <v>11</v>
       </c>
       <c r="AX346">
+        <v>6</v>
+      </c>
+      <c r="AY346">
+        <v>21</v>
+      </c>
+      <c r="AZ346">
+        <v>11</v>
+      </c>
+      <c r="BA346">
+        <v>4</v>
+      </c>
+      <c r="BB346">
+        <v>5</v>
+      </c>
+      <c r="BC346">
         <v>9</v>
       </c>
-      <c r="AY346">
-        <v>18</v>
-      </c>
-      <c r="AZ346">
-        <v>12</v>
-      </c>
-      <c r="BA346">
-        <v>6</v>
-      </c>
-      <c r="BB346">
-        <v>0</v>
-      </c>
-      <c r="BC346">
-        <v>6</v>
-      </c>
       <c r="BD346">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="BE346">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="BF346">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="BG346">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="BH346">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BI346">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="BJ346">
         <v>3.05</v>
       </c>
       <c r="BK346">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="BL346">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="BM346">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="BN346">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="BO346">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="BP346">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="347" spans="1:68">
@@ -73209,7 +73209,7 @@
         <v>347</v>
       </c>
       <c r="B348">
-        <v>7727228</v>
+        <v>7727236</v>
       </c>
       <c r="C348" t="s">
         <v>68</v>
@@ -73224,10 +73224,10 @@
         <v>31</v>
       </c>
       <c r="G348" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="H348" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="I348">
         <v>0</v>
@@ -73239,13 +73239,13 @@
         <v>0</v>
       </c>
       <c r="L348">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M348">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N348">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O348" t="s">
         <v>309</v>
@@ -73254,160 +73254,160 @@
         <v>447</v>
       </c>
       <c r="Q348">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="R348">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="S348">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="T348">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="U348">
-        <v>3.5</v>
+        <v>2.63</v>
       </c>
       <c r="V348">
-        <v>2.25</v>
+        <v>3.25</v>
       </c>
       <c r="W348">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="X348">
-        <v>5.5</v>
+        <v>9</v>
       </c>
       <c r="Y348">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="Z348">
-        <v>1.43</v>
+        <v>1.66</v>
       </c>
       <c r="AA348">
-        <v>5</v>
+        <v>3.68</v>
       </c>
       <c r="AB348">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="AC348">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AD348">
+        <v>8.5</v>
+      </c>
+      <c r="AE348">
+        <v>1.35</v>
+      </c>
+      <c r="AF348">
+        <v>3.1</v>
+      </c>
+      <c r="AG348">
+        <v>2</v>
+      </c>
+      <c r="AH348">
+        <v>1.73</v>
+      </c>
+      <c r="AI348">
+        <v>2</v>
+      </c>
+      <c r="AJ348">
+        <v>1.75</v>
+      </c>
+      <c r="AK348">
+        <v>1.15</v>
+      </c>
+      <c r="AL348">
+        <v>1.22</v>
+      </c>
+      <c r="AM348">
+        <v>2.15</v>
+      </c>
+      <c r="AN348">
+        <v>1.93</v>
+      </c>
+      <c r="AO348">
+        <v>0.43</v>
+      </c>
+      <c r="AP348">
+        <v>1.8</v>
+      </c>
+      <c r="AQ348">
+        <v>0.6</v>
+      </c>
+      <c r="AR348">
+        <v>1.63</v>
+      </c>
+      <c r="AS348">
+        <v>1.01</v>
+      </c>
+      <c r="AT348">
+        <v>2.64</v>
+      </c>
+      <c r="AU348">
+        <v>3</v>
+      </c>
+      <c r="AV348">
+        <v>3</v>
+      </c>
+      <c r="AW348">
+        <v>7</v>
+      </c>
+      <c r="AX348">
+        <v>1</v>
+      </c>
+      <c r="AY348">
         <v>10</v>
       </c>
-      <c r="AE348">
-        <v>1.17</v>
-      </c>
-      <c r="AF348">
-        <v>5</v>
-      </c>
-      <c r="AG348">
-        <v>1.55</v>
-      </c>
-      <c r="AH348">
-        <v>2.37</v>
-      </c>
-      <c r="AI348">
-        <v>1.7</v>
-      </c>
-      <c r="AJ348">
-        <v>2.05</v>
-      </c>
-      <c r="AK348">
-        <v>1.1</v>
-      </c>
-      <c r="AL348">
-        <v>1.14</v>
-      </c>
-      <c r="AM348">
-        <v>2.75</v>
-      </c>
-      <c r="AN348">
-        <v>1.6</v>
-      </c>
-      <c r="AO348">
-        <v>0.8</v>
-      </c>
-      <c r="AP348">
-        <v>1.69</v>
-      </c>
-      <c r="AQ348">
-        <v>0.75</v>
-      </c>
-      <c r="AR348">
-        <v>1.73</v>
-      </c>
-      <c r="AS348">
-        <v>1.32</v>
-      </c>
-      <c r="AT348">
-        <v>3.05</v>
-      </c>
-      <c r="AU348">
-        <v>7</v>
-      </c>
-      <c r="AV348">
-        <v>5</v>
-      </c>
-      <c r="AW348">
-        <v>11</v>
-      </c>
-      <c r="AX348">
-        <v>6</v>
-      </c>
-      <c r="AY348">
-        <v>21</v>
-      </c>
       <c r="AZ348">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="BA348">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="BB348">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BC348">
         <v>9</v>
       </c>
       <c r="BD348">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="BE348">
         <v>7.5</v>
       </c>
       <c r="BF348">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="BG348">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="BH348">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="BI348">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="BJ348">
-        <v>3.05</v>
+        <v>2.55</v>
       </c>
       <c r="BK348">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="BL348">
-        <v>2.32</v>
+        <v>2.02</v>
       </c>
       <c r="BM348">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="BN348">
-        <v>1.82</v>
+        <v>1.66</v>
       </c>
       <c r="BO348">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="BP348">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England EFL League One_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England EFL League One_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2150" uniqueCount="448">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2192" uniqueCount="453">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -946,6 +946,24 @@
     <t>['76']</t>
   </si>
   <si>
+    <t>['54', '89']</t>
+  </si>
+  <si>
+    <t>['23', '39', '40', '79']</t>
+  </si>
+  <si>
+    <t>['50', '87', '90+4']</t>
+  </si>
+  <si>
+    <t>['6', '17', '32']</t>
+  </si>
+  <si>
+    <t>['90+1']</t>
+  </si>
+  <si>
+    <t>['28']</t>
+  </si>
+  <si>
     <t>['13', '18']</t>
   </si>
   <si>
@@ -1070,9 +1088,6 @@
   </si>
   <si>
     <t>['26', '68']</t>
-  </si>
-  <si>
-    <t>['90+1']</t>
   </si>
   <si>
     <t>['6', '23', '60', '83']</t>
@@ -1719,7 +1734,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP348"/>
+  <dimension ref="A1:BP355"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1975,7 +1990,7 @@
         <v>94</v>
       </c>
       <c r="P2" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -2056,7 +2071,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ2">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2387,7 +2402,7 @@
         <v>96</v>
       </c>
       <c r="P4" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="Q4">
         <v>3.2</v>
@@ -2674,7 +2689,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ5">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2799,7 +2814,7 @@
         <v>96</v>
       </c>
       <c r="P6" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="Q6">
         <v>2.75</v>
@@ -3005,7 +3020,7 @@
         <v>98</v>
       </c>
       <c r="P7" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="Q7">
         <v>4</v>
@@ -3083,7 +3098,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ7">
         <v>1.43</v>
@@ -3292,7 +3307,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ8">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3495,7 +3510,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ9">
         <v>1.47</v>
@@ -3623,7 +3638,7 @@
         <v>101</v>
       </c>
       <c r="P10" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="Q10">
         <v>3.75</v>
@@ -3907,7 +3922,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ11">
         <v>0.88</v>
@@ -4035,7 +4050,7 @@
         <v>103</v>
       </c>
       <c r="P12" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="Q12">
         <v>2.1</v>
@@ -4113,7 +4128,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ12">
         <v>0.9399999999999999</v>
@@ -4322,7 +4337,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ13">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4447,7 +4462,7 @@
         <v>105</v>
       </c>
       <c r="P14" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="Q14">
         <v>4</v>
@@ -4528,7 +4543,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ14">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4731,7 +4746,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ15">
         <v>1.54</v>
@@ -4937,7 +4952,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AQ16">
         <v>1.29</v>
@@ -5271,7 +5286,7 @@
         <v>107</v>
       </c>
       <c r="P18" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="Q18">
         <v>4.33</v>
@@ -5889,7 +5904,7 @@
         <v>109</v>
       </c>
       <c r="P21" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q21">
         <v>2.75</v>
@@ -6095,7 +6110,7 @@
         <v>110</v>
       </c>
       <c r="P22" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="Q22">
         <v>2.3</v>
@@ -6176,7 +6191,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ22">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -6301,7 +6316,7 @@
         <v>96</v>
       </c>
       <c r="P23" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="Q23">
         <v>2.75</v>
@@ -6379,10 +6394,10 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ23">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AR23">
         <v>0</v>
@@ -6507,7 +6522,7 @@
         <v>111</v>
       </c>
       <c r="P24" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="Q24">
         <v>2.5</v>
@@ -7206,7 +7221,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="AQ27">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR27">
         <v>1.26</v>
@@ -7412,7 +7427,7 @@
         <v>2</v>
       </c>
       <c r="AQ28">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR28">
         <v>0.87</v>
@@ -7949,7 +7964,7 @@
         <v>116</v>
       </c>
       <c r="P31" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -8030,7 +8045,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ31">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR31">
         <v>1.84</v>
@@ -8155,7 +8170,7 @@
         <v>117</v>
       </c>
       <c r="P32" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="Q32">
         <v>4.5</v>
@@ -8442,7 +8457,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ33">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="AR33">
         <v>1.14</v>
@@ -8567,7 +8582,7 @@
         <v>119</v>
       </c>
       <c r="P34" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="Q34">
         <v>3.75</v>
@@ -8648,7 +8663,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ34">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR34">
         <v>1.76</v>
@@ -8851,7 +8866,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ35">
         <v>1.43</v>
@@ -8979,7 +8994,7 @@
         <v>121</v>
       </c>
       <c r="P36" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="Q36">
         <v>2.2</v>
@@ -9185,7 +9200,7 @@
         <v>122</v>
       </c>
       <c r="P37" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="Q37">
         <v>4.33</v>
@@ -9263,7 +9278,7 @@
         <v>3</v>
       </c>
       <c r="AP37">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ37">
         <v>2.14</v>
@@ -9391,7 +9406,7 @@
         <v>123</v>
       </c>
       <c r="P38" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="Q38">
         <v>2.63</v>
@@ -9469,7 +9484,7 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ38">
         <v>2.07</v>
@@ -10293,7 +10308,7 @@
         <v>3</v>
       </c>
       <c r="AP42">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AQ42">
         <v>1.29</v>
@@ -10421,7 +10436,7 @@
         <v>96</v>
       </c>
       <c r="P43" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="Q43">
         <v>2.63</v>
@@ -10833,7 +10848,7 @@
         <v>96</v>
       </c>
       <c r="P45" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="Q45">
         <v>3.6</v>
@@ -10911,7 +10926,7 @@
         <v>3</v>
       </c>
       <c r="AP45">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ45">
         <v>1.67</v>
@@ -11117,10 +11132,10 @@
         <v>0</v>
       </c>
       <c r="AP46">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ46">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR46">
         <v>1.46</v>
@@ -11245,7 +11260,7 @@
         <v>96</v>
       </c>
       <c r="P47" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="Q47">
         <v>2.05</v>
@@ -11529,7 +11544,7 @@
         <v>0</v>
       </c>
       <c r="AP48">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ48">
         <v>1.29</v>
@@ -11738,7 +11753,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ49">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AR49">
         <v>1.81</v>
@@ -12150,7 +12165,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ51">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="AR51">
         <v>1.47</v>
@@ -12353,10 +12368,10 @@
         <v>0</v>
       </c>
       <c r="AP52">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ52">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR52">
         <v>1.21</v>
@@ -12562,7 +12577,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ53">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR53">
         <v>1.26</v>
@@ -12687,7 +12702,7 @@
         <v>119</v>
       </c>
       <c r="P54" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="Q54">
         <v>3.5</v>
@@ -13305,7 +13320,7 @@
         <v>135</v>
       </c>
       <c r="P57" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="Q57">
         <v>2.2</v>
@@ -13511,7 +13526,7 @@
         <v>136</v>
       </c>
       <c r="P58" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="Q58">
         <v>2.75</v>
@@ -13795,10 +13810,10 @@
         <v>2</v>
       </c>
       <c r="AP59">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ59">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AR59">
         <v>0.65</v>
@@ -13923,7 +13938,7 @@
         <v>96</v>
       </c>
       <c r="P60" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="Q60">
         <v>2.75</v>
@@ -14001,7 +14016,7 @@
         <v>0</v>
       </c>
       <c r="AP60">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ60">
         <v>1.29</v>
@@ -14207,7 +14222,7 @@
         <v>0</v>
       </c>
       <c r="AP61">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AQ61">
         <v>1.54</v>
@@ -14413,7 +14428,7 @@
         <v>1.5</v>
       </c>
       <c r="AP62">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ62">
         <v>1</v>
@@ -14541,7 +14556,7 @@
         <v>96</v>
       </c>
       <c r="P63" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="Q63">
         <v>2.88</v>
@@ -14747,7 +14762,7 @@
         <v>139</v>
       </c>
       <c r="P64" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="Q64">
         <v>2.5</v>
@@ -14825,7 +14840,7 @@
         <v>2</v>
       </c>
       <c r="AP64">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ64">
         <v>1.23</v>
@@ -15240,7 +15255,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ66">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR66">
         <v>1.55</v>
@@ -15365,7 +15380,7 @@
         <v>141</v>
       </c>
       <c r="P67" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -15446,7 +15461,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ67">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="AR67">
         <v>1.39</v>
@@ -15571,7 +15586,7 @@
         <v>142</v>
       </c>
       <c r="P68" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="Q68">
         <v>1.83</v>
@@ -15777,7 +15792,7 @@
         <v>143</v>
       </c>
       <c r="P69" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="Q69">
         <v>3.1</v>
@@ -15855,7 +15870,7 @@
         <v>0.5</v>
       </c>
       <c r="AP69">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ69">
         <v>1.47</v>
@@ -15983,7 +15998,7 @@
         <v>144</v>
       </c>
       <c r="P70" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="Q70">
         <v>4.33</v>
@@ -16189,7 +16204,7 @@
         <v>145</v>
       </c>
       <c r="P71" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="Q71">
         <v>2.4</v>
@@ -16395,7 +16410,7 @@
         <v>146</v>
       </c>
       <c r="P72" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="Q72">
         <v>2.05</v>
@@ -16888,7 +16903,7 @@
         <v>2</v>
       </c>
       <c r="AQ74">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR74">
         <v>1.14</v>
@@ -17013,7 +17028,7 @@
         <v>149</v>
       </c>
       <c r="P75" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="Q75">
         <v>2.3</v>
@@ -17219,7 +17234,7 @@
         <v>96</v>
       </c>
       <c r="P76" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="Q76">
         <v>3.75</v>
@@ -17506,7 +17521,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ77">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR77">
         <v>0.73</v>
@@ -17631,7 +17646,7 @@
         <v>96</v>
       </c>
       <c r="P78" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="Q78">
         <v>2.4</v>
@@ -17837,7 +17852,7 @@
         <v>150</v>
       </c>
       <c r="P79" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="Q79">
         <v>3.15</v>
@@ -17915,10 +17930,10 @@
         <v>3</v>
       </c>
       <c r="AP79">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ79">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR79">
         <v>1.23</v>
@@ -18121,7 +18136,7 @@
         <v>2</v>
       </c>
       <c r="AP80">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AQ80">
         <v>1.62</v>
@@ -18249,7 +18264,7 @@
         <v>96</v>
       </c>
       <c r="P81" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="Q81">
         <v>4.33</v>
@@ -18327,7 +18342,7 @@
         <v>1.5</v>
       </c>
       <c r="AP81">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ81">
         <v>1.43</v>
@@ -18536,7 +18551,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ82">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR82">
         <v>1.22</v>
@@ -19073,7 +19088,7 @@
         <v>96</v>
       </c>
       <c r="P85" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="Q85">
         <v>3.4</v>
@@ -19154,7 +19169,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ85">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR85">
         <v>1.19</v>
@@ -19357,7 +19372,7 @@
         <v>1.33</v>
       </c>
       <c r="AP86">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ86">
         <v>1.23</v>
@@ -19485,7 +19500,7 @@
         <v>153</v>
       </c>
       <c r="P87" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="Q87">
         <v>3.4</v>
@@ -19563,7 +19578,7 @@
         <v>1.33</v>
       </c>
       <c r="AP87">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ87">
         <v>2.07</v>
@@ -19769,7 +19784,7 @@
         <v>1</v>
       </c>
       <c r="AP88">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ88">
         <v>0.93</v>
@@ -19897,7 +19912,7 @@
         <v>155</v>
       </c>
       <c r="P89" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="Q89">
         <v>2.05</v>
@@ -19975,10 +19990,10 @@
         <v>2.33</v>
       </c>
       <c r="AP89">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ89">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR89">
         <v>1.7</v>
@@ -20103,7 +20118,7 @@
         <v>96</v>
       </c>
       <c r="P90" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="Q90">
         <v>4</v>
@@ -20309,7 +20324,7 @@
         <v>119</v>
       </c>
       <c r="P91" t="s">
-        <v>352</v>
+        <v>314</v>
       </c>
       <c r="Q91">
         <v>2.88</v>
@@ -20390,7 +20405,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ91">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AR91">
         <v>1.71</v>
@@ -20515,7 +20530,7 @@
         <v>156</v>
       </c>
       <c r="P92" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="Q92">
         <v>4.75</v>
@@ -20802,7 +20817,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ93">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR93">
         <v>0.93</v>
@@ -21133,7 +21148,7 @@
         <v>96</v>
       </c>
       <c r="P95" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="Q95">
         <v>4.5</v>
@@ -21214,7 +21229,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ95">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AR95">
         <v>1.05</v>
@@ -21417,7 +21432,7 @@
         <v>1</v>
       </c>
       <c r="AP96">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ96">
         <v>1</v>
@@ -21545,7 +21560,7 @@
         <v>96</v>
       </c>
       <c r="P97" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="Q97">
         <v>3.2</v>
@@ -21623,10 +21638,10 @@
         <v>2</v>
       </c>
       <c r="AP97">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ97">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR97">
         <v>0.86</v>
@@ -21832,7 +21847,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ98">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR98">
         <v>1.36</v>
@@ -21957,7 +21972,7 @@
         <v>159</v>
       </c>
       <c r="P99" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="Q99">
         <v>3.6</v>
@@ -22035,7 +22050,7 @@
         <v>1.5</v>
       </c>
       <c r="AP99">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ99">
         <v>1.29</v>
@@ -22163,7 +22178,7 @@
         <v>160</v>
       </c>
       <c r="P100" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="Q100">
         <v>2.5</v>
@@ -22241,7 +22256,7 @@
         <v>2.5</v>
       </c>
       <c r="AP100">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ100">
         <v>1.2</v>
@@ -22447,7 +22462,7 @@
         <v>1.5</v>
       </c>
       <c r="AP101">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ101">
         <v>1.62</v>
@@ -22575,7 +22590,7 @@
         <v>162</v>
       </c>
       <c r="P102" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="Q102">
         <v>2.75</v>
@@ -22859,7 +22874,7 @@
         <v>0.75</v>
       </c>
       <c r="AP103">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AQ103">
         <v>0.93</v>
@@ -22987,7 +23002,7 @@
         <v>164</v>
       </c>
       <c r="P104" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="Q104">
         <v>2.63</v>
@@ -23068,7 +23083,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ104">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR104">
         <v>1.16</v>
@@ -24098,7 +24113,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ109">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR109">
         <v>1.44</v>
@@ -24429,7 +24444,7 @@
         <v>170</v>
       </c>
       <c r="P111" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="Q111">
         <v>3</v>
@@ -24635,7 +24650,7 @@
         <v>171</v>
       </c>
       <c r="P112" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="Q112">
         <v>1.91</v>
@@ -24716,7 +24731,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ112">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="AR112">
         <v>1.46</v>
@@ -25125,7 +25140,7 @@
         <v>3</v>
       </c>
       <c r="AP114">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ114">
         <v>2.14</v>
@@ -25459,7 +25474,7 @@
         <v>174</v>
       </c>
       <c r="P116" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="Q116">
         <v>3</v>
@@ -25540,7 +25555,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ116">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR116">
         <v>1.13</v>
@@ -25665,7 +25680,7 @@
         <v>175</v>
       </c>
       <c r="P117" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25743,10 +25758,10 @@
         <v>0.2</v>
       </c>
       <c r="AP117">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ117">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="AR117">
         <v>0.93</v>
@@ -25871,7 +25886,7 @@
         <v>96</v>
       </c>
       <c r="P118" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="Q118">
         <v>3.4</v>
@@ -26155,7 +26170,7 @@
         <v>0.75</v>
       </c>
       <c r="AP119">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AQ119">
         <v>0.75</v>
@@ -26364,7 +26379,7 @@
         <v>2</v>
       </c>
       <c r="AQ120">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR120">
         <v>1.35</v>
@@ -26570,7 +26585,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ121">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR121">
         <v>1.32</v>
@@ -26695,7 +26710,7 @@
         <v>178</v>
       </c>
       <c r="P122" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="Q122">
         <v>4.5</v>
@@ -26901,7 +26916,7 @@
         <v>179</v>
       </c>
       <c r="P123" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="Q123">
         <v>2</v>
@@ -27107,7 +27122,7 @@
         <v>180</v>
       </c>
       <c r="P124" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="Q124">
         <v>3.2</v>
@@ -27185,10 +27200,10 @@
         <v>1.8</v>
       </c>
       <c r="AP124">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ124">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AR124">
         <v>1.2</v>
@@ -27931,7 +27946,7 @@
         <v>137</v>
       </c>
       <c r="P128" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="Q128">
         <v>2.6</v>
@@ -28009,7 +28024,7 @@
         <v>1.8</v>
       </c>
       <c r="AP128">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ128">
         <v>1.67</v>
@@ -28421,10 +28436,10 @@
         <v>1</v>
       </c>
       <c r="AP130">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ130">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR130">
         <v>1.33</v>
@@ -28549,7 +28564,7 @@
         <v>184</v>
       </c>
       <c r="P131" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="Q131">
         <v>4.5</v>
@@ -28833,10 +28848,10 @@
         <v>0.67</v>
       </c>
       <c r="AP132">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ132">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="AR132">
         <v>1.15</v>
@@ -29039,7 +29054,7 @@
         <v>2.25</v>
       </c>
       <c r="AP133">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ133">
         <v>1.43</v>
@@ -29373,7 +29388,7 @@
         <v>96</v>
       </c>
       <c r="P135" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="Q135">
         <v>2.3</v>
@@ -29454,7 +29469,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ135">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR135">
         <v>1.1</v>
@@ -29579,7 +29594,7 @@
         <v>188</v>
       </c>
       <c r="P136" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="Q136">
         <v>2.88</v>
@@ -29991,7 +30006,7 @@
         <v>189</v>
       </c>
       <c r="P138" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="Q138">
         <v>3</v>
@@ -30072,7 +30087,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ138">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR138">
         <v>0.95</v>
@@ -30403,7 +30418,7 @@
         <v>99</v>
       </c>
       <c r="P140" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="Q140">
         <v>3.1</v>
@@ -30687,7 +30702,7 @@
         <v>2.2</v>
       </c>
       <c r="AP141">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ141">
         <v>1.2</v>
@@ -31099,7 +31114,7 @@
         <v>0.67</v>
       </c>
       <c r="AP143">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AQ143">
         <v>0.67</v>
@@ -31227,7 +31242,7 @@
         <v>191</v>
       </c>
       <c r="P144" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="Q144">
         <v>3.25</v>
@@ -31305,7 +31320,7 @@
         <v>1.33</v>
       </c>
       <c r="AP144">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ144">
         <v>1.23</v>
@@ -31720,7 +31735,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ146">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AR146">
         <v>1.33</v>
@@ -32132,7 +32147,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ148">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR148">
         <v>1.62</v>
@@ -32257,7 +32272,7 @@
         <v>96</v>
       </c>
       <c r="P149" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="Q149">
         <v>4</v>
@@ -32956,7 +32971,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ152">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR152">
         <v>1.5</v>
@@ -33081,7 +33096,7 @@
         <v>199</v>
       </c>
       <c r="P153" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="Q153">
         <v>2.38</v>
@@ -33159,7 +33174,7 @@
         <v>0.83</v>
       </c>
       <c r="AP153">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ153">
         <v>1.29</v>
@@ -33493,7 +33508,7 @@
         <v>201</v>
       </c>
       <c r="P155" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="Q155">
         <v>2.5</v>
@@ -33699,7 +33714,7 @@
         <v>109</v>
       </c>
       <c r="P156" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="Q156">
         <v>3.5</v>
@@ -34111,7 +34126,7 @@
         <v>96</v>
       </c>
       <c r="P158" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="Q158">
         <v>2.75</v>
@@ -34398,7 +34413,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ159">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR159">
         <v>1.65</v>
@@ -34604,7 +34619,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ160">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR160">
         <v>1.49</v>
@@ -34810,7 +34825,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="AQ161">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="AR161">
         <v>1.04</v>
@@ -34935,7 +34950,7 @@
         <v>205</v>
       </c>
       <c r="P162" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="Q162">
         <v>3.6</v>
@@ -35013,7 +35028,7 @@
         <v>1.83</v>
       </c>
       <c r="AP162">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ162">
         <v>1.2</v>
@@ -35219,7 +35234,7 @@
         <v>0.83</v>
       </c>
       <c r="AP163">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ163">
         <v>0.88</v>
@@ -35347,7 +35362,7 @@
         <v>96</v>
       </c>
       <c r="P164" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="Q164">
         <v>3.25</v>
@@ -35840,7 +35855,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ166">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR166">
         <v>1.2</v>
@@ -36043,7 +36058,7 @@
         <v>1.17</v>
       </c>
       <c r="AP167">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ167">
         <v>1.47</v>
@@ -36583,7 +36598,7 @@
         <v>211</v>
       </c>
       <c r="P170" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="Q170">
         <v>4.33</v>
@@ -36661,7 +36676,7 @@
         <v>1.17</v>
       </c>
       <c r="AP170">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ170">
         <v>1.62</v>
@@ -37073,7 +37088,7 @@
         <v>0.86</v>
       </c>
       <c r="AP172">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ172">
         <v>0.88</v>
@@ -37279,7 +37294,7 @@
         <v>0.57</v>
       </c>
       <c r="AP173">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ173">
         <v>0.75</v>
@@ -38025,7 +38040,7 @@
         <v>214</v>
       </c>
       <c r="P177" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="Q177">
         <v>7.5</v>
@@ -38515,10 +38530,10 @@
         <v>0.75</v>
       </c>
       <c r="AP179">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ179">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR179">
         <v>0.97</v>
@@ -38849,7 +38864,7 @@
         <v>216</v>
       </c>
       <c r="P181" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="Q181">
         <v>3.4</v>
@@ -39055,7 +39070,7 @@
         <v>96</v>
       </c>
       <c r="P182" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="Q182">
         <v>2.3</v>
@@ -39342,7 +39357,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ183">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR183">
         <v>1.26</v>
@@ -39673,7 +39688,7 @@
         <v>96</v>
       </c>
       <c r="P185" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="Q185">
         <v>2.6</v>
@@ -39879,7 +39894,7 @@
         <v>96</v>
       </c>
       <c r="P186" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="Q186">
         <v>4.33</v>
@@ -39960,7 +39975,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="AQ186">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AR186">
         <v>1.08</v>
@@ -40085,7 +40100,7 @@
         <v>143</v>
       </c>
       <c r="P187" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="Q187">
         <v>2.4</v>
@@ -40291,7 +40306,7 @@
         <v>218</v>
       </c>
       <c r="P188" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="Q188">
         <v>2.4</v>
@@ -40703,7 +40718,7 @@
         <v>96</v>
       </c>
       <c r="P190" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="Q190">
         <v>3.75</v>
@@ -40781,7 +40796,7 @@
         <v>0.88</v>
       </c>
       <c r="AP190">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ190">
         <v>1.47</v>
@@ -40909,7 +40924,7 @@
         <v>96</v>
       </c>
       <c r="P191" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="Q191">
         <v>3.5</v>
@@ -40987,7 +41002,7 @@
         <v>1.14</v>
       </c>
       <c r="AP191">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ191">
         <v>1.62</v>
@@ -41321,7 +41336,7 @@
         <v>96</v>
       </c>
       <c r="P193" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="Q193">
         <v>5.5</v>
@@ -41608,7 +41623,7 @@
         <v>2</v>
       </c>
       <c r="AQ194">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR194">
         <v>1.45</v>
@@ -41733,7 +41748,7 @@
         <v>221</v>
       </c>
       <c r="P195" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="Q195">
         <v>2.4</v>
@@ -42223,7 +42238,7 @@
         <v>0.88</v>
       </c>
       <c r="AP197">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ197">
         <v>0.67</v>
@@ -42351,7 +42366,7 @@
         <v>137</v>
       </c>
       <c r="P198" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="Q198">
         <v>2.25</v>
@@ -42429,7 +42444,7 @@
         <v>0.63</v>
       </c>
       <c r="AP198">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ198">
         <v>0.75</v>
@@ -42638,7 +42653,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ199">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR199">
         <v>1.67</v>
@@ -42969,7 +42984,7 @@
         <v>224</v>
       </c>
       <c r="P201" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="Q201">
         <v>4</v>
@@ -43665,10 +43680,10 @@
         <v>0.5</v>
       </c>
       <c r="AP204">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AQ204">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR204">
         <v>1.32</v>
@@ -43999,7 +44014,7 @@
         <v>119</v>
       </c>
       <c r="P206" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="Q206">
         <v>4</v>
@@ -44283,10 +44298,10 @@
         <v>1.63</v>
       </c>
       <c r="AP207">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ207">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AR207">
         <v>1.67</v>
@@ -44411,7 +44426,7 @@
         <v>96</v>
       </c>
       <c r="P208" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="Q208">
         <v>2.05</v>
@@ -44823,7 +44838,7 @@
         <v>96</v>
       </c>
       <c r="P210" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="Q210">
         <v>3.1</v>
@@ -45029,7 +45044,7 @@
         <v>99</v>
       </c>
       <c r="P211" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="Q211">
         <v>4.33</v>
@@ -45522,7 +45537,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ213">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="AR213">
         <v>1.31</v>
@@ -45647,7 +45662,7 @@
         <v>230</v>
       </c>
       <c r="P214" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="Q214">
         <v>3.75</v>
@@ -46265,7 +46280,7 @@
         <v>233</v>
       </c>
       <c r="P217" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="Q217">
         <v>3.75</v>
@@ -46346,7 +46361,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ217">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR217">
         <v>1.24</v>
@@ -46549,7 +46564,7 @@
         <v>0.75</v>
       </c>
       <c r="AP218">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ218">
         <v>0.93</v>
@@ -46677,7 +46692,7 @@
         <v>96</v>
       </c>
       <c r="P219" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="Q219">
         <v>2.3</v>
@@ -46883,7 +46898,7 @@
         <v>234</v>
       </c>
       <c r="P220" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="Q220">
         <v>2.1</v>
@@ -47089,7 +47104,7 @@
         <v>96</v>
       </c>
       <c r="P221" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="Q221">
         <v>2.88</v>
@@ -47167,7 +47182,7 @@
         <v>1.3</v>
       </c>
       <c r="AP221">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AQ221">
         <v>1.47</v>
@@ -47373,10 +47388,10 @@
         <v>1.5</v>
       </c>
       <c r="AP222">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ222">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR222">
         <v>1.36</v>
@@ -47707,7 +47722,7 @@
         <v>132</v>
       </c>
       <c r="P224" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="Q224">
         <v>5</v>
@@ -47994,7 +48009,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ225">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AR225">
         <v>1.15</v>
@@ -48119,7 +48134,7 @@
         <v>237</v>
       </c>
       <c r="P226" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="Q226">
         <v>2.2</v>
@@ -48200,7 +48215,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ226">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR226">
         <v>1.41</v>
@@ -48403,7 +48418,7 @@
         <v>0.78</v>
       </c>
       <c r="AP227">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ227">
         <v>0.67</v>
@@ -48531,7 +48546,7 @@
         <v>239</v>
       </c>
       <c r="P228" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="Q228">
         <v>2.5</v>
@@ -48737,7 +48752,7 @@
         <v>240</v>
       </c>
       <c r="P229" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="Q229">
         <v>3.75</v>
@@ -49230,7 +49245,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ231">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR231">
         <v>1.64</v>
@@ -49355,7 +49370,7 @@
         <v>96</v>
       </c>
       <c r="P232" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="Q232">
         <v>4.5</v>
@@ -49845,7 +49860,7 @@
         <v>1.33</v>
       </c>
       <c r="AP234">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ234">
         <v>1.23</v>
@@ -49973,7 +49988,7 @@
         <v>244</v>
       </c>
       <c r="P235" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="Q235">
         <v>3.5</v>
@@ -50257,10 +50272,10 @@
         <v>0.71</v>
       </c>
       <c r="AP236">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ236">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR236">
         <v>1.6</v>
@@ -50385,7 +50400,7 @@
         <v>96</v>
       </c>
       <c r="P237" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="Q237">
         <v>2.6</v>
@@ -50591,7 +50606,7 @@
         <v>245</v>
       </c>
       <c r="P238" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="Q238">
         <v>2.38</v>
@@ -50672,7 +50687,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ238">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="AR238">
         <v>1.17</v>
@@ -50797,7 +50812,7 @@
         <v>96</v>
       </c>
       <c r="P239" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="Q239">
         <v>4</v>
@@ -51084,7 +51099,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ240">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR240">
         <v>1.39</v>
@@ -51209,7 +51224,7 @@
         <v>96</v>
       </c>
       <c r="P241" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="Q241">
         <v>6.5</v>
@@ -51287,7 +51302,7 @@
         <v>2.11</v>
       </c>
       <c r="AP241">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ241">
         <v>2.14</v>
@@ -51493,7 +51508,7 @@
         <v>0.8</v>
       </c>
       <c r="AP242">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ242">
         <v>0.75</v>
@@ -51699,7 +51714,7 @@
         <v>0.78</v>
       </c>
       <c r="AP243">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ243">
         <v>0.93</v>
@@ -51827,7 +51842,7 @@
         <v>249</v>
       </c>
       <c r="P244" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="Q244">
         <v>2.6</v>
@@ -52033,7 +52048,7 @@
         <v>250</v>
       </c>
       <c r="P245" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="Q245">
         <v>2.4</v>
@@ -52111,10 +52126,10 @@
         <v>0.5</v>
       </c>
       <c r="AP245">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ245">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR245">
         <v>1.31</v>
@@ -52526,7 +52541,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ247">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AR247">
         <v>1.39</v>
@@ -52651,7 +52666,7 @@
         <v>96</v>
       </c>
       <c r="P248" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="Q248">
         <v>2.75</v>
@@ -52732,7 +52747,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ248">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR248">
         <v>1.32</v>
@@ -52857,7 +52872,7 @@
         <v>252</v>
       </c>
       <c r="P249" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="Q249">
         <v>2.2</v>
@@ -52935,7 +52950,7 @@
         <v>0.64</v>
       </c>
       <c r="AP249">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AQ249">
         <v>0.88</v>
@@ -53063,7 +53078,7 @@
         <v>253</v>
       </c>
       <c r="P250" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="Q250">
         <v>2.5</v>
@@ -53269,7 +53284,7 @@
         <v>96</v>
       </c>
       <c r="P251" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="Q251">
         <v>3.75</v>
@@ -53475,7 +53490,7 @@
         <v>96</v>
       </c>
       <c r="P252" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="Q252">
         <v>2.75</v>
@@ -53968,7 +53983,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ254">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AR254">
         <v>1.52</v>
@@ -54171,7 +54186,7 @@
         <v>2.25</v>
       </c>
       <c r="AP255">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ255">
         <v>2.07</v>
@@ -54299,7 +54314,7 @@
         <v>257</v>
       </c>
       <c r="P256" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="Q256">
         <v>2.75</v>
@@ -54377,10 +54392,10 @@
         <v>1.6</v>
       </c>
       <c r="AP256">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AQ256">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR256">
         <v>1.34</v>
@@ -54505,7 +54520,7 @@
         <v>160</v>
       </c>
       <c r="P257" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="Q257">
         <v>3.1</v>
@@ -54789,10 +54804,10 @@
         <v>0.45</v>
       </c>
       <c r="AP258">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ258">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR258">
         <v>1.51</v>
@@ -55123,7 +55138,7 @@
         <v>259</v>
       </c>
       <c r="P260" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="Q260">
         <v>2.5</v>
@@ -55613,7 +55628,7 @@
         <v>1.33</v>
       </c>
       <c r="AP262">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ262">
         <v>1.47</v>
@@ -56153,7 +56168,7 @@
         <v>263</v>
       </c>
       <c r="P265" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="Q265">
         <v>2.38</v>
@@ -56359,7 +56374,7 @@
         <v>264</v>
       </c>
       <c r="P266" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="Q266">
         <v>3.75</v>
@@ -56852,7 +56867,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ268">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR268">
         <v>1.19</v>
@@ -57261,10 +57276,10 @@
         <v>0.5</v>
       </c>
       <c r="AP270">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ270">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="AR270">
         <v>1.54</v>
@@ -57389,7 +57404,7 @@
         <v>268</v>
       </c>
       <c r="P271" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="Q271">
         <v>3.75</v>
@@ -57467,7 +57482,7 @@
         <v>1.3</v>
       </c>
       <c r="AP271">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ271">
         <v>1.54</v>
@@ -57595,7 +57610,7 @@
         <v>96</v>
       </c>
       <c r="P272" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="Q272">
         <v>2.63</v>
@@ -57676,7 +57691,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ272">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR272">
         <v>1.38</v>
@@ -57801,7 +57816,7 @@
         <v>183</v>
       </c>
       <c r="P273" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="Q273">
         <v>3.25</v>
@@ -58007,7 +58022,7 @@
         <v>269</v>
       </c>
       <c r="P274" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="Q274">
         <v>3.2</v>
@@ -58088,7 +58103,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="AQ274">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR274">
         <v>1</v>
@@ -59118,7 +59133,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ279">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR279">
         <v>1.38</v>
@@ -59243,7 +59258,7 @@
         <v>96</v>
       </c>
       <c r="P280" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="Q280">
         <v>5.5</v>
@@ -59449,7 +59464,7 @@
         <v>118</v>
       </c>
       <c r="P281" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="Q281">
         <v>2.6</v>
@@ -59530,7 +59545,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ281">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR281">
         <v>1.62</v>
@@ -59736,7 +59751,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ282">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR282">
         <v>1.32</v>
@@ -59939,10 +59954,10 @@
         <v>0.55</v>
       </c>
       <c r="AP283">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ283">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="AR283">
         <v>1.5</v>
@@ -60148,7 +60163,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ284">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR284">
         <v>1.41</v>
@@ -60351,7 +60366,7 @@
         <v>1.08</v>
       </c>
       <c r="AP285">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ285">
         <v>0.9399999999999999</v>
@@ -60685,7 +60700,7 @@
         <v>172</v>
       </c>
       <c r="P287" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="Q287">
         <v>3.6</v>
@@ -61509,7 +61524,7 @@
         <v>275</v>
       </c>
       <c r="P291" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="Q291">
         <v>3.4</v>
@@ -61587,7 +61602,7 @@
         <v>1.82</v>
       </c>
       <c r="AP291">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ291">
         <v>1.62</v>
@@ -62205,7 +62220,7 @@
         <v>2.08</v>
       </c>
       <c r="AP294">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ294">
         <v>1.67</v>
@@ -62333,7 +62348,7 @@
         <v>132</v>
       </c>
       <c r="P295" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="Q295">
         <v>2.75</v>
@@ -62411,7 +62426,7 @@
         <v>0.73</v>
       </c>
       <c r="AP295">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ295">
         <v>0.93</v>
@@ -62539,7 +62554,7 @@
         <v>137</v>
       </c>
       <c r="P296" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="Q296">
         <v>3.25</v>
@@ -62823,7 +62838,7 @@
         <v>1.18</v>
       </c>
       <c r="AP297">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ297">
         <v>1</v>
@@ -62951,7 +62966,7 @@
         <v>278</v>
       </c>
       <c r="P298" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="Q298">
         <v>3.2</v>
@@ -63157,7 +63172,7 @@
         <v>279</v>
       </c>
       <c r="P299" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="Q299">
         <v>3.25</v>
@@ -63363,7 +63378,7 @@
         <v>267</v>
       </c>
       <c r="P300" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="Q300">
         <v>3.6</v>
@@ -63441,10 +63456,10 @@
         <v>1.17</v>
       </c>
       <c r="AP300">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AQ300">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AR300">
         <v>1.33</v>
@@ -63569,7 +63584,7 @@
         <v>280</v>
       </c>
       <c r="P301" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="Q301">
         <v>2</v>
@@ -63650,7 +63665,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ301">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR301">
         <v>1.64</v>
@@ -63775,7 +63790,7 @@
         <v>281</v>
       </c>
       <c r="P302" t="s">
-        <v>352</v>
+        <v>314</v>
       </c>
       <c r="Q302">
         <v>2.63</v>
@@ -63981,7 +63996,7 @@
         <v>282</v>
       </c>
       <c r="P303" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="Q303">
         <v>2.88</v>
@@ -64187,7 +64202,7 @@
         <v>94</v>
       </c>
       <c r="P304" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="Q304">
         <v>2.25</v>
@@ -64805,7 +64820,7 @@
         <v>283</v>
       </c>
       <c r="P307" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="Q307">
         <v>4</v>
@@ -64886,7 +64901,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ307">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR307">
         <v>1.4</v>
@@ -65092,7 +65107,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ308">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR308">
         <v>1.62</v>
@@ -65217,7 +65232,7 @@
         <v>284</v>
       </c>
       <c r="P309" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="Q309">
         <v>4.33</v>
@@ -65298,7 +65313,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="AQ309">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR309">
         <v>1</v>
@@ -65707,7 +65722,7 @@
         <v>1.08</v>
       </c>
       <c r="AP311">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ311">
         <v>0.9399999999999999</v>
@@ -65916,7 +65931,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ312">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR312">
         <v>1.29</v>
@@ -66453,7 +66468,7 @@
         <v>289</v>
       </c>
       <c r="P315" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="Q315">
         <v>3.25</v>
@@ -66737,10 +66752,10 @@
         <v>0.5</v>
       </c>
       <c r="AP316">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ316">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="AR316">
         <v>1.34</v>
@@ -67071,7 +67086,7 @@
         <v>291</v>
       </c>
       <c r="P318" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="Q318">
         <v>3.25</v>
@@ -67355,7 +67370,7 @@
         <v>0.71</v>
       </c>
       <c r="AP319">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ319">
         <v>0.67</v>
@@ -67483,7 +67498,7 @@
         <v>293</v>
       </c>
       <c r="P320" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="Q320">
         <v>3.75</v>
@@ -67689,7 +67704,7 @@
         <v>96</v>
       </c>
       <c r="P321" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="Q321">
         <v>3</v>
@@ -68101,7 +68116,7 @@
         <v>294</v>
       </c>
       <c r="P323" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="Q323">
         <v>2.38</v>
@@ -68182,7 +68197,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ323">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR323">
         <v>1.6</v>
@@ -68388,7 +68403,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ324">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="AR324">
         <v>1.62</v>
@@ -68513,7 +68528,7 @@
         <v>296</v>
       </c>
       <c r="P325" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="Q325">
         <v>2.88</v>
@@ -68594,7 +68609,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ325">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR325">
         <v>1.42</v>
@@ -68925,7 +68940,7 @@
         <v>96</v>
       </c>
       <c r="P327" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="Q327">
         <v>2.1</v>
@@ -69131,7 +69146,7 @@
         <v>96</v>
       </c>
       <c r="P328" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="Q328">
         <v>3.5</v>
@@ -69337,7 +69352,7 @@
         <v>298</v>
       </c>
       <c r="P329" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="Q329">
         <v>2.6</v>
@@ -69749,7 +69764,7 @@
         <v>299</v>
       </c>
       <c r="P331" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="Q331">
         <v>2.1</v>
@@ -69827,10 +69842,10 @@
         <v>0.77</v>
       </c>
       <c r="AP331">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ331">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AR331">
         <v>1.62</v>
@@ -70161,7 +70176,7 @@
         <v>301</v>
       </c>
       <c r="P333" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="Q333">
         <v>3.75</v>
@@ -70242,7 +70257,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ333">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR333">
         <v>1.04</v>
@@ -70445,7 +70460,7 @@
         <v>1.54</v>
       </c>
       <c r="AP334">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AQ334">
         <v>1.43</v>
@@ -70573,7 +70588,7 @@
         <v>302</v>
       </c>
       <c r="P335" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="Q335">
         <v>4.75</v>
@@ -70857,10 +70872,10 @@
         <v>1.31</v>
       </c>
       <c r="AP336">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ336">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AR336">
         <v>1.52</v>
@@ -70985,7 +71000,7 @@
         <v>303</v>
       </c>
       <c r="P337" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="Q337">
         <v>4.33</v>
@@ -71063,7 +71078,7 @@
         <v>1.08</v>
       </c>
       <c r="AP337">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AQ337">
         <v>1.23</v>
@@ -71397,7 +71412,7 @@
         <v>304</v>
       </c>
       <c r="P339" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="Q339">
         <v>2.88</v>
@@ -71475,7 +71490,7 @@
         <v>1.31</v>
       </c>
       <c r="AP339">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ339">
         <v>1.29</v>
@@ -71603,7 +71618,7 @@
         <v>305</v>
       </c>
       <c r="P340" t="s">
-        <v>352</v>
+        <v>314</v>
       </c>
       <c r="Q340">
         <v>3.4</v>
@@ -71681,10 +71696,10 @@
         <v>0.67</v>
       </c>
       <c r="AP340">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ340">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR340">
         <v>1.1</v>
@@ -72093,10 +72108,10 @@
         <v>1.17</v>
       </c>
       <c r="AP342">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ342">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR342">
         <v>1.41</v>
@@ -72427,7 +72442,7 @@
         <v>153</v>
       </c>
       <c r="P344" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="Q344">
         <v>2.38</v>
@@ -72508,7 +72523,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ344">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR344">
         <v>1.38</v>
@@ -72839,7 +72854,7 @@
         <v>308</v>
       </c>
       <c r="P346" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="Q346">
         <v>1.91</v>
@@ -73045,7 +73060,7 @@
         <v>255</v>
       </c>
       <c r="P347" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="Q347">
         <v>4</v>
@@ -73251,7 +73266,7 @@
         <v>309</v>
       </c>
       <c r="P348" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="Q348">
         <v>2.3</v>
@@ -73332,7 +73347,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ348">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="AR348">
         <v>1.63</v>
@@ -73408,6 +73423,1448 @@
       </c>
       <c r="BP348">
         <v>1.42</v>
+      </c>
+    </row>
+    <row r="349" spans="1:68">
+      <c r="A349" s="1">
+        <v>348</v>
+      </c>
+      <c r="B349">
+        <v>7727036</v>
+      </c>
+      <c r="C349" t="s">
+        <v>68</v>
+      </c>
+      <c r="D349" t="s">
+        <v>69</v>
+      </c>
+      <c r="E349" s="2">
+        <v>45699.69791666666</v>
+      </c>
+      <c r="F349">
+        <v>16</v>
+      </c>
+      <c r="G349" t="s">
+        <v>83</v>
+      </c>
+      <c r="H349" t="s">
+        <v>74</v>
+      </c>
+      <c r="I349">
+        <v>0</v>
+      </c>
+      <c r="J349">
+        <v>0</v>
+      </c>
+      <c r="K349">
+        <v>0</v>
+      </c>
+      <c r="L349">
+        <v>2</v>
+      </c>
+      <c r="M349">
+        <v>1</v>
+      </c>
+      <c r="N349">
+        <v>3</v>
+      </c>
+      <c r="O349" t="s">
+        <v>310</v>
+      </c>
+      <c r="P349" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q349">
+        <v>2.63</v>
+      </c>
+      <c r="R349">
+        <v>2.38</v>
+      </c>
+      <c r="S349">
+        <v>3.5</v>
+      </c>
+      <c r="T349">
+        <v>1.29</v>
+      </c>
+      <c r="U349">
+        <v>3.5</v>
+      </c>
+      <c r="V349">
+        <v>2.38</v>
+      </c>
+      <c r="W349">
+        <v>1.53</v>
+      </c>
+      <c r="X349">
+        <v>5.5</v>
+      </c>
+      <c r="Y349">
+        <v>1.14</v>
+      </c>
+      <c r="Z349">
+        <v>1.91</v>
+      </c>
+      <c r="AA349">
+        <v>3.61</v>
+      </c>
+      <c r="AB349">
+        <v>3.73</v>
+      </c>
+      <c r="AC349">
+        <v>1.02</v>
+      </c>
+      <c r="AD349">
+        <v>17</v>
+      </c>
+      <c r="AE349">
+        <v>1.18</v>
+      </c>
+      <c r="AF349">
+        <v>4.83</v>
+      </c>
+      <c r="AG349">
+        <v>1.73</v>
+      </c>
+      <c r="AH349">
+        <v>2</v>
+      </c>
+      <c r="AI349">
+        <v>1.5</v>
+      </c>
+      <c r="AJ349">
+        <v>2.5</v>
+      </c>
+      <c r="AK349">
+        <v>1.35</v>
+      </c>
+      <c r="AL349">
+        <v>1.22</v>
+      </c>
+      <c r="AM349">
+        <v>1.67</v>
+      </c>
+      <c r="AN349">
+        <v>1.93</v>
+      </c>
+      <c r="AO349">
+        <v>0.62</v>
+      </c>
+      <c r="AP349">
+        <v>2</v>
+      </c>
+      <c r="AQ349">
+        <v>0.57</v>
+      </c>
+      <c r="AR349">
+        <v>1.44</v>
+      </c>
+      <c r="AS349">
+        <v>1.24</v>
+      </c>
+      <c r="AT349">
+        <v>2.68</v>
+      </c>
+      <c r="AU349">
+        <v>10</v>
+      </c>
+      <c r="AV349">
+        <v>4</v>
+      </c>
+      <c r="AW349">
+        <v>13</v>
+      </c>
+      <c r="AX349">
+        <v>2</v>
+      </c>
+      <c r="AY349">
+        <v>29</v>
+      </c>
+      <c r="AZ349">
+        <v>6</v>
+      </c>
+      <c r="BA349">
+        <v>8</v>
+      </c>
+      <c r="BB349">
+        <v>0</v>
+      </c>
+      <c r="BC349">
+        <v>8</v>
+      </c>
+      <c r="BD349">
+        <v>1.77</v>
+      </c>
+      <c r="BE349">
+        <v>6.4</v>
+      </c>
+      <c r="BF349">
+        <v>2.12</v>
+      </c>
+      <c r="BG349">
+        <v>1.24</v>
+      </c>
+      <c r="BH349">
+        <v>3.55</v>
+      </c>
+      <c r="BI349">
+        <v>1.43</v>
+      </c>
+      <c r="BJ349">
+        <v>2.55</v>
+      </c>
+      <c r="BK349">
+        <v>1.71</v>
+      </c>
+      <c r="BL349">
+        <v>2</v>
+      </c>
+      <c r="BM349">
+        <v>2.1</v>
+      </c>
+      <c r="BN349">
+        <v>1.64</v>
+      </c>
+      <c r="BO349">
+        <v>2.65</v>
+      </c>
+      <c r="BP349">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="350" spans="1:68">
+      <c r="A350" s="1">
+        <v>349</v>
+      </c>
+      <c r="B350">
+        <v>7727068</v>
+      </c>
+      <c r="C350" t="s">
+        <v>68</v>
+      </c>
+      <c r="D350" t="s">
+        <v>69</v>
+      </c>
+      <c r="E350" s="2">
+        <v>45699.69791666666</v>
+      </c>
+      <c r="F350">
+        <v>19</v>
+      </c>
+      <c r="G350" t="s">
+        <v>91</v>
+      </c>
+      <c r="H350" t="s">
+        <v>85</v>
+      </c>
+      <c r="I350">
+        <v>0</v>
+      </c>
+      <c r="J350">
+        <v>0</v>
+      </c>
+      <c r="K350">
+        <v>0</v>
+      </c>
+      <c r="L350">
+        <v>0</v>
+      </c>
+      <c r="M350">
+        <v>0</v>
+      </c>
+      <c r="N350">
+        <v>0</v>
+      </c>
+      <c r="O350" t="s">
+        <v>96</v>
+      </c>
+      <c r="P350" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q350">
+        <v>2.75</v>
+      </c>
+      <c r="R350">
+        <v>2.2</v>
+      </c>
+      <c r="S350">
+        <v>3.75</v>
+      </c>
+      <c r="T350">
+        <v>1.4</v>
+      </c>
+      <c r="U350">
+        <v>2.75</v>
+      </c>
+      <c r="V350">
+        <v>2.75</v>
+      </c>
+      <c r="W350">
+        <v>1.4</v>
+      </c>
+      <c r="X350">
+        <v>8</v>
+      </c>
+      <c r="Y350">
+        <v>1.08</v>
+      </c>
+      <c r="Z350">
+        <v>2.09</v>
+      </c>
+      <c r="AA350">
+        <v>3.47</v>
+      </c>
+      <c r="AB350">
+        <v>3.28</v>
+      </c>
+      <c r="AC350">
+        <v>1.05</v>
+      </c>
+      <c r="AD350">
+        <v>9</v>
+      </c>
+      <c r="AE350">
+        <v>1.3</v>
+      </c>
+      <c r="AF350">
+        <v>3.45</v>
+      </c>
+      <c r="AG350">
+        <v>1.98</v>
+      </c>
+      <c r="AH350">
+        <v>1.77</v>
+      </c>
+      <c r="AI350">
+        <v>1.7</v>
+      </c>
+      <c r="AJ350">
+        <v>2.05</v>
+      </c>
+      <c r="AK350">
+        <v>1.3</v>
+      </c>
+      <c r="AL350">
+        <v>1.25</v>
+      </c>
+      <c r="AM350">
+        <v>1.7</v>
+      </c>
+      <c r="AN350">
+        <v>1.17</v>
+      </c>
+      <c r="AO350">
+        <v>0.71</v>
+      </c>
+      <c r="AP350">
+        <v>1.15</v>
+      </c>
+      <c r="AQ350">
+        <v>0.73</v>
+      </c>
+      <c r="AR350">
+        <v>1.57</v>
+      </c>
+      <c r="AS350">
+        <v>1.29</v>
+      </c>
+      <c r="AT350">
+        <v>2.86</v>
+      </c>
+      <c r="AU350">
+        <v>3</v>
+      </c>
+      <c r="AV350">
+        <v>9</v>
+      </c>
+      <c r="AW350">
+        <v>15</v>
+      </c>
+      <c r="AX350">
+        <v>8</v>
+      </c>
+      <c r="AY350">
+        <v>24</v>
+      </c>
+      <c r="AZ350">
+        <v>24</v>
+      </c>
+      <c r="BA350">
+        <v>5</v>
+      </c>
+      <c r="BB350">
+        <v>9</v>
+      </c>
+      <c r="BC350">
+        <v>14</v>
+      </c>
+      <c r="BD350">
+        <v>1.67</v>
+      </c>
+      <c r="BE350">
+        <v>6.75</v>
+      </c>
+      <c r="BF350">
+        <v>2.43</v>
+      </c>
+      <c r="BG350">
+        <v>1.26</v>
+      </c>
+      <c r="BH350">
+        <v>3.4</v>
+      </c>
+      <c r="BI350">
+        <v>1.46</v>
+      </c>
+      <c r="BJ350">
+        <v>2.48</v>
+      </c>
+      <c r="BK350">
+        <v>1.75</v>
+      </c>
+      <c r="BL350">
+        <v>1.95</v>
+      </c>
+      <c r="BM350">
+        <v>2.15</v>
+      </c>
+      <c r="BN350">
+        <v>1.61</v>
+      </c>
+      <c r="BO350">
+        <v>2.7</v>
+      </c>
+      <c r="BP350">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="351" spans="1:68">
+      <c r="A351" s="1">
+        <v>350</v>
+      </c>
+      <c r="B351">
+        <v>7477937</v>
+      </c>
+      <c r="C351" t="s">
+        <v>68</v>
+      </c>
+      <c r="D351" t="s">
+        <v>69</v>
+      </c>
+      <c r="E351" s="2">
+        <v>45699.69791666666</v>
+      </c>
+      <c r="F351">
+        <v>11</v>
+      </c>
+      <c r="G351" t="s">
+        <v>80</v>
+      </c>
+      <c r="H351" t="s">
+        <v>88</v>
+      </c>
+      <c r="I351">
+        <v>3</v>
+      </c>
+      <c r="J351">
+        <v>0</v>
+      </c>
+      <c r="K351">
+        <v>3</v>
+      </c>
+      <c r="L351">
+        <v>4</v>
+      </c>
+      <c r="M351">
+        <v>0</v>
+      </c>
+      <c r="N351">
+        <v>4</v>
+      </c>
+      <c r="O351" t="s">
+        <v>311</v>
+      </c>
+      <c r="P351" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q351">
+        <v>1.8</v>
+      </c>
+      <c r="R351">
+        <v>2.5</v>
+      </c>
+      <c r="S351">
+        <v>9</v>
+      </c>
+      <c r="T351">
+        <v>1.33</v>
+      </c>
+      <c r="U351">
+        <v>3.25</v>
+      </c>
+      <c r="V351">
+        <v>2.63</v>
+      </c>
+      <c r="W351">
+        <v>1.44</v>
+      </c>
+      <c r="X351">
+        <v>6.5</v>
+      </c>
+      <c r="Y351">
+        <v>1.11</v>
+      </c>
+      <c r="Z351">
+        <v>1.25</v>
+      </c>
+      <c r="AA351">
+        <v>6</v>
+      </c>
+      <c r="AB351">
+        <v>10</v>
+      </c>
+      <c r="AC351">
+        <v>1.04</v>
+      </c>
+      <c r="AD351">
+        <v>10</v>
+      </c>
+      <c r="AE351">
+        <v>1.22</v>
+      </c>
+      <c r="AF351">
+        <v>4.2</v>
+      </c>
+      <c r="AG351">
+        <v>1.7</v>
+      </c>
+      <c r="AH351">
+        <v>2.05</v>
+      </c>
+      <c r="AI351">
+        <v>2.2</v>
+      </c>
+      <c r="AJ351">
+        <v>1.62</v>
+      </c>
+      <c r="AK351">
+        <v>1.05</v>
+      </c>
+      <c r="AL351">
+        <v>1.14</v>
+      </c>
+      <c r="AM351">
+        <v>3.35</v>
+      </c>
+      <c r="AN351">
+        <v>2.54</v>
+      </c>
+      <c r="AO351">
+        <v>0.47</v>
+      </c>
+      <c r="AP351">
+        <v>2.57</v>
+      </c>
+      <c r="AQ351">
+        <v>0.44</v>
+      </c>
+      <c r="AR351">
+        <v>1.7</v>
+      </c>
+      <c r="AS351">
+        <v>1.11</v>
+      </c>
+      <c r="AT351">
+        <v>2.81</v>
+      </c>
+      <c r="AU351">
+        <v>13</v>
+      </c>
+      <c r="AV351">
+        <v>0</v>
+      </c>
+      <c r="AW351">
+        <v>13</v>
+      </c>
+      <c r="AX351">
+        <v>3</v>
+      </c>
+      <c r="AY351">
+        <v>32</v>
+      </c>
+      <c r="AZ351">
+        <v>4</v>
+      </c>
+      <c r="BA351">
+        <v>11</v>
+      </c>
+      <c r="BB351">
+        <v>3</v>
+      </c>
+      <c r="BC351">
+        <v>14</v>
+      </c>
+      <c r="BD351">
+        <v>1.17</v>
+      </c>
+      <c r="BE351">
+        <v>12</v>
+      </c>
+      <c r="BF351">
+        <v>6.5</v>
+      </c>
+      <c r="BG351">
+        <v>1.26</v>
+      </c>
+      <c r="BH351">
+        <v>3.22</v>
+      </c>
+      <c r="BI351">
+        <v>1.5</v>
+      </c>
+      <c r="BJ351">
+        <v>2.35</v>
+      </c>
+      <c r="BK351">
+        <v>1.88</v>
+      </c>
+      <c r="BL351">
+        <v>1.82</v>
+      </c>
+      <c r="BM351">
+        <v>2.42</v>
+      </c>
+      <c r="BN351">
+        <v>1.47</v>
+      </c>
+      <c r="BO351">
+        <v>3.2</v>
+      </c>
+      <c r="BP351">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="352" spans="1:68">
+      <c r="A352" s="1">
+        <v>351</v>
+      </c>
+      <c r="B352">
+        <v>7727072</v>
+      </c>
+      <c r="C352" t="s">
+        <v>68</v>
+      </c>
+      <c r="D352" t="s">
+        <v>69</v>
+      </c>
+      <c r="E352" s="2">
+        <v>45699.69791666666</v>
+      </c>
+      <c r="F352">
+        <v>19</v>
+      </c>
+      <c r="G352" t="s">
+        <v>77</v>
+      </c>
+      <c r="H352" t="s">
+        <v>76</v>
+      </c>
+      <c r="I352">
+        <v>0</v>
+      </c>
+      <c r="J352">
+        <v>0</v>
+      </c>
+      <c r="K352">
+        <v>0</v>
+      </c>
+      <c r="L352">
+        <v>3</v>
+      </c>
+      <c r="M352">
+        <v>1</v>
+      </c>
+      <c r="N352">
+        <v>4</v>
+      </c>
+      <c r="O352" t="s">
+        <v>312</v>
+      </c>
+      <c r="P352" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q352">
+        <v>3.75</v>
+      </c>
+      <c r="R352">
+        <v>1.95</v>
+      </c>
+      <c r="S352">
+        <v>3.4</v>
+      </c>
+      <c r="T352">
+        <v>1.53</v>
+      </c>
+      <c r="U352">
+        <v>2.38</v>
+      </c>
+      <c r="V352">
+        <v>3.5</v>
+      </c>
+      <c r="W352">
+        <v>1.29</v>
+      </c>
+      <c r="X352">
+        <v>11</v>
+      </c>
+      <c r="Y352">
+        <v>1.05</v>
+      </c>
+      <c r="Z352">
+        <v>2.98</v>
+      </c>
+      <c r="AA352">
+        <v>3.47</v>
+      </c>
+      <c r="AB352">
+        <v>2.24</v>
+      </c>
+      <c r="AC352">
+        <v>1.08</v>
+      </c>
+      <c r="AD352">
+        <v>7.5</v>
+      </c>
+      <c r="AE352">
+        <v>1.45</v>
+      </c>
+      <c r="AF352">
+        <v>2.7</v>
+      </c>
+      <c r="AG352">
+        <v>2.23</v>
+      </c>
+      <c r="AH352">
+        <v>1.58</v>
+      </c>
+      <c r="AI352">
+        <v>2</v>
+      </c>
+      <c r="AJ352">
+        <v>1.75</v>
+      </c>
+      <c r="AK352">
+        <v>1.53</v>
+      </c>
+      <c r="AL352">
+        <v>1.28</v>
+      </c>
+      <c r="AM352">
+        <v>1.38</v>
+      </c>
+      <c r="AN352">
+        <v>1</v>
+      </c>
+      <c r="AO352">
+        <v>1.08</v>
+      </c>
+      <c r="AP352">
+        <v>1.15</v>
+      </c>
+      <c r="AQ352">
+        <v>1</v>
+      </c>
+      <c r="AR352">
+        <v>1.07</v>
+      </c>
+      <c r="AS352">
+        <v>1.08</v>
+      </c>
+      <c r="AT352">
+        <v>2.15</v>
+      </c>
+      <c r="AU352">
+        <v>7</v>
+      </c>
+      <c r="AV352">
+        <v>5</v>
+      </c>
+      <c r="AW352">
+        <v>13</v>
+      </c>
+      <c r="AX352">
+        <v>4</v>
+      </c>
+      <c r="AY352">
+        <v>23</v>
+      </c>
+      <c r="AZ352">
+        <v>11</v>
+      </c>
+      <c r="BA352">
+        <v>2</v>
+      </c>
+      <c r="BB352">
+        <v>8</v>
+      </c>
+      <c r="BC352">
+        <v>10</v>
+      </c>
+      <c r="BD352">
+        <v>2.23</v>
+      </c>
+      <c r="BE352">
+        <v>6.75</v>
+      </c>
+      <c r="BF352">
+        <v>1.78</v>
+      </c>
+      <c r="BG352">
+        <v>1.26</v>
+      </c>
+      <c r="BH352">
+        <v>3.4</v>
+      </c>
+      <c r="BI352">
+        <v>1.46</v>
+      </c>
+      <c r="BJ352">
+        <v>2.5</v>
+      </c>
+      <c r="BK352">
+        <v>1.73</v>
+      </c>
+      <c r="BL352">
+        <v>1.96</v>
+      </c>
+      <c r="BM352">
+        <v>2.15</v>
+      </c>
+      <c r="BN352">
+        <v>1.61</v>
+      </c>
+      <c r="BO352">
+        <v>2.7</v>
+      </c>
+      <c r="BP352">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="353" spans="1:68">
+      <c r="A353" s="1">
+        <v>352</v>
+      </c>
+      <c r="B353">
+        <v>7727038</v>
+      </c>
+      <c r="C353" t="s">
+        <v>68</v>
+      </c>
+      <c r="D353" t="s">
+        <v>69</v>
+      </c>
+      <c r="E353" s="2">
+        <v>45699.69791666666</v>
+      </c>
+      <c r="F353">
+        <v>16</v>
+      </c>
+      <c r="G353" t="s">
+        <v>75</v>
+      </c>
+      <c r="H353" t="s">
+        <v>92</v>
+      </c>
+      <c r="I353">
+        <v>3</v>
+      </c>
+      <c r="J353">
+        <v>0</v>
+      </c>
+      <c r="K353">
+        <v>3</v>
+      </c>
+      <c r="L353">
+        <v>3</v>
+      </c>
+      <c r="M353">
+        <v>0</v>
+      </c>
+      <c r="N353">
+        <v>3</v>
+      </c>
+      <c r="O353" t="s">
+        <v>313</v>
+      </c>
+      <c r="P353" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q353">
+        <v>2.7</v>
+      </c>
+      <c r="R353">
+        <v>2.05</v>
+      </c>
+      <c r="S353">
+        <v>3.8</v>
+      </c>
+      <c r="T353">
+        <v>1.4</v>
+      </c>
+      <c r="U353">
+        <v>2.75</v>
+      </c>
+      <c r="V353">
+        <v>2.8</v>
+      </c>
+      <c r="W353">
+        <v>1.38</v>
+      </c>
+      <c r="X353">
+        <v>6.6</v>
+      </c>
+      <c r="Y353">
+        <v>1.08</v>
+      </c>
+      <c r="Z353">
+        <v>1.99</v>
+      </c>
+      <c r="AA353">
+        <v>3.35</v>
+      </c>
+      <c r="AB353">
+        <v>3.72</v>
+      </c>
+      <c r="AC353">
+        <v>1.06</v>
+      </c>
+      <c r="AD353">
+        <v>8.5</v>
+      </c>
+      <c r="AE353">
+        <v>1.3</v>
+      </c>
+      <c r="AF353">
+        <v>3.35</v>
+      </c>
+      <c r="AG353">
+        <v>1.98</v>
+      </c>
+      <c r="AH353">
+        <v>1.77</v>
+      </c>
+      <c r="AI353">
+        <v>1.73</v>
+      </c>
+      <c r="AJ353">
+        <v>1.95</v>
+      </c>
+      <c r="AK353">
+        <v>1.3</v>
+      </c>
+      <c r="AL353">
+        <v>1.25</v>
+      </c>
+      <c r="AM353">
+        <v>1.67</v>
+      </c>
+      <c r="AN353">
+        <v>1.6</v>
+      </c>
+      <c r="AO353">
+        <v>1.36</v>
+      </c>
+      <c r="AP353">
+        <v>1.69</v>
+      </c>
+      <c r="AQ353">
+        <v>1.27</v>
+      </c>
+      <c r="AR353">
+        <v>1.5</v>
+      </c>
+      <c r="AS353">
+        <v>1.31</v>
+      </c>
+      <c r="AT353">
+        <v>2.81</v>
+      </c>
+      <c r="AU353">
+        <v>8</v>
+      </c>
+      <c r="AV353">
+        <v>5</v>
+      </c>
+      <c r="AW353">
+        <v>3</v>
+      </c>
+      <c r="AX353">
+        <v>3</v>
+      </c>
+      <c r="AY353">
+        <v>13</v>
+      </c>
+      <c r="AZ353">
+        <v>10</v>
+      </c>
+      <c r="BA353">
+        <v>5</v>
+      </c>
+      <c r="BB353">
+        <v>3</v>
+      </c>
+      <c r="BC353">
+        <v>8</v>
+      </c>
+      <c r="BD353">
+        <v>1.45</v>
+      </c>
+      <c r="BE353">
+        <v>7.6</v>
+      </c>
+      <c r="BF353">
+        <v>3.2</v>
+      </c>
+      <c r="BG353">
+        <v>1.17</v>
+      </c>
+      <c r="BH353">
+        <v>4.35</v>
+      </c>
+      <c r="BI353">
+        <v>1.37</v>
+      </c>
+      <c r="BJ353">
+        <v>2.82</v>
+      </c>
+      <c r="BK353">
+        <v>1.65</v>
+      </c>
+      <c r="BL353">
+        <v>2.05</v>
+      </c>
+      <c r="BM353">
+        <v>2.12</v>
+      </c>
+      <c r="BN353">
+        <v>1.62</v>
+      </c>
+      <c r="BO353">
+        <v>2.92</v>
+      </c>
+      <c r="BP353">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="354" spans="1:68">
+      <c r="A354" s="1">
+        <v>353</v>
+      </c>
+      <c r="B354">
+        <v>7727153</v>
+      </c>
+      <c r="C354" t="s">
+        <v>68</v>
+      </c>
+      <c r="D354" t="s">
+        <v>69</v>
+      </c>
+      <c r="E354" s="2">
+        <v>45699.69791666666</v>
+      </c>
+      <c r="F354">
+        <v>26</v>
+      </c>
+      <c r="G354" t="s">
+        <v>79</v>
+      </c>
+      <c r="H354" t="s">
+        <v>73</v>
+      </c>
+      <c r="I354">
+        <v>0</v>
+      </c>
+      <c r="J354">
+        <v>0</v>
+      </c>
+      <c r="K354">
+        <v>0</v>
+      </c>
+      <c r="L354">
+        <v>1</v>
+      </c>
+      <c r="M354">
+        <v>1</v>
+      </c>
+      <c r="N354">
+        <v>2</v>
+      </c>
+      <c r="O354" t="s">
+        <v>314</v>
+      </c>
+      <c r="P354" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q354">
+        <v>5</v>
+      </c>
+      <c r="R354">
+        <v>2.2</v>
+      </c>
+      <c r="S354">
+        <v>2.4</v>
+      </c>
+      <c r="T354">
+        <v>1.4</v>
+      </c>
+      <c r="U354">
+        <v>2.75</v>
+      </c>
+      <c r="V354">
+        <v>3</v>
+      </c>
+      <c r="W354">
+        <v>1.36</v>
+      </c>
+      <c r="X354">
+        <v>8</v>
+      </c>
+      <c r="Y354">
+        <v>1.08</v>
+      </c>
+      <c r="Z354">
+        <v>4.4</v>
+      </c>
+      <c r="AA354">
+        <v>3.56</v>
+      </c>
+      <c r="AB354">
+        <v>1.78</v>
+      </c>
+      <c r="AC354">
+        <v>1.05</v>
+      </c>
+      <c r="AD354">
+        <v>10</v>
+      </c>
+      <c r="AE354">
+        <v>1.33</v>
+      </c>
+      <c r="AF354">
+        <v>3.25</v>
+      </c>
+      <c r="AG354">
+        <v>1.98</v>
+      </c>
+      <c r="AH354">
+        <v>1.77</v>
+      </c>
+      <c r="AI354">
+        <v>1.91</v>
+      </c>
+      <c r="AJ354">
+        <v>1.91</v>
+      </c>
+      <c r="AK354">
+        <v>2</v>
+      </c>
+      <c r="AL354">
+        <v>1.25</v>
+      </c>
+      <c r="AM354">
+        <v>1.2</v>
+      </c>
+      <c r="AN354">
+        <v>1.62</v>
+      </c>
+      <c r="AO354">
+        <v>1.43</v>
+      </c>
+      <c r="AP354">
+        <v>1.57</v>
+      </c>
+      <c r="AQ354">
+        <v>1.4</v>
+      </c>
+      <c r="AR354">
+        <v>1.15</v>
+      </c>
+      <c r="AS354">
+        <v>1.34</v>
+      </c>
+      <c r="AT354">
+        <v>2.49</v>
+      </c>
+      <c r="AU354">
+        <v>3</v>
+      </c>
+      <c r="AV354">
+        <v>5</v>
+      </c>
+      <c r="AW354">
+        <v>5</v>
+      </c>
+      <c r="AX354">
+        <v>5</v>
+      </c>
+      <c r="AY354">
+        <v>10</v>
+      </c>
+      <c r="AZ354">
+        <v>13</v>
+      </c>
+      <c r="BA354">
+        <v>2</v>
+      </c>
+      <c r="BB354">
+        <v>7</v>
+      </c>
+      <c r="BC354">
+        <v>9</v>
+      </c>
+      <c r="BD354">
+        <v>3.14</v>
+      </c>
+      <c r="BE354">
+        <v>8.9</v>
+      </c>
+      <c r="BF354">
+        <v>1.51</v>
+      </c>
+      <c r="BG354">
+        <v>1.25</v>
+      </c>
+      <c r="BH354">
+        <v>3.28</v>
+      </c>
+      <c r="BI354">
+        <v>1.7</v>
+      </c>
+      <c r="BJ354">
+        <v>2.05</v>
+      </c>
+      <c r="BK354">
+        <v>1.85</v>
+      </c>
+      <c r="BL354">
+        <v>1.85</v>
+      </c>
+      <c r="BM354">
+        <v>2.4</v>
+      </c>
+      <c r="BN354">
+        <v>1.48</v>
+      </c>
+      <c r="BO354">
+        <v>3.2</v>
+      </c>
+      <c r="BP354">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="355" spans="1:68">
+      <c r="A355" s="1">
+        <v>354</v>
+      </c>
+      <c r="B355">
+        <v>7727039</v>
+      </c>
+      <c r="C355" t="s">
+        <v>68</v>
+      </c>
+      <c r="D355" t="s">
+        <v>69</v>
+      </c>
+      <c r="E355" s="2">
+        <v>45699.70833333334</v>
+      </c>
+      <c r="F355">
+        <v>16</v>
+      </c>
+      <c r="G355" t="s">
+        <v>84</v>
+      </c>
+      <c r="H355" t="s">
+        <v>82</v>
+      </c>
+      <c r="I355">
+        <v>1</v>
+      </c>
+      <c r="J355">
+        <v>0</v>
+      </c>
+      <c r="K355">
+        <v>1</v>
+      </c>
+      <c r="L355">
+        <v>1</v>
+      </c>
+      <c r="M355">
+        <v>1</v>
+      </c>
+      <c r="N355">
+        <v>2</v>
+      </c>
+      <c r="O355" t="s">
+        <v>315</v>
+      </c>
+      <c r="P355" t="s">
+        <v>389</v>
+      </c>
+      <c r="Q355">
+        <v>2.2</v>
+      </c>
+      <c r="R355">
+        <v>2.25</v>
+      </c>
+      <c r="S355">
+        <v>4.5</v>
+      </c>
+      <c r="T355">
+        <v>1.33</v>
+      </c>
+      <c r="U355">
+        <v>3.1</v>
+      </c>
+      <c r="V355">
+        <v>2.45</v>
+      </c>
+      <c r="W355">
+        <v>1.48</v>
+      </c>
+      <c r="X355">
+        <v>5.7</v>
+      </c>
+      <c r="Y355">
+        <v>1.11</v>
+      </c>
+      <c r="Z355">
+        <v>1.94</v>
+      </c>
+      <c r="AA355">
+        <v>3.73</v>
+      </c>
+      <c r="AB355">
+        <v>3.47</v>
+      </c>
+      <c r="AC355">
+        <v>1.04</v>
+      </c>
+      <c r="AD355">
+        <v>10</v>
+      </c>
+      <c r="AE355">
+        <v>1.22</v>
+      </c>
+      <c r="AF355">
+        <v>4</v>
+      </c>
+      <c r="AG355">
+        <v>1.82</v>
+      </c>
+      <c r="AH355">
+        <v>1.92</v>
+      </c>
+      <c r="AI355">
+        <v>1.67</v>
+      </c>
+      <c r="AJ355">
+        <v>2.05</v>
+      </c>
+      <c r="AK355">
+        <v>1.17</v>
+      </c>
+      <c r="AL355">
+        <v>1.2</v>
+      </c>
+      <c r="AM355">
+        <v>2.15</v>
+      </c>
+      <c r="AN355">
+        <v>2.31</v>
+      </c>
+      <c r="AO355">
+        <v>0.6</v>
+      </c>
+      <c r="AP355">
+        <v>2.21</v>
+      </c>
+      <c r="AQ355">
+        <v>0.63</v>
+      </c>
+      <c r="AR355">
+        <v>1.3</v>
+      </c>
+      <c r="AS355">
+        <v>0.99</v>
+      </c>
+      <c r="AT355">
+        <v>2.29</v>
+      </c>
+      <c r="AU355">
+        <v>4</v>
+      </c>
+      <c r="AV355">
+        <v>3</v>
+      </c>
+      <c r="AW355">
+        <v>5</v>
+      </c>
+      <c r="AX355">
+        <v>6</v>
+      </c>
+      <c r="AY355">
+        <v>13</v>
+      </c>
+      <c r="AZ355">
+        <v>15</v>
+      </c>
+      <c r="BA355">
+        <v>1</v>
+      </c>
+      <c r="BB355">
+        <v>7</v>
+      </c>
+      <c r="BC355">
+        <v>8</v>
+      </c>
+      <c r="BD355">
+        <v>1.92</v>
+      </c>
+      <c r="BE355">
+        <v>6.6</v>
+      </c>
+      <c r="BF355">
+        <v>2.38</v>
+      </c>
+      <c r="BG355">
+        <v>1.16</v>
+      </c>
+      <c r="BH355">
+        <v>4.15</v>
+      </c>
+      <c r="BI355">
+        <v>1.34</v>
+      </c>
+      <c r="BJ355">
+        <v>2.88</v>
+      </c>
+      <c r="BK355">
+        <v>1.63</v>
+      </c>
+      <c r="BL355">
+        <v>2.14</v>
+      </c>
+      <c r="BM355">
+        <v>2.01</v>
+      </c>
+      <c r="BN355">
+        <v>1.68</v>
+      </c>
+      <c r="BO355">
+        <v>2.59</v>
+      </c>
+      <c r="BP355">
+        <v>1.39</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England EFL League One_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England EFL League One_20242025.xlsx
@@ -940,25 +940,25 @@
     <t>['31', '35']</t>
   </si>
   <si>
+    <t>['76']</t>
+  </si>
+  <si>
     <t>['52', '68', '85', '90+9']</t>
   </si>
   <si>
-    <t>['76']</t>
+    <t>['6', '17', '32']</t>
   </si>
   <si>
-    <t>['54', '89']</t>
+    <t>['50', '87', '90+4']</t>
   </si>
   <si>
     <t>['23', '39', '40', '79']</t>
   </si>
   <si>
-    <t>['50', '87', '90+4']</t>
+    <t>['90+1']</t>
   </si>
   <si>
-    <t>['6', '17', '32']</t>
-  </si>
-  <si>
-    <t>['90+1']</t>
+    <t>['54', '89']</t>
   </si>
   <si>
     <t>['28']</t>
@@ -1366,13 +1366,13 @@
     <t>['52', '54']</t>
   </si>
   <si>
-    <t>['50', '54', '62']</t>
+    <t>['68', '77']</t>
   </si>
   <si>
     <t>['90+4']</t>
   </si>
   <si>
-    <t>['68', '77']</t>
+    <t>['50', '54', '62']</t>
   </si>
 </sst>
 </file>
@@ -20324,7 +20324,7 @@
         <v>119</v>
       </c>
       <c r="P91" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="Q91">
         <v>2.88</v>
@@ -63790,7 +63790,7 @@
         <v>281</v>
       </c>
       <c r="P302" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="Q302">
         <v>2.63</v>
@@ -71618,7 +71618,7 @@
         <v>305</v>
       </c>
       <c r="P340" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="Q340">
         <v>3.4</v>
@@ -72400,7 +72400,7 @@
         <v>343</v>
       </c>
       <c r="B344">
-        <v>7727233</v>
+        <v>7727236</v>
       </c>
       <c r="C344" t="s">
         <v>68</v>
@@ -72415,37 +72415,37 @@
         <v>31</v>
       </c>
       <c r="G344" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="H344" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="I344">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J344">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K344">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L344">
         <v>1</v>
       </c>
       <c r="M344">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N344">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O344" t="s">
-        <v>153</v>
+        <v>308</v>
       </c>
       <c r="P344" t="s">
-        <v>321</v>
+        <v>450</v>
       </c>
       <c r="Q344">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="R344">
         <v>2.1</v>
@@ -72472,31 +72472,31 @@
         <v>1.07</v>
       </c>
       <c r="Z344">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AA344">
-        <v>3.74</v>
+        <v>3.68</v>
       </c>
       <c r="AB344">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AC344">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AD344">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AE344">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AF344">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AG344">
         <v>2</v>
       </c>
       <c r="AH344">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AI344">
         <v>2</v>
@@ -72505,100 +72505,100 @@
         <v>1.75</v>
       </c>
       <c r="AK344">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AL344">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AM344">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AN344">
-        <v>1.5</v>
+        <v>1.93</v>
       </c>
       <c r="AO344">
         <v>0.43</v>
       </c>
       <c r="AP344">
-        <v>1.47</v>
+        <v>1.8</v>
       </c>
       <c r="AQ344">
-        <v>0.44</v>
+        <v>0.63</v>
       </c>
       <c r="AR344">
-        <v>1.38</v>
+        <v>1.63</v>
       </c>
       <c r="AS344">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="AT344">
-        <v>2.48</v>
+        <v>2.64</v>
       </c>
       <c r="AU344">
         <v>3</v>
       </c>
       <c r="AV344">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AW344">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="AX344">
+        <v>1</v>
+      </c>
+      <c r="AY344">
+        <v>10</v>
+      </c>
+      <c r="AZ344">
         <v>4</v>
       </c>
-      <c r="AY344">
-        <v>21</v>
-      </c>
-      <c r="AZ344">
-        <v>11</v>
-      </c>
       <c r="BA344">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="BB344">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BC344">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BD344">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="BE344">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="BF344">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="BG344">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="BH344">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="BI344">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="BJ344">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="BK344">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="BL344">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="BM344">
-        <v>2.18</v>
+        <v>2.07</v>
       </c>
       <c r="BN344">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="BO344">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="BP344">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="345" spans="1:68">
@@ -72606,7 +72606,7 @@
         <v>344</v>
       </c>
       <c r="B345">
-        <v>7727232</v>
+        <v>7727233</v>
       </c>
       <c r="C345" t="s">
         <v>68</v>
@@ -72621,190 +72621,190 @@
         <v>31</v>
       </c>
       <c r="G345" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H345" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="I345">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J345">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K345">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L345">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M345">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N345">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O345" t="s">
-        <v>96</v>
+        <v>153</v>
       </c>
       <c r="P345" t="s">
-        <v>96</v>
+        <v>321</v>
       </c>
       <c r="Q345">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="R345">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="S345">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="T345">
+        <v>1.44</v>
+      </c>
+      <c r="U345">
+        <v>2.63</v>
+      </c>
+      <c r="V345">
+        <v>3.25</v>
+      </c>
+      <c r="W345">
         <v>1.33</v>
       </c>
-      <c r="U345">
-        <v>3.25</v>
-      </c>
-      <c r="V345">
-        <v>2.63</v>
-      </c>
-      <c r="W345">
-        <v>1.44</v>
-      </c>
       <c r="X345">
-        <v>6.5</v>
+        <v>9</v>
       </c>
       <c r="Y345">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Z345">
-        <v>1.51</v>
+        <v>1.64</v>
       </c>
       <c r="AA345">
-        <v>4.2</v>
+        <v>3.74</v>
       </c>
       <c r="AB345">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="AC345">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AD345">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE345">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="AF345">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="AG345">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AH345">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AI345">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AJ345">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AK345">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AL345">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AM345">
-        <v>2.55</v>
+        <v>2.05</v>
       </c>
       <c r="AN345">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AO345">
-        <v>0.93</v>
+        <v>0.43</v>
       </c>
       <c r="AP345">
-        <v>1.75</v>
+        <v>1.47</v>
       </c>
       <c r="AQ345">
-        <v>0.9399999999999999</v>
+        <v>0.44</v>
       </c>
       <c r="AR345">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AS345">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="AT345">
-        <v>2.64</v>
+        <v>2.48</v>
       </c>
       <c r="AU345">
+        <v>3</v>
+      </c>
+      <c r="AV345">
+        <v>5</v>
+      </c>
+      <c r="AW345">
+        <v>14</v>
+      </c>
+      <c r="AX345">
+        <v>4</v>
+      </c>
+      <c r="AY345">
+        <v>21</v>
+      </c>
+      <c r="AZ345">
+        <v>11</v>
+      </c>
+      <c r="BA345">
+        <v>4</v>
+      </c>
+      <c r="BB345">
+        <v>3</v>
+      </c>
+      <c r="BC345">
         <v>7</v>
       </c>
-      <c r="AV345">
-        <v>2</v>
-      </c>
-      <c r="AW345">
-        <v>11</v>
-      </c>
-      <c r="AX345">
-        <v>9</v>
-      </c>
-      <c r="AY345">
-        <v>18</v>
-      </c>
-      <c r="AZ345">
-        <v>12</v>
-      </c>
-      <c r="BA345">
-        <v>6</v>
-      </c>
-      <c r="BB345">
-        <v>0</v>
-      </c>
-      <c r="BC345">
-        <v>6</v>
-      </c>
       <c r="BD345">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="BE345">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BF345">
-        <v>3.8</v>
+        <v>3.05</v>
       </c>
       <c r="BG345">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="BH345">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="BI345">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="BJ345">
-        <v>3.05</v>
+        <v>2.45</v>
       </c>
       <c r="BK345">
-        <v>1.52</v>
+        <v>1.85</v>
       </c>
       <c r="BL345">
-        <v>2.33</v>
+        <v>1.95</v>
       </c>
       <c r="BM345">
-        <v>1.85</v>
+        <v>2.18</v>
       </c>
       <c r="BN345">
-        <v>1.95</v>
+        <v>1.58</v>
       </c>
       <c r="BO345">
-        <v>2.23</v>
+        <v>2.8</v>
       </c>
       <c r="BP345">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="346" spans="1:68">
@@ -72812,7 +72812,7 @@
         <v>345</v>
       </c>
       <c r="B346">
-        <v>7727228</v>
+        <v>7727232</v>
       </c>
       <c r="C346" t="s">
         <v>68</v>
@@ -72827,10 +72827,10 @@
         <v>31</v>
       </c>
       <c r="G346" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="H346" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I346">
         <v>0</v>
@@ -72842,55 +72842,55 @@
         <v>0</v>
       </c>
       <c r="L346">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M346">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N346">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O346" t="s">
-        <v>308</v>
+        <v>96</v>
       </c>
       <c r="P346" t="s">
-        <v>450</v>
+        <v>96</v>
       </c>
       <c r="Q346">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="R346">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="S346">
         <v>6</v>
       </c>
       <c r="T346">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="U346">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="V346">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="W346">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="X346">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="Y346">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z346">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="AA346">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="AB346">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AC346">
         <v>1.04</v>
@@ -72899,118 +72899,118 @@
         <v>10</v>
       </c>
       <c r="AE346">
+        <v>1.22</v>
+      </c>
+      <c r="AF346">
+        <v>4.2</v>
+      </c>
+      <c r="AG346">
+        <v>1.73</v>
+      </c>
+      <c r="AH346">
+        <v>2</v>
+      </c>
+      <c r="AI346">
+        <v>1.91</v>
+      </c>
+      <c r="AJ346">
+        <v>1.91</v>
+      </c>
+      <c r="AK346">
+        <v>1.12</v>
+      </c>
+      <c r="AL346">
         <v>1.17</v>
       </c>
-      <c r="AF346">
-        <v>5</v>
-      </c>
-      <c r="AG346">
-        <v>1.55</v>
-      </c>
-      <c r="AH346">
-        <v>2.37</v>
-      </c>
-      <c r="AI346">
-        <v>1.7</v>
-      </c>
-      <c r="AJ346">
-        <v>2.05</v>
-      </c>
-      <c r="AK346">
-        <v>1.1</v>
-      </c>
-      <c r="AL346">
-        <v>1.14</v>
-      </c>
       <c r="AM346">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="AN346">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AO346">
-        <v>0.8</v>
+        <v>0.93</v>
       </c>
       <c r="AP346">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AQ346">
-        <v>0.75</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR346">
-        <v>1.73</v>
+        <v>1.43</v>
       </c>
       <c r="AS346">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="AT346">
-        <v>3.05</v>
+        <v>2.64</v>
       </c>
       <c r="AU346">
         <v>7</v>
       </c>
       <c r="AV346">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AW346">
         <v>11</v>
       </c>
       <c r="AX346">
+        <v>9</v>
+      </c>
+      <c r="AY346">
+        <v>18</v>
+      </c>
+      <c r="AZ346">
+        <v>12</v>
+      </c>
+      <c r="BA346">
         <v>6</v>
       </c>
-      <c r="AY346">
-        <v>21</v>
-      </c>
-      <c r="AZ346">
-        <v>11</v>
-      </c>
-      <c r="BA346">
-        <v>4</v>
-      </c>
       <c r="BB346">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BC346">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BD346">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="BE346">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="BF346">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="BG346">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BH346">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BI346">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="BJ346">
         <v>3.05</v>
       </c>
       <c r="BK346">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="BL346">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="BM346">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="BN346">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="BO346">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="BP346">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="347" spans="1:68">
@@ -73224,7 +73224,7 @@
         <v>347</v>
       </c>
       <c r="B348">
-        <v>7727236</v>
+        <v>7727228</v>
       </c>
       <c r="C348" t="s">
         <v>68</v>
@@ -73239,10 +73239,10 @@
         <v>31</v>
       </c>
       <c r="G348" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="H348" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="I348">
         <v>0</v>
@@ -73254,13 +73254,13 @@
         <v>0</v>
       </c>
       <c r="L348">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M348">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N348">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O348" t="s">
         <v>309</v>
@@ -73269,160 +73269,160 @@
         <v>452</v>
       </c>
       <c r="Q348">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="R348">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="S348">
+        <v>6</v>
+      </c>
+      <c r="T348">
+        <v>1.29</v>
+      </c>
+      <c r="U348">
+        <v>3.5</v>
+      </c>
+      <c r="V348">
+        <v>2.25</v>
+      </c>
+      <c r="W348">
+        <v>1.57</v>
+      </c>
+      <c r="X348">
         <v>5.5</v>
       </c>
-      <c r="T348">
-        <v>1.44</v>
-      </c>
-      <c r="U348">
-        <v>2.63</v>
-      </c>
-      <c r="V348">
-        <v>3.25</v>
-      </c>
-      <c r="W348">
-        <v>1.33</v>
-      </c>
-      <c r="X348">
-        <v>9</v>
-      </c>
       <c r="Y348">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="Z348">
-        <v>1.66</v>
+        <v>1.43</v>
       </c>
       <c r="AA348">
-        <v>3.68</v>
+        <v>5</v>
       </c>
       <c r="AB348">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="AC348">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AD348">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="AE348">
-        <v>1.35</v>
+        <v>1.17</v>
       </c>
       <c r="AF348">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="AG348">
-        <v>2</v>
+        <v>1.55</v>
       </c>
       <c r="AH348">
+        <v>2.37</v>
+      </c>
+      <c r="AI348">
+        <v>1.7</v>
+      </c>
+      <c r="AJ348">
+        <v>2.05</v>
+      </c>
+      <c r="AK348">
+        <v>1.1</v>
+      </c>
+      <c r="AL348">
+        <v>1.14</v>
+      </c>
+      <c r="AM348">
+        <v>2.75</v>
+      </c>
+      <c r="AN348">
+        <v>1.6</v>
+      </c>
+      <c r="AO348">
+        <v>0.8</v>
+      </c>
+      <c r="AP348">
+        <v>1.69</v>
+      </c>
+      <c r="AQ348">
+        <v>0.75</v>
+      </c>
+      <c r="AR348">
         <v>1.73</v>
       </c>
-      <c r="AI348">
-        <v>2</v>
-      </c>
-      <c r="AJ348">
-        <v>1.75</v>
-      </c>
-      <c r="AK348">
-        <v>1.15</v>
-      </c>
-      <c r="AL348">
-        <v>1.22</v>
-      </c>
-      <c r="AM348">
-        <v>2.15</v>
-      </c>
-      <c r="AN348">
-        <v>1.93</v>
-      </c>
-      <c r="AO348">
-        <v>0.43</v>
-      </c>
-      <c r="AP348">
-        <v>1.8</v>
-      </c>
-      <c r="AQ348">
-        <v>0.63</v>
-      </c>
-      <c r="AR348">
-        <v>1.63</v>
-      </c>
       <c r="AS348">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="AT348">
-        <v>2.64</v>
+        <v>3.05</v>
       </c>
       <c r="AU348">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AV348">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AW348">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AX348">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AY348">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="AZ348">
+        <v>11</v>
+      </c>
+      <c r="BA348">
         <v>4</v>
       </c>
-      <c r="BA348">
-        <v>8</v>
-      </c>
       <c r="BB348">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BC348">
         <v>9</v>
       </c>
       <c r="BD348">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BE348">
         <v>7.5</v>
       </c>
       <c r="BF348">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="BG348">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="BH348">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="BI348">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="BJ348">
-        <v>2.55</v>
+        <v>3.05</v>
       </c>
       <c r="BK348">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="BL348">
-        <v>2.02</v>
+        <v>2.32</v>
       </c>
       <c r="BM348">
-        <v>2.07</v>
+        <v>1.98</v>
       </c>
       <c r="BN348">
-        <v>1.66</v>
+        <v>1.82</v>
       </c>
       <c r="BO348">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="BP348">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="349" spans="1:68">
@@ -73430,7 +73430,7 @@
         <v>348</v>
       </c>
       <c r="B349">
-        <v>7727036</v>
+        <v>7727038</v>
       </c>
       <c r="C349" t="s">
         <v>68</v>
@@ -73445,25 +73445,25 @@
         <v>16</v>
       </c>
       <c r="G349" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H349" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="I349">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J349">
         <v>0</v>
       </c>
       <c r="K349">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L349">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M349">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N349">
         <v>3</v>
@@ -73472,163 +73472,163 @@
         <v>310</v>
       </c>
       <c r="P349" t="s">
-        <v>161</v>
+        <v>96</v>
       </c>
       <c r="Q349">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="R349">
-        <v>2.38</v>
+        <v>2.05</v>
       </c>
       <c r="S349">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="T349">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="U349">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="V349">
-        <v>2.38</v>
+        <v>2.8</v>
       </c>
       <c r="W349">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="X349">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="Y349">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Z349">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="AA349">
-        <v>3.61</v>
+        <v>3.35</v>
       </c>
       <c r="AB349">
-        <v>3.73</v>
+        <v>3.72</v>
       </c>
       <c r="AC349">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AD349">
-        <v>17</v>
+        <v>8.5</v>
       </c>
       <c r="AE349">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AF349">
-        <v>4.83</v>
+        <v>3.35</v>
       </c>
       <c r="AG349">
+        <v>1.98</v>
+      </c>
+      <c r="AH349">
+        <v>1.77</v>
+      </c>
+      <c r="AI349">
         <v>1.73</v>
       </c>
-      <c r="AH349">
-        <v>2</v>
-      </c>
-      <c r="AI349">
-        <v>1.5</v>
-      </c>
       <c r="AJ349">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="AK349">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AL349">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AM349">
         <v>1.67</v>
       </c>
       <c r="AN349">
-        <v>1.93</v>
+        <v>1.6</v>
       </c>
       <c r="AO349">
-        <v>0.62</v>
+        <v>1.36</v>
       </c>
       <c r="AP349">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="AQ349">
-        <v>0.57</v>
+        <v>1.27</v>
       </c>
       <c r="AR349">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AS349">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="AT349">
-        <v>2.68</v>
+        <v>2.81</v>
       </c>
       <c r="AU349">
+        <v>8</v>
+      </c>
+      <c r="AV349">
+        <v>5</v>
+      </c>
+      <c r="AW349">
+        <v>3</v>
+      </c>
+      <c r="AX349">
+        <v>3</v>
+      </c>
+      <c r="AY349">
+        <v>13</v>
+      </c>
+      <c r="AZ349">
         <v>10</v>
       </c>
-      <c r="AV349">
-        <v>4</v>
-      </c>
-      <c r="AW349">
-        <v>13</v>
-      </c>
-      <c r="AX349">
-        <v>2</v>
-      </c>
-      <c r="AY349">
-        <v>29</v>
-      </c>
-      <c r="AZ349">
-        <v>6</v>
-      </c>
       <c r="BA349">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BB349">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BC349">
         <v>8</v>
       </c>
       <c r="BD349">
-        <v>1.77</v>
+        <v>1.45</v>
       </c>
       <c r="BE349">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF349">
+        <v>3.2</v>
+      </c>
+      <c r="BG349">
+        <v>1.17</v>
+      </c>
+      <c r="BH349">
+        <v>4.35</v>
+      </c>
+      <c r="BI349">
+        <v>1.37</v>
+      </c>
+      <c r="BJ349">
+        <v>2.82</v>
+      </c>
+      <c r="BK349">
+        <v>1.65</v>
+      </c>
+      <c r="BL349">
+        <v>2.05</v>
+      </c>
+      <c r="BM349">
         <v>2.12</v>
       </c>
-      <c r="BG349">
-        <v>1.24</v>
-      </c>
-      <c r="BH349">
-        <v>3.55</v>
-      </c>
-      <c r="BI349">
-        <v>1.43</v>
-      </c>
-      <c r="BJ349">
-        <v>2.55</v>
-      </c>
-      <c r="BK349">
-        <v>1.71</v>
-      </c>
-      <c r="BL349">
-        <v>2</v>
-      </c>
-      <c r="BM349">
-        <v>2.1</v>
-      </c>
       <c r="BN349">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="BO349">
-        <v>2.65</v>
+        <v>2.92</v>
       </c>
       <c r="BP349">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="350" spans="1:68">
@@ -73636,7 +73636,7 @@
         <v>349</v>
       </c>
       <c r="B350">
-        <v>7727068</v>
+        <v>7727072</v>
       </c>
       <c r="C350" t="s">
         <v>68</v>
@@ -73651,10 +73651,10 @@
         <v>19</v>
       </c>
       <c r="G350" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="H350" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="I350">
         <v>0</v>
@@ -73666,145 +73666,145 @@
         <v>0</v>
       </c>
       <c r="L350">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M350">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N350">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O350" t="s">
-        <v>96</v>
+        <v>311</v>
       </c>
       <c r="P350" t="s">
-        <v>96</v>
+        <v>189</v>
       </c>
       <c r="Q350">
-        <v>2.75</v>
+        <v>3.75</v>
       </c>
       <c r="R350">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="S350">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="T350">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="U350">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="V350">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="W350">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="X350">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="Y350">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Z350">
-        <v>2.09</v>
+        <v>2.98</v>
       </c>
       <c r="AA350">
         <v>3.47</v>
       </c>
       <c r="AB350">
-        <v>3.28</v>
+        <v>2.24</v>
       </c>
       <c r="AC350">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AD350">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="AE350">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AF350">
-        <v>3.45</v>
+        <v>2.7</v>
       </c>
       <c r="AG350">
-        <v>1.98</v>
+        <v>2.23</v>
       </c>
       <c r="AH350">
-        <v>1.77</v>
+        <v>1.58</v>
       </c>
       <c r="AI350">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AJ350">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AK350">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AL350">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AM350">
-        <v>1.7</v>
+        <v>1.38</v>
       </c>
       <c r="AN350">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AO350">
-        <v>0.71</v>
+        <v>1.08</v>
       </c>
       <c r="AP350">
         <v>1.15</v>
       </c>
       <c r="AQ350">
-        <v>0.73</v>
+        <v>1</v>
       </c>
       <c r="AR350">
-        <v>1.57</v>
+        <v>1.07</v>
       </c>
       <c r="AS350">
-        <v>1.29</v>
+        <v>1.08</v>
       </c>
       <c r="AT350">
-        <v>2.86</v>
+        <v>2.15</v>
       </c>
       <c r="AU350">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AV350">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AW350">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AX350">
+        <v>4</v>
+      </c>
+      <c r="AY350">
+        <v>23</v>
+      </c>
+      <c r="AZ350">
+        <v>11</v>
+      </c>
+      <c r="BA350">
+        <v>2</v>
+      </c>
+      <c r="BB350">
         <v>8</v>
       </c>
-      <c r="AY350">
-        <v>24</v>
-      </c>
-      <c r="AZ350">
-        <v>24</v>
-      </c>
-      <c r="BA350">
-        <v>5</v>
-      </c>
-      <c r="BB350">
-        <v>9</v>
-      </c>
       <c r="BC350">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="BD350">
-        <v>1.67</v>
+        <v>2.23</v>
       </c>
       <c r="BE350">
         <v>6.75</v>
       </c>
       <c r="BF350">
-        <v>2.43</v>
+        <v>1.78</v>
       </c>
       <c r="BG350">
         <v>1.26</v>
@@ -73816,13 +73816,13 @@
         <v>1.46</v>
       </c>
       <c r="BJ350">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="BK350">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="BL350">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="BM350">
         <v>2.15</v>
@@ -73834,7 +73834,7 @@
         <v>2.7</v>
       </c>
       <c r="BP350">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="351" spans="1:68">
@@ -73881,7 +73881,7 @@
         <v>4</v>
       </c>
       <c r="O351" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="P351" t="s">
         <v>96</v>
@@ -74048,7 +74048,7 @@
         <v>351</v>
       </c>
       <c r="B352">
-        <v>7727072</v>
+        <v>7727153</v>
       </c>
       <c r="C352" t="s">
         <v>68</v>
@@ -74060,13 +74060,13 @@
         <v>45699.69791666666</v>
       </c>
       <c r="F352">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G352" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H352" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="I352">
         <v>0</v>
@@ -74078,175 +74078,175 @@
         <v>0</v>
       </c>
       <c r="L352">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M352">
         <v>1</v>
       </c>
       <c r="N352">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O352" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P352" t="s">
         <v>189</v>
       </c>
       <c r="Q352">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="R352">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="S352">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="T352">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="U352">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="V352">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="W352">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="X352">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Y352">
+        <v>1.08</v>
+      </c>
+      <c r="Z352">
+        <v>4.4</v>
+      </c>
+      <c r="AA352">
+        <v>3.56</v>
+      </c>
+      <c r="AB352">
+        <v>1.78</v>
+      </c>
+      <c r="AC352">
         <v>1.05</v>
       </c>
-      <c r="Z352">
-        <v>2.98</v>
-      </c>
-      <c r="AA352">
-        <v>3.47</v>
-      </c>
-      <c r="AB352">
-        <v>2.24</v>
-      </c>
-      <c r="AC352">
-        <v>1.08</v>
-      </c>
       <c r="AD352">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="AE352">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AF352">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="AG352">
-        <v>2.23</v>
+        <v>1.98</v>
       </c>
       <c r="AH352">
-        <v>1.58</v>
+        <v>1.77</v>
       </c>
       <c r="AI352">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AJ352">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AK352">
-        <v>1.53</v>
+        <v>2</v>
       </c>
       <c r="AL352">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AM352">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="AN352">
-        <v>1</v>
+        <v>1.62</v>
       </c>
       <c r="AO352">
-        <v>1.08</v>
+        <v>1.43</v>
       </c>
       <c r="AP352">
+        <v>1.57</v>
+      </c>
+      <c r="AQ352">
+        <v>1.4</v>
+      </c>
+      <c r="AR352">
         <v>1.15</v>
       </c>
-      <c r="AQ352">
-        <v>1</v>
-      </c>
-      <c r="AR352">
-        <v>1.07</v>
-      </c>
       <c r="AS352">
-        <v>1.08</v>
+        <v>1.34</v>
       </c>
       <c r="AT352">
-        <v>2.15</v>
+        <v>2.49</v>
       </c>
       <c r="AU352">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AV352">
         <v>5</v>
       </c>
       <c r="AW352">
+        <v>5</v>
+      </c>
+      <c r="AX352">
+        <v>5</v>
+      </c>
+      <c r="AY352">
+        <v>10</v>
+      </c>
+      <c r="AZ352">
         <v>13</v>
       </c>
-      <c r="AX352">
-        <v>4</v>
-      </c>
-      <c r="AY352">
-        <v>23</v>
-      </c>
-      <c r="AZ352">
-        <v>11</v>
-      </c>
       <c r="BA352">
         <v>2</v>
       </c>
       <c r="BB352">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC352">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD352">
-        <v>2.23</v>
+        <v>3.14</v>
       </c>
       <c r="BE352">
-        <v>6.75</v>
+        <v>8.9</v>
       </c>
       <c r="BF352">
-        <v>1.78</v>
+        <v>1.51</v>
       </c>
       <c r="BG352">
+        <v>1.25</v>
+      </c>
+      <c r="BH352">
+        <v>3.28</v>
+      </c>
+      <c r="BI352">
+        <v>1.7</v>
+      </c>
+      <c r="BJ352">
+        <v>2.05</v>
+      </c>
+      <c r="BK352">
+        <v>1.85</v>
+      </c>
+      <c r="BL352">
+        <v>1.85</v>
+      </c>
+      <c r="BM352">
+        <v>2.4</v>
+      </c>
+      <c r="BN352">
+        <v>1.48</v>
+      </c>
+      <c r="BO352">
+        <v>3.2</v>
+      </c>
+      <c r="BP352">
         <v>1.26</v>
-      </c>
-      <c r="BH352">
-        <v>3.4</v>
-      </c>
-      <c r="BI352">
-        <v>1.46</v>
-      </c>
-      <c r="BJ352">
-        <v>2.5</v>
-      </c>
-      <c r="BK352">
-        <v>1.73</v>
-      </c>
-      <c r="BL352">
-        <v>1.96</v>
-      </c>
-      <c r="BM352">
-        <v>2.15</v>
-      </c>
-      <c r="BN352">
-        <v>1.61</v>
-      </c>
-      <c r="BO352">
-        <v>2.7</v>
-      </c>
-      <c r="BP352">
-        <v>1.38</v>
       </c>
     </row>
     <row r="353" spans="1:68">
@@ -74254,7 +74254,7 @@
         <v>352</v>
       </c>
       <c r="B353">
-        <v>7727038</v>
+        <v>7727036</v>
       </c>
       <c r="C353" t="s">
         <v>68</v>
@@ -74269,190 +74269,190 @@
         <v>16</v>
       </c>
       <c r="G353" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H353" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="I353">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J353">
         <v>0</v>
       </c>
       <c r="K353">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L353">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M353">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N353">
         <v>3</v>
       </c>
       <c r="O353" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="P353" t="s">
-        <v>96</v>
+        <v>161</v>
       </c>
       <c r="Q353">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="R353">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="S353">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="T353">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="U353">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="V353">
-        <v>2.8</v>
+        <v>2.38</v>
       </c>
       <c r="W353">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="X353">
-        <v>6.6</v>
+        <v>5.5</v>
       </c>
       <c r="Y353">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Z353">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="AA353">
-        <v>3.35</v>
+        <v>3.61</v>
       </c>
       <c r="AB353">
-        <v>3.72</v>
+        <v>3.73</v>
       </c>
       <c r="AC353">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AD353">
-        <v>8.5</v>
+        <v>17</v>
       </c>
       <c r="AE353">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AF353">
-        <v>3.35</v>
+        <v>4.83</v>
       </c>
       <c r="AG353">
-        <v>1.98</v>
+        <v>1.73</v>
       </c>
       <c r="AH353">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="AI353">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AJ353">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="AK353">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AL353">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AM353">
         <v>1.67</v>
       </c>
       <c r="AN353">
-        <v>1.6</v>
+        <v>1.93</v>
       </c>
       <c r="AO353">
-        <v>1.36</v>
+        <v>0.62</v>
       </c>
       <c r="AP353">
-        <v>1.69</v>
+        <v>2</v>
       </c>
       <c r="AQ353">
-        <v>1.27</v>
+        <v>0.57</v>
       </c>
       <c r="AR353">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AS353">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AT353">
-        <v>2.81</v>
+        <v>2.68</v>
       </c>
       <c r="AU353">
+        <v>10</v>
+      </c>
+      <c r="AV353">
+        <v>4</v>
+      </c>
+      <c r="AW353">
+        <v>13</v>
+      </c>
+      <c r="AX353">
+        <v>2</v>
+      </c>
+      <c r="AY353">
+        <v>29</v>
+      </c>
+      <c r="AZ353">
+        <v>6</v>
+      </c>
+      <c r="BA353">
         <v>8</v>
       </c>
-      <c r="AV353">
-        <v>5</v>
-      </c>
-      <c r="AW353">
-        <v>3</v>
-      </c>
-      <c r="AX353">
-        <v>3</v>
-      </c>
-      <c r="AY353">
-        <v>13</v>
-      </c>
-      <c r="AZ353">
-        <v>10</v>
-      </c>
-      <c r="BA353">
-        <v>5</v>
-      </c>
       <c r="BB353">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BC353">
         <v>8</v>
       </c>
       <c r="BD353">
-        <v>1.45</v>
+        <v>1.77</v>
       </c>
       <c r="BE353">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="BF353">
-        <v>3.2</v>
+        <v>2.12</v>
       </c>
       <c r="BG353">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="BH353">
-        <v>4.35</v>
+        <v>3.55</v>
       </c>
       <c r="BI353">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="BJ353">
-        <v>2.82</v>
+        <v>2.55</v>
       </c>
       <c r="BK353">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="BL353">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="BM353">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="BN353">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="BO353">
-        <v>2.92</v>
+        <v>2.65</v>
       </c>
       <c r="BP353">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="354" spans="1:68">
@@ -74460,7 +74460,7 @@
         <v>353</v>
       </c>
       <c r="B354">
-        <v>7727153</v>
+        <v>7727068</v>
       </c>
       <c r="C354" t="s">
         <v>68</v>
@@ -74472,13 +74472,13 @@
         <v>45699.69791666666</v>
       </c>
       <c r="F354">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="G354" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H354" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="I354">
         <v>0</v>
@@ -74490,28 +74490,28 @@
         <v>0</v>
       </c>
       <c r="L354">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M354">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N354">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O354" t="s">
-        <v>314</v>
+        <v>96</v>
       </c>
       <c r="P354" t="s">
-        <v>189</v>
+        <v>96</v>
       </c>
       <c r="Q354">
-        <v>5</v>
+        <v>2.75</v>
       </c>
       <c r="R354">
         <v>2.2</v>
       </c>
       <c r="S354">
-        <v>2.4</v>
+        <v>3.75</v>
       </c>
       <c r="T354">
         <v>1.4</v>
@@ -74520,10 +74520,10 @@
         <v>2.75</v>
       </c>
       <c r="V354">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="W354">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="X354">
         <v>8</v>
@@ -74532,25 +74532,25 @@
         <v>1.08</v>
       </c>
       <c r="Z354">
-        <v>4.4</v>
+        <v>2.09</v>
       </c>
       <c r="AA354">
-        <v>3.56</v>
+        <v>3.47</v>
       </c>
       <c r="AB354">
-        <v>1.78</v>
+        <v>3.28</v>
       </c>
       <c r="AC354">
         <v>1.05</v>
       </c>
       <c r="AD354">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE354">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AF354">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="AG354">
         <v>1.98</v>
@@ -74559,106 +74559,106 @@
         <v>1.77</v>
       </c>
       <c r="AI354">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AJ354">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AK354">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="AL354">
         <v>1.25</v>
       </c>
       <c r="AM354">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="AN354">
-        <v>1.62</v>
+        <v>1.17</v>
       </c>
       <c r="AO354">
-        <v>1.43</v>
+        <v>0.71</v>
       </c>
       <c r="AP354">
+        <v>1.15</v>
+      </c>
+      <c r="AQ354">
+        <v>0.73</v>
+      </c>
+      <c r="AR354">
         <v>1.57</v>
       </c>
-      <c r="AQ354">
+      <c r="AS354">
+        <v>1.29</v>
+      </c>
+      <c r="AT354">
+        <v>2.86</v>
+      </c>
+      <c r="AU354">
+        <v>3</v>
+      </c>
+      <c r="AV354">
+        <v>9</v>
+      </c>
+      <c r="AW354">
+        <v>15</v>
+      </c>
+      <c r="AX354">
+        <v>8</v>
+      </c>
+      <c r="AY354">
+        <v>24</v>
+      </c>
+      <c r="AZ354">
+        <v>24</v>
+      </c>
+      <c r="BA354">
+        <v>5</v>
+      </c>
+      <c r="BB354">
+        <v>9</v>
+      </c>
+      <c r="BC354">
+        <v>14</v>
+      </c>
+      <c r="BD354">
+        <v>1.67</v>
+      </c>
+      <c r="BE354">
+        <v>6.75</v>
+      </c>
+      <c r="BF354">
+        <v>2.43</v>
+      </c>
+      <c r="BG354">
+        <v>1.26</v>
+      </c>
+      <c r="BH354">
+        <v>3.4</v>
+      </c>
+      <c r="BI354">
+        <v>1.46</v>
+      </c>
+      <c r="BJ354">
+        <v>2.48</v>
+      </c>
+      <c r="BK354">
+        <v>1.75</v>
+      </c>
+      <c r="BL354">
+        <v>1.95</v>
+      </c>
+      <c r="BM354">
+        <v>2.15</v>
+      </c>
+      <c r="BN354">
+        <v>1.61</v>
+      </c>
+      <c r="BO354">
+        <v>2.7</v>
+      </c>
+      <c r="BP354">
         <v>1.4</v>
-      </c>
-      <c r="AR354">
-        <v>1.15</v>
-      </c>
-      <c r="AS354">
-        <v>1.34</v>
-      </c>
-      <c r="AT354">
-        <v>2.49</v>
-      </c>
-      <c r="AU354">
-        <v>3</v>
-      </c>
-      <c r="AV354">
-        <v>5</v>
-      </c>
-      <c r="AW354">
-        <v>5</v>
-      </c>
-      <c r="AX354">
-        <v>5</v>
-      </c>
-      <c r="AY354">
-        <v>10</v>
-      </c>
-      <c r="AZ354">
-        <v>13</v>
-      </c>
-      <c r="BA354">
-        <v>2</v>
-      </c>
-      <c r="BB354">
-        <v>7</v>
-      </c>
-      <c r="BC354">
-        <v>9</v>
-      </c>
-      <c r="BD354">
-        <v>3.14</v>
-      </c>
-      <c r="BE354">
-        <v>8.9</v>
-      </c>
-      <c r="BF354">
-        <v>1.51</v>
-      </c>
-      <c r="BG354">
-        <v>1.25</v>
-      </c>
-      <c r="BH354">
-        <v>3.28</v>
-      </c>
-      <c r="BI354">
-        <v>1.7</v>
-      </c>
-      <c r="BJ354">
-        <v>2.05</v>
-      </c>
-      <c r="BK354">
-        <v>1.85</v>
-      </c>
-      <c r="BL354">
-        <v>1.85</v>
-      </c>
-      <c r="BM354">
-        <v>2.4</v>
-      </c>
-      <c r="BN354">
-        <v>1.48</v>
-      </c>
-      <c r="BO354">
-        <v>3.2</v>
-      </c>
-      <c r="BP354">
-        <v>1.26</v>
       </c>
     </row>
     <row r="355" spans="1:68">

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England EFL League One_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England EFL League One_20242025.xlsx
@@ -76094,13 +76094,13 @@
         <v>16</v>
       </c>
       <c r="BA361">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB361">
         <v>3</v>
       </c>
       <c r="BC361">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD361">
         <v>2.43</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England EFL League One_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England EFL League One_20242025.xlsx
@@ -81922,22 +81922,22 @@
         <v>2.63</v>
       </c>
       <c r="AU389">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV389">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AW389">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AX389">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AY389">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ389">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="BA389">
         <v>5</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England EFL League One_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England EFL League One_20242025.xlsx
@@ -1069,7 +1069,7 @@
     <t>['49']</t>
   </si>
   <si>
-    <t>['31', '49', '52', '65', '81']</t>
+    <t>['11', '90']</t>
   </si>
   <si>
     <t>['3', '8', '16', '29', '76']</t>
@@ -1078,7 +1078,7 @@
     <t>['11', '38']</t>
   </si>
   <si>
-    <t>['11', '90']</t>
+    <t>['31', '49', '52', '65', '81']</t>
   </si>
   <si>
     <t>['66', '90+5']</t>
@@ -1537,13 +1537,13 @@
     <t>['33', '64']</t>
   </si>
   <si>
+    <t>['22', '60']</t>
+  </si>
+  <si>
     <t>['11', '45']</t>
   </si>
   <si>
     <t>['56', '64', '73']</t>
-  </si>
-  <si>
-    <t>['22', '60']</t>
   </si>
   <si>
     <t>['38', '70']</t>
@@ -87209,7 +87209,7 @@
         <v>414</v>
       </c>
       <c r="B415">
-        <v>7727299</v>
+        <v>7727291</v>
       </c>
       <c r="C415" t="s">
         <v>68</v>
@@ -87224,190 +87224,190 @@
         <v>36</v>
       </c>
       <c r="G415" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="H415" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="I415">
         <v>0</v>
       </c>
       <c r="J415">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K415">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L415">
         <v>1</v>
       </c>
       <c r="M415">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N415">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O415" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="P415" t="s">
-        <v>96</v>
+        <v>507</v>
       </c>
       <c r="Q415">
-        <v>2.4</v>
+        <v>3.75</v>
       </c>
       <c r="R415">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S415">
-        <v>5.5</v>
+        <v>2.88</v>
       </c>
       <c r="T415">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="U415">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="V415">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="W415">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="X415">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y415">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Z415">
-        <v>1.72</v>
+        <v>3.08</v>
       </c>
       <c r="AA415">
         <v>3.47</v>
       </c>
       <c r="AB415">
+        <v>2.19</v>
+      </c>
+      <c r="AC415">
+        <v>1.05</v>
+      </c>
+      <c r="AD415">
+        <v>9.5</v>
+      </c>
+      <c r="AE415">
+        <v>1.3</v>
+      </c>
+      <c r="AF415">
+        <v>3.45</v>
+      </c>
+      <c r="AG415">
+        <v>1.87</v>
+      </c>
+      <c r="AH415">
+        <v>1.87</v>
+      </c>
+      <c r="AI415">
+        <v>1.75</v>
+      </c>
+      <c r="AJ415">
+        <v>2</v>
+      </c>
+      <c r="AK415">
+        <v>1.65</v>
+      </c>
+      <c r="AL415">
+        <v>1.25</v>
+      </c>
+      <c r="AM415">
+        <v>1.35</v>
+      </c>
+      <c r="AN415">
+        <v>0.82</v>
+      </c>
+      <c r="AO415">
+        <v>1.5</v>
+      </c>
+      <c r="AP415">
+        <v>0.78</v>
+      </c>
+      <c r="AQ415">
+        <v>1.5</v>
+      </c>
+      <c r="AR415">
+        <v>1.11</v>
+      </c>
+      <c r="AS415">
+        <v>1.14</v>
+      </c>
+      <c r="AT415">
+        <v>2.25</v>
+      </c>
+      <c r="AU415">
         <v>5</v>
       </c>
-      <c r="AC415">
-        <v>0</v>
-      </c>
-      <c r="AD415">
-        <v>0</v>
-      </c>
-      <c r="AE415">
-        <v>1.89</v>
-      </c>
-      <c r="AF415">
-        <v>1.91</v>
-      </c>
-      <c r="AG415">
-        <v>2.13</v>
-      </c>
-      <c r="AH415">
-        <v>1.65</v>
-      </c>
-      <c r="AI415">
-        <v>2.05</v>
-      </c>
-      <c r="AJ415">
-        <v>1.7</v>
-      </c>
-      <c r="AK415">
-        <v>0</v>
-      </c>
-      <c r="AL415">
-        <v>0</v>
-      </c>
-      <c r="AM415">
-        <v>0</v>
-      </c>
-      <c r="AN415">
-        <v>2.22</v>
-      </c>
-      <c r="AO415">
-        <v>0.82</v>
-      </c>
-      <c r="AP415">
-        <v>2.26</v>
-      </c>
-      <c r="AQ415">
-        <v>0.78</v>
-      </c>
-      <c r="AR415">
-        <v>1.45</v>
-      </c>
-      <c r="AS415">
-        <v>1.41</v>
-      </c>
-      <c r="AT415">
-        <v>2.86</v>
-      </c>
-      <c r="AU415">
-        <v>4</v>
-      </c>
       <c r="AV415">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW415">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AX415">
+        <v>7</v>
+      </c>
+      <c r="AY415">
+        <v>15</v>
+      </c>
+      <c r="AZ415">
+        <v>13</v>
+      </c>
+      <c r="BA415">
         <v>8</v>
       </c>
-      <c r="AY415">
-        <v>9</v>
-      </c>
-      <c r="AZ415">
-        <v>12</v>
-      </c>
-      <c r="BA415">
-        <v>2</v>
-      </c>
       <c r="BB415">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BC415">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="BD415">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BE415">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="BF415">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BG415">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="BH415">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="BI415">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BJ415">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BK415">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="BL415">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BM415">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="BN415">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BO415">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BP415">
-        <v>0</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="416" spans="1:68">
@@ -87415,7 +87415,7 @@
         <v>415</v>
       </c>
       <c r="B416">
-        <v>7727298</v>
+        <v>7727299</v>
       </c>
       <c r="C416" t="s">
         <v>68</v>
@@ -87430,10 +87430,10 @@
         <v>36</v>
       </c>
       <c r="G416" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H416" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="I416">
         <v>0</v>
@@ -87454,19 +87454,19 @@
         <v>1</v>
       </c>
       <c r="O416" t="s">
-        <v>341</v>
+        <v>183</v>
       </c>
       <c r="P416" t="s">
         <v>96</v>
       </c>
       <c r="Q416">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="R416">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S416">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="T416">
         <v>1.44</v>
@@ -87487,37 +87487,37 @@
         <v>1.06</v>
       </c>
       <c r="Z416">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AA416">
-        <v>3.3</v>
+        <v>3.47</v>
       </c>
       <c r="AB416">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AC416">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AD416">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AE416">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF416">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG416">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AH416">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AI416">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AJ416">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AK416">
         <v>0</v>
@@ -87529,52 +87529,52 @@
         <v>0</v>
       </c>
       <c r="AN416">
-        <v>1.12</v>
+        <v>2.22</v>
       </c>
       <c r="AO416">
-        <v>0.59</v>
+        <v>0.82</v>
       </c>
       <c r="AP416">
-        <v>1.22</v>
+        <v>2.26</v>
       </c>
       <c r="AQ416">
-        <v>0.53</v>
+        <v>0.78</v>
       </c>
       <c r="AR416">
-        <v>1.21</v>
+        <v>1.45</v>
       </c>
       <c r="AS416">
-        <v>1.08</v>
+        <v>1.41</v>
       </c>
       <c r="AT416">
-        <v>2.29</v>
+        <v>2.86</v>
       </c>
       <c r="AU416">
+        <v>4</v>
+      </c>
+      <c r="AV416">
+        <v>4</v>
+      </c>
+      <c r="AW416">
         <v>5</v>
       </c>
-      <c r="AV416">
-        <v>3</v>
-      </c>
-      <c r="AW416">
-        <v>2</v>
-      </c>
       <c r="AX416">
+        <v>8</v>
+      </c>
+      <c r="AY416">
         <v>9</v>
-      </c>
-      <c r="AY416">
-        <v>7</v>
       </c>
       <c r="AZ416">
         <v>12</v>
       </c>
       <c r="BA416">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BB416">
+        <v>7</v>
+      </c>
+      <c r="BC416">
         <v>9</v>
-      </c>
-      <c r="BC416">
-        <v>14</v>
       </c>
       <c r="BD416">
         <v>0</v>
@@ -87621,7 +87621,7 @@
         <v>416</v>
       </c>
       <c r="B417">
-        <v>7727296</v>
+        <v>7727298</v>
       </c>
       <c r="C417" t="s">
         <v>68</v>
@@ -87636,34 +87636,34 @@
         <v>36</v>
       </c>
       <c r="G417" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H417" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="I417">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J417">
         <v>0</v>
       </c>
       <c r="K417">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L417">
         <v>1</v>
       </c>
       <c r="M417">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N417">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O417" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="P417" t="s">
-        <v>357</v>
+        <v>96</v>
       </c>
       <c r="Q417">
         <v>2.5</v>
@@ -87675,10 +87675,10 @@
         <v>5</v>
       </c>
       <c r="T417">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="U417">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="V417">
         <v>3.4</v>
@@ -87693,25 +87693,25 @@
         <v>1.06</v>
       </c>
       <c r="Z417">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AA417">
-        <v>3.26</v>
+        <v>3.3</v>
       </c>
       <c r="AB417">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="AC417">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AD417">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE417">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AF417">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG417">
         <v>2.2</v>
@@ -87720,10 +87720,10 @@
         <v>1.61</v>
       </c>
       <c r="AI417">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AJ417">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AK417">
         <v>0</v>
@@ -87735,52 +87735,52 @@
         <v>0</v>
       </c>
       <c r="AN417">
-        <v>1.5</v>
+        <v>1.12</v>
       </c>
       <c r="AO417">
-        <v>1.24</v>
+        <v>0.59</v>
       </c>
       <c r="AP417">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="AQ417">
-        <v>1.16</v>
+        <v>0.53</v>
       </c>
       <c r="AR417">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AS417">
-        <v>1.39</v>
+        <v>1.08</v>
       </c>
       <c r="AT417">
-        <v>2.67</v>
+        <v>2.29</v>
       </c>
       <c r="AU417">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AV417">
         <v>3</v>
       </c>
       <c r="AW417">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AX417">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AY417">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ417">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="BA417">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BB417">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="BC417">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="BD417">
         <v>0</v>
@@ -87827,7 +87827,7 @@
         <v>417</v>
       </c>
       <c r="B418">
-        <v>7727295</v>
+        <v>7727296</v>
       </c>
       <c r="C418" t="s">
         <v>68</v>
@@ -87842,10 +87842,10 @@
         <v>36</v>
       </c>
       <c r="G418" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H418" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="I418">
         <v>1</v>
@@ -87866,127 +87866,127 @@
         <v>2</v>
       </c>
       <c r="O418" t="s">
-        <v>329</v>
+        <v>342</v>
       </c>
       <c r="P418" t="s">
-        <v>220</v>
+        <v>357</v>
       </c>
       <c r="Q418">
+        <v>2.5</v>
+      </c>
+      <c r="R418">
+        <v>2.05</v>
+      </c>
+      <c r="S418">
+        <v>5</v>
+      </c>
+      <c r="T418">
+        <v>1.5</v>
+      </c>
+      <c r="U418">
+        <v>2.5</v>
+      </c>
+      <c r="V418">
         <v>3.4</v>
       </c>
-      <c r="R418">
-        <v>2.25</v>
-      </c>
-      <c r="S418">
+      <c r="W418">
+        <v>1.3</v>
+      </c>
+      <c r="X418">
+        <v>10</v>
+      </c>
+      <c r="Y418">
+        <v>1.06</v>
+      </c>
+      <c r="Z418">
+        <v>1.79</v>
+      </c>
+      <c r="AA418">
+        <v>3.26</v>
+      </c>
+      <c r="AB418">
+        <v>4.9</v>
+      </c>
+      <c r="AC418">
+        <v>0</v>
+      </c>
+      <c r="AD418">
+        <v>0</v>
+      </c>
+      <c r="AE418">
+        <v>2.09</v>
+      </c>
+      <c r="AF418">
+        <v>1.73</v>
+      </c>
+      <c r="AG418">
+        <v>2.2</v>
+      </c>
+      <c r="AH418">
+        <v>1.61</v>
+      </c>
+      <c r="AI418">
+        <v>2.05</v>
+      </c>
+      <c r="AJ418">
+        <v>1.7</v>
+      </c>
+      <c r="AK418">
+        <v>0</v>
+      </c>
+      <c r="AL418">
+        <v>0</v>
+      </c>
+      <c r="AM418">
+        <v>0</v>
+      </c>
+      <c r="AN418">
+        <v>1.5</v>
+      </c>
+      <c r="AO418">
+        <v>1.24</v>
+      </c>
+      <c r="AP418">
+        <v>1.47</v>
+      </c>
+      <c r="AQ418">
+        <v>1.16</v>
+      </c>
+      <c r="AR418">
+        <v>1.28</v>
+      </c>
+      <c r="AS418">
+        <v>1.39</v>
+      </c>
+      <c r="AT418">
+        <v>2.67</v>
+      </c>
+      <c r="AU418">
+        <v>2</v>
+      </c>
+      <c r="AV418">
         <v>3</v>
       </c>
-      <c r="T418">
-        <v>1.36</v>
-      </c>
-      <c r="U418">
-        <v>3</v>
-      </c>
-      <c r="V418">
-        <v>2.63</v>
-      </c>
-      <c r="W418">
-        <v>1.44</v>
-      </c>
-      <c r="X418">
+      <c r="AW418">
+        <v>4</v>
+      </c>
+      <c r="AX418">
+        <v>4</v>
+      </c>
+      <c r="AY418">
+        <v>6</v>
+      </c>
+      <c r="AZ418">
         <v>7</v>
-      </c>
-      <c r="Y418">
-        <v>1.1</v>
-      </c>
-      <c r="Z418">
-        <v>2.88</v>
-      </c>
-      <c r="AA418">
-        <v>3.38</v>
-      </c>
-      <c r="AB418">
-        <v>2.34</v>
-      </c>
-      <c r="AC418">
-        <v>0</v>
-      </c>
-      <c r="AD418">
-        <v>0</v>
-      </c>
-      <c r="AE418">
-        <v>0</v>
-      </c>
-      <c r="AF418">
-        <v>0</v>
-      </c>
-      <c r="AG418">
-        <v>1.75</v>
-      </c>
-      <c r="AH418">
-        <v>2</v>
-      </c>
-      <c r="AI418">
-        <v>1.62</v>
-      </c>
-      <c r="AJ418">
-        <v>2.2</v>
-      </c>
-      <c r="AK418">
-        <v>0</v>
-      </c>
-      <c r="AL418">
-        <v>0</v>
-      </c>
-      <c r="AM418">
-        <v>0</v>
-      </c>
-      <c r="AN418">
-        <v>1.47</v>
-      </c>
-      <c r="AO418">
-        <v>1.88</v>
-      </c>
-      <c r="AP418">
-        <v>1.44</v>
-      </c>
-      <c r="AQ418">
-        <v>1.89</v>
-      </c>
-      <c r="AR418">
-        <v>1.27</v>
-      </c>
-      <c r="AS418">
-        <v>1.37</v>
-      </c>
-      <c r="AT418">
-        <v>2.64</v>
-      </c>
-      <c r="AU418">
-        <v>4</v>
-      </c>
-      <c r="AV418">
-        <v>5</v>
-      </c>
-      <c r="AW418">
-        <v>6</v>
-      </c>
-      <c r="AX418">
-        <v>10</v>
-      </c>
-      <c r="AY418">
-        <v>10</v>
-      </c>
-      <c r="AZ418">
-        <v>15</v>
       </c>
       <c r="BA418">
         <v>3</v>
       </c>
       <c r="BB418">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BC418">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BD418">
         <v>0</v>
@@ -88033,7 +88033,7 @@
         <v>418</v>
       </c>
       <c r="B419">
-        <v>7727294</v>
+        <v>7727295</v>
       </c>
       <c r="C419" t="s">
         <v>68</v>
@@ -88048,190 +88048,190 @@
         <v>36</v>
       </c>
       <c r="G419" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H419" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I419">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J419">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K419">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L419">
         <v>1</v>
       </c>
       <c r="M419">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N419">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O419" t="s">
-        <v>261</v>
+        <v>329</v>
       </c>
       <c r="P419" t="s">
-        <v>507</v>
+        <v>220</v>
       </c>
       <c r="Q419">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="R419">
         <v>2.25</v>
       </c>
       <c r="S419">
-        <v>6.5</v>
+        <v>3</v>
       </c>
       <c r="T419">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="U419">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="V419">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="W419">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="X419">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y419">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z419">
-        <v>1.52</v>
+        <v>2.88</v>
       </c>
       <c r="AA419">
-        <v>3.74</v>
+        <v>3.38</v>
       </c>
       <c r="AB419">
-        <v>6.9</v>
+        <v>2.34</v>
       </c>
       <c r="AC419">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AD419">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AE419">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF419">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AG419">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AH419">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AI419">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AJ419">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AK419">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AL419">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AM419">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AN419">
-        <v>1.67</v>
+        <v>1.47</v>
       </c>
       <c r="AO419">
-        <v>0.89</v>
+        <v>1.88</v>
       </c>
       <c r="AP419">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="AQ419">
-        <v>1</v>
+        <v>1.89</v>
       </c>
       <c r="AR419">
-        <v>1.52</v>
+        <v>1.27</v>
       </c>
       <c r="AS419">
-        <v>1.04</v>
+        <v>1.37</v>
       </c>
       <c r="AT419">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="AU419">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV419">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AW419">
         <v>6</v>
       </c>
       <c r="AX419">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY419">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ419">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BA419">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB419">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BC419">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="BD419">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BE419">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="BF419">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BG419">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="BH419">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="BI419">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BJ419">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="BK419">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="BL419">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BM419">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="BN419">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="BO419">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BP419">
-        <v>1.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="420" spans="1:68">
@@ -88239,7 +88239,7 @@
         <v>419</v>
       </c>
       <c r="B420">
-        <v>7727293</v>
+        <v>7727294</v>
       </c>
       <c r="C420" t="s">
         <v>68</v>
@@ -88254,43 +88254,43 @@
         <v>36</v>
       </c>
       <c r="G420" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H420" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="I420">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J420">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K420">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L420">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M420">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N420">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O420" t="s">
-        <v>343</v>
+        <v>261</v>
       </c>
       <c r="P420" t="s">
-        <v>96</v>
+        <v>508</v>
       </c>
       <c r="Q420">
-        <v>2.88</v>
+        <v>2.1</v>
       </c>
       <c r="R420">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S420">
-        <v>3.75</v>
+        <v>6.5</v>
       </c>
       <c r="T420">
         <v>1.4</v>
@@ -88299,10 +88299,10 @@
         <v>2.75</v>
       </c>
       <c r="V420">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="W420">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="X420">
         <v>8</v>
@@ -88311,13 +88311,13 @@
         <v>1.08</v>
       </c>
       <c r="Z420">
-        <v>2.2</v>
+        <v>1.52</v>
       </c>
       <c r="AA420">
-        <v>3.35</v>
+        <v>3.74</v>
       </c>
       <c r="AB420">
-        <v>3.15</v>
+        <v>6.9</v>
       </c>
       <c r="AC420">
         <v>1.06</v>
@@ -88326,10 +88326,10 @@
         <v>8.5</v>
       </c>
       <c r="AE420">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AF420">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AG420">
         <v>1.91</v>
@@ -88338,58 +88338,58 @@
         <v>1.83</v>
       </c>
       <c r="AI420">
+        <v>2</v>
+      </c>
+      <c r="AJ420">
         <v>1.75</v>
       </c>
-      <c r="AJ420">
-        <v>2</v>
-      </c>
       <c r="AK420">
-        <v>1.35</v>
+        <v>1.11</v>
       </c>
       <c r="AL420">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AM420">
-        <v>1.65</v>
+        <v>2.45</v>
       </c>
       <c r="AN420">
-        <v>1.19</v>
+        <v>1.67</v>
       </c>
       <c r="AO420">
-        <v>0.59</v>
+        <v>0.89</v>
       </c>
       <c r="AP420">
-        <v>1.39</v>
+        <v>1.58</v>
       </c>
       <c r="AQ420">
-        <v>0.5600000000000001</v>
+        <v>1</v>
       </c>
       <c r="AR420">
-        <v>1.3</v>
+        <v>1.52</v>
       </c>
       <c r="AS420">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AT420">
-        <v>2.3</v>
+        <v>2.56</v>
       </c>
       <c r="AU420">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AV420">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AW420">
+        <v>6</v>
+      </c>
+      <c r="AX420">
+        <v>11</v>
+      </c>
+      <c r="AY420">
         <v>9</v>
       </c>
-      <c r="AX420">
-        <v>7</v>
-      </c>
-      <c r="AY420">
-        <v>14</v>
-      </c>
       <c r="AZ420">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="BA420">
         <v>4</v>
@@ -88401,43 +88401,43 @@
         <v>10</v>
       </c>
       <c r="BD420">
-        <v>1.58</v>
+        <v>1.28</v>
       </c>
       <c r="BE420">
-        <v>6.75</v>
+        <v>7.5</v>
       </c>
       <c r="BF420">
-        <v>2.55</v>
+        <v>4</v>
       </c>
       <c r="BG420">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="BH420">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="BI420">
-        <v>1.46</v>
+        <v>1.6</v>
       </c>
       <c r="BJ420">
-        <v>2.5</v>
+        <v>2.17</v>
       </c>
       <c r="BK420">
-        <v>1.74</v>
+        <v>1.96</v>
       </c>
       <c r="BL420">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="BM420">
-        <v>2.17</v>
+        <v>2.48</v>
       </c>
       <c r="BN420">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="BO420">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="BP420">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="421" spans="1:68">
@@ -88487,7 +88487,7 @@
         <v>96</v>
       </c>
       <c r="P421" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="Q421">
         <v>2.75</v>
@@ -89063,7 +89063,7 @@
         <v>423</v>
       </c>
       <c r="B424">
-        <v>7727291</v>
+        <v>7727293</v>
       </c>
       <c r="C424" t="s">
         <v>68</v>
@@ -89078,43 +89078,43 @@
         <v>36</v>
       </c>
       <c r="G424" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H424" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I424">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J424">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K424">
         <v>1</v>
       </c>
       <c r="L424">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M424">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N424">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O424" t="s">
-        <v>189</v>
+        <v>343</v>
       </c>
       <c r="P424" t="s">
-        <v>509</v>
+        <v>96</v>
       </c>
       <c r="Q424">
-        <v>3.75</v>
+        <v>2.88</v>
       </c>
       <c r="R424">
         <v>2.2</v>
       </c>
       <c r="S424">
-        <v>2.88</v>
+        <v>3.75</v>
       </c>
       <c r="T424">
         <v>1.4</v>
@@ -89135,31 +89135,31 @@
         <v>1.08</v>
       </c>
       <c r="Z424">
-        <v>3.08</v>
+        <v>2.2</v>
       </c>
       <c r="AA424">
-        <v>3.47</v>
+        <v>3.35</v>
       </c>
       <c r="AB424">
-        <v>2.19</v>
+        <v>3.15</v>
       </c>
       <c r="AC424">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AD424">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="AE424">
         <v>1.3</v>
       </c>
       <c r="AF424">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="AG424">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AH424">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AI424">
         <v>1.75</v>
@@ -89168,34 +89168,34 @@
         <v>2</v>
       </c>
       <c r="AK424">
-        <v>1.65</v>
+        <v>1.35</v>
       </c>
       <c r="AL424">
         <v>1.25</v>
       </c>
       <c r="AM424">
-        <v>1.35</v>
+        <v>1.65</v>
       </c>
       <c r="AN424">
-        <v>0.82</v>
+        <v>1.19</v>
       </c>
       <c r="AO424">
-        <v>1.5</v>
+        <v>0.59</v>
       </c>
       <c r="AP424">
-        <v>0.78</v>
+        <v>1.39</v>
       </c>
       <c r="AQ424">
-        <v>1.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR424">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AS424">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AT424">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AU424">
         <v>5</v>
@@ -89204,64 +89204,64 @@
         <v>3</v>
       </c>
       <c r="AW424">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AX424">
         <v>7</v>
       </c>
       <c r="AY424">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ424">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BA424">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="BB424">
         <v>6</v>
       </c>
       <c r="BC424">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="BD424">
-        <v>2.32</v>
+        <v>1.58</v>
       </c>
       <c r="BE424">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
       <c r="BF424">
+        <v>2.55</v>
+      </c>
+      <c r="BG424">
+        <v>1.26</v>
+      </c>
+      <c r="BH424">
+        <v>3.4</v>
+      </c>
+      <c r="BI424">
+        <v>1.46</v>
+      </c>
+      <c r="BJ424">
+        <v>2.5</v>
+      </c>
+      <c r="BK424">
         <v>1.74</v>
       </c>
-      <c r="BG424">
-        <v>1.34</v>
-      </c>
-      <c r="BH424">
-        <v>2.9</v>
-      </c>
-      <c r="BI424">
-        <v>1.58</v>
-      </c>
-      <c r="BJ424">
-        <v>2.2</v>
-      </c>
-      <c r="BK424">
-        <v>1.93</v>
-      </c>
       <c r="BL424">
-        <v>1.76</v>
+        <v>1.95</v>
       </c>
       <c r="BM424">
-        <v>2.43</v>
+        <v>2.17</v>
       </c>
       <c r="BN424">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="BO424">
-        <v>3.15</v>
+        <v>2.7</v>
       </c>
       <c r="BP424">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="425" spans="1:68">
@@ -89475,7 +89475,7 @@
         <v>425</v>
       </c>
       <c r="B426">
-        <v>7727032</v>
+        <v>7727132</v>
       </c>
       <c r="C426" t="s">
         <v>68</v>
@@ -89487,193 +89487,193 @@
         <v>45727.69791666666</v>
       </c>
       <c r="F426">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G426" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="H426" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I426">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J426">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K426">
         <v>1</v>
       </c>
       <c r="L426">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M426">
         <v>1</v>
       </c>
       <c r="N426">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O426" t="s">
-        <v>345</v>
+        <v>96</v>
       </c>
       <c r="P426" t="s">
-        <v>484</v>
+        <v>294</v>
       </c>
       <c r="Q426">
-        <v>1.91</v>
+        <v>4</v>
       </c>
       <c r="R426">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S426">
-        <v>6.5</v>
+        <v>2.88</v>
       </c>
       <c r="T426">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="U426">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="V426">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="W426">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="X426">
-        <v>6.6</v>
+        <v>9</v>
       </c>
       <c r="Y426">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z426">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="AA426">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="AB426">
-        <v>6.2</v>
+        <v>2.04</v>
       </c>
       <c r="AC426">
         <v>1.05</v>
       </c>
       <c r="AD426">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="AE426">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AF426">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="AG426">
-        <v>2.13</v>
+        <v>1.82</v>
       </c>
       <c r="AH426">
-        <v>1.65</v>
+        <v>1.92</v>
       </c>
       <c r="AI426">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AJ426">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AK426">
-        <v>1.08</v>
+        <v>1.7</v>
       </c>
       <c r="AL426">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AM426">
-        <v>2.75</v>
+        <v>1.33</v>
       </c>
       <c r="AN426">
-        <v>2.67</v>
+        <v>1.06</v>
       </c>
       <c r="AO426">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AP426">
-        <v>2.68</v>
+        <v>1</v>
       </c>
       <c r="AQ426">
-        <v>1.17</v>
+        <v>1.39</v>
       </c>
       <c r="AR426">
-        <v>1.84</v>
+        <v>1.19</v>
       </c>
       <c r="AS426">
-        <v>1.12</v>
+        <v>1.32</v>
       </c>
       <c r="AT426">
-        <v>2.96</v>
+        <v>2.51</v>
       </c>
       <c r="AU426">
+        <v>0</v>
+      </c>
+      <c r="AV426">
+        <v>2</v>
+      </c>
+      <c r="AW426">
+        <v>0</v>
+      </c>
+      <c r="AX426">
+        <v>0</v>
+      </c>
+      <c r="AY426">
         <v>4</v>
       </c>
-      <c r="AV426">
+      <c r="AZ426">
         <v>4</v>
       </c>
-      <c r="AW426">
-        <v>9</v>
-      </c>
-      <c r="AX426">
+      <c r="BA426">
         <v>7</v>
-      </c>
-      <c r="AY426">
-        <v>13</v>
-      </c>
-      <c r="AZ426">
-        <v>11</v>
-      </c>
-      <c r="BA426">
-        <v>8</v>
       </c>
       <c r="BB426">
         <v>4</v>
       </c>
       <c r="BC426">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BD426">
-        <v>1.31</v>
+        <v>2.1</v>
       </c>
       <c r="BE426">
-        <v>10.25</v>
+        <v>6.75</v>
       </c>
       <c r="BF426">
-        <v>4.33</v>
+        <v>1.86</v>
       </c>
       <c r="BG426">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="BH426">
-        <v>3.42</v>
+        <v>3.55</v>
       </c>
       <c r="BI426">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="BJ426">
-        <v>2.48</v>
+        <v>2.65</v>
       </c>
       <c r="BK426">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="BL426">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="BM426">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="BN426">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="BO426">
-        <v>3.05</v>
+        <v>2.55</v>
       </c>
       <c r="BP426">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="427" spans="1:68">
@@ -89681,7 +89681,7 @@
         <v>426</v>
       </c>
       <c r="B427">
-        <v>7477943</v>
+        <v>7727032</v>
       </c>
       <c r="C427" t="s">
         <v>68</v>
@@ -89693,13 +89693,13 @@
         <v>45727.69791666666</v>
       </c>
       <c r="F427">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G427" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H427" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="I427">
         <v>1</v>
@@ -89714,172 +89714,172 @@
         <v>2</v>
       </c>
       <c r="M427">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N427">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O427" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="P427" t="s">
-        <v>96</v>
+        <v>484</v>
       </c>
       <c r="Q427">
-        <v>3.75</v>
+        <v>1.91</v>
       </c>
       <c r="R427">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S427">
-        <v>2.88</v>
+        <v>6.5</v>
       </c>
       <c r="T427">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="U427">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="V427">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="W427">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="X427">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="Y427">
         <v>1.08</v>
       </c>
       <c r="Z427">
-        <v>2.57</v>
+        <v>1.5</v>
       </c>
       <c r="AA427">
-        <v>3.61</v>
+        <v>4.1</v>
       </c>
       <c r="AB427">
-        <v>2.47</v>
+        <v>6.2</v>
       </c>
       <c r="AC427">
         <v>1.05</v>
       </c>
       <c r="AD427">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="AE427">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AF427">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="AG427">
-        <v>1.71</v>
+        <v>2.13</v>
       </c>
       <c r="AH427">
-        <v>2.01</v>
+        <v>1.65</v>
       </c>
       <c r="AI427">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AJ427">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="AK427">
-        <v>1.66</v>
+        <v>1.08</v>
       </c>
       <c r="AL427">
+        <v>1.17</v>
+      </c>
+      <c r="AM427">
+        <v>2.75</v>
+      </c>
+      <c r="AN427">
+        <v>2.67</v>
+      </c>
+      <c r="AO427">
         <v>1.25</v>
       </c>
-      <c r="AM427">
-        <v>1.36</v>
-      </c>
-      <c r="AN427">
-        <v>1.29</v>
-      </c>
-      <c r="AO427">
-        <v>1.22</v>
-      </c>
       <c r="AP427">
-        <v>1.39</v>
+        <v>2.68</v>
       </c>
       <c r="AQ427">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AR427">
-        <v>1.32</v>
+        <v>1.84</v>
       </c>
       <c r="AS427">
-        <v>1.36</v>
+        <v>1.12</v>
       </c>
       <c r="AT427">
-        <v>2.68</v>
+        <v>2.96</v>
       </c>
       <c r="AU427">
+        <v>4</v>
+      </c>
+      <c r="AV427">
+        <v>4</v>
+      </c>
+      <c r="AW427">
+        <v>9</v>
+      </c>
+      <c r="AX427">
         <v>7</v>
-      </c>
-      <c r="AV427">
-        <v>0</v>
-      </c>
-      <c r="AW427">
-        <v>6</v>
-      </c>
-      <c r="AX427">
-        <v>6</v>
       </c>
       <c r="AY427">
         <v>13</v>
       </c>
       <c r="AZ427">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="BA427">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BB427">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BC427">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="BD427">
-        <v>2.23</v>
+        <v>1.31</v>
       </c>
       <c r="BE427">
-        <v>8.800000000000001</v>
+        <v>10.25</v>
       </c>
       <c r="BF427">
-        <v>1.88</v>
+        <v>4.33</v>
       </c>
       <c r="BG427">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="BH427">
-        <v>4</v>
+        <v>3.42</v>
       </c>
       <c r="BI427">
-        <v>1.29</v>
+        <v>1.45</v>
       </c>
       <c r="BJ427">
-        <v>3.04</v>
+        <v>2.48</v>
       </c>
       <c r="BK427">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="BL427">
-        <v>2.23</v>
+        <v>1.91</v>
       </c>
       <c r="BM427">
-        <v>1.94</v>
+        <v>2.3</v>
       </c>
       <c r="BN427">
-        <v>1.77</v>
+        <v>1.52</v>
       </c>
       <c r="BO427">
-        <v>2.48</v>
+        <v>3.05</v>
       </c>
       <c r="BP427">
-        <v>1.45</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="428" spans="1:68">
@@ -89887,7 +89887,7 @@
         <v>427</v>
       </c>
       <c r="B428">
-        <v>7727151</v>
+        <v>7477943</v>
       </c>
       <c r="C428" t="s">
         <v>68</v>
@@ -89899,46 +89899,46 @@
         <v>45727.69791666666</v>
       </c>
       <c r="F428">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="G428" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H428" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="I428">
         <v>1</v>
       </c>
       <c r="J428">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K428">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L428">
         <v>2</v>
       </c>
       <c r="M428">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N428">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O428" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="P428" t="s">
-        <v>381</v>
+        <v>96</v>
       </c>
       <c r="Q428">
+        <v>3.75</v>
+      </c>
+      <c r="R428">
         <v>2.2</v>
       </c>
-      <c r="R428">
-        <v>2.25</v>
-      </c>
       <c r="S428">
-        <v>5.5</v>
+        <v>2.88</v>
       </c>
       <c r="T428">
         <v>1.36</v>
@@ -89953,139 +89953,139 @@
         <v>1.4</v>
       </c>
       <c r="X428">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y428">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z428">
-        <v>1.53</v>
+        <v>2.57</v>
       </c>
       <c r="AA428">
-        <v>4</v>
+        <v>3.61</v>
       </c>
       <c r="AB428">
-        <v>6</v>
+        <v>2.47</v>
       </c>
       <c r="AC428">
         <v>1.05</v>
       </c>
       <c r="AD428">
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="AE428">
         <v>1.28</v>
       </c>
       <c r="AF428">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="AG428">
+        <v>1.71</v>
+      </c>
+      <c r="AH428">
+        <v>2.01</v>
+      </c>
+      <c r="AI428">
+        <v>1.67</v>
+      </c>
+      <c r="AJ428">
+        <v>2.1</v>
+      </c>
+      <c r="AK428">
+        <v>1.66</v>
+      </c>
+      <c r="AL428">
+        <v>1.25</v>
+      </c>
+      <c r="AM428">
+        <v>1.36</v>
+      </c>
+      <c r="AN428">
+        <v>1.29</v>
+      </c>
+      <c r="AO428">
+        <v>1.22</v>
+      </c>
+      <c r="AP428">
+        <v>1.39</v>
+      </c>
+      <c r="AQ428">
+        <v>1.16</v>
+      </c>
+      <c r="AR428">
+        <v>1.32</v>
+      </c>
+      <c r="AS428">
+        <v>1.36</v>
+      </c>
+      <c r="AT428">
+        <v>2.68</v>
+      </c>
+      <c r="AU428">
+        <v>7</v>
+      </c>
+      <c r="AV428">
+        <v>0</v>
+      </c>
+      <c r="AW428">
+        <v>6</v>
+      </c>
+      <c r="AX428">
+        <v>6</v>
+      </c>
+      <c r="AY428">
+        <v>13</v>
+      </c>
+      <c r="AZ428">
+        <v>6</v>
+      </c>
+      <c r="BA428">
+        <v>5</v>
+      </c>
+      <c r="BB428">
+        <v>1</v>
+      </c>
+      <c r="BC428">
+        <v>6</v>
+      </c>
+      <c r="BD428">
+        <v>2.23</v>
+      </c>
+      <c r="BE428">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF428">
+        <v>1.88</v>
+      </c>
+      <c r="BG428">
+        <v>1.2</v>
+      </c>
+      <c r="BH428">
+        <v>4</v>
+      </c>
+      <c r="BI428">
+        <v>1.29</v>
+      </c>
+      <c r="BJ428">
+        <v>3.04</v>
+      </c>
+      <c r="BK428">
+        <v>1.55</v>
+      </c>
+      <c r="BL428">
+        <v>2.23</v>
+      </c>
+      <c r="BM428">
+        <v>1.94</v>
+      </c>
+      <c r="BN428">
         <v>1.77</v>
       </c>
-      <c r="AH428">
-        <v>1.98</v>
-      </c>
-      <c r="AI428">
-        <v>1.91</v>
-      </c>
-      <c r="AJ428">
-        <v>1.91</v>
-      </c>
-      <c r="AK428">
-        <v>1.14</v>
-      </c>
-      <c r="AL428">
-        <v>1.2</v>
-      </c>
-      <c r="AM428">
-        <v>2.25</v>
-      </c>
-      <c r="AN428">
-        <v>1.25</v>
-      </c>
-      <c r="AO428">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="AP428">
-        <v>1.28</v>
-      </c>
-      <c r="AQ428">
-        <v>0.53</v>
-      </c>
-      <c r="AR428">
-        <v>1.56</v>
-      </c>
-      <c r="AS428">
-        <v>1.09</v>
-      </c>
-      <c r="AT428">
-        <v>2.65</v>
-      </c>
-      <c r="AU428">
-        <v>11</v>
-      </c>
-      <c r="AV428">
-        <v>4</v>
-      </c>
-      <c r="AW428">
-        <v>1</v>
-      </c>
-      <c r="AX428">
-        <v>11</v>
-      </c>
-      <c r="AY428">
-        <v>12</v>
-      </c>
-      <c r="AZ428">
-        <v>15</v>
-      </c>
-      <c r="BA428">
-        <v>6</v>
-      </c>
-      <c r="BB428">
-        <v>7</v>
-      </c>
-      <c r="BC428">
-        <v>13</v>
-      </c>
-      <c r="BD428">
+      <c r="BO428">
+        <v>2.48</v>
+      </c>
+      <c r="BP428">
         <v>1.45</v>
-      </c>
-      <c r="BE428">
-        <v>6.75</v>
-      </c>
-      <c r="BF428">
-        <v>3.15</v>
-      </c>
-      <c r="BG428">
-        <v>1.33</v>
-      </c>
-      <c r="BH428">
-        <v>2.95</v>
-      </c>
-      <c r="BI428">
-        <v>1.56</v>
-      </c>
-      <c r="BJ428">
-        <v>2.23</v>
-      </c>
-      <c r="BK428">
-        <v>1.91</v>
-      </c>
-      <c r="BL428">
-        <v>1.77</v>
-      </c>
-      <c r="BM428">
-        <v>2.4</v>
-      </c>
-      <c r="BN428">
-        <v>1.49</v>
-      </c>
-      <c r="BO428">
-        <v>3.05</v>
-      </c>
-      <c r="BP428">
-        <v>1.3</v>
       </c>
     </row>
     <row r="429" spans="1:68">
@@ -90093,7 +90093,7 @@
         <v>428</v>
       </c>
       <c r="B429">
-        <v>7727132</v>
+        <v>7727151</v>
       </c>
       <c r="C429" t="s">
         <v>68</v>
@@ -90105,193 +90105,193 @@
         <v>45727.69791666666</v>
       </c>
       <c r="F429">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G429" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="H429" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="I429">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J429">
         <v>1</v>
       </c>
       <c r="K429">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L429">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M429">
         <v>1</v>
       </c>
       <c r="N429">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O429" t="s">
-        <v>96</v>
+        <v>347</v>
       </c>
       <c r="P429" t="s">
-        <v>294</v>
+        <v>381</v>
       </c>
       <c r="Q429">
+        <v>2.2</v>
+      </c>
+      <c r="R429">
+        <v>2.25</v>
+      </c>
+      <c r="S429">
+        <v>5.5</v>
+      </c>
+      <c r="T429">
+        <v>1.36</v>
+      </c>
+      <c r="U429">
+        <v>3</v>
+      </c>
+      <c r="V429">
+        <v>2.75</v>
+      </c>
+      <c r="W429">
+        <v>1.4</v>
+      </c>
+      <c r="X429">
+        <v>7</v>
+      </c>
+      <c r="Y429">
+        <v>1.1</v>
+      </c>
+      <c r="Z429">
+        <v>1.53</v>
+      </c>
+      <c r="AA429">
         <v>4</v>
       </c>
-      <c r="R429">
-        <v>2.1</v>
-      </c>
-      <c r="S429">
-        <v>2.88</v>
-      </c>
-      <c r="T429">
-        <v>1.44</v>
-      </c>
-      <c r="U429">
-        <v>2.63</v>
-      </c>
-      <c r="V429">
-        <v>3.25</v>
-      </c>
-      <c r="W429">
-        <v>1.33</v>
-      </c>
-      <c r="X429">
-        <v>9</v>
-      </c>
-      <c r="Y429">
-        <v>1.07</v>
-      </c>
-      <c r="Z429">
-        <v>3.4</v>
-      </c>
-      <c r="AA429">
-        <v>3.5</v>
-      </c>
       <c r="AB429">
-        <v>2.04</v>
+        <v>6</v>
       </c>
       <c r="AC429">
         <v>1.05</v>
       </c>
       <c r="AD429">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="AE429">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AF429">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="AG429">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="AH429">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="AI429">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AJ429">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AK429">
-        <v>1.7</v>
+        <v>1.14</v>
       </c>
       <c r="AL429">
+        <v>1.2</v>
+      </c>
+      <c r="AM429">
+        <v>2.25</v>
+      </c>
+      <c r="AN429">
         <v>1.25</v>
       </c>
-      <c r="AM429">
-        <v>1.33</v>
-      </c>
-      <c r="AN429">
-        <v>1.06</v>
-      </c>
       <c r="AO429">
-        <v>1.29</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP429">
-        <v>1</v>
+        <v>1.28</v>
       </c>
       <c r="AQ429">
-        <v>1.39</v>
+        <v>0.53</v>
       </c>
       <c r="AR429">
-        <v>1.19</v>
+        <v>1.56</v>
       </c>
       <c r="AS429">
-        <v>1.32</v>
+        <v>1.09</v>
       </c>
       <c r="AT429">
-        <v>2.51</v>
+        <v>2.65</v>
       </c>
       <c r="AU429">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AV429">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AW429">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX429">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AY429">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AZ429">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="BA429">
+        <v>6</v>
+      </c>
+      <c r="BB429">
         <v>7</v>
       </c>
-      <c r="BB429">
-        <v>4</v>
-      </c>
       <c r="BC429">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BD429">
-        <v>2.1</v>
+        <v>1.45</v>
       </c>
       <c r="BE429">
         <v>6.75</v>
       </c>
       <c r="BF429">
-        <v>1.86</v>
+        <v>3.15</v>
       </c>
       <c r="BG429">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="BH429">
-        <v>3.55</v>
+        <v>2.95</v>
       </c>
       <c r="BI429">
-        <v>1.41</v>
+        <v>1.56</v>
       </c>
       <c r="BJ429">
-        <v>2.65</v>
+        <v>2.23</v>
       </c>
       <c r="BK429">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="BL429">
-        <v>2.05</v>
+        <v>1.77</v>
       </c>
       <c r="BM429">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="BN429">
-        <v>1.67</v>
+        <v>1.49</v>
       </c>
       <c r="BO429">
-        <v>2.55</v>
+        <v>3.05</v>
       </c>
       <c r="BP429">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="430" spans="1:68">
@@ -90917,7 +90917,7 @@
         <v>432</v>
       </c>
       <c r="B433">
-        <v>7727311</v>
+        <v>7727310</v>
       </c>
       <c r="C433" t="s">
         <v>68</v>
@@ -90932,10 +90932,10 @@
         <v>37</v>
       </c>
       <c r="G433" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="H433" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="I433">
         <v>0</v>
@@ -90950,172 +90950,172 @@
         <v>0</v>
       </c>
       <c r="M433">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N433">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O433" t="s">
         <v>96</v>
       </c>
       <c r="P433" t="s">
-        <v>264</v>
+        <v>511</v>
       </c>
       <c r="Q433">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="R433">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S433">
         <v>4</v>
       </c>
       <c r="T433">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="U433">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="V433">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="W433">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="X433">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y433">
+        <v>1.06</v>
+      </c>
+      <c r="Z433">
+        <v>2.25</v>
+      </c>
+      <c r="AA433">
+        <v>3.09</v>
+      </c>
+      <c r="AB433">
+        <v>3.32</v>
+      </c>
+      <c r="AC433">
+        <v>1.09</v>
+      </c>
+      <c r="AD433">
+        <v>7</v>
+      </c>
+      <c r="AE433">
+        <v>1.45</v>
+      </c>
+      <c r="AF433">
+        <v>2.7</v>
+      </c>
+      <c r="AG433">
+        <v>2.2</v>
+      </c>
+      <c r="AH433">
+        <v>1.61</v>
+      </c>
+      <c r="AI433">
+        <v>1.95</v>
+      </c>
+      <c r="AJ433">
+        <v>1.8</v>
+      </c>
+      <c r="AK433">
+        <v>1.34</v>
+      </c>
+      <c r="AL433">
+        <v>1.34</v>
+      </c>
+      <c r="AM433">
+        <v>1.6</v>
+      </c>
+      <c r="AN433">
+        <v>1</v>
+      </c>
+      <c r="AO433">
+        <v>1.06</v>
+      </c>
+      <c r="AP433">
+        <v>0.95</v>
+      </c>
+      <c r="AQ433">
+        <v>1.16</v>
+      </c>
+      <c r="AR433">
+        <v>1.15</v>
+      </c>
+      <c r="AS433">
         <v>1.08</v>
       </c>
-      <c r="Z433">
-        <v>2.09</v>
-      </c>
-      <c r="AA433">
-        <v>3.5</v>
-      </c>
-      <c r="AB433">
-        <v>3.28</v>
-      </c>
-      <c r="AC433">
-        <v>1.07</v>
-      </c>
-      <c r="AD433">
-        <v>8</v>
-      </c>
-      <c r="AE433">
-        <v>1.4</v>
-      </c>
-      <c r="AF433">
-        <v>2.9</v>
-      </c>
-      <c r="AG433">
-        <v>1.92</v>
-      </c>
-      <c r="AH433">
-        <v>1.82</v>
-      </c>
-      <c r="AI433">
-        <v>1.8</v>
-      </c>
-      <c r="AJ433">
-        <v>1.95</v>
-      </c>
-      <c r="AK433">
-        <v>1.25</v>
-      </c>
-      <c r="AL433">
-        <v>1.25</v>
-      </c>
-      <c r="AM433">
-        <v>1.77</v>
-      </c>
-      <c r="AN433">
-        <v>2.06</v>
-      </c>
-      <c r="AO433">
-        <v>1.47</v>
-      </c>
-      <c r="AP433">
-        <v>1.94</v>
-      </c>
-      <c r="AQ433">
-        <v>1.56</v>
-      </c>
-      <c r="AR433">
-        <v>1.49</v>
-      </c>
-      <c r="AS433">
-        <v>1.27</v>
-      </c>
       <c r="AT433">
-        <v>2.76</v>
+        <v>2.23</v>
       </c>
       <c r="AU433">
         <v>4</v>
       </c>
       <c r="AV433">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW433">
+        <v>7</v>
+      </c>
+      <c r="AX433">
         <v>8</v>
       </c>
-      <c r="AX433">
-        <v>2</v>
-      </c>
       <c r="AY433">
+        <v>11</v>
+      </c>
+      <c r="AZ433">
         <v>12</v>
       </c>
-      <c r="AZ433">
+      <c r="BA433">
         <v>5</v>
       </c>
-      <c r="BA433">
-        <v>2</v>
-      </c>
       <c r="BB433">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="BC433">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="BD433">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="BE433">
         <v>7.1</v>
       </c>
       <c r="BF433">
-        <v>3.55</v>
+        <v>3.34</v>
       </c>
       <c r="BG433">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="BH433">
-        <v>3.34</v>
+        <v>3.8</v>
       </c>
       <c r="BI433">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="BJ433">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="BK433">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="BL433">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="BM433">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="BN433">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="BO433">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="BP433">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="434" spans="1:68">
@@ -91123,7 +91123,7 @@
         <v>433</v>
       </c>
       <c r="B434">
-        <v>7727310</v>
+        <v>7727309</v>
       </c>
       <c r="C434" t="s">
         <v>68</v>
@@ -91138,190 +91138,190 @@
         <v>37</v>
       </c>
       <c r="G434" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H434" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="I434">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J434">
         <v>0</v>
       </c>
       <c r="K434">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L434">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M434">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N434">
         <v>2</v>
       </c>
       <c r="O434" t="s">
-        <v>96</v>
+        <v>349</v>
       </c>
       <c r="P434" t="s">
-        <v>511</v>
+        <v>425</v>
       </c>
       <c r="Q434">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="R434">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S434">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="T434">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="U434">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="V434">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="W434">
+        <v>1.33</v>
+      </c>
+      <c r="X434">
+        <v>9</v>
+      </c>
+      <c r="Y434">
+        <v>1.07</v>
+      </c>
+      <c r="Z434">
+        <v>1.72</v>
+      </c>
+      <c r="AA434">
+        <v>3.79</v>
+      </c>
+      <c r="AB434">
+        <v>4.4</v>
+      </c>
+      <c r="AC434">
+        <v>1.05</v>
+      </c>
+      <c r="AD434">
+        <v>9</v>
+      </c>
+      <c r="AE434">
         <v>1.3</v>
       </c>
-      <c r="X434">
-        <v>10</v>
-      </c>
-      <c r="Y434">
-        <v>1.06</v>
-      </c>
-      <c r="Z434">
-        <v>2.25</v>
-      </c>
-      <c r="AA434">
-        <v>3.09</v>
-      </c>
-      <c r="AB434">
-        <v>3.32</v>
-      </c>
-      <c r="AC434">
-        <v>1.09</v>
-      </c>
-      <c r="AD434">
-        <v>7</v>
-      </c>
-      <c r="AE434">
-        <v>1.45</v>
-      </c>
       <c r="AF434">
-        <v>2.7</v>
+        <v>3.35</v>
       </c>
       <c r="AG434">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="AH434">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="AI434">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AJ434">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AK434">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="AL434">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="AM434">
-        <v>1.6</v>
+        <v>2.05</v>
       </c>
       <c r="AN434">
-        <v>1</v>
+        <v>1.76</v>
       </c>
       <c r="AO434">
         <v>1.06</v>
       </c>
       <c r="AP434">
-        <v>0.95</v>
+        <v>1.63</v>
       </c>
       <c r="AQ434">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="AR434">
-        <v>1.15</v>
+        <v>1.62</v>
       </c>
       <c r="AS434">
-        <v>1.08</v>
+        <v>0.92</v>
       </c>
       <c r="AT434">
-        <v>2.23</v>
+        <v>2.54</v>
       </c>
       <c r="AU434">
+        <v>10</v>
+      </c>
+      <c r="AV434">
+        <v>5</v>
+      </c>
+      <c r="AW434">
+        <v>13</v>
+      </c>
+      <c r="AX434">
         <v>4</v>
       </c>
-      <c r="AV434">
-        <v>4</v>
-      </c>
-      <c r="AW434">
+      <c r="AY434">
+        <v>23</v>
+      </c>
+      <c r="AZ434">
+        <v>9</v>
+      </c>
+      <c r="BA434">
         <v>7</v>
       </c>
-      <c r="AX434">
+      <c r="BB434">
         <v>8</v>
       </c>
-      <c r="AY434">
-        <v>11</v>
-      </c>
-      <c r="AZ434">
-        <v>12</v>
-      </c>
-      <c r="BA434">
-        <v>5</v>
-      </c>
-      <c r="BB434">
-        <v>7</v>
-      </c>
       <c r="BC434">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BD434">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="BE434">
-        <v>7.1</v>
+        <v>9.9</v>
       </c>
       <c r="BF434">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="BG434">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="BH434">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="BI434">
+        <v>1.32</v>
+      </c>
+      <c r="BJ434">
+        <v>3</v>
+      </c>
+      <c r="BK434">
+        <v>1.58</v>
+      </c>
+      <c r="BL434">
+        <v>2.15</v>
+      </c>
+      <c r="BM434">
+        <v>1.98</v>
+      </c>
+      <c r="BN434">
+        <v>1.68</v>
+      </c>
+      <c r="BO434">
+        <v>2.65</v>
+      </c>
+      <c r="BP434">
         <v>1.4</v>
-      </c>
-      <c r="BJ434">
-        <v>2.6</v>
-      </c>
-      <c r="BK434">
-        <v>1.71</v>
-      </c>
-      <c r="BL434">
-        <v>1.95</v>
-      </c>
-      <c r="BM434">
-        <v>2.2</v>
-      </c>
-      <c r="BN434">
-        <v>1.55</v>
-      </c>
-      <c r="BO434">
-        <v>3</v>
-      </c>
-      <c r="BP434">
-        <v>1.31</v>
       </c>
     </row>
     <row r="435" spans="1:68">
@@ -91329,7 +91329,7 @@
         <v>434</v>
       </c>
       <c r="B435">
-        <v>7727309</v>
+        <v>7727308</v>
       </c>
       <c r="C435" t="s">
         <v>68</v>
@@ -91344,19 +91344,19 @@
         <v>37</v>
       </c>
       <c r="G435" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H435" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="I435">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J435">
         <v>0</v>
       </c>
       <c r="K435">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L435">
         <v>1</v>
@@ -91368,19 +91368,19 @@
         <v>2</v>
       </c>
       <c r="O435" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P435" t="s">
-        <v>425</v>
+        <v>261</v>
       </c>
       <c r="Q435">
-        <v>2.38</v>
+        <v>3.25</v>
       </c>
       <c r="R435">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S435">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="T435">
         <v>1.44</v>
@@ -91389,145 +91389,145 @@
         <v>2.63</v>
       </c>
       <c r="V435">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="W435">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="X435">
+        <v>10</v>
+      </c>
+      <c r="Y435">
+        <v>1.06</v>
+      </c>
+      <c r="Z435">
+        <v>2.84</v>
+      </c>
+      <c r="AA435">
+        <v>3.45</v>
+      </c>
+      <c r="AB435">
+        <v>2.33</v>
+      </c>
+      <c r="AC435">
+        <v>1.06</v>
+      </c>
+      <c r="AD435">
+        <v>8.5</v>
+      </c>
+      <c r="AE435">
+        <v>1.38</v>
+      </c>
+      <c r="AF435">
+        <v>3</v>
+      </c>
+      <c r="AG435">
+        <v>2.1</v>
+      </c>
+      <c r="AH435">
+        <v>1.67</v>
+      </c>
+      <c r="AI435">
+        <v>1.95</v>
+      </c>
+      <c r="AJ435">
+        <v>1.8</v>
+      </c>
+      <c r="AK435">
+        <v>1.42</v>
+      </c>
+      <c r="AL435">
+        <v>1.25</v>
+      </c>
+      <c r="AM435">
+        <v>1.5</v>
+      </c>
+      <c r="AN435">
+        <v>2.17</v>
+      </c>
+      <c r="AO435">
+        <v>1.18</v>
+      </c>
+      <c r="AP435">
+        <v>2.11</v>
+      </c>
+      <c r="AQ435">
+        <v>1.17</v>
+      </c>
+      <c r="AR435">
+        <v>1.36</v>
+      </c>
+      <c r="AS435">
+        <v>1.12</v>
+      </c>
+      <c r="AT435">
+        <v>2.48</v>
+      </c>
+      <c r="AU435">
+        <v>4</v>
+      </c>
+      <c r="AV435">
+        <v>7</v>
+      </c>
+      <c r="AW435">
+        <v>5</v>
+      </c>
+      <c r="AX435">
+        <v>11</v>
+      </c>
+      <c r="AY435">
         <v>9</v>
       </c>
-      <c r="Y435">
-        <v>1.07</v>
-      </c>
-      <c r="Z435">
-        <v>1.72</v>
-      </c>
-      <c r="AA435">
-        <v>3.79</v>
-      </c>
-      <c r="AB435">
-        <v>4.4</v>
-      </c>
-      <c r="AC435">
-        <v>1.05</v>
-      </c>
-      <c r="AD435">
+      <c r="AZ435">
+        <v>18</v>
+      </c>
+      <c r="BA435">
+        <v>6</v>
+      </c>
+      <c r="BB435">
+        <v>3</v>
+      </c>
+      <c r="BC435">
         <v>9</v>
       </c>
-      <c r="AE435">
-        <v>1.3</v>
-      </c>
-      <c r="AF435">
-        <v>3.35</v>
-      </c>
-      <c r="AG435">
-        <v>1.94</v>
-      </c>
-      <c r="AH435">
-        <v>1.8</v>
-      </c>
-      <c r="AI435">
-        <v>2</v>
-      </c>
-      <c r="AJ435">
-        <v>1.75</v>
-      </c>
-      <c r="AK435">
-        <v>1.19</v>
-      </c>
-      <c r="AL435">
+      <c r="BD435">
+        <v>2.12</v>
+      </c>
+      <c r="BE435">
+        <v>6.55</v>
+      </c>
+      <c r="BF435">
+        <v>2.13</v>
+      </c>
+      <c r="BG435">
         <v>1.27</v>
       </c>
-      <c r="AM435">
-        <v>2.05</v>
-      </c>
-      <c r="AN435">
-        <v>1.76</v>
-      </c>
-      <c r="AO435">
-        <v>1.06</v>
-      </c>
-      <c r="AP435">
-        <v>1.63</v>
-      </c>
-      <c r="AQ435">
-        <v>1.06</v>
-      </c>
-      <c r="AR435">
-        <v>1.62</v>
-      </c>
-      <c r="AS435">
-        <v>0.92</v>
-      </c>
-      <c r="AT435">
-        <v>2.54</v>
-      </c>
-      <c r="AU435">
-        <v>10</v>
-      </c>
-      <c r="AV435">
-        <v>5</v>
-      </c>
-      <c r="AW435">
-        <v>13</v>
-      </c>
-      <c r="AX435">
-        <v>4</v>
-      </c>
-      <c r="AY435">
-        <v>23</v>
-      </c>
-      <c r="AZ435">
-        <v>9</v>
-      </c>
-      <c r="BA435">
-        <v>7</v>
-      </c>
-      <c r="BB435">
-        <v>8</v>
-      </c>
-      <c r="BC435">
-        <v>15</v>
-      </c>
-      <c r="BD435">
-        <v>1.4</v>
-      </c>
-      <c r="BE435">
-        <v>9.9</v>
-      </c>
-      <c r="BF435">
-        <v>3.6</v>
-      </c>
-      <c r="BG435">
-        <v>1.24</v>
-      </c>
       <c r="BH435">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="BI435">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="BJ435">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="BK435">
-        <v>1.58</v>
+        <v>1.77</v>
       </c>
       <c r="BL435">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="BM435">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="BN435">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="BO435">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="BP435">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="436" spans="1:68">
@@ -91535,7 +91535,7 @@
         <v>435</v>
       </c>
       <c r="B436">
-        <v>7727308</v>
+        <v>7727307</v>
       </c>
       <c r="C436" t="s">
         <v>68</v>
@@ -91550,19 +91550,19 @@
         <v>37</v>
       </c>
       <c r="G436" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="H436" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="I436">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J436">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K436">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L436">
         <v>1</v>
@@ -91574,19 +91574,19 @@
         <v>2</v>
       </c>
       <c r="O436" t="s">
-        <v>350</v>
+        <v>153</v>
       </c>
       <c r="P436" t="s">
-        <v>261</v>
+        <v>277</v>
       </c>
       <c r="Q436">
-        <v>3.25</v>
+        <v>7.5</v>
       </c>
       <c r="R436">
+        <v>2.2</v>
+      </c>
+      <c r="S436">
         <v>2.05</v>
-      </c>
-      <c r="S436">
-        <v>3.6</v>
       </c>
       <c r="T436">
         <v>1.44</v>
@@ -91595,25 +91595,25 @@
         <v>2.63</v>
       </c>
       <c r="V436">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="W436">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="X436">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y436">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Z436">
-        <v>2.84</v>
+        <v>6.8</v>
       </c>
       <c r="AA436">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="AB436">
-        <v>2.33</v>
+        <v>1.47</v>
       </c>
       <c r="AC436">
         <v>1.06</v>
@@ -91622,10 +91622,10 @@
         <v>8.5</v>
       </c>
       <c r="AE436">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AF436">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AG436">
         <v>2.1</v>
@@ -91634,106 +91634,106 @@
         <v>1.67</v>
       </c>
       <c r="AI436">
-        <v>1.95</v>
+        <v>2.38</v>
       </c>
       <c r="AJ436">
+        <v>1.53</v>
+      </c>
+      <c r="AK436">
+        <v>2.35</v>
+      </c>
+      <c r="AL436">
+        <v>1.24</v>
+      </c>
+      <c r="AM436">
+        <v>1.13</v>
+      </c>
+      <c r="AN436">
+        <v>1.29</v>
+      </c>
+      <c r="AO436">
+        <v>1.94</v>
+      </c>
+      <c r="AP436">
+        <v>1.28</v>
+      </c>
+      <c r="AQ436">
+        <v>1.88</v>
+      </c>
+      <c r="AR436">
+        <v>1.23</v>
+      </c>
+      <c r="AS436">
+        <v>1.17</v>
+      </c>
+      <c r="AT436">
+        <v>2.4</v>
+      </c>
+      <c r="AU436">
+        <v>5</v>
+      </c>
+      <c r="AV436">
+        <v>6</v>
+      </c>
+      <c r="AW436">
+        <v>11</v>
+      </c>
+      <c r="AX436">
+        <v>8</v>
+      </c>
+      <c r="AY436">
+        <v>16</v>
+      </c>
+      <c r="AZ436">
+        <v>14</v>
+      </c>
+      <c r="BA436">
+        <v>1</v>
+      </c>
+      <c r="BB436">
+        <v>4</v>
+      </c>
+      <c r="BC436">
+        <v>5</v>
+      </c>
+      <c r="BD436">
+        <v>3.92</v>
+      </c>
+      <c r="BE436">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="BF436">
+        <v>1.36</v>
+      </c>
+      <c r="BG436">
+        <v>1.24</v>
+      </c>
+      <c r="BH436">
+        <v>3.5</v>
+      </c>
+      <c r="BI436">
+        <v>1.44</v>
+      </c>
+      <c r="BJ436">
+        <v>2.45</v>
+      </c>
+      <c r="BK436">
         <v>1.8</v>
       </c>
-      <c r="AK436">
-        <v>1.42</v>
-      </c>
-      <c r="AL436">
-        <v>1.25</v>
-      </c>
-      <c r="AM436">
-        <v>1.5</v>
-      </c>
-      <c r="AN436">
-        <v>2.17</v>
-      </c>
-      <c r="AO436">
-        <v>1.18</v>
-      </c>
-      <c r="AP436">
-        <v>2.11</v>
-      </c>
-      <c r="AQ436">
-        <v>1.17</v>
-      </c>
-      <c r="AR436">
-        <v>1.36</v>
-      </c>
-      <c r="AS436">
-        <v>1.12</v>
-      </c>
-      <c r="AT436">
-        <v>2.48</v>
-      </c>
-      <c r="AU436">
-        <v>4</v>
-      </c>
-      <c r="AV436">
-        <v>7</v>
-      </c>
-      <c r="AW436">
-        <v>5</v>
-      </c>
-      <c r="AX436">
-        <v>11</v>
-      </c>
-      <c r="AY436">
-        <v>9</v>
-      </c>
-      <c r="AZ436">
-        <v>18</v>
-      </c>
-      <c r="BA436">
-        <v>6</v>
-      </c>
-      <c r="BB436">
-        <v>3</v>
-      </c>
-      <c r="BC436">
-        <v>9</v>
-      </c>
-      <c r="BD436">
-        <v>2.12</v>
-      </c>
-      <c r="BE436">
-        <v>6.55</v>
-      </c>
-      <c r="BF436">
-        <v>2.13</v>
-      </c>
-      <c r="BG436">
+      <c r="BL436">
+        <v>1.83</v>
+      </c>
+      <c r="BM436">
+        <v>2.35</v>
+      </c>
+      <c r="BN436">
+        <v>1.49</v>
+      </c>
+      <c r="BO436">
+        <v>3.3</v>
+      </c>
+      <c r="BP436">
         <v>1.27</v>
-      </c>
-      <c r="BH436">
-        <v>3.3</v>
-      </c>
-      <c r="BI436">
-        <v>1.34</v>
-      </c>
-      <c r="BJ436">
-        <v>2.78</v>
-      </c>
-      <c r="BK436">
-        <v>1.77</v>
-      </c>
-      <c r="BL436">
-        <v>1.95</v>
-      </c>
-      <c r="BM436">
-        <v>2.07</v>
-      </c>
-      <c r="BN436">
-        <v>1.67</v>
-      </c>
-      <c r="BO436">
-        <v>2.67</v>
-      </c>
-      <c r="BP436">
-        <v>1.39</v>
       </c>
     </row>
     <row r="437" spans="1:68">
@@ -91741,7 +91741,7 @@
         <v>436</v>
       </c>
       <c r="B437">
-        <v>7727307</v>
+        <v>7727306</v>
       </c>
       <c r="C437" t="s">
         <v>68</v>
@@ -91756,190 +91756,190 @@
         <v>37</v>
       </c>
       <c r="G437" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="H437" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="I437">
         <v>1</v>
       </c>
       <c r="J437">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K437">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L437">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M437">
         <v>1</v>
       </c>
       <c r="N437">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O437" t="s">
-        <v>153</v>
+        <v>351</v>
       </c>
       <c r="P437" t="s">
-        <v>277</v>
+        <v>172</v>
       </c>
       <c r="Q437">
-        <v>7.5</v>
+        <v>3.25</v>
       </c>
       <c r="R437">
         <v>2.2</v>
       </c>
       <c r="S437">
+        <v>3.2</v>
+      </c>
+      <c r="T437">
+        <v>1.4</v>
+      </c>
+      <c r="U437">
+        <v>2.75</v>
+      </c>
+      <c r="V437">
+        <v>2.75</v>
+      </c>
+      <c r="W437">
+        <v>1.4</v>
+      </c>
+      <c r="X437">
+        <v>8</v>
+      </c>
+      <c r="Y437">
+        <v>1.08</v>
+      </c>
+      <c r="Z437">
+        <v>2.84</v>
+      </c>
+      <c r="AA437">
+        <v>3.45</v>
+      </c>
+      <c r="AB437">
+        <v>2.33</v>
+      </c>
+      <c r="AC437">
+        <v>1.05</v>
+      </c>
+      <c r="AD437">
+        <v>9.5</v>
+      </c>
+      <c r="AE437">
+        <v>1.25</v>
+      </c>
+      <c r="AF437">
+        <v>3.75</v>
+      </c>
+      <c r="AG437">
+        <v>1.87</v>
+      </c>
+      <c r="AH437">
+        <v>1.87</v>
+      </c>
+      <c r="AI437">
+        <v>1.7</v>
+      </c>
+      <c r="AJ437">
         <v>2.05</v>
       </c>
-      <c r="T437">
+      <c r="AK437">
+        <v>1.42</v>
+      </c>
+      <c r="AL437">
+        <v>1.29</v>
+      </c>
+      <c r="AM437">
+        <v>1.55</v>
+      </c>
+      <c r="AN437">
+        <v>1.12</v>
+      </c>
+      <c r="AO437">
+        <v>1.72</v>
+      </c>
+      <c r="AP437">
+        <v>1.22</v>
+      </c>
+      <c r="AQ437">
+        <v>1.63</v>
+      </c>
+      <c r="AR437">
+        <v>1.49</v>
+      </c>
+      <c r="AS437">
+        <v>1.42</v>
+      </c>
+      <c r="AT437">
+        <v>2.91</v>
+      </c>
+      <c r="AU437">
+        <v>7</v>
+      </c>
+      <c r="AV437">
+        <v>7</v>
+      </c>
+      <c r="AW437">
+        <v>7</v>
+      </c>
+      <c r="AX437">
+        <v>2</v>
+      </c>
+      <c r="AY437">
+        <v>14</v>
+      </c>
+      <c r="AZ437">
+        <v>9</v>
+      </c>
+      <c r="BA437">
+        <v>5</v>
+      </c>
+      <c r="BB437">
+        <v>5</v>
+      </c>
+      <c r="BC437">
+        <v>10</v>
+      </c>
+      <c r="BD437">
+        <v>1.73</v>
+      </c>
+      <c r="BE437">
+        <v>6.85</v>
+      </c>
+      <c r="BF437">
+        <v>2.71</v>
+      </c>
+      <c r="BG437">
+        <v>1.22</v>
+      </c>
+      <c r="BH437">
+        <v>3.7</v>
+      </c>
+      <c r="BI437">
+        <v>1.28</v>
+      </c>
+      <c r="BJ437">
+        <v>3.2</v>
+      </c>
+      <c r="BK437">
+        <v>1.51</v>
+      </c>
+      <c r="BL437">
+        <v>2.3</v>
+      </c>
+      <c r="BM437">
+        <v>1.88</v>
+      </c>
+      <c r="BN437">
+        <v>1.75</v>
+      </c>
+      <c r="BO437">
+        <v>2.45</v>
+      </c>
+      <c r="BP437">
         <v>1.44</v>
-      </c>
-      <c r="U437">
-        <v>2.63</v>
-      </c>
-      <c r="V437">
-        <v>3.25</v>
-      </c>
-      <c r="W437">
-        <v>1.33</v>
-      </c>
-      <c r="X437">
-        <v>9</v>
-      </c>
-      <c r="Y437">
-        <v>1.07</v>
-      </c>
-      <c r="Z437">
-        <v>6.8</v>
-      </c>
-      <c r="AA437">
-        <v>4.2</v>
-      </c>
-      <c r="AB437">
-        <v>1.47</v>
-      </c>
-      <c r="AC437">
-        <v>1.06</v>
-      </c>
-      <c r="AD437">
-        <v>8.5</v>
-      </c>
-      <c r="AE437">
-        <v>1.35</v>
-      </c>
-      <c r="AF437">
-        <v>3.1</v>
-      </c>
-      <c r="AG437">
-        <v>2.1</v>
-      </c>
-      <c r="AH437">
-        <v>1.67</v>
-      </c>
-      <c r="AI437">
-        <v>2.38</v>
-      </c>
-      <c r="AJ437">
-        <v>1.53</v>
-      </c>
-      <c r="AK437">
-        <v>2.35</v>
-      </c>
-      <c r="AL437">
-        <v>1.24</v>
-      </c>
-      <c r="AM437">
-        <v>1.13</v>
-      </c>
-      <c r="AN437">
-        <v>1.29</v>
-      </c>
-      <c r="AO437">
-        <v>1.94</v>
-      </c>
-      <c r="AP437">
-        <v>1.28</v>
-      </c>
-      <c r="AQ437">
-        <v>1.88</v>
-      </c>
-      <c r="AR437">
-        <v>1.23</v>
-      </c>
-      <c r="AS437">
-        <v>1.17</v>
-      </c>
-      <c r="AT437">
-        <v>2.4</v>
-      </c>
-      <c r="AU437">
-        <v>5</v>
-      </c>
-      <c r="AV437">
-        <v>6</v>
-      </c>
-      <c r="AW437">
-        <v>11</v>
-      </c>
-      <c r="AX437">
-        <v>8</v>
-      </c>
-      <c r="AY437">
-        <v>16</v>
-      </c>
-      <c r="AZ437">
-        <v>14</v>
-      </c>
-      <c r="BA437">
-        <v>1</v>
-      </c>
-      <c r="BB437">
-        <v>4</v>
-      </c>
-      <c r="BC437">
-        <v>5</v>
-      </c>
-      <c r="BD437">
-        <v>3.92</v>
-      </c>
-      <c r="BE437">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="BF437">
-        <v>1.36</v>
-      </c>
-      <c r="BG437">
-        <v>1.24</v>
-      </c>
-      <c r="BH437">
-        <v>3.5</v>
-      </c>
-      <c r="BI437">
-        <v>1.44</v>
-      </c>
-      <c r="BJ437">
-        <v>2.45</v>
-      </c>
-      <c r="BK437">
-        <v>1.8</v>
-      </c>
-      <c r="BL437">
-        <v>1.83</v>
-      </c>
-      <c r="BM437">
-        <v>2.35</v>
-      </c>
-      <c r="BN437">
-        <v>1.49</v>
-      </c>
-      <c r="BO437">
-        <v>3.3</v>
-      </c>
-      <c r="BP437">
-        <v>1.27</v>
       </c>
     </row>
     <row r="438" spans="1:68">
@@ -91947,7 +91947,7 @@
         <v>437</v>
       </c>
       <c r="B438">
-        <v>7727305</v>
+        <v>7727311</v>
       </c>
       <c r="C438" t="s">
         <v>68</v>
@@ -91962,43 +91962,43 @@
         <v>37</v>
       </c>
       <c r="G438" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H438" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I438">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J438">
         <v>0</v>
       </c>
       <c r="K438">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L438">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M438">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N438">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O438" t="s">
-        <v>351</v>
+        <v>96</v>
       </c>
       <c r="P438" t="s">
-        <v>96</v>
+        <v>264</v>
       </c>
       <c r="Q438">
+        <v>2.75</v>
+      </c>
+      <c r="R438">
         <v>2.1</v>
       </c>
-      <c r="R438">
-        <v>2.25</v>
-      </c>
       <c r="S438">
-        <v>6.5</v>
+        <v>4</v>
       </c>
       <c r="T438">
         <v>1.4</v>
@@ -92019,25 +92019,25 @@
         <v>1.08</v>
       </c>
       <c r="Z438">
-        <v>1.5</v>
+        <v>2.09</v>
       </c>
       <c r="AA438">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="AB438">
-        <v>6.2</v>
+        <v>3.28</v>
       </c>
       <c r="AC438">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AD438">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="AE438">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AF438">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="AG438">
         <v>1.92</v>
@@ -92046,106 +92046,106 @@
         <v>1.82</v>
       </c>
       <c r="AI438">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AJ438">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AK438">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AL438">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AM438">
-        <v>2.4</v>
+        <v>1.77</v>
       </c>
       <c r="AN438">
+        <v>2.06</v>
+      </c>
+      <c r="AO438">
         <v>1.47</v>
       </c>
-      <c r="AO438">
-        <v>0.61</v>
-      </c>
       <c r="AP438">
+        <v>1.94</v>
+      </c>
+      <c r="AQ438">
         <v>1.56</v>
       </c>
-      <c r="AQ438">
-        <v>0.58</v>
-      </c>
       <c r="AR438">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="AS438">
-        <v>1.02</v>
+        <v>1.27</v>
       </c>
       <c r="AT438">
-        <v>2.44</v>
+        <v>2.76</v>
       </c>
       <c r="AU438">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="AV438">
         <v>3</v>
       </c>
       <c r="AW438">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX438">
         <v>2</v>
       </c>
       <c r="AY438">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="AZ438">
         <v>5</v>
       </c>
       <c r="BA438">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="BB438">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BC438">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="BD438">
-        <v>1.28</v>
+        <v>1.49</v>
       </c>
       <c r="BE438">
-        <v>10.5</v>
+        <v>7.1</v>
       </c>
       <c r="BF438">
-        <v>4.55</v>
+        <v>3.55</v>
       </c>
       <c r="BG438">
+        <v>1.24</v>
+      </c>
+      <c r="BH438">
+        <v>3.34</v>
+      </c>
+      <c r="BI438">
+        <v>1.48</v>
+      </c>
+      <c r="BJ438">
+        <v>2.4</v>
+      </c>
+      <c r="BK438">
+        <v>1.85</v>
+      </c>
+      <c r="BL438">
+        <v>1.85</v>
+      </c>
+      <c r="BM438">
+        <v>2.38</v>
+      </c>
+      <c r="BN438">
+        <v>1.49</v>
+      </c>
+      <c r="BO438">
+        <v>3.14</v>
+      </c>
+      <c r="BP438">
         <v>1.27</v>
-      </c>
-      <c r="BH438">
-        <v>3.3</v>
-      </c>
-      <c r="BI438">
-        <v>1.35</v>
-      </c>
-      <c r="BJ438">
-        <v>2.74</v>
-      </c>
-      <c r="BK438">
-        <v>1.64</v>
-      </c>
-      <c r="BL438">
-        <v>2.07</v>
-      </c>
-      <c r="BM438">
-        <v>2.08</v>
-      </c>
-      <c r="BN438">
-        <v>1.67</v>
-      </c>
-      <c r="BO438">
-        <v>2.71</v>
-      </c>
-      <c r="BP438">
-        <v>1.38</v>
       </c>
     </row>
     <row r="439" spans="1:68">
@@ -92771,7 +92771,7 @@
         <v>441</v>
       </c>
       <c r="B442">
-        <v>7727306</v>
+        <v>7727305</v>
       </c>
       <c r="C442" t="s">
         <v>68</v>
@@ -92786,10 +92786,10 @@
         <v>37</v>
       </c>
       <c r="G442" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="H442" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="I442">
         <v>1</v>
@@ -92801,28 +92801,28 @@
         <v>1</v>
       </c>
       <c r="L442">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M442">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N442">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O442" t="s">
         <v>354</v>
       </c>
       <c r="P442" t="s">
-        <v>172</v>
+        <v>96</v>
       </c>
       <c r="Q442">
-        <v>3.25</v>
+        <v>2.1</v>
       </c>
       <c r="R442">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S442">
-        <v>3.2</v>
+        <v>6.5</v>
       </c>
       <c r="T442">
         <v>1.4</v>
@@ -92831,10 +92831,10 @@
         <v>2.75</v>
       </c>
       <c r="V442">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="W442">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="X442">
         <v>8</v>
@@ -92843,13 +92843,13 @@
         <v>1.08</v>
       </c>
       <c r="Z442">
-        <v>2.84</v>
+        <v>1.5</v>
       </c>
       <c r="AA442">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="AB442">
-        <v>2.33</v>
+        <v>6.2</v>
       </c>
       <c r="AC442">
         <v>1.05</v>
@@ -92858,118 +92858,118 @@
         <v>9.5</v>
       </c>
       <c r="AE442">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AF442">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="AG442">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="AH442">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="AI442">
+        <v>2.05</v>
+      </c>
+      <c r="AJ442">
         <v>1.7</v>
       </c>
-      <c r="AJ442">
-        <v>2.05</v>
-      </c>
       <c r="AK442">
+        <v>1.12</v>
+      </c>
+      <c r="AL442">
+        <v>1.18</v>
+      </c>
+      <c r="AM442">
+        <v>2.4</v>
+      </c>
+      <c r="AN442">
+        <v>1.47</v>
+      </c>
+      <c r="AO442">
+        <v>0.61</v>
+      </c>
+      <c r="AP442">
+        <v>1.56</v>
+      </c>
+      <c r="AQ442">
+        <v>0.58</v>
+      </c>
+      <c r="AR442">
         <v>1.42</v>
       </c>
-      <c r="AL442">
-        <v>1.29</v>
-      </c>
-      <c r="AM442">
-        <v>1.55</v>
-      </c>
-      <c r="AN442">
-        <v>1.12</v>
-      </c>
-      <c r="AO442">
-        <v>1.72</v>
-      </c>
-      <c r="AP442">
-        <v>1.22</v>
-      </c>
-      <c r="AQ442">
-        <v>1.63</v>
-      </c>
-      <c r="AR442">
-        <v>1.49</v>
-      </c>
       <c r="AS442">
-        <v>1.42</v>
+        <v>1.02</v>
       </c>
       <c r="AT442">
-        <v>2.91</v>
+        <v>2.44</v>
       </c>
       <c r="AU442">
+        <v>14</v>
+      </c>
+      <c r="AV442">
+        <v>3</v>
+      </c>
+      <c r="AW442">
+        <v>9</v>
+      </c>
+      <c r="AX442">
+        <v>2</v>
+      </c>
+      <c r="AY442">
+        <v>23</v>
+      </c>
+      <c r="AZ442">
+        <v>5</v>
+      </c>
+      <c r="BA442">
         <v>7</v>
-      </c>
-      <c r="AV442">
-        <v>7</v>
-      </c>
-      <c r="AW442">
-        <v>7</v>
-      </c>
-      <c r="AX442">
-        <v>2</v>
-      </c>
-      <c r="AY442">
-        <v>14</v>
-      </c>
-      <c r="AZ442">
-        <v>9</v>
-      </c>
-      <c r="BA442">
-        <v>5</v>
       </c>
       <c r="BB442">
         <v>5</v>
       </c>
       <c r="BC442">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BD442">
-        <v>1.73</v>
+        <v>1.28</v>
       </c>
       <c r="BE442">
-        <v>6.85</v>
+        <v>10.5</v>
       </c>
       <c r="BF442">
+        <v>4.55</v>
+      </c>
+      <c r="BG442">
+        <v>1.27</v>
+      </c>
+      <c r="BH442">
+        <v>3.3</v>
+      </c>
+      <c r="BI442">
+        <v>1.35</v>
+      </c>
+      <c r="BJ442">
+        <v>2.74</v>
+      </c>
+      <c r="BK442">
+        <v>1.64</v>
+      </c>
+      <c r="BL442">
+        <v>2.07</v>
+      </c>
+      <c r="BM442">
+        <v>2.08</v>
+      </c>
+      <c r="BN442">
+        <v>1.67</v>
+      </c>
+      <c r="BO442">
         <v>2.71</v>
       </c>
-      <c r="BG442">
-        <v>1.22</v>
-      </c>
-      <c r="BH442">
-        <v>3.7</v>
-      </c>
-      <c r="BI442">
-        <v>1.28</v>
-      </c>
-      <c r="BJ442">
-        <v>3.2</v>
-      </c>
-      <c r="BK442">
-        <v>1.51</v>
-      </c>
-      <c r="BL442">
-        <v>2.3</v>
-      </c>
-      <c r="BM442">
-        <v>1.88</v>
-      </c>
-      <c r="BN442">
-        <v>1.75</v>
-      </c>
-      <c r="BO442">
-        <v>2.45</v>
-      </c>
       <c r="BP442">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="443" spans="1:68">

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England EFL League One_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England EFL League One_20242025.xlsx
@@ -97725,13 +97725,13 @@
         <v>15</v>
       </c>
       <c r="BA465">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB465">
         <v>4</v>
       </c>
       <c r="BC465">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD465">
         <v>2.65</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England EFL League One_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England EFL League One_20242025.xlsx
@@ -87765,46 +87765,46 @@
         <v>96</v>
       </c>
       <c r="Q417">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R417">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S417">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="T417">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="U417">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V417">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="W417">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X417">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Y417">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Z417">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AA417">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AB417">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AC417">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AD417">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AE417">
         <v>0</v>
@@ -87813,16 +87813,16 @@
         <v>0</v>
       </c>
       <c r="AG417">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH417">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AI417">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AJ417">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AK417">
         <v>0</v>
